--- a/Result/checksun_type/電鍍材料.xlsx
+++ b/Result/checksun_type/電鍍材料.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CI13"/>
+  <dimension ref="A1:CI23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>358.0</t>
+          <t>369.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>42.35</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -903,17 +903,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-27.59</t>
+          <t>-43.86</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-7.87</t>
+          <t>-4.72</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>8.79</t>
+          <t>9.06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,77 +1009,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>369</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>41.18</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>14.84</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-3.31</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>42.04000000000001</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>43.48</t>
+          <t>43.53</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>44.31</t>
+          <t>44.23</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>44.85</t>
+          <t>44.87</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-59.38</t>
+          <t>-40.91</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-114.70</t>
+          <t>-116.38</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>28216.53690303907</t>
+          <t>28209.25794797688</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>14757.0</t>
+          <t>15453.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>15111.8</t>
+          <t>11783.2</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>20870.2</t>
+          <t>20989.4</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>12172.68</t>
+          <t>12346.96</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-5758</t>
+          <t>-9206</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>1074.691386655718</t>
+          <t>797.4475068096988</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-760.62</v>
+        <v>-727.39</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-17.94</t>
+          <t>-15.13</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1182,17 +1182,17 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.4880769767117557</t>
+          <t>-10.56465687102404</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-5.040521842261317</t>
+          <t>-13.69932964657055</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>12.92544182292656</t>
+          <t>7.80229574004913</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
@@ -1202,47 +1202,47 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>5.18</t>
+          <t>6.59</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>70.17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>16.40%</t>
+          <t>8.25%</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
         <is>
-          <t>-4.57%</t>
+          <t>-14.21%</t>
         </is>
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>44.82</t>
+          <t>43.93</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>1869</t>
+          <t>1880</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,12 +1262,12 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>42.45</t>
+          <t>42.7</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1277,12 +1277,12 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>42.35</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>19.49</t>
+          <t>18.72</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>358.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-29.63</t>
+          <t>-27.59</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-5.29</t>
+          <t>-7.87</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>8.79</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,17 +1440,17 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>369</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -1460,57 +1460,57 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-3.31</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>42.55</t>
+          <t>42.04000000000001</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.48</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>44.42</t>
+          <t>44.31</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>44.84</t>
+          <t>44.85</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-46.96</t>
+          <t>-59.38</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-112.52</t>
+          <t>-114.70</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>28216.53690303907</t>
+          <t>28209.25794797688</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>4814.0</t>
+          <t>14757.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>14458.8</t>
+          <t>15111.8</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>20545.5</t>
+          <t>20870.2</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>12162.98</t>
+          <t>12172.68</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-6086</t>
+          <t>-5758</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>1408.384988086925</t>
+          <t>1074.691386655718</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-706.36</v>
+        <v>-760.62</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-15.63</t>
+          <t>-17.94</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1613,17 +1613,17 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.4880769767117557</t>
+          <t>-10.56465687102404</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-5.040521842261317</t>
+          <t>-13.69932964657055</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>12.92544182292656</t>
+          <t>7.80229574004913</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
@@ -1633,47 +1633,47 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>5.18</t>
+          <t>6.59</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>70.17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>16.40%</t>
+          <t>8.25%</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
         <is>
-          <t>-4.57%</t>
+          <t>-14.21%</t>
         </is>
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>44.82</t>
+          <t>43.93</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>1869</t>
+          <t>1880</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,27 +1693,27 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
+          <t>42.1</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
           <t>42.45</t>
         </is>
       </c>
-      <c r="CD3" t="inlineStr">
-        <is>
-          <t>42.7</t>
-        </is>
-      </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>41.95</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>19.49</t>
+          <t>18.72</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>114.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>42.4</t>
+          <t>42.1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-7.97</t>
+          <t>-29.63</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-4.61</t>
+          <t>-5.29</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,77 +1871,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>369</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>42.88</t>
+          <t>42.55</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>43.46</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>44.54</t>
+          <t>44.42</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>44.81</t>
+          <t>44.84</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-44.19</t>
+          <t>-46.96</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-111.05</t>
+          <t>-112.52</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>28216.53690303907</t>
+          <t>28209.25794797688</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>5444.0</t>
+          <t>4814.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>20437.4</t>
+          <t>14458.8</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>22206.9</t>
+          <t>20545.5</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>13085.46</t>
+          <t>12162.98</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-1769</t>
+          <t>-6086</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>1792.883660776302</t>
+          <t>1408.384988086925</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>461.71</v>
+        <v>-706.36</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-15.03</t>
+          <t>-15.63</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2044,67 +2044,67 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.4880769767117557</t>
+          <t>-10.56465687102404</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-5.040521842261317</t>
+          <t>-13.69932964657055</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>12.92544182292656</t>
+          <t>7.80229574004913</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>5.18</t>
+          <t>6.59</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>70.17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>16.40%</t>
+          <t>8.25%</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
         <is>
-          <t>-4.57%</t>
+          <t>-14.21%</t>
         </is>
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>44.82</t>
+          <t>43.93</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>1869</t>
+          <t>1880</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,27 +2124,27 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>42.45</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>42.7</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>41.95</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>42.4</t>
+          <t>42.1</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>19.49</t>
+          <t>18.72</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>441.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>42.4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>15.49</t>
+          <t>-7.97</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-5.51</t>
+          <t>-4.61</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10.82</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,47 +2302,47 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>369</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>43.27</t>
+          <t>42.88</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -2352,27 +2352,27 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>44.68</t>
+          <t>44.54</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>44.79</t>
+          <t>44.81</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-38.94</t>
+          <t>-44.19</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-109.83</t>
+          <t>-111.05</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>28216.53690303907</t>
+          <t>28209.25794797688</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>18448.0</t>
+          <t>5444.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>26755.2</t>
+          <t>20437.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>23167.0</t>
+          <t>22206.9</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>14024.46</t>
+          <t>13085.46</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>3588</t>
+          <t>-1769</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>2034.914649979622</t>
+          <t>1792.883660776302</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>2046.4</v>
+        <v>461.71</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-15.83</t>
+          <t>-15.03</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2475,22 +2475,22 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.4880769767117557</t>
+          <t>-10.56465687102404</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-5.040521842261317</t>
+          <t>-13.69932964657055</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>12.92544182292656</t>
+          <t>7.80229574004913</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2500,42 +2500,42 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>5.18</t>
+          <t>6.59</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>70.17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>16.40%</t>
+          <t>8.25%</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
         <is>
-          <t>-4.57%</t>
+          <t>-14.21%</t>
         </is>
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>44.82</t>
+          <t>43.93</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>1869</t>
+          <t>1880</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,27 +2555,27 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>42.85</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>42.4</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>19.49</t>
+          <t>18.72</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>441.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>42.75</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>30.99</t>
+          <t>15.49</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-3.82</t>
+          <t>-5.51</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>18.40</t>
+          <t>10.82</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,12 +2733,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>369</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2753,57 +2753,57 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>43.87</t>
+          <t>43.27</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>43.52</t>
+          <t>43.46</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>44.87</t>
+          <t>44.68</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>44.77</t>
+          <t>44.79</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-38.94</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-108.87</t>
+          <t>-109.83</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>28216.53690303907</t>
+          <t>28209.25794797688</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>32096.0</t>
+          <t>18448.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>30195.6</t>
+          <t>26755.2</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>23051.9</t>
+          <t>23167.0</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>14111.94</t>
+          <t>14024.46</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>7143</t>
+          <t>3588</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>2032.827091412444</t>
+          <t>2034.914649979622</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>2843.86</v>
+        <v>2046.4</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-14.33</t>
+          <t>-15.83</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2906,22 +2906,22 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.4880769767117557</t>
+          <t>-10.56465687102404</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-5.040521842261317</t>
+          <t>-13.69932964657055</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>12.92544182292656</t>
+          <t>7.80229574004913</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -2931,42 +2931,42 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>5.18</t>
+          <t>6.59</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>70.17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>16.40%</t>
+          <t>8.25%</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
         <is>
-          <t>-4.57%</t>
+          <t>-14.21%</t>
         </is>
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>44.82</t>
+          <t>43.93</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>1869</t>
+          <t>1880</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,27 +2986,27 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>42.85</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>42.75</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>19.49</t>
+          <t>18.72</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>266.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>42.75</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-3.33</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>22.62</t>
+          <t>30.99</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-3.82</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>6.53</t>
+          <t>18.40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,12 +3164,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>369</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3179,62 +3179,62 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>15.28</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>44.17999999999999</t>
+          <t>43.87</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>43.52</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>44.87</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>44.74</t>
+          <t>44.77</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>33.46</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-108.82</t>
+          <t>-108.87</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>28216.53690303907</t>
+          <t>28209.25794797688</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>11492.0</t>
+          <t>32096.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>26628.6</t>
+          <t>30195.6</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>21717.1</t>
+          <t>23051.9</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>13933.04</t>
+          <t>14111.94</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>4911</t>
+          <t>7143</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>1885.366964693159</t>
+          <t>2032.827091412444</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>2419.24</v>
+        <v>2843.86</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-12.83</t>
+          <t>-14.33</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3337,67 +3337,67 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.4880769767117557</t>
+          <t>-10.56465687102404</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-5.040521842261317</t>
+          <t>-13.69932964657055</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>12.92544182292656</t>
+          <t>7.80229574004913</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>5.18</t>
+          <t>6.59</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>70.17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>16.40%</t>
+          <t>8.25%</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
         <is>
-          <t>-4.57%</t>
+          <t>-14.21%</t>
         </is>
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>44.82</t>
+          <t>43.93</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>1869</t>
+          <t>1880</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,27 +3417,27 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>43.8</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>42.65</t>
+          <t>42.1</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>42.75</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>19.49</t>
+          <t>18.72</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>791.0</t>
+          <t>266.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>43.75</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>22.13</t>
+          <t>22.62</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>19.41</t>
+          <t>6.53</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,12 +3595,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>369</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3610,62 +3610,62 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>36.33</t>
+          <t>15.28</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>44.27999999999999</t>
+          <t>44.17999999999999</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>43.65</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>45.22</t>
+          <t>45.05</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>44.69</t>
+          <t>44.74</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>53.56</t>
+          <t>33.46</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-109.56</t>
+          <t>-108.82</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>28216.53690303907</t>
+          <t>28209.25794797688</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>34707.0</t>
+          <t>11492.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>26632.2</t>
+          <t>26628.6</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>21806.1</t>
+          <t>21717.1</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>14945.28</t>
+          <t>13933.04</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>4826</t>
+          <t>4911</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>1788.299770372915</t>
+          <t>1885.366964693159</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>3933.8</v>
+        <v>2419.24</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-12.32</t>
+          <t>-12.83</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3768,67 +3768,67 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.4880769767117557</t>
+          <t>-10.56465687102404</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-5.040521842261317</t>
+          <t>-13.69932964657055</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>12.92544182292656</t>
+          <t>7.80229574004913</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>5.18</t>
+          <t>6.59</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>70.17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>16.40%</t>
+          <t>8.25%</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
         <is>
-          <t>-4.57%</t>
+          <t>-14.21%</t>
         </is>
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>44.82</t>
+          <t>43.93</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>1869</t>
+          <t>1880</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,27 +3848,27 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>44.85</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>43.8</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>42.75</t>
+          <t>42.65</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>43.75</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>19.49</t>
+          <t>18.72</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>827.0</t>
+          <t>791.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>44.35</t>
+          <t>43.75</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-5.34</t>
+          <t>-3.31</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>12.85</t>
+          <t>22.13</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>20.29</t>
+          <t>19.41</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>369</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>45.83</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>36.33</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>44.33</t>
+          <t>44.27999999999999</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>43.69</t>
+          <t>43.65</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>45.34</t>
+          <t>45.22</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>44.65</t>
+          <t>44.69</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>67.99</t>
+          <t>53.56</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-110.84</t>
+          <t>-109.56</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>28216.53690303907</t>
+          <t>28209.25794797688</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>37033.0</t>
+          <t>34707.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>23976.4</t>
+          <t>26632.2</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>21246.9</t>
+          <t>21806.1</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>14725.58</t>
+          <t>14945.28</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>2729</t>
+          <t>4826</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>1398.207935072465</t>
+          <t>1788.299770372915</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>3469.66</v>
+        <v>3933.8</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-11.12</t>
+          <t>-12.32</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4199,22 +4199,22 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.4880769767117557</t>
+          <t>-10.56465687102404</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-5.040521842261317</t>
+          <t>-13.69932964657055</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>12.92544182292656</t>
+          <t>7.80229574004913</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4224,42 +4224,42 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>5.18</t>
+          <t>6.59</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>70.17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>16.40%</t>
+          <t>8.25%</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
         <is>
-          <t>-4.57%</t>
+          <t>-14.21%</t>
         </is>
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>44.82</t>
+          <t>43.93</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>1869</t>
+          <t>1880</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,27 +4279,27 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>44.85</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>43.95</t>
+          <t>42.75</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>44.35</t>
+          <t>43.75</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>19.49</t>
+          <t>18.72</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>796.0</t>
+          <t>827.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>44.35</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-6.89</t>
+          <t>-4.72</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>12.85</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>19.53</t>
+          <t>20.29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,27 +4457,27 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>369</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>63.16</t>
+          <t>45.83</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>48.63</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
@@ -4487,47 +4487,47 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>44.36</t>
+          <t>44.33</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>43.72</t>
+          <t>43.69</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>45.48</t>
+          <t>45.34</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>44.61</t>
+          <t>44.65</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>65.41</t>
+          <t>67.99</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-112.68</t>
+          <t>-110.84</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>28216.53690303907</t>
+          <t>28209.25794797688</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>35650.0</t>
+          <t>37033.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>19578.8</t>
+          <t>23976.4</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>19368.6</t>
+          <t>21246.9</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>14937.52</t>
+          <t>14725.58</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>2729</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>1021.580387001086</t>
+          <t>1398.207935072465</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>2433.46</v>
+        <v>3469.66</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-9.82</t>
+          <t>-11.12</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4630,22 +4630,22 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.4880769767117557</t>
+          <t>-10.56465687102404</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-5.040521842261317</t>
+          <t>-13.69932964657055</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>12.92544182292656</t>
+          <t>7.80229574004913</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,42 +4655,42 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>5.18</t>
+          <t>6.59</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>70.17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>16.40%</t>
+          <t>8.25%</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
         <is>
-          <t>-4.57%</t>
+          <t>-14.21%</t>
         </is>
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>44.82</t>
+          <t>43.93</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>1869</t>
+          <t>1880</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,27 +4710,27 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>45.95</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.95</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>44.35</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>19.49</t>
+          <t>18.72</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>322.0</t>
+          <t>796.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-5.23</t>
+          <t>-6.26</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>7.90</t>
+          <t>19.53</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4888,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>369</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>26.32</t>
+          <t>63.16</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>48.03</t>
+          <t>48.63</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-4.11</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>44.12</t>
+          <t>44.36</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>43.75</t>
+          <t>43.72</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>45.63</t>
+          <t>45.48</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>44.56</t>
+          <t>44.61</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>46.58</t>
+          <t>65.41</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-114.75</t>
+          <t>-112.68</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>28216.53690303907</t>
+          <t>28209.25794797688</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>14261.0</t>
+          <t>35650.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>15908.2</t>
+          <t>19578.8</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>16389.4</t>
+          <t>19368.6</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>18175.4</t>
+          <t>14937.52</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-481</t>
+          <t>210</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>764.8742980587986</t>
+          <t>1021.580387001086</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>1014.45</v>
+        <v>2433.46</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-11.22</t>
+          <t>-9.82</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5061,22 +5061,22 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.4880769767117557</t>
+          <t>-10.56465687102404</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-5.040521842261317</t>
+          <t>-13.69932964657055</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>12.92544182292656</t>
+          <t>7.80229574004913</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,42 +5086,42 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>5.18</t>
+          <t>6.59</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>70.17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>16.40%</t>
+          <t>8.25%</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
         <is>
-          <t>-4.57%</t>
+          <t>-14.21%</t>
         </is>
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>44.82</t>
+          <t>43.93</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>1869</t>
+          <t>1880</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,27 +5141,27 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>44.45</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>45.95</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>19.49</t>
+          <t>18.72</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>261.0</t>
+          <t>322.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-4.51</t>
+          <t>-4.6</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>9.80</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-99.0</t>
+          <t>-95.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>6.40</t>
+          <t>7.90</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5319,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>369</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>56.41</t>
+          <t>26.32</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>63.5</t>
+          <t>48.03</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-4.18</t>
+          <t>-4.11</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>44.05</t>
+          <t>44.12</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>43.82</t>
+          <t>43.75</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>45.74</t>
+          <t>45.63</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>44.52</t>
+          <t>44.56</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>41.38</t>
+          <t>46.58</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-116.47</t>
+          <t>-114.75</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>28216.53690303907</t>
+          <t>28209.25794797688</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>11510.0</t>
+          <t>14261.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>16805.6</t>
+          <t>15908.2</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>15306.2</t>
+          <t>16389.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>18754.5</t>
+          <t>18175.4</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>1499</t>
+          <t>-481</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>719.496237149335</t>
+          <t>764.8742980587986</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>1242.74</v>
+        <v>1014.45</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-11.82</t>
+          <t>-11.22</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5492,22 +5492,22 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.4880769767117557</t>
+          <t>-10.56465687102404</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-5.040521842261317</t>
+          <t>-13.69932964657055</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>12.92544182292656</t>
+          <t>7.80229574004913</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,42 +5517,42 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>5.18</t>
+          <t>6.59</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>70.17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>16.40%</t>
+          <t>8.25%</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
         <is>
-          <t>-4.57%</t>
+          <t>-14.21%</t>
         </is>
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>44.82</t>
+          <t>43.93</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>1869</t>
+          <t>1880</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,7 +5572,7 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>44.45</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
@@ -5582,17 +5582,17 @@
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>43.35</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>19.49</t>
+          <t>18.72</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3339.54</t>
+          <t>1631.485</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>96.5</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5644,17 +5644,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-6.04</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>19.15</t>
+          <t>-20.69</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-9.81</t>
+          <t>-16.26</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16.14</t>
+          <t>7.89</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,288 +5750,4598 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>32</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>1816</t>
+          <t>1631</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>36.84</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>12.28</t>
+          <t>13.16</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>-3.30</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-4.66</t>
+          <t>-3.32</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-1.9</t>
+          <t>-6.3</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>9.23</t>
+          <t>5.78</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>95.85999999999999</t>
+          <t>92.66</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>100.55</t>
+          <t>95.84</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>102.5</t>
+          <t>102.28</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>93.84</t>
+          <t>96.69</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-73.38</t>
+          <t>-16.84</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
+          <t>-2.54</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>-2.18</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>7.19</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr">
+        <is>
+          <t>-130.25</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>2025/07/15</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>357139500.2514451</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>147034386.0</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>146439342.4</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>184645225.3</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>461884050.18</t>
+        </is>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>-38205882</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>-28795522.72575311</t>
+        </is>
+      </c>
+      <c r="BC13" t="n">
+        <v>-28080257.81</v>
+      </c>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
+          <t>81.3</t>
+        </is>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
+          <t>2025/07/28</t>
+        </is>
+      </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>10.21</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>鉅祥</t>
+        </is>
+      </c>
+      <c r="BI13" t="inlineStr">
+        <is>
+          <t>鉅祥</t>
+        </is>
+      </c>
+      <c r="BJ13" t="inlineStr">
+        <is>
+          <t>電子零組件業</t>
+        </is>
+      </c>
+      <c r="BK13" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL13" t="inlineStr">
+        <is>
+          <t>1.04</t>
+        </is>
+      </c>
+      <c r="BM13" t="inlineStr">
+        <is>
+          <t>-7.291353668658945</t>
+        </is>
+      </c>
+      <c r="BN13" t="inlineStr">
+        <is>
+          <t>11.64963320584363</t>
+        </is>
+      </c>
+      <c r="BO13" t="inlineStr">
+        <is>
+          <t>10.65346457950322</t>
+        </is>
+      </c>
+      <c r="BP13" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ13" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR13" t="inlineStr">
+        <is>
+          <t>2.36</t>
+        </is>
+      </c>
+      <c r="BS13" t="inlineStr">
+        <is>
+          <t>3.9</t>
+        </is>
+      </c>
+      <c r="BT13" t="inlineStr">
+        <is>
+          <t>9.36</t>
+        </is>
+      </c>
+      <c r="BU13" t="inlineStr">
+        <is>
+          <t>23.03</t>
+        </is>
+      </c>
+      <c r="BV13" t="inlineStr">
+        <is>
+          <t>29.60%</t>
+        </is>
+      </c>
+      <c r="BW13" t="inlineStr">
+        <is>
+          <t>15.93%</t>
+        </is>
+      </c>
+      <c r="BX13" t="inlineStr">
+        <is>
+          <t>33.74</t>
+        </is>
+      </c>
+      <c r="BY13" t="inlineStr">
+        <is>
+          <t>18896</t>
+        </is>
+      </c>
+      <c r="BZ13" t="inlineStr">
+        <is>
+          <t>部品95.14%、模具3.09%、商品銷售1.03%、治具0.75% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA13" t="inlineStr">
+        <is>
+          <t>鉅祥-電子零組件業-上市</t>
+        </is>
+      </c>
+      <c r="CB13" t="inlineStr">
+        <is>
+          <t>電子零組件業右上上市</t>
+        </is>
+      </c>
+      <c r="CC13" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="CD13" t="inlineStr">
+        <is>
+          <t>91.5</t>
+        </is>
+      </c>
+      <c r="CE13" t="inlineStr">
+        <is>
+          <t>89.4</t>
+        </is>
+      </c>
+      <c r="CF13" t="inlineStr">
+        <is>
+          <t>89.6</t>
+        </is>
+      </c>
+      <c r="CG13" t="inlineStr">
+        <is>
+          <t>38.04</t>
+        </is>
+      </c>
+      <c r="CH13" t="inlineStr">
+        <is>
+          <t>** 平面顯示器 - 其他零組件** 通信網路 - 主/被動元件、塑膠/金屬機殼** 連接器 - 金屬材料、電鍍材料、塑膠材料** 醫療器材 - 塑化材料</t>
+        </is>
+      </c>
+      <c r="CI13" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2476</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>-4.0</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1815.561</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-1.56</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>-1.22</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>-32.28</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2025-07-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2025-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2025-03-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2025-03-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>78.2</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>107.0</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>95.8</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>92.1</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>-14.95</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>-15.09</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>8.78</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>-2.53</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>1631</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>15.79</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>-2.55</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>-3.05</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>-6.05</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>6.20</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>93.38</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>96.32</t>
+        </is>
+      </c>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>102.52</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>96.53</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>-10.98</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>-2.31</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>-2.08</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>7.19</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>-128.98</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>2025/07/15</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>357139500.2514451</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>166787289.0</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>135964184.0</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>200767284.9</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>481289771.06</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>-64803100</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>-28925570.89173124</t>
+        </is>
+      </c>
+      <c r="BC14" t="n">
+        <v>-29607378.16</v>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>81.3</t>
+        </is>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>2025/07/28</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>11.93</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>鉅祥</t>
+        </is>
+      </c>
+      <c r="BI14" t="inlineStr">
+        <is>
+          <t>鉅祥</t>
+        </is>
+      </c>
+      <c r="BJ14" t="inlineStr">
+        <is>
+          <t>電子零組件業</t>
+        </is>
+      </c>
+      <c r="BK14" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL14" t="inlineStr">
+        <is>
+          <t>1.04</t>
+        </is>
+      </c>
+      <c r="BM14" t="inlineStr">
+        <is>
+          <t>-7.291353668658945</t>
+        </is>
+      </c>
+      <c r="BN14" t="inlineStr">
+        <is>
+          <t>11.64963320584363</t>
+        </is>
+      </c>
+      <c r="BO14" t="inlineStr">
+        <is>
+          <t>10.65346457950322</t>
+        </is>
+      </c>
+      <c r="BP14" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ14" t="inlineStr">
+        <is>
+          <t>價跌量-</t>
+        </is>
+      </c>
+      <c r="BR14" t="inlineStr">
+        <is>
+          <t>2.39</t>
+        </is>
+      </c>
+      <c r="BS14" t="inlineStr">
+        <is>
+          <t>3.9</t>
+        </is>
+      </c>
+      <c r="BT14" t="inlineStr">
+        <is>
+          <t>9.36</t>
+        </is>
+      </c>
+      <c r="BU14" t="inlineStr">
+        <is>
+          <t>23.03</t>
+        </is>
+      </c>
+      <c r="BV14" t="inlineStr">
+        <is>
+          <t>29.60%</t>
+        </is>
+      </c>
+      <c r="BW14" t="inlineStr">
+        <is>
+          <t>15.93%</t>
+        </is>
+      </c>
+      <c r="BX14" t="inlineStr">
+        <is>
+          <t>33.74</t>
+        </is>
+      </c>
+      <c r="BY14" t="inlineStr">
+        <is>
+          <t>18896</t>
+        </is>
+      </c>
+      <c r="BZ14" t="inlineStr">
+        <is>
+          <t>部品95.14%、模具3.09%、商品銷售1.03%、治具0.75% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA14" t="inlineStr">
+        <is>
+          <t>鉅祥-電子零組件業-上市</t>
+        </is>
+      </c>
+      <c r="CB14" t="inlineStr">
+        <is>
+          <t>電子零組件業右上上市</t>
+        </is>
+      </c>
+      <c r="CC14" t="inlineStr">
+        <is>
+          <t>92.5</t>
+        </is>
+      </c>
+      <c r="CD14" t="inlineStr">
+        <is>
+          <t>93.3</t>
+        </is>
+      </c>
+      <c r="CE14" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="CF14" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="CG14" t="inlineStr">
+        <is>
+          <t>38.04</t>
+        </is>
+      </c>
+      <c r="CH14" t="inlineStr">
+        <is>
+          <t>** 平面顯示器 - 其他零組件** 通信網路 - 主/被動元件、塑膠/金屬機殼** 連接器 - 金屬材料、電鍍材料、塑膠材料** 醫療器材 - 塑化材料</t>
+        </is>
+      </c>
+      <c r="CI14" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2476</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1.28</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>1433.749</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>94.7</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-5.69</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>-1.22</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>-41.55</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2025-07-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2025-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2025-03-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2025-03-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>78.2</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>107.0</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>95.8</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>92.1</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>-11.50</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>-15.09</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>6.93</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>1631</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>39.47</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>28.29</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>0.85</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>-2.99</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>-5.8</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>6.60</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>93.9</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>96.8</t>
+        </is>
+      </c>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>102.75</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>96.39</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>-5.06</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>-2.13</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
           <t>-2.03</t>
         </is>
       </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>-1.17</t>
-        </is>
-      </c>
-      <c r="AS13" t="inlineStr">
+      <c r="AS15" t="inlineStr">
         <is>
           <t>7.19</t>
         </is>
       </c>
-      <c r="AT13" t="inlineStr">
-        <is>
-          <t>-116.28</t>
-        </is>
-      </c>
-      <c r="AU13" t="inlineStr">
+      <c r="AT15" t="inlineStr">
+        <is>
+          <t>-128.18</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
         <is>
           <t>2025/07/15</t>
         </is>
       </c>
-      <c r="AV13" t="inlineStr">
-        <is>
-          <t>358162222.2048458</t>
-        </is>
-      </c>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>320473332.0</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>289387136.2</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>242878046.6</t>
-        </is>
-      </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>605817013.44</t>
-        </is>
-      </c>
-      <c r="BA13" t="inlineStr">
-        <is>
-          <t>46509089</t>
-        </is>
-      </c>
-      <c r="BB13" t="inlineStr">
-        <is>
-          <t>-44830050.93434317</t>
-        </is>
-      </c>
-      <c r="BC13" t="n">
-        <v>-18533020.64</v>
-      </c>
-      <c r="BD13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE13" t="inlineStr">
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>357139500.2514451</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>135185330.0</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>126336486.8</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>216135889.2</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>501408648.9</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>-89799402</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>-28801605.93323361</t>
+        </is>
+      </c>
+      <c r="BC15" t="n">
+        <v>-32847954.77</v>
+      </c>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE15" t="inlineStr">
         <is>
           <t>81.3</t>
         </is>
       </c>
-      <c r="BF13" t="inlineStr">
+      <c r="BF15" t="inlineStr">
         <is>
           <t>2025/07/28</t>
         </is>
       </c>
-      <c r="BG13" t="inlineStr">
-        <is>
-          <t>18.70</t>
-        </is>
-      </c>
-      <c r="BH13" t="inlineStr">
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>16.48</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
         <is>
           <t>鉅祥</t>
         </is>
       </c>
-      <c r="BI13" t="inlineStr">
+      <c r="BI15" t="inlineStr">
         <is>
           <t>鉅祥</t>
         </is>
       </c>
-      <c r="BJ13" t="inlineStr">
+      <c r="BJ15" t="inlineStr">
         <is>
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="BK13" t="inlineStr">
+      <c r="BK15" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL13" t="inlineStr">
-        <is>
-          <t>1.05</t>
-        </is>
-      </c>
-      <c r="BM13" t="inlineStr">
-        <is>
-          <t>7.243628495975055</t>
-        </is>
-      </c>
-      <c r="BN13" t="inlineStr">
-        <is>
-          <t>10.93608575876562</t>
-        </is>
-      </c>
-      <c r="BO13" t="inlineStr">
-        <is>
-          <t>10.47688511853321</t>
-        </is>
-      </c>
-      <c r="BP13" t="inlineStr">
+      <c r="BL15" t="inlineStr">
+        <is>
+          <t>1.04</t>
+        </is>
+      </c>
+      <c r="BM15" t="inlineStr">
+        <is>
+          <t>-7.291353668658945</t>
+        </is>
+      </c>
+      <c r="BN15" t="inlineStr">
+        <is>
+          <t>11.64963320584363</t>
+        </is>
+      </c>
+      <c r="BO15" t="inlineStr">
+        <is>
+          <t>10.65346457950322</t>
+        </is>
+      </c>
+      <c r="BP15" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ15" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR15" t="inlineStr">
+        <is>
+          <t>2.49</t>
+        </is>
+      </c>
+      <c r="BS15" t="inlineStr">
+        <is>
+          <t>3.9</t>
+        </is>
+      </c>
+      <c r="BT15" t="inlineStr">
+        <is>
+          <t>9.36</t>
+        </is>
+      </c>
+      <c r="BU15" t="inlineStr">
+        <is>
+          <t>23.03</t>
+        </is>
+      </c>
+      <c r="BV15" t="inlineStr">
+        <is>
+          <t>29.60%</t>
+        </is>
+      </c>
+      <c r="BW15" t="inlineStr">
+        <is>
+          <t>15.93%</t>
+        </is>
+      </c>
+      <c r="BX15" t="inlineStr">
+        <is>
+          <t>33.74</t>
+        </is>
+      </c>
+      <c r="BY15" t="inlineStr">
+        <is>
+          <t>18896</t>
+        </is>
+      </c>
+      <c r="BZ15" t="inlineStr">
+        <is>
+          <t>部品95.14%、模具3.09%、商品銷售1.03%、治具0.75% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA15" t="inlineStr">
+        <is>
+          <t>鉅祥-電子零組件業-上市</t>
+        </is>
+      </c>
+      <c r="CB15" t="inlineStr">
+        <is>
+          <t>電子零組件業右上上市</t>
+        </is>
+      </c>
+      <c r="CC15" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="CD15" t="inlineStr">
+        <is>
+          <t>95.3</t>
+        </is>
+      </c>
+      <c r="CE15" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="CF15" t="inlineStr">
+        <is>
+          <t>94.7</t>
+        </is>
+      </c>
+      <c r="CG15" t="inlineStr">
+        <is>
+          <t>38.04</t>
+        </is>
+      </c>
+      <c r="CH15" t="inlineStr">
+        <is>
+          <t>** 平面顯示器 - 其他零組件** 通信網路 - 主/被動元件、塑膠/金屬機殼** 連接器 - 金屬材料、電鍍材料、塑膠材料** 醫療器材 - 塑化材料</t>
+        </is>
+      </c>
+      <c r="CI15" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2476</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>-1.05</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1479.927</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>93.5</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-4.35</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>-1.22</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>-38.14</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2025-07-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2025-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2025-03-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2025-03-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>78.2</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>107.0</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>95.8</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>92.1</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>-12.62</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>-15.09</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-11-12</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>7.15</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>-2.67</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>1631</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>7.89</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>16.8</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>-0.38</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>-3.29</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>-5.69</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>93.86</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>97.05</t>
+        </is>
+      </c>
+      <c r="AN16" t="inlineStr">
+        <is>
+          <t>102.91</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>96.17</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>-11.98</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>-2.24</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>-2.00</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>7.19</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr">
+        <is>
+          <t>-127.83</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>2025/07/15</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>357139500.2514451</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>140181204.0</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>137059889.8</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>221562336.5</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>538168556.64</t>
+        </is>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>-84502446</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>-28065906.14552652</t>
+        </is>
+      </c>
+      <c r="BC16" t="n">
+        <v>-32918284.49</v>
+      </c>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE16" t="inlineStr">
+        <is>
+          <t>81.3</t>
+        </is>
+      </c>
+      <c r="BF16" t="inlineStr">
+        <is>
+          <t>2025/07/28</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>15.01</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>鉅祥</t>
+        </is>
+      </c>
+      <c r="BI16" t="inlineStr">
+        <is>
+          <t>鉅祥</t>
+        </is>
+      </c>
+      <c r="BJ16" t="inlineStr">
+        <is>
+          <t>電子零組件業</t>
+        </is>
+      </c>
+      <c r="BK16" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL16" t="inlineStr">
+        <is>
+          <t>1.04</t>
+        </is>
+      </c>
+      <c r="BM16" t="inlineStr">
+        <is>
+          <t>-7.291353668658945</t>
+        </is>
+      </c>
+      <c r="BN16" t="inlineStr">
+        <is>
+          <t>11.64963320584363</t>
+        </is>
+      </c>
+      <c r="BO16" t="inlineStr">
+        <is>
+          <t>10.65346457950322</t>
+        </is>
+      </c>
+      <c r="BP16" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BQ13" t="inlineStr">
+      <c r="BQ16" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR13" t="inlineStr">
+      <c r="BR16" t="inlineStr">
+        <is>
+          <t>2.46</t>
+        </is>
+      </c>
+      <c r="BS16" t="inlineStr">
+        <is>
+          <t>3.9</t>
+        </is>
+      </c>
+      <c r="BT16" t="inlineStr">
+        <is>
+          <t>9.36</t>
+        </is>
+      </c>
+      <c r="BU16" t="inlineStr">
+        <is>
+          <t>23.03</t>
+        </is>
+      </c>
+      <c r="BV16" t="inlineStr">
+        <is>
+          <t>29.60%</t>
+        </is>
+      </c>
+      <c r="BW16" t="inlineStr">
+        <is>
+          <t>15.93%</t>
+        </is>
+      </c>
+      <c r="BX16" t="inlineStr">
+        <is>
+          <t>33.74</t>
+        </is>
+      </c>
+      <c r="BY16" t="inlineStr">
+        <is>
+          <t>18896</t>
+        </is>
+      </c>
+      <c r="BZ16" t="inlineStr">
+        <is>
+          <t>部品95.14%、模具3.09%、商品銷售1.03%、治具0.75% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA16" t="inlineStr">
+        <is>
+          <t>鉅祥-電子零組件業-上市</t>
+        </is>
+      </c>
+      <c r="CB16" t="inlineStr">
+        <is>
+          <t>電子零組件業右上上市</t>
+        </is>
+      </c>
+      <c r="CC16" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
+      <c r="CD16" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
+      <c r="CE16" t="inlineStr">
+        <is>
+          <t>93.5</t>
+        </is>
+      </c>
+      <c r="CF16" t="inlineStr">
+        <is>
+          <t>93.5</t>
+        </is>
+      </c>
+      <c r="CG16" t="inlineStr">
+        <is>
+          <t>38.04</t>
+        </is>
+      </c>
+      <c r="CH16" t="inlineStr">
+        <is>
+          <t>** 平面顯示器 - 其他零組件** 通信網路 - 主/被動元件、塑膠/金屬機殼** 連接器 - 金屬材料、電鍍材料、塑膠材料** 醫療器材 - 塑化材料</t>
+        </is>
+      </c>
+      <c r="CI16" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2476</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>1504.164</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>94.5</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-5.47</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>-1.22</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>-34.56</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2025-07-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2025-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>2025-03-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2025-03-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>78.2</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>107.0</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>95.8</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>92.1</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>-11.68</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>-15.09</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-11-11</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>7.27</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>-0.83</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>1631</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>37.5</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>19.17</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>0.28</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>-3.11</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>-5.57</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>7.35</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>94.24</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>97.26</t>
+        </is>
+      </c>
+      <c r="AN17" t="inlineStr">
+        <is>
+          <t>103.0</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>95.95</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>-14.81</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>-2.23</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>-1.94</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>7.19</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr">
+        <is>
+          <t>-126.99</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>2025/07/15</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>357139500.2514451</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>143008503.0</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>152789337.4</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>233463581.9</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>553861277.88</t>
+        </is>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>-80674244</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>-27183655.53719378</t>
+        </is>
+      </c>
+      <c r="BC17" t="n">
+        <v>-32378374.72</v>
+      </c>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE17" t="inlineStr">
+        <is>
+          <t>81.3</t>
+        </is>
+      </c>
+      <c r="BF17" t="inlineStr">
+        <is>
+          <t>2025/07/28</t>
+        </is>
+      </c>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>16.24</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>鉅祥</t>
+        </is>
+      </c>
+      <c r="BI17" t="inlineStr">
+        <is>
+          <t>鉅祥</t>
+        </is>
+      </c>
+      <c r="BJ17" t="inlineStr">
+        <is>
+          <t>電子零組件業</t>
+        </is>
+      </c>
+      <c r="BK17" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL17" t="inlineStr">
+        <is>
+          <t>1.04</t>
+        </is>
+      </c>
+      <c r="BM17" t="inlineStr">
+        <is>
+          <t>-7.291353668658945</t>
+        </is>
+      </c>
+      <c r="BN17" t="inlineStr">
+        <is>
+          <t>11.64963320584363</t>
+        </is>
+      </c>
+      <c r="BO17" t="inlineStr">
+        <is>
+          <t>10.65346457950322</t>
+        </is>
+      </c>
+      <c r="BP17" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ17" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR17" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="BS17" t="inlineStr">
+        <is>
+          <t>3.9</t>
+        </is>
+      </c>
+      <c r="BT17" t="inlineStr">
+        <is>
+          <t>9.36</t>
+        </is>
+      </c>
+      <c r="BU17" t="inlineStr">
+        <is>
+          <t>23.03</t>
+        </is>
+      </c>
+      <c r="BV17" t="inlineStr">
+        <is>
+          <t>29.60%</t>
+        </is>
+      </c>
+      <c r="BW17" t="inlineStr">
+        <is>
+          <t>15.93%</t>
+        </is>
+      </c>
+      <c r="BX17" t="inlineStr">
+        <is>
+          <t>33.74</t>
+        </is>
+      </c>
+      <c r="BY17" t="inlineStr">
+        <is>
+          <t>18896</t>
+        </is>
+      </c>
+      <c r="BZ17" t="inlineStr">
+        <is>
+          <t>部品95.14%、模具3.09%、商品銷售1.03%、治具0.75% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA17" t="inlineStr">
+        <is>
+          <t>鉅祥-電子零組件業-上市</t>
+        </is>
+      </c>
+      <c r="CB17" t="inlineStr">
+        <is>
+          <t>電子零組件業右上上市</t>
+        </is>
+      </c>
+      <c r="CC17" t="inlineStr">
+        <is>
+          <t>93.3</t>
+        </is>
+      </c>
+      <c r="CD17" t="inlineStr">
+        <is>
+          <t>96.5</t>
+        </is>
+      </c>
+      <c r="CE17" t="inlineStr">
+        <is>
+          <t>93.3</t>
+        </is>
+      </c>
+      <c r="CF17" t="inlineStr">
+        <is>
+          <t>94.5</t>
+        </is>
+      </c>
+      <c r="CG17" t="inlineStr">
+        <is>
+          <t>38.04</t>
+        </is>
+      </c>
+      <c r="CH17" t="inlineStr">
+        <is>
+          <t>** 平面顯示器 - 其他零組件** 通信網路 - 主/被動元件、塑膠/金屬機殼** 連接器 - 金屬材料、電鍍材料、塑膠材料** 醫療器材 - 塑化材料</t>
+        </is>
+      </c>
+      <c r="CI17" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2476</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>-0.43</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>1012.26</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>93.2</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-4.02</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-1.22</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>-18.35</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2025-07-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2025-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>2025-03-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2025-03-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>78.2</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>107.0</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>95.8</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>92.1</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>-12.90</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>-15.09</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-11-10</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>-1.82</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>1631</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>13.33</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>-1.54</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>-3.03</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>-5.24</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>7.68</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>94.66</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>97.62</t>
+        </is>
+      </c>
+      <c r="AN18" t="inlineStr">
+        <is>
+          <t>103.01</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>95.66</t>
+        </is>
+      </c>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>-22.08</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>-2.28</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>-1.87</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>7.19</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr">
+        <is>
+          <t>-125.99</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>2025/07/15</t>
+        </is>
+      </c>
+      <c r="AV18" t="inlineStr">
+        <is>
+          <t>357139500.2514451</t>
+        </is>
+      </c>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>94658594.0</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>222851108.2</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>272945780.2</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>561353465.26</t>
+        </is>
+      </c>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>-50094672</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>-26239161.13943687</t>
+        </is>
+      </c>
+      <c r="BC18" t="n">
+        <v>-30753629.43</v>
+      </c>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE18" t="inlineStr">
+        <is>
+          <t>81.3</t>
+        </is>
+      </c>
+      <c r="BF18" t="inlineStr">
+        <is>
+          <t>2025/07/28</t>
+        </is>
+      </c>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>14.64</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>鉅祥</t>
+        </is>
+      </c>
+      <c r="BI18" t="inlineStr">
+        <is>
+          <t>鉅祥</t>
+        </is>
+      </c>
+      <c r="BJ18" t="inlineStr">
+        <is>
+          <t>電子零組件業</t>
+        </is>
+      </c>
+      <c r="BK18" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL18" t="inlineStr">
+        <is>
+          <t>1.04</t>
+        </is>
+      </c>
+      <c r="BM18" t="inlineStr">
+        <is>
+          <t>-7.291353668658945</t>
+        </is>
+      </c>
+      <c r="BN18" t="inlineStr">
+        <is>
+          <t>11.64963320584363</t>
+        </is>
+      </c>
+      <c r="BO18" t="inlineStr">
+        <is>
+          <t>10.65346457950322</t>
+        </is>
+      </c>
+      <c r="BP18" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BQ18" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR18" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="BS18" t="inlineStr">
+        <is>
+          <t>3.9</t>
+        </is>
+      </c>
+      <c r="BT18" t="inlineStr">
+        <is>
+          <t>9.36</t>
+        </is>
+      </c>
+      <c r="BU18" t="inlineStr">
+        <is>
+          <t>23.03</t>
+        </is>
+      </c>
+      <c r="BV18" t="inlineStr">
+        <is>
+          <t>29.60%</t>
+        </is>
+      </c>
+      <c r="BW18" t="inlineStr">
+        <is>
+          <t>15.93%</t>
+        </is>
+      </c>
+      <c r="BX18" t="inlineStr">
+        <is>
+          <t>33.74</t>
+        </is>
+      </c>
+      <c r="BY18" t="inlineStr">
+        <is>
+          <t>18896</t>
+        </is>
+      </c>
+      <c r="BZ18" t="inlineStr">
+        <is>
+          <t>部品95.14%、模具3.09%、商品銷售1.03%、治具0.75% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA18" t="inlineStr">
+        <is>
+          <t>鉅祥-電子零組件業-上市</t>
+        </is>
+      </c>
+      <c r="CB18" t="inlineStr">
+        <is>
+          <t>電子零組件業右上上市</t>
+        </is>
+      </c>
+      <c r="CC18" t="inlineStr">
+        <is>
+          <t>93.7</t>
+        </is>
+      </c>
+      <c r="CD18" t="inlineStr">
+        <is>
+          <t>95.3</t>
+        </is>
+      </c>
+      <c r="CE18" t="inlineStr">
+        <is>
+          <t>92.8</t>
+        </is>
+      </c>
+      <c r="CF18" t="inlineStr">
+        <is>
+          <t>93.2</t>
+        </is>
+      </c>
+      <c r="CG18" t="inlineStr">
+        <is>
+          <t>38.04</t>
+        </is>
+      </c>
+      <c r="CH18" t="inlineStr">
+        <is>
+          <t>** 平面顯示器 - 其他零組件** 通信網路 - 主/被動元件、塑膠/金屬機殼** 連接器 - 金屬材料、電鍍材料、塑膠材料** 醫療器材 - 塑化材料</t>
+        </is>
+      </c>
+      <c r="CI18" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2476</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>-0.96</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>1267.489</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>93.6</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-4.46</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>-1.22</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>-4.29</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2025-07-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2025-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>2025-03-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2025-03-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>78.2</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>107.0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>95.8</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>92.1</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>-12.52</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>-15.09</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>6.13</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>-0.10</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>1631</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>15.0</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>22.33</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>-1.91</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>-2.81</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>-4.71</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>8.01</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>95.42</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>98.18</t>
+        </is>
+      </c>
+      <c r="AN19" t="inlineStr">
+        <is>
+          <t>103.03</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>95.39</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>-23.72</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>-2.19</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>-1.77</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>7.19</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr">
+        <is>
+          <t>-124.56</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>2025/07/15</t>
+        </is>
+      </c>
+      <c r="AV19" t="inlineStr">
+        <is>
+          <t>357139500.2514451</t>
+        </is>
+      </c>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>118648803.0</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>265570385.8</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>277478761.0</t>
+        </is>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>570658631.0</t>
+        </is>
+      </c>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>-11908375</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>-25418348.72380762</t>
+        </is>
+      </c>
+      <c r="BC19" t="n">
+        <v>-22153873.41</v>
+      </c>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE19" t="inlineStr">
+        <is>
+          <t>81.3</t>
+        </is>
+      </c>
+      <c r="BF19" t="inlineStr">
+        <is>
+          <t>2025/07/28</t>
+        </is>
+      </c>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>15.13</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>鉅祥</t>
+        </is>
+      </c>
+      <c r="BI19" t="inlineStr">
+        <is>
+          <t>鉅祥</t>
+        </is>
+      </c>
+      <c r="BJ19" t="inlineStr">
+        <is>
+          <t>電子零組件業</t>
+        </is>
+      </c>
+      <c r="BK19" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL19" t="inlineStr">
+        <is>
+          <t>1.04</t>
+        </is>
+      </c>
+      <c r="BM19" t="inlineStr">
+        <is>
+          <t>-7.291353668658945</t>
+        </is>
+      </c>
+      <c r="BN19" t="inlineStr">
+        <is>
+          <t>11.64963320584363</t>
+        </is>
+      </c>
+      <c r="BO19" t="inlineStr">
+        <is>
+          <t>10.65346457950322</t>
+        </is>
+      </c>
+      <c r="BP19" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ19" t="inlineStr">
+        <is>
+          <t>價-量縮</t>
+        </is>
+      </c>
+      <c r="BR19" t="inlineStr">
+        <is>
+          <t>2.46</t>
+        </is>
+      </c>
+      <c r="BS19" t="inlineStr">
+        <is>
+          <t>3.9</t>
+        </is>
+      </c>
+      <c r="BT19" t="inlineStr">
+        <is>
+          <t>9.36</t>
+        </is>
+      </c>
+      <c r="BU19" t="inlineStr">
+        <is>
+          <t>23.03</t>
+        </is>
+      </c>
+      <c r="BV19" t="inlineStr">
+        <is>
+          <t>29.60%</t>
+        </is>
+      </c>
+      <c r="BW19" t="inlineStr">
+        <is>
+          <t>15.93%</t>
+        </is>
+      </c>
+      <c r="BX19" t="inlineStr">
+        <is>
+          <t>33.74</t>
+        </is>
+      </c>
+      <c r="BY19" t="inlineStr">
+        <is>
+          <t>18896</t>
+        </is>
+      </c>
+      <c r="BZ19" t="inlineStr">
+        <is>
+          <t>部品95.14%、模具3.09%、商品銷售1.03%、治具0.75% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA19" t="inlineStr">
+        <is>
+          <t>鉅祥-電子零組件業-上市</t>
+        </is>
+      </c>
+      <c r="CB19" t="inlineStr">
+        <is>
+          <t>電子零組件業右上上市</t>
+        </is>
+      </c>
+      <c r="CC19" t="inlineStr">
+        <is>
+          <t>93.8</t>
+        </is>
+      </c>
+      <c r="CD19" t="inlineStr">
+        <is>
+          <t>94.5</t>
+        </is>
+      </c>
+      <c r="CE19" t="inlineStr">
+        <is>
+          <t>92.8</t>
+        </is>
+      </c>
+      <c r="CF19" t="inlineStr">
+        <is>
+          <t>93.6</t>
+        </is>
+      </c>
+      <c r="CG19" t="inlineStr">
+        <is>
+          <t>38.04</t>
+        </is>
+      </c>
+      <c r="CH19" t="inlineStr">
+        <is>
+          <t>** 平面顯示器 - 其他零組件** 通信網路 - 主/被動元件、塑膠/金屬機殼** 連接器 - 金屬材料、電鍍材料、塑膠材料** 醫療器材 - 塑化材料</t>
+        </is>
+      </c>
+      <c r="CI19" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2476</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>-0.93</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1991.474</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>94.5</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-5.47</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>-1.22</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>9.77</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2025-07-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>2025-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>2025-03-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2025-03-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>78.2</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>107.0</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>95.8</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>92.1</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>-11.68</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>-15.09</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>9.63</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>-1.36</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>1631</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>20.0</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>33.33</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>-1.56</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>-2.78</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>-4.12</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>8.29</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>98.75</t>
+        </is>
+      </c>
+      <c r="AN20" t="inlineStr">
+        <is>
+          <t>102.99</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>95.11</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>-24.59</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>-2.07</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>-1.66</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>7.19</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr">
+        <is>
+          <t>-123.10</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>2025/07/15</t>
+        </is>
+      </c>
+      <c r="AV20" t="inlineStr">
+        <is>
+          <t>357139500.2514451</t>
+        </is>
+      </c>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>188802345.0</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>305935291.6</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>278708338.6</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>581698082.72</t>
+        </is>
+      </c>
+      <c r="BA20" t="inlineStr">
+        <is>
+          <t>27226953</t>
+        </is>
+      </c>
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>-26011889.68977666</t>
+        </is>
+      </c>
+      <c r="BC20" t="n">
+        <v>-11647677.45</v>
+      </c>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE20" t="inlineStr">
+        <is>
+          <t>81.3</t>
+        </is>
+      </c>
+      <c r="BF20" t="inlineStr">
+        <is>
+          <t>2025/07/28</t>
+        </is>
+      </c>
+      <c r="BG20" t="inlineStr">
+        <is>
+          <t>16.24</t>
+        </is>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>鉅祥</t>
+        </is>
+      </c>
+      <c r="BI20" t="inlineStr">
+        <is>
+          <t>鉅祥</t>
+        </is>
+      </c>
+      <c r="BJ20" t="inlineStr">
+        <is>
+          <t>電子零組件業</t>
+        </is>
+      </c>
+      <c r="BK20" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL20" t="inlineStr">
+        <is>
+          <t>1.04</t>
+        </is>
+      </c>
+      <c r="BM20" t="inlineStr">
+        <is>
+          <t>-7.291353668658945</t>
+        </is>
+      </c>
+      <c r="BN20" t="inlineStr">
+        <is>
+          <t>11.64963320584363</t>
+        </is>
+      </c>
+      <c r="BO20" t="inlineStr">
+        <is>
+          <t>10.65346457950322</t>
+        </is>
+      </c>
+      <c r="BP20" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ20" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR20" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="BS20" t="inlineStr">
+        <is>
+          <t>3.9</t>
+        </is>
+      </c>
+      <c r="BT20" t="inlineStr">
+        <is>
+          <t>9.36</t>
+        </is>
+      </c>
+      <c r="BU20" t="inlineStr">
+        <is>
+          <t>23.03</t>
+        </is>
+      </c>
+      <c r="BV20" t="inlineStr">
+        <is>
+          <t>29.60%</t>
+        </is>
+      </c>
+      <c r="BW20" t="inlineStr">
+        <is>
+          <t>15.93%</t>
+        </is>
+      </c>
+      <c r="BX20" t="inlineStr">
+        <is>
+          <t>33.74</t>
+        </is>
+      </c>
+      <c r="BY20" t="inlineStr">
+        <is>
+          <t>18896</t>
+        </is>
+      </c>
+      <c r="BZ20" t="inlineStr">
+        <is>
+          <t>部品95.14%、模具3.09%、商品銷售1.03%、治具0.75% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA20" t="inlineStr">
+        <is>
+          <t>鉅祥-電子零組件業-上市</t>
+        </is>
+      </c>
+      <c r="CB20" t="inlineStr">
+        <is>
+          <t>電子零組件業右上上市</t>
+        </is>
+      </c>
+      <c r="CC20" t="inlineStr">
+        <is>
+          <t>96.3</t>
+        </is>
+      </c>
+      <c r="CD20" t="inlineStr">
+        <is>
+          <t>97.1</t>
+        </is>
+      </c>
+      <c r="CE20" t="inlineStr">
+        <is>
+          <t>93.2</t>
+        </is>
+      </c>
+      <c r="CF20" t="inlineStr">
+        <is>
+          <t>94.5</t>
+        </is>
+      </c>
+      <c r="CG20" t="inlineStr">
+        <is>
+          <t>38.04</t>
+        </is>
+      </c>
+      <c r="CH20" t="inlineStr">
+        <is>
+          <t>** 平面顯示器 - 其他零組件** 通信網路 - 主/被動元件、塑膠/金屬機殼** 連接器 - 金屬材料、電鍍材料、塑膠材料** 醫療器材 - 塑化材料</t>
+        </is>
+      </c>
+      <c r="CI20" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2476</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>-1.26</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2312.284</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>95.4</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-6.47</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>-1.22</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2025-07-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>2025-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>2025-03-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2025-03-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>78.2</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>107.0</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>95.8</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>92.1</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>-10.84</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>-15.09</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11.18</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>1631</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>32.0</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>40.7</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>-0.31</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>-3.72</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>-3.41</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>8.52</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>95.7</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>99.4</t>
+        </is>
+      </c>
+      <c r="AN21" t="inlineStr">
+        <is>
+          <t>102.9</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>94.83</t>
+        </is>
+      </c>
+      <c r="AP21" t="inlineStr">
+        <is>
+          <t>-27.28</t>
+        </is>
+      </c>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>-1.98</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>-1.56</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>7.19</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr">
+        <is>
+          <t>-121.68</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>2025/07/15</t>
+        </is>
+      </c>
+      <c r="AV21" t="inlineStr">
+        <is>
+          <t>357139500.2514451</t>
+        </is>
+      </c>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>218828442.0</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>306064783.2</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>278240578.4</t>
+        </is>
+      </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>594226537.62</t>
+        </is>
+      </c>
+      <c r="BA21" t="inlineStr">
+        <is>
+          <t>27824204</t>
+        </is>
+      </c>
+      <c r="BB21" t="inlineStr">
+        <is>
+          <t>-28623564.64298534</t>
+        </is>
+      </c>
+      <c r="BC21" t="n">
+        <v>-3739288.52</v>
+      </c>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE21" t="inlineStr">
+        <is>
+          <t>81.3</t>
+        </is>
+      </c>
+      <c r="BF21" t="inlineStr">
+        <is>
+          <t>2025/07/28</t>
+        </is>
+      </c>
+      <c r="BG21" t="inlineStr">
+        <is>
+          <t>17.34</t>
+        </is>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>鉅祥</t>
+        </is>
+      </c>
+      <c r="BI21" t="inlineStr">
+        <is>
+          <t>鉅祥</t>
+        </is>
+      </c>
+      <c r="BJ21" t="inlineStr">
+        <is>
+          <t>電子零組件業</t>
+        </is>
+      </c>
+      <c r="BK21" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL21" t="inlineStr">
+        <is>
+          <t>1.04</t>
+        </is>
+      </c>
+      <c r="BM21" t="inlineStr">
+        <is>
+          <t>-7.291353668658945</t>
+        </is>
+      </c>
+      <c r="BN21" t="inlineStr">
+        <is>
+          <t>11.64963320584363</t>
+        </is>
+      </c>
+      <c r="BO21" t="inlineStr">
+        <is>
+          <t>10.65346457950322</t>
+        </is>
+      </c>
+      <c r="BP21" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ21" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BR21" t="inlineStr">
+        <is>
+          <t>2.51</t>
+        </is>
+      </c>
+      <c r="BS21" t="inlineStr">
+        <is>
+          <t>3.9</t>
+        </is>
+      </c>
+      <c r="BT21" t="inlineStr">
+        <is>
+          <t>9.36</t>
+        </is>
+      </c>
+      <c r="BU21" t="inlineStr">
+        <is>
+          <t>23.03</t>
+        </is>
+      </c>
+      <c r="BV21" t="inlineStr">
+        <is>
+          <t>29.60%</t>
+        </is>
+      </c>
+      <c r="BW21" t="inlineStr">
+        <is>
+          <t>15.93%</t>
+        </is>
+      </c>
+      <c r="BX21" t="inlineStr">
+        <is>
+          <t>33.74</t>
+        </is>
+      </c>
+      <c r="BY21" t="inlineStr">
+        <is>
+          <t>18896</t>
+        </is>
+      </c>
+      <c r="BZ21" t="inlineStr">
+        <is>
+          <t>部品95.14%、模具3.09%、商品銷售1.03%、治具0.75% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA21" t="inlineStr">
+        <is>
+          <t>鉅祥-電子零組件業-上市</t>
+        </is>
+      </c>
+      <c r="CB21" t="inlineStr">
+        <is>
+          <t>電子零組件業右上上市</t>
+        </is>
+      </c>
+      <c r="CC21" t="inlineStr">
+        <is>
+          <t>95.1</t>
+        </is>
+      </c>
+      <c r="CD21" t="inlineStr">
+        <is>
+          <t>96.2</t>
+        </is>
+      </c>
+      <c r="CE21" t="inlineStr">
+        <is>
+          <t>93.5</t>
+        </is>
+      </c>
+      <c r="CF21" t="inlineStr">
+        <is>
+          <t>95.4</t>
+        </is>
+      </c>
+      <c r="CG21" t="inlineStr">
+        <is>
+          <t>38.04</t>
+        </is>
+      </c>
+      <c r="CH21" t="inlineStr">
+        <is>
+          <t>** 平面顯示器 - 其他零組件** 通信網路 - 主/被動元件、塑膠/金屬機殼** 連接器 - 金屬材料、電鍍材料、塑膠材料** 醫療器材 - 塑化材料</t>
+        </is>
+      </c>
+      <c r="CI21" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2476</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>-0.4</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>4980.394</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>96.6</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-7.81</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>-1.22</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2025-07-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>2025-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>2025-03-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2025-03-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>78.2</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>107.0</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>95.8</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>92.1</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>-9.72</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>-15.09</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-11-04</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>24.07</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>-5.49</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>1631</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>48.0</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>42.32</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>-4.32</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>-2.9</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>8.78</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>95.52000000000001</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>99.83</t>
+        </is>
+      </c>
+      <c r="AN22" t="inlineStr">
+        <is>
+          <t>102.81</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>94.52</t>
+        </is>
+      </c>
+      <c r="AP22" t="inlineStr">
+        <is>
+          <t>-33.42</t>
+        </is>
+      </c>
+      <c r="AQ22" t="inlineStr">
+        <is>
+          <t>-1.94</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>-1.45</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>7.19</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr">
+        <is>
+          <t>-120.20</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>2025/07/15</t>
+        </is>
+      </c>
+      <c r="AV22" t="inlineStr">
+        <is>
+          <t>357139500.2514451</t>
+        </is>
+      </c>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>493317357.0</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>314137826.4</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>296369265.5</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>598741786.76</t>
+        </is>
+      </c>
+      <c r="BA22" t="inlineStr">
+        <is>
+          <t>17768560</t>
+        </is>
+      </c>
+      <c r="BB22" t="inlineStr">
+        <is>
+          <t>-33147978.48379749</t>
+        </is>
+      </c>
+      <c r="BC22" t="n">
+        <v>4474874.15</v>
+      </c>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE22" t="inlineStr">
+        <is>
+          <t>81.3</t>
+        </is>
+      </c>
+      <c r="BF22" t="inlineStr">
+        <is>
+          <t>2025/07/28</t>
+        </is>
+      </c>
+      <c r="BG22" t="inlineStr">
+        <is>
+          <t>18.82</t>
+        </is>
+      </c>
+      <c r="BH22" t="inlineStr">
+        <is>
+          <t>鉅祥</t>
+        </is>
+      </c>
+      <c r="BI22" t="inlineStr">
+        <is>
+          <t>鉅祥</t>
+        </is>
+      </c>
+      <c r="BJ22" t="inlineStr">
+        <is>
+          <t>電子零組件業</t>
+        </is>
+      </c>
+      <c r="BK22" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL22" t="inlineStr">
+        <is>
+          <t>1.04</t>
+        </is>
+      </c>
+      <c r="BM22" t="inlineStr">
+        <is>
+          <t>-7.291353668658945</t>
+        </is>
+      </c>
+      <c r="BN22" t="inlineStr">
+        <is>
+          <t>11.64963320584363</t>
+        </is>
+      </c>
+      <c r="BO22" t="inlineStr">
+        <is>
+          <t>10.65346457950322</t>
+        </is>
+      </c>
+      <c r="BP22" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ22" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR22" t="inlineStr">
         <is>
           <t>2.54</t>
         </is>
       </c>
-      <c r="BS13" t="inlineStr">
-        <is>
-          <t>3.84</t>
-        </is>
-      </c>
-      <c r="BT13" t="inlineStr">
+      <c r="BS22" t="inlineStr">
+        <is>
+          <t>3.9</t>
+        </is>
+      </c>
+      <c r="BT22" t="inlineStr">
         <is>
           <t>9.36</t>
         </is>
       </c>
-      <c r="BU13" t="inlineStr">
-        <is>
-          <t>23.39</t>
-        </is>
-      </c>
-      <c r="BV13" t="inlineStr">
+      <c r="BU22" t="inlineStr">
+        <is>
+          <t>23.03</t>
+        </is>
+      </c>
+      <c r="BV22" t="inlineStr">
         <is>
           <t>29.60%</t>
         </is>
       </c>
-      <c r="BW13" t="inlineStr">
+      <c r="BW22" t="inlineStr">
         <is>
           <t>15.93%</t>
         </is>
       </c>
-      <c r="BX13" t="inlineStr">
-        <is>
-          <t>34.89</t>
-        </is>
-      </c>
-      <c r="BY13" t="inlineStr">
-        <is>
-          <t>19192</t>
-        </is>
-      </c>
-      <c r="BZ13" t="inlineStr">
+      <c r="BX22" t="inlineStr">
+        <is>
+          <t>33.74</t>
+        </is>
+      </c>
+      <c r="BY22" t="inlineStr">
+        <is>
+          <t>18896</t>
+        </is>
+      </c>
+      <c r="BZ22" t="inlineStr">
         <is>
           <t>部品95.14%、模具3.09%、商品銷售1.03%、治具0.75% (2024年)</t>
         </is>
       </c>
-      <c r="CA13" t="inlineStr">
+      <c r="CA22" t="inlineStr">
         <is>
           <t>鉅祥-電子零組件業-上市</t>
         </is>
       </c>
-      <c r="CB13" t="inlineStr">
+      <c r="CB22" t="inlineStr">
         <is>
           <t>電子零組件業右上上市</t>
         </is>
       </c>
-      <c r="CC13" t="inlineStr">
-        <is>
-          <t>95.0</t>
-        </is>
-      </c>
-      <c r="CD13" t="inlineStr">
-        <is>
-          <t>97.3</t>
-        </is>
-      </c>
-      <c r="CE13" t="inlineStr">
-        <is>
-          <t>93.5</t>
-        </is>
-      </c>
-      <c r="CF13" t="inlineStr">
+      <c r="CC22" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="CD22" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
+      <c r="CE22" t="inlineStr">
         <is>
           <t>96.5</t>
         </is>
       </c>
-      <c r="CG13" t="inlineStr">
+      <c r="CF22" t="inlineStr">
+        <is>
+          <t>96.6</t>
+        </is>
+      </c>
+      <c r="CG22" t="inlineStr">
         <is>
           <t>38.04</t>
         </is>
       </c>
-      <c r="CH13" t="inlineStr">
+      <c r="CH22" t="inlineStr">
         <is>
           <t>** 平面顯示器 - 其他零組件** 通信網路 - 主/被動元件、塑膠/金屬機殼** 連接器 - 金屬材料、電鍍材料、塑膠材料** 醫療器材 - 塑化材料</t>
         </is>
       </c>
-      <c r="CI13" t="inlineStr">
+      <c r="CI22" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2476</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>0.52</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>3171.123</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-8.26</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>-1.22</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>23.09</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2025-07-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>2025-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>2025-03-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2025-03-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>78.2</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>107.0</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>95.8</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>92.1</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>-9.35</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>-15.09</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-11-03</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>15.33</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>0.07</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>1631</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>42.11</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>26.32</t>
+        </is>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>-5.03</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>-2.37</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>8.98</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>95.16</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>100.2</t>
+        </is>
+      </c>
+      <c r="AN23" t="inlineStr">
+        <is>
+          <t>102.64</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>94.18</t>
+        </is>
+      </c>
+      <c r="AP23" t="inlineStr">
+        <is>
+          <t>-48.21</t>
+        </is>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>-1.97</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>-1.33</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>7.19</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr">
+        <is>
+          <t>-118.51</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>2025/07/15</t>
+        </is>
+      </c>
+      <c r="AV23" t="inlineStr">
+        <is>
+          <t>357139500.2514451</t>
+        </is>
+      </c>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>308254982.0</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>323040452.2</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>262443491.2</t>
+        </is>
+      </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>598029457.84</t>
+        </is>
+      </c>
+      <c r="BA23" t="inlineStr">
+        <is>
+          <t>60596961</t>
+        </is>
+      </c>
+      <c r="BB23" t="inlineStr">
+        <is>
+          <t>-39988497.144127</t>
+        </is>
+      </c>
+      <c r="BC23" t="n">
+        <v>-13359951.3</v>
+      </c>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE23" t="inlineStr">
+        <is>
+          <t>81.3</t>
+        </is>
+      </c>
+      <c r="BF23" t="inlineStr">
+        <is>
+          <t>2025/07/28</t>
+        </is>
+      </c>
+      <c r="BG23" t="inlineStr">
+        <is>
+          <t>19.31</t>
+        </is>
+      </c>
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>鉅祥</t>
+        </is>
+      </c>
+      <c r="BI23" t="inlineStr">
+        <is>
+          <t>鉅祥</t>
+        </is>
+      </c>
+      <c r="BJ23" t="inlineStr">
+        <is>
+          <t>電子零組件業</t>
+        </is>
+      </c>
+      <c r="BK23" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL23" t="inlineStr">
+        <is>
+          <t>1.04</t>
+        </is>
+      </c>
+      <c r="BM23" t="inlineStr">
+        <is>
+          <t>-7.291353668658945</t>
+        </is>
+      </c>
+      <c r="BN23" t="inlineStr">
+        <is>
+          <t>11.64963320584363</t>
+        </is>
+      </c>
+      <c r="BO23" t="inlineStr">
+        <is>
+          <t>10.65346457950322</t>
+        </is>
+      </c>
+      <c r="BP23" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ23" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR23" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="BS23" t="inlineStr">
+        <is>
+          <t>3.9</t>
+        </is>
+      </c>
+      <c r="BT23" t="inlineStr">
+        <is>
+          <t>9.36</t>
+        </is>
+      </c>
+      <c r="BU23" t="inlineStr">
+        <is>
+          <t>23.03</t>
+        </is>
+      </c>
+      <c r="BV23" t="inlineStr">
+        <is>
+          <t>29.60%</t>
+        </is>
+      </c>
+      <c r="BW23" t="inlineStr">
+        <is>
+          <t>15.93%</t>
+        </is>
+      </c>
+      <c r="BX23" t="inlineStr">
+        <is>
+          <t>33.74</t>
+        </is>
+      </c>
+      <c r="BY23" t="inlineStr">
+        <is>
+          <t>18896</t>
+        </is>
+      </c>
+      <c r="BZ23" t="inlineStr">
+        <is>
+          <t>部品95.14%、模具3.09%、商品銷售1.03%、治具0.75% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA23" t="inlineStr">
+        <is>
+          <t>鉅祥-電子零組件業-上市</t>
+        </is>
+      </c>
+      <c r="CB23" t="inlineStr">
+        <is>
+          <t>電子零組件業右上上市</t>
+        </is>
+      </c>
+      <c r="CC23" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
+      <c r="CD23" t="inlineStr">
+        <is>
+          <t>99.6</t>
+        </is>
+      </c>
+      <c r="CE23" t="inlineStr">
+        <is>
+          <t>94.4</t>
+        </is>
+      </c>
+      <c r="CF23" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
+      <c r="CG23" t="inlineStr">
+        <is>
+          <t>38.04</t>
+        </is>
+      </c>
+      <c r="CH23" t="inlineStr">
+        <is>
+          <t>** 平面顯示器 - 其他零組件** 通信網路 - 主/被動元件、塑膠/金屬機殼** 連接器 - 金屬材料、電鍍材料、塑膠材料** 醫療器材 - 塑化材料</t>
+        </is>
+      </c>
+      <c r="CI23" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/電鍍材料.xlsx
+++ b/Result/checksun_type/電鍍材料.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>369.0</t>
+          <t>655.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>42.35</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-43.86</t>
+          <t>-32.14</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-4.72</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>9.06</t>
+          <t>16.07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,72 +1014,72 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>655</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>41.18</t>
+          <t>83.93</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>14.84</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>42.22000000000001</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>43.53</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>44.23</t>
+          <t>44.15</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>44.87</t>
+          <t>44.89</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-40.91</t>
+          <t>-16.05</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-116.38</t>
+          <t>-117.06</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>28209.25794797688</t>
+          <t>28229.64502164502</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>15453.0</t>
+          <t>28225.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>11783.2</t>
+          <t>13738.6</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>20989.4</t>
+          <t>20246.9</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>12346.96</t>
+          <t>12733.2</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-9206</t>
+          <t>-6508</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>797.4475068096988</t>
+          <t>716.6020020198885</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-727.39</v>
+        <v>271.95</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-15.13</t>
+          <t>-13.23</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1207,12 +1207,12 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>42.34</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>1880</t>
+          <t>1922</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>42.7</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>42.35</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>42.35</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>358.0</t>
+          <t>369.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>42.35</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-27.59</t>
+          <t>-43.86</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-7.87</t>
+          <t>-4.72</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>8.79</t>
+          <t>9.06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1445,72 +1445,72 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>655</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>41.18</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>14.84</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-3.31</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>42.04000000000001</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>43.48</t>
+          <t>43.53</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>44.31</t>
+          <t>44.23</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>44.85</t>
+          <t>44.87</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-59.38</t>
+          <t>-40.91</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-114.70</t>
+          <t>-116.38</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>28209.25794797688</t>
+          <t>28229.64502164502</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>14757.0</t>
+          <t>15453.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>15111.8</t>
+          <t>11783.2</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>20870.2</t>
+          <t>20989.4</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>12172.68</t>
+          <t>12346.96</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-5758</t>
+          <t>-9206</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>1074.691386655718</t>
+          <t>797.4475068096988</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-760.62</v>
+        <v>-727.39</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-17.94</t>
+          <t>-15.13</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1633,17 +1633,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>42.34</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>1880</t>
+          <t>1922</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,12 +1693,12 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>42.45</t>
+          <t>42.7</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>42.35</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>358.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>5.43</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-29.63</t>
+          <t>-27.59</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-5.29</t>
+          <t>-7.87</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>8.79</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1876,12 +1876,12 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>655</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1891,57 +1891,57 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-3.31</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>42.55</t>
+          <t>42.04000000000001</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.48</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>44.42</t>
+          <t>44.31</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>44.84</t>
+          <t>44.85</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-46.96</t>
+          <t>-59.38</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-112.52</t>
+          <t>-114.70</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>28209.25794797688</t>
+          <t>28229.64502164502</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>4814.0</t>
+          <t>14757.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>14458.8</t>
+          <t>15111.8</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>20545.5</t>
+          <t>20870.2</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>12162.98</t>
+          <t>12172.68</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-6086</t>
+          <t>-5758</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>1408.384988086925</t>
+          <t>1074.691386655718</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-706.36</v>
+        <v>-760.62</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-15.63</t>
+          <t>-17.94</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2064,17 +2064,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>42.34</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>1880</t>
+          <t>1922</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
+          <t>42.1</t>
+        </is>
+      </c>
+      <c r="CD4" t="inlineStr">
+        <is>
           <t>42.45</t>
         </is>
       </c>
-      <c r="CD4" t="inlineStr">
-        <is>
-          <t>42.7</t>
-        </is>
-      </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>41.95</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>114.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>42.4</t>
+          <t>42.1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-7.97</t>
+          <t>-29.63</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-4.61</t>
+          <t>-5.29</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2307,72 +2307,72 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>655</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>42.88</t>
+          <t>42.55</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>43.46</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>44.54</t>
+          <t>44.42</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>44.81</t>
+          <t>44.84</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-44.19</t>
+          <t>-46.96</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-111.05</t>
+          <t>-112.52</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>28209.25794797688</t>
+          <t>28229.64502164502</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>5444.0</t>
+          <t>4814.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>20437.4</t>
+          <t>14458.8</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>22206.9</t>
+          <t>20545.5</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>13085.46</t>
+          <t>12162.98</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-1769</t>
+          <t>-6086</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>1792.883660776302</t>
+          <t>1408.384988086925</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>461.71</v>
+        <v>-706.36</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-15.03</t>
+          <t>-15.63</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2490,22 +2490,22 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>42.34</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>1880</t>
+          <t>1922</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>42.45</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>42.7</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>41.95</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>42.4</t>
+          <t>42.1</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>441.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>42.4</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>15.49</t>
+          <t>-7.97</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-5.51</t>
+          <t>-4.61</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10.82</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2738,42 +2738,42 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>655</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>43.27</t>
+          <t>42.88</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -2783,27 +2783,27 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>44.68</t>
+          <t>44.54</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>44.79</t>
+          <t>44.81</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-38.94</t>
+          <t>-44.19</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-109.83</t>
+          <t>-111.05</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>28209.25794797688</t>
+          <t>28229.64502164502</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>18448.0</t>
+          <t>5444.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>26755.2</t>
+          <t>20437.4</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>23167.0</t>
+          <t>22206.9</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>14024.46</t>
+          <t>13085.46</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>3588</t>
+          <t>-1769</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>2034.914649979622</t>
+          <t>1792.883660776302</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>2046.4</v>
+        <v>461.71</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-15.83</t>
+          <t>-15.03</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>42.34</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>1880</t>
+          <t>1922</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>42.85</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>42.4</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>441.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>42.75</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>30.99</t>
+          <t>15.49</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-3.82</t>
+          <t>-5.51</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18.40</t>
+          <t>10.82</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>655</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3184,57 +3184,57 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>43.87</t>
+          <t>43.27</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>43.52</t>
+          <t>43.46</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>44.87</t>
+          <t>44.68</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>44.77</t>
+          <t>44.79</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-38.94</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-108.87</t>
+          <t>-109.83</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>28209.25794797688</t>
+          <t>28229.64502164502</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>32096.0</t>
+          <t>18448.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>30195.6</t>
+          <t>26755.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>23051.9</t>
+          <t>23167.0</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>14111.94</t>
+          <t>14024.46</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>7143</t>
+          <t>3588</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>2032.827091412444</t>
+          <t>2034.914649979622</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>2843.86</v>
+        <v>2046.4</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-14.33</t>
+          <t>-15.83</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>42.34</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>1880</t>
+          <t>1922</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>42.85</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>42.75</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>266.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>42.75</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>22.62</t>
+          <t>30.99</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-3.82</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>6.53</t>
+          <t>18.40</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3600,7 +3600,7 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>655</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3610,62 +3610,62 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>15.28</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>44.17999999999999</t>
+          <t>43.87</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>43.52</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>44.87</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>44.74</t>
+          <t>44.77</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>33.46</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-108.82</t>
+          <t>-108.87</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>28209.25794797688</t>
+          <t>28229.64502164502</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>11492.0</t>
+          <t>32096.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>26628.6</t>
+          <t>30195.6</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>21717.1</t>
+          <t>23051.9</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>13933.04</t>
+          <t>14111.94</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>4911</t>
+          <t>7143</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>1885.366964693159</t>
+          <t>2032.827091412444</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>2419.24</v>
+        <v>2843.86</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-12.83</t>
+          <t>-14.33</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3783,22 +3783,22 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>42.34</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>1880</t>
+          <t>1922</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>43.8</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>42.65</t>
+          <t>42.1</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>42.75</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>791.0</t>
+          <t>266.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>43.75</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-3.31</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>22.13</t>
+          <t>22.62</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>19.41</t>
+          <t>6.53</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>655</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4041,62 +4041,62 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>36.33</t>
+          <t>15.28</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>44.27999999999999</t>
+          <t>44.17999999999999</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>43.65</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>45.22</t>
+          <t>45.05</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>44.69</t>
+          <t>44.74</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>53.56</t>
+          <t>33.46</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-109.56</t>
+          <t>-108.82</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>28209.25794797688</t>
+          <t>28229.64502164502</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>34707.0</t>
+          <t>11492.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>26632.2</t>
+          <t>26628.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>21806.1</t>
+          <t>21717.1</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>14945.28</t>
+          <t>13933.04</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>4826</t>
+          <t>4911</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>1788.299770372915</t>
+          <t>1885.366964693159</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>3933.8</v>
+        <v>2419.24</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-12.32</t>
+          <t>-12.83</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4214,22 +4214,22 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>42.34</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>1880</t>
+          <t>1922</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>44.85</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>43.8</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>42.75</t>
+          <t>42.65</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>43.75</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>827.0</t>
+          <t>791.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>44.35</t>
+          <t>43.75</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-4.72</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>12.85</t>
+          <t>22.13</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>20.29</t>
+          <t>19.41</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4462,72 +4462,72 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>655</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>45.83</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>36.33</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>44.33</t>
+          <t>44.27999999999999</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>43.69</t>
+          <t>43.65</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>45.34</t>
+          <t>45.22</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>44.65</t>
+          <t>44.69</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>67.99</t>
+          <t>53.56</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-110.84</t>
+          <t>-109.56</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>28209.25794797688</t>
+          <t>28229.64502164502</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>37033.0</t>
+          <t>34707.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>23976.4</t>
+          <t>26632.2</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>21246.9</t>
+          <t>21806.1</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>14725.58</t>
+          <t>14945.28</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>2729</t>
+          <t>4826</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>1398.207935072465</t>
+          <t>1788.299770372915</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>3469.66</v>
+        <v>3933.8</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-11.12</t>
+          <t>-12.32</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>42.34</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>1880</t>
+          <t>1922</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>44.85</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>43.95</t>
+          <t>42.75</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>44.35</t>
+          <t>43.75</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>796.0</t>
+          <t>827.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>44.35</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-6.26</t>
+          <t>-2.42</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>12.85</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>19.53</t>
+          <t>20.29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4893,22 +4893,22 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>655</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>63.16</t>
+          <t>45.83</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>48.63</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
@@ -4918,47 +4918,47 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>44.36</t>
+          <t>44.33</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>43.72</t>
+          <t>43.69</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>45.48</t>
+          <t>45.34</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>44.61</t>
+          <t>44.65</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>65.41</t>
+          <t>67.99</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-112.68</t>
+          <t>-110.84</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>28209.25794797688</t>
+          <t>28229.64502164502</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>35650.0</t>
+          <t>37033.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>19578.8</t>
+          <t>23976.4</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>19368.6</t>
+          <t>21246.9</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>14937.52</t>
+          <t>14725.58</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>2729</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>1021.580387001086</t>
+          <t>1398.207935072465</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>2433.46</v>
+        <v>3469.66</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-9.82</t>
+          <t>-11.12</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>42.34</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>1880</t>
+          <t>1922</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>45.95</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.95</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>44.35</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>322.0</t>
+          <t>796.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-4.6</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>7.90</t>
+          <t>19.53</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5324,72 +5324,72 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>655</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>26.32</t>
+          <t>63.16</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>48.03</t>
+          <t>48.63</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-4.11</t>
+          <t>-3.86</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>44.12</t>
+          <t>44.36</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>43.75</t>
+          <t>43.72</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>45.63</t>
+          <t>45.48</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>44.56</t>
+          <t>44.61</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>46.58</t>
+          <t>65.41</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-114.75</t>
+          <t>-112.68</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>28209.25794797688</t>
+          <t>28229.64502164502</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>14261.0</t>
+          <t>35650.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>15908.2</t>
+          <t>19578.8</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>16389.4</t>
+          <t>19368.6</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>18175.4</t>
+          <t>14937.52</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-481</t>
+          <t>210</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>764.8742980587986</t>
+          <t>1021.580387001086</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>1014.45</v>
+        <v>2433.46</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-11.22</t>
+          <t>-9.82</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>43.93</t>
+          <t>42.34</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>1880</t>
+          <t>1922</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>44.45</t>
+          <t>44.3</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>45.95</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1631.485</t>
+          <t>1638.11</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-20.69</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-16.26</t>
+          <t>-18.22</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>7.89</t>
+          <t>7.92</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-2.40</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,12 +5750,12 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>1631</t>
+          <t>1638</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5765,62 +5765,62 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>13.16</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-3.30</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>-4.10</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-6.3</t>
+          <t>-6.67</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>5.78</t>
+          <t>5.33</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>92.66</t>
+          <t>91.26</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>95.84</t>
+          <t>95.16</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>102.28</t>
+          <t>101.96</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>96.69</t>
+          <t>96.8</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-16.84</t>
+          <t>-23.67</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-2.86</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-130.25</t>
+          <t>-132.15</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,41 +5840,41 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>357139500.2514451</t>
+          <t>356936222.4610389</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>147034386.0</t>
+          <t>144178661.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>146439342.4</t>
+          <t>146673374.0</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>184645225.3</t>
+          <t>149731355.7</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>461884050.18</t>
+          <t>454484548.46</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-38205882</t>
+          <t>-3057981</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-28795522.72575311</t>
+          <t>-28445972.53673498</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>-28080257.81</v>
+        <v>-26523446.5</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>10.21</t>
+          <t>7.63</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5938,7 +5938,7 @@
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
@@ -5948,12 +5948,12 @@
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>23.03</t>
+          <t>22.49</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>33.74</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>18896</t>
+          <t>18453</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>89.9</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>89.4</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-4.0</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1815.561</t>
+          <t>1631.485</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-2.4</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-32.28</t>
+          <t>-20.69</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-14.95</t>
+          <t>-16.26</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>8.78</t>
+          <t>7.89</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,12 +6181,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>1631</t>
+          <t>1638</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6196,62 +6196,62 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>15.79</t>
+          <t>13.16</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-3.30</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-3.32</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-6.05</t>
+          <t>-6.3</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>6.20</t>
+          <t>5.78</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>93.38</t>
+          <t>92.66</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>96.32</t>
+          <t>95.84</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>102.52</t>
+          <t>102.28</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>96.53</t>
+          <t>96.69</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-10.98</t>
+          <t>-16.84</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-128.98</t>
+          <t>-130.25</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,41 +6271,41 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>357139500.2514451</t>
+          <t>356936222.4610389</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>166787289.0</t>
+          <t>147034386.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>135964184.0</t>
+          <t>146439342.4</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>200767284.9</t>
+          <t>184645225.3</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>481289771.06</t>
+          <t>461884050.18</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-64803100</t>
+          <t>-38205882</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-28925570.89173124</t>
+          <t>-28795522.72575311</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>-29607378.16</v>
+        <v>-28080257.81</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>11.93</t>
+          <t>10.21</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6369,22 +6369,22 @@
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>23.03</t>
+          <t>22.49</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>33.74</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>18896</t>
+          <t>18453</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>89.4</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1433.749</t>
+          <t>1815.561</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>94.7</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,17 +6506,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-5.69</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-41.55</t>
+          <t>-32.28</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6526,7 +6526,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-11.50</t>
+          <t>-14.95</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>8.78</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,77 +6612,77 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>1631</t>
+          <t>1638</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>39.47</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>28.29</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-5.8</t>
+          <t>-6.05</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>6.60</t>
+          <t>6.20</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>93.9</t>
+          <t>93.38</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>96.8</t>
+          <t>96.32</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>102.75</t>
+          <t>102.52</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>96.39</t>
+          <t>96.53</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-5.06</t>
+          <t>-10.98</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-128.18</t>
+          <t>-128.98</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,41 +6702,41 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>357139500.2514451</t>
+          <t>356936222.4610389</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>135185330.0</t>
+          <t>166787289.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>126336486.8</t>
+          <t>135964184.0</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>216135889.2</t>
+          <t>200767284.9</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>501408648.9</t>
+          <t>481289771.06</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-89799402</t>
+          <t>-64803100</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-28801605.93323361</t>
+          <t>-28925570.89173124</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>-32847954.77</v>
+        <v>-29607378.16</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>16.48</t>
+          <t>11.93</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6800,22 +6800,22 @@
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>23.03</t>
+          <t>22.49</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>33.74</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>18896</t>
+          <t>18453</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>95.3</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>94.7</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1479.927</t>
+          <t>1433.749</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-8.23</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-38.14</t>
+          <t>-41.55</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6957,7 +6957,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-12.62</t>
+          <t>-11.50</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>7.15</t>
+          <t>6.93</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,77 +7043,77 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>1631</t>
+          <t>1638</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>7.89</t>
+          <t>39.47</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>28.29</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-5.69</t>
+          <t>-5.8</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>6.60</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>93.86</t>
+          <t>93.9</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>97.05</t>
+          <t>96.8</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>102.91</t>
+          <t>102.75</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>96.17</t>
+          <t>96.39</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-11.98</t>
+          <t>-5.06</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-127.83</t>
+          <t>-128.18</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,41 +7133,41 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>357139500.2514451</t>
+          <t>356936222.4610389</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>140181204.0</t>
+          <t>135185330.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>137059889.8</t>
+          <t>126336486.8</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>221562336.5</t>
+          <t>216135889.2</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>538168556.64</t>
+          <t>501408648.9</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-84502446</t>
+          <t>-89799402</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-28065906.14552652</t>
+          <t>-28801605.93323361</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>-32918284.49</v>
+        <v>-32847954.77</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>15.01</t>
+          <t>16.48</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>23.03</t>
+          <t>22.49</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>33.74</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>18896</t>
+          <t>18453</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>95.3</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1504.164</t>
+          <t>1479.927</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-5.47</t>
+          <t>-6.86</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-34.56</t>
+          <t>-38.14</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-11.68</t>
+          <t>-12.62</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>7.27</t>
+          <t>7.15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,77 +7474,77 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>1631</t>
+          <t>1638</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>7.89</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>19.17</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-3.11</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-5.57</t>
+          <t>-5.69</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>7.35</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>94.24</t>
+          <t>93.86</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>97.26</t>
+          <t>97.05</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>102.91</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>95.95</t>
+          <t>96.17</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-14.81</t>
+          <t>-11.98</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-126.99</t>
+          <t>-127.83</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,41 +7564,41 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>357139500.2514451</t>
+          <t>356936222.4610389</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>143008503.0</t>
+          <t>140181204.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>152789337.4</t>
+          <t>137059889.8</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>233463581.9</t>
+          <t>221562336.5</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>553861277.88</t>
+          <t>538168556.64</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-80674244</t>
+          <t>-84502446</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-27183655.53719378</t>
+          <t>-28065906.14552652</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>-32378374.72</v>
+        <v>-32918284.49</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>16.24</t>
+          <t>15.01</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7662,7 +7662,7 @@
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
@@ -7672,12 +7672,12 @@
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>23.03</t>
+          <t>22.49</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>33.74</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>18896</t>
+          <t>18453</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>96.5</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1012.26</t>
+          <t>1504.164</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>93.2</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-4.02</t>
+          <t>-8.0</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-18.35</t>
+          <t>-34.56</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7819,7 +7819,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-12.90</t>
+          <t>-11.68</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>7.27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,77 +7905,77 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>1631</t>
+          <t>1638</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>19.17</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-3.11</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-5.57</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>7.68</t>
+          <t>7.35</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>94.66</t>
+          <t>94.24</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>97.62</t>
+          <t>97.26</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>103.01</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>95.66</t>
+          <t>95.95</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-22.08</t>
+          <t>-14.81</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-125.99</t>
+          <t>-126.99</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,41 +7995,41 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>357139500.2514451</t>
+          <t>356936222.4610389</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>94658594.0</t>
+          <t>143008503.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>222851108.2</t>
+          <t>152789337.4</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>272945780.2</t>
+          <t>233463581.9</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>561353465.26</t>
+          <t>553861277.88</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-50094672</t>
+          <t>-80674244</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-26239161.13943687</t>
+          <t>-27183655.53719378</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>-30753629.43</v>
+        <v>-32378374.72</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>14.64</t>
+          <t>16.24</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8093,7 +8093,7 @@
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
@@ -8103,12 +8103,12 @@
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>23.03</t>
+          <t>22.49</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>33.74</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>18896</t>
+          <t>18453</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,22 +8158,22 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>93.7</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>95.3</t>
+          <t>96.5</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>92.8</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>93.2</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1267.489</t>
+          <t>1012.26</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>93.6</t>
+          <t>93.2</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-4.46</t>
+          <t>-6.51</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-4.29</t>
+          <t>-18.35</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8250,7 +8250,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-12.52</t>
+          <t>-12.90</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>6.13</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,77 +8336,77 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>1631</t>
+          <t>1638</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>22.33</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>8.01</t>
+          <t>7.68</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>95.42</t>
+          <t>94.66</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>98.18</t>
+          <t>97.62</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>103.03</t>
+          <t>103.01</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>95.39</t>
+          <t>95.66</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-23.72</t>
+          <t>-22.08</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-124.56</t>
+          <t>-125.99</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,41 +8426,41 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>357139500.2514451</t>
+          <t>356936222.4610389</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>118648803.0</t>
+          <t>94658594.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>265570385.8</t>
+          <t>222851108.2</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>277478761.0</t>
+          <t>272945780.2</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>570658631.0</t>
+          <t>561353465.26</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-11908375</t>
+          <t>-50094672</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-25418348.72380762</t>
+          <t>-26239161.13943687</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>-22153873.41</v>
+        <v>-30753629.43</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>15.13</t>
+          <t>14.64</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8524,22 +8524,22 @@
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>23.03</t>
+          <t>22.49</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>33.74</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>18896</t>
+          <t>18453</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>93.7</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>95.3</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
@@ -8604,7 +8604,7 @@
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>93.6</t>
+          <t>93.2</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1991.474</t>
+          <t>1267.489</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>93.6</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-5.47</t>
+          <t>-6.97</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>9.77</t>
+          <t>-4.29</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8681,7 +8681,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-11.68</t>
+          <t>-12.52</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>9.63</t>
+          <t>6.13</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,77 +8767,77 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>1631</t>
+          <t>1638</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>22.33</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-2.78</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-4.12</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>8.29</t>
+          <t>8.01</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>95.42</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>98.75</t>
+          <t>98.18</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>102.99</t>
+          <t>103.03</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>95.11</t>
+          <t>95.39</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-24.59</t>
+          <t>-23.72</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-123.10</t>
+          <t>-124.56</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,41 +8857,41 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>357139500.2514451</t>
+          <t>356936222.4610389</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>188802345.0</t>
+          <t>118648803.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>305935291.6</t>
+          <t>265570385.8</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>278708338.6</t>
+          <t>277478761.0</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>581698082.72</t>
+          <t>570658631.0</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>27226953</t>
+          <t>-11908375</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-26011889.68977666</t>
+          <t>-25418348.72380762</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>-11647677.45</v>
+        <v>-22153873.41</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>16.24</t>
+          <t>15.13</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8955,22 +8955,22 @@
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>23.03</t>
+          <t>22.49</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>33.74</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>18896</t>
+          <t>18453</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>97.1</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>93.2</t>
+          <t>92.8</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>93.6</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2312.284</t>
+          <t>1991.474</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>95.4</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-6.47</t>
+          <t>-8.0</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>9.77</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9112,7 +9112,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-10.84</t>
+          <t>-11.68</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11.18</t>
+          <t>9.63</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,77 +9198,77 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>1631</t>
+          <t>1638</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>-2.78</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-3.41</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>8.52</t>
+          <t>8.29</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>95.7</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>99.4</t>
+          <t>98.75</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>102.9</t>
+          <t>102.99</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>94.83</t>
+          <t>95.11</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-27.28</t>
+          <t>-24.59</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-121.68</t>
+          <t>-123.10</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,41 +9288,41 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>357139500.2514451</t>
+          <t>356936222.4610389</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>218828442.0</t>
+          <t>188802345.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>306064783.2</t>
+          <t>305935291.6</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>278240578.4</t>
+          <t>278708338.6</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>594226537.62</t>
+          <t>581698082.72</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>27824204</t>
+          <t>27226953</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-28623564.64298534</t>
+          <t>-26011889.68977666</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>-3739288.52</v>
+        <v>-11647677.45</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>17.34</t>
+          <t>16.24</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>23.03</t>
+          <t>22.49</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>33.74</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>18896</t>
+          <t>18453</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,22 +9451,22 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>95.1</t>
+          <t>96.3</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>97.1</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>93.2</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>95.4</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>4980.394</t>
+          <t>2312.284</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>95.4</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-7.81</t>
+          <t>-9.03</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9543,7 +9543,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-9.72</t>
+          <t>-10.84</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>24.07</t>
+          <t>11.18</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-5.49</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,77 +9629,77 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>1631</t>
+          <t>1638</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>42.32</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-2.9</t>
+          <t>-3.41</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>8.78</t>
+          <t>8.52</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>95.52000000000001</t>
+          <t>95.7</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>99.83</t>
+          <t>99.4</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>102.81</t>
+          <t>102.9</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>94.52</t>
+          <t>94.83</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-33.42</t>
+          <t>-27.28</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-120.20</t>
+          <t>-121.68</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>357139500.2514451</t>
+          <t>356936222.4610389</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>493317357.0</t>
+          <t>218828442.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>314137826.4</t>
+          <t>306064783.2</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>296369265.5</t>
+          <t>278240578.4</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>598741786.76</t>
+          <t>594226537.62</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>17768560</t>
+          <t>27824204</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-33147978.48379749</t>
+          <t>-28623564.64298534</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>4474874.15</v>
+        <v>-3739288.52</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>18.82</t>
+          <t>17.34</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9827,12 +9827,12 @@
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>23.03</t>
+          <t>22.49</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>33.74</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>18896</t>
+          <t>18453</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,22 +9882,22 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>95.1</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>96.5</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>95.4</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>3171.123</t>
+          <t>4980.394</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>96.6</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-8.26</t>
+          <t>-10.4</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>23.09</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-9.35</t>
+          <t>-9.72</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15.33</t>
+          <t>24.07</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>-5.49</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,77 +10060,77 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>1631</t>
+          <t>1638</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>42.11</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>26.32</t>
+          <t>42.32</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-5.03</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-2.37</t>
+          <t>-2.9</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>8.98</t>
+          <t>8.78</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>95.16</t>
+          <t>95.52000000000001</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>100.2</t>
+          <t>99.83</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>102.64</t>
+          <t>102.81</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>94.18</t>
+          <t>94.52</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-48.21</t>
+          <t>-33.42</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-118.51</t>
+          <t>-120.20</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>357139500.2514451</t>
+          <t>356936222.4610389</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>308254982.0</t>
+          <t>493317357.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>323040452.2</t>
+          <t>314137826.4</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>262443491.2</t>
+          <t>296369265.5</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>598029457.84</t>
+          <t>598741786.76</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>60596961</t>
+          <t>17768560</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-39988497.144127</t>
+          <t>-33147978.48379749</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-13359951.3</v>
+        <v>4474874.15</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>19.31</t>
+          <t>18.82</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10258,12 +10258,12 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>23.03</t>
+          <t>22.49</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>33.74</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>18896</t>
+          <t>18453</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,22 +10313,22 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>99.6</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>96.5</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>96.6</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/電鍍材料.xlsx
+++ b/Result/checksun_type/電鍍材料.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>655.0</t>
+          <t>685.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-32.14</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -923,7 +923,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>16.81</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,77 +1009,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>685</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>83.93</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>75.04</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>42.22000000000001</t>
+          <t>42.73999999999999</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>43.61</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>44.15</t>
+          <t>44.12</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>44.89</t>
+          <t>44.95</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-16.05</t>
+          <t>24.64</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,51 +1089,51 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-117.06</t>
+          <t>-116.07</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>2025/10/22</t>
+          <t>2025/11/19</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>28229.64502164502</t>
+          <t>28255.31195965418</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>28225.0</t>
+          <t>30695.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>13738.6</t>
+          <t>18788.8</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>20246.9</t>
+          <t>19613.1</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>12733.2</t>
+          <t>13049.74</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-6508</t>
+          <t>-824</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>716.6020020198885</t>
+          <t>783.2701283472239</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>271.95</v>
+        <v>1149.94</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-13.23</t>
+          <t>-9.82</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1197,22 +1197,22 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>1922</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>42.35</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>369.0</t>
+          <t>655.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>42.35</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-43.86</t>
+          <t>-32.14</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-4.72</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>9.06</t>
+          <t>16.07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,240 +1440,240 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>685</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>41.18</t>
+          <t>83.93</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>14.84</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
+          <t>42.22000000000001</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>43.6</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>44.15</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>44.89</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>-16.05</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>-0.55</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>-0.47</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>2.77</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>-117.06</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>2025/11/19</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>28255.31195965418</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>28225.0</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>13738.6</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>20246.9</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>12733.2</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>-6508</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>716.6020020198885</t>
+        </is>
+      </c>
+      <c r="BC3" t="n">
+        <v>271.95</v>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>49.9</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>2025/08/12</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>-13.23</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>匯鑽科</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>匯鑽科</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>0.78</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>-10.56465687102404</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>-13.69932964657055</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>7.80229574004913</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>6.59</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>8.25%</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>-14.21%</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
           <t>41.96</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>43.53</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>44.23</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>44.87</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>-40.91</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>-0.64</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>-0.45</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>2.77</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>-116.38</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>2025/10/22</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>28229.64502164502</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>15453.0</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>11783.2</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>20989.4</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>12346.96</t>
-        </is>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>-9206</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>797.4475068096988</t>
-        </is>
-      </c>
-      <c r="BC3" t="n">
-        <v>-727.39</v>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>49.9</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>2025/08/12</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>-15.13</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>匯鑽科</t>
-        </is>
-      </c>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>匯鑽科</t>
-        </is>
-      </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>0.8</t>
-        </is>
-      </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>-10.56465687102404</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
-        <is>
-          <t>-13.69932964657055</t>
-        </is>
-      </c>
-      <c r="BO3" t="inlineStr">
-        <is>
-          <t>7.80229574004913</t>
-        </is>
-      </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BQ3" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BR3" t="inlineStr">
-        <is>
-          <t>2.26</t>
-        </is>
-      </c>
-      <c r="BS3" t="inlineStr">
-        <is>
-          <t>2.59</t>
-        </is>
-      </c>
-      <c r="BT3" t="inlineStr">
-        <is>
-          <t>6.59</t>
-        </is>
-      </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BV3" t="inlineStr">
-        <is>
-          <t>8.25%</t>
-        </is>
-      </c>
-      <c r="BW3" t="inlineStr">
-        <is>
-          <t>-14.21%</t>
-        </is>
-      </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>42.34</t>
-        </is>
-      </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>1922</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>42.7</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>42.35</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>42.35</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1723,7 +1723,7 @@
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>358.0</t>
+          <t>369.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>42.35</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>5.43</t>
+          <t>5.89</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-27.59</t>
+          <t>-43.86</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-7.87</t>
+          <t>-4.72</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>8.79</t>
+          <t>9.06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,77 +1871,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>685</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>41.18</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>14.84</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-3.31</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>42.04000000000001</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>43.48</t>
+          <t>43.53</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>44.31</t>
+          <t>44.23</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>44.85</t>
+          <t>44.87</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-59.38</t>
+          <t>-40.91</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,51 +1951,51 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-114.70</t>
+          <t>-116.38</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>2025/10/22</t>
+          <t>2025/11/19</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>28229.64502164502</t>
+          <t>28255.31195965418</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>14757.0</t>
+          <t>15453.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>15111.8</t>
+          <t>11783.2</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>20870.2</t>
+          <t>20989.4</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>12172.68</t>
+          <t>12346.96</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-5758</t>
+          <t>-9206</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>1074.691386655718</t>
+          <t>797.4475068096988</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-760.62</v>
+        <v>-727.39</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-17.94</t>
+          <t>-15.13</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2064,17 +2064,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>1922</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>42.45</t>
+          <t>42.7</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>42.35</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>358.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-29.63</t>
+          <t>-27.59</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-5.29</t>
+          <t>-7.87</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>8.79</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,17 +2302,17 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>685</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -2322,57 +2322,57 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-3.31</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>42.55</t>
+          <t>42.04000000000001</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.48</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>44.42</t>
+          <t>44.31</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>44.84</t>
+          <t>44.85</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-46.96</t>
+          <t>-59.38</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,51 +2382,51 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-112.52</t>
+          <t>-114.70</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>2025/10/22</t>
+          <t>2025/11/19</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>28229.64502164502</t>
+          <t>28255.31195965418</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>4814.0</t>
+          <t>14757.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>14458.8</t>
+          <t>15111.8</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>20545.5</t>
+          <t>20870.2</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>12162.98</t>
+          <t>12172.68</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-6086</t>
+          <t>-5758</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>1408.384988086925</t>
+          <t>1074.691386655718</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-706.36</v>
+        <v>-760.62</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-15.63</t>
+          <t>-17.94</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2495,17 +2495,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>1922</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
+          <t>42.1</t>
+        </is>
+      </c>
+      <c r="CD5" t="inlineStr">
+        <is>
           <t>42.45</t>
         </is>
       </c>
-      <c r="CD5" t="inlineStr">
-        <is>
-          <t>42.7</t>
-        </is>
-      </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>41.95</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2585,7 +2585,7 @@
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>114.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>42.4</t>
+          <t>42.1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>6.44</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-7.97</t>
+          <t>-29.63</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-4.61</t>
+          <t>-5.29</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,77 +2733,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>685</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>42.88</t>
+          <t>42.55</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>43.46</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>44.54</t>
+          <t>44.42</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>44.81</t>
+          <t>44.84</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-44.19</t>
+          <t>-46.96</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,51 +2813,51 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-111.05</t>
+          <t>-112.52</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2025/10/22</t>
+          <t>2025/11/19</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>28229.64502164502</t>
+          <t>28255.31195965418</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>5444.0</t>
+          <t>4814.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>20437.4</t>
+          <t>14458.8</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>22206.9</t>
+          <t>20545.5</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>13085.46</t>
+          <t>12162.98</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-1769</t>
+          <t>-6086</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>1792.883660776302</t>
+          <t>1408.384988086925</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>461.71</v>
+        <v>-706.36</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-15.03</t>
+          <t>-15.63</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>1922</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>42.45</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>42.7</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>41.95</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>42.4</t>
+          <t>42.1</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>441.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>42.4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>5.78</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>15.49</t>
+          <t>-7.97</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-5.51</t>
+          <t>-4.61</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10.82</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,47 +3164,47 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>685</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>43.27</t>
+          <t>42.88</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -3214,27 +3214,27 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>44.68</t>
+          <t>44.54</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>44.79</t>
+          <t>44.81</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-38.94</t>
+          <t>-44.19</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,51 +3244,51 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-109.83</t>
+          <t>-111.05</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2025/10/22</t>
+          <t>2025/11/19</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>28229.64502164502</t>
+          <t>28255.31195965418</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>18448.0</t>
+          <t>5444.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>26755.2</t>
+          <t>20437.4</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>23167.0</t>
+          <t>22206.9</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>14024.46</t>
+          <t>13085.46</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>3588</t>
+          <t>-1769</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>2034.914649979622</t>
+          <t>1792.883660776302</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>2046.4</v>
+        <v>461.71</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-15.83</t>
+          <t>-15.03</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>1922</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>42.85</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>42.4</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>441.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>42.75</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>30.99</t>
+          <t>15.49</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-3.82</t>
+          <t>-5.51</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18.40</t>
+          <t>10.82</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,12 +3595,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>685</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3615,57 +3615,57 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>43.87</t>
+          <t>43.27</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>43.52</t>
+          <t>43.46</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>44.87</t>
+          <t>44.68</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>44.77</t>
+          <t>44.79</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-38.94</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,51 +3675,51 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-108.87</t>
+          <t>-109.83</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2025/10/22</t>
+          <t>2025/11/19</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>28229.64502164502</t>
+          <t>28255.31195965418</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>32096.0</t>
+          <t>18448.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>30195.6</t>
+          <t>26755.2</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>23051.9</t>
+          <t>23167.0</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>14111.94</t>
+          <t>14024.46</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>7143</t>
+          <t>3588</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>2032.827091412444</t>
+          <t>2034.914649979622</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>2843.86</v>
+        <v>2046.4</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-14.33</t>
+          <t>-15.83</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>1922</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>42.85</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>42.75</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3878,7 +3878,7 @@
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>266.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>42.75</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>22.62</t>
+          <t>30.99</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-3.82</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>6.53</t>
+          <t>18.40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,12 +4026,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>685</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4041,62 +4041,62 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>15.28</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>44.17999999999999</t>
+          <t>43.87</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>43.52</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>44.87</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>44.74</t>
+          <t>44.77</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>33.46</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,51 +4106,51 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-108.82</t>
+          <t>-108.87</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2025/10/22</t>
+          <t>2025/11/19</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>28229.64502164502</t>
+          <t>28255.31195965418</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>11492.0</t>
+          <t>32096.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>26628.6</t>
+          <t>30195.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>21717.1</t>
+          <t>23051.9</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>13933.04</t>
+          <t>14111.94</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>4911</t>
+          <t>7143</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>1885.366964693159</t>
+          <t>2032.827091412444</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>2419.24</v>
+        <v>2843.86</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-12.83</t>
+          <t>-14.33</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4214,22 +4214,22 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>1922</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>43.8</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>42.65</t>
+          <t>42.1</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>42.75</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4309,7 +4309,7 @@
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>791.0</t>
+          <t>266.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>43.75</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>22.13</t>
+          <t>22.62</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>19.41</t>
+          <t>6.53</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,12 +4457,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>685</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4472,62 +4472,62 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>36.33</t>
+          <t>15.28</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>44.27999999999999</t>
+          <t>44.17999999999999</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>43.65</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>45.22</t>
+          <t>45.05</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>44.69</t>
+          <t>44.74</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>53.56</t>
+          <t>33.46</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,51 +4537,51 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-109.56</t>
+          <t>-108.82</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2025/10/22</t>
+          <t>2025/11/19</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>28229.64502164502</t>
+          <t>28255.31195965418</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>34707.0</t>
+          <t>11492.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>26632.2</t>
+          <t>26628.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>21806.1</t>
+          <t>21717.1</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>14945.28</t>
+          <t>13933.04</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>4826</t>
+          <t>4911</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>1788.299770372915</t>
+          <t>1885.366964693159</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>3933.8</v>
+        <v>2419.24</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-12.32</t>
+          <t>-12.83</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>1922</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>44.85</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>43.8</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>42.75</t>
+          <t>42.65</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>43.75</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4740,7 +4740,7 @@
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>827.0</t>
+          <t>791.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>44.35</t>
+          <t>43.75</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-2.42</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>12.85</t>
+          <t>22.13</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>20.29</t>
+          <t>19.41</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4888,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>685</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>45.83</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>36.33</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>44.33</t>
+          <t>44.27999999999999</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>43.69</t>
+          <t>43.65</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>45.34</t>
+          <t>45.22</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>44.65</t>
+          <t>44.69</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>67.99</t>
+          <t>53.56</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,51 +4968,51 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-110.84</t>
+          <t>-109.56</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2025/10/22</t>
+          <t>2025/11/19</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>28229.64502164502</t>
+          <t>28255.31195965418</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>37033.0</t>
+          <t>34707.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>23976.4</t>
+          <t>26632.2</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>21246.9</t>
+          <t>21806.1</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>14725.58</t>
+          <t>14945.28</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>2729</t>
+          <t>4826</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>1398.207935072465</t>
+          <t>1788.299770372915</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>3469.66</v>
+        <v>3933.8</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-11.12</t>
+          <t>-12.32</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>1922</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>44.85</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>43.95</t>
+          <t>42.75</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>44.35</t>
+          <t>43.75</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>796.0</t>
+          <t>827.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>44.35</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>12.85</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-95.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>19.53</t>
+          <t>20.29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,27 +5319,27 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>685</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>63.16</t>
+          <t>45.83</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>48.63</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
@@ -5349,47 +5349,47 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>44.36</t>
+          <t>44.33</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>43.72</t>
+          <t>43.69</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>45.48</t>
+          <t>45.34</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>44.61</t>
+          <t>44.65</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>65.41</t>
+          <t>67.99</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,51 +5399,51 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-112.68</t>
+          <t>-110.84</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2025/10/22</t>
+          <t>2025/11/19</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>28229.64502164502</t>
+          <t>28255.31195965418</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>35650.0</t>
+          <t>37033.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>19578.8</t>
+          <t>23976.4</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>19368.6</t>
+          <t>21246.9</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>14937.52</t>
+          <t>14725.58</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>210</t>
+          <t>2729</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>1021.580387001086</t>
+          <t>1398.207935072465</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>2433.46</v>
+        <v>3469.66</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-9.82</t>
+          <t>-11.12</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>1922</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>44.3</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>45.95</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.95</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>44.35</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5602,7 +5602,7 @@
       </c>
       <c r="CI12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1638.11</t>
+          <t>1153.082</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5654,7 +5654,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-18.22</t>
+          <t>-19.16</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>7.92</t>
+          <t>5.57</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-2.40</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,12 +5750,12 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>1638</t>
+          <t>1153</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5770,57 +5770,57 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-4.12</t>
+          <t>-3.74</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-4.10</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-6.67</t>
+          <t>-7.14</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>91.26</t>
+          <t>89.86</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>95.16</t>
+          <t>94.36</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>101.96</t>
+          <t>101.62</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>96.8</t>
+          <t>96.9</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-23.67</t>
+          <t>-27.21</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-2.86</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-132.15</t>
+          <t>-134.50</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,41 +5840,41 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>356936222.4610389</t>
+          <t>356637749.5785303</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>144178661.0</t>
+          <t>99864028.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>146673374.0</t>
+          <t>138609938.8</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>149731355.7</t>
+          <t>137834914.3</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>454484548.46</t>
+          <t>443270959.36</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-3057981</t>
+          <t>775024</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-28445972.53673498</t>
+          <t>-28391852.12934346</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>-26523446.5</v>
+        <v>-28094189.89</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>7.63</t>
+          <t>6.40</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5948,12 +5948,12 @@
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>22.49</t>
+          <t>22.24</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>18453</t>
+          <t>18243</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>89.9</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>85.9</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1631.485</t>
+          <t>1638.11</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,7 +6075,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-2.4</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -6085,7 +6085,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-20.69</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-16.26</t>
+          <t>-18.22</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>7.89</t>
+          <t>7.92</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-2.40</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,12 +6181,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>1638</t>
+          <t>1153</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6196,62 +6196,62 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>13.16</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-3.30</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>-4.10</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-6.3</t>
+          <t>-6.67</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>5.78</t>
+          <t>5.33</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>92.66</t>
+          <t>91.26</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>95.84</t>
+          <t>95.16</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>102.28</t>
+          <t>101.96</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>96.69</t>
+          <t>96.8</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-16.84</t>
+          <t>-23.67</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-2.86</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-130.25</t>
+          <t>-132.15</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,41 +6271,41 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>356936222.4610389</t>
+          <t>356637749.5785303</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>147034386.0</t>
+          <t>144178661.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>146439342.4</t>
+          <t>146673374.0</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>184645225.3</t>
+          <t>149731355.7</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>461884050.18</t>
+          <t>454484548.46</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-38205882</t>
+          <t>-3057981</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-28795522.72575311</t>
+          <t>-28445972.53673498</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>-28080257.81</v>
+        <v>-26523446.5</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>10.21</t>
+          <t>7.63</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
@@ -6379,12 +6379,12 @@
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>22.49</t>
+          <t>22.24</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>18453</t>
+          <t>18243</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>89.9</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>89.4</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-4.0</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1815.561</t>
+          <t>1631.485</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,7 +6506,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-4.0</t>
+          <t>-3.58</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -6516,7 +6516,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-32.28</t>
+          <t>-20.69</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-14.95</t>
+          <t>-16.26</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>8.78</t>
+          <t>7.89</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,12 +6612,12 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>1638</t>
+          <t>1153</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6627,62 +6627,62 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>15.79</t>
+          <t>13.16</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-3.30</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-3.32</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-6.05</t>
+          <t>-6.3</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>6.20</t>
+          <t>5.78</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>93.38</t>
+          <t>92.66</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>96.32</t>
+          <t>95.84</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>102.52</t>
+          <t>102.28</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>96.53</t>
+          <t>96.69</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-10.98</t>
+          <t>-16.84</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-128.98</t>
+          <t>-130.25</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,41 +6702,41 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>356936222.4610389</t>
+          <t>356637749.5785303</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>166787289.0</t>
+          <t>147034386.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>135964184.0</t>
+          <t>146439342.4</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>200767284.9</t>
+          <t>184645225.3</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>481289771.06</t>
+          <t>461884050.18</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-64803100</t>
+          <t>-38205882</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-28925570.89173124</t>
+          <t>-28795522.72575311</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>-29607378.16</v>
+        <v>-28080257.81</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>11.93</t>
+          <t>10.21</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6800,22 +6800,22 @@
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>22.49</t>
+          <t>22.24</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>18453</t>
+          <t>18243</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>89.4</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1433.749</t>
+          <t>1815.561</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>94.7</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,7 +6937,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-8.23</t>
+          <t>-5.2</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -6947,7 +6947,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-41.55</t>
+          <t>-32.28</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-11.50</t>
+          <t>-14.95</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>8.78</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,77 +7043,77 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>1638</t>
+          <t>1153</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>39.47</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>28.29</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-5.8</t>
+          <t>-6.05</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>6.60</t>
+          <t>6.20</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>93.9</t>
+          <t>93.38</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>96.8</t>
+          <t>96.32</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>102.75</t>
+          <t>102.52</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>96.39</t>
+          <t>96.53</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-5.06</t>
+          <t>-10.98</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-128.18</t>
+          <t>-128.98</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,41 +7133,41 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>356936222.4610389</t>
+          <t>356637749.5785303</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>135185330.0</t>
+          <t>166787289.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>126336486.8</t>
+          <t>135964184.0</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>216135889.2</t>
+          <t>200767284.9</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>501408648.9</t>
+          <t>481289771.06</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-89799402</t>
+          <t>-64803100</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-28801605.93323361</t>
+          <t>-28925570.89173124</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>-32847954.77</v>
+        <v>-29607378.16</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>16.48</t>
+          <t>11.93</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7231,22 +7231,22 @@
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>22.49</t>
+          <t>22.24</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>18453</t>
+          <t>18243</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>95.3</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>94.7</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1479.927</t>
+          <t>1433.749</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,7 +7368,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-6.86</t>
+          <t>-9.48</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -7378,7 +7378,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-38.14</t>
+          <t>-41.55</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-12.62</t>
+          <t>-11.50</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>7.15</t>
+          <t>6.93</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,77 +7474,77 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>1638</t>
+          <t>1153</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>7.89</t>
+          <t>39.47</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>28.29</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-5.69</t>
+          <t>-5.8</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>6.60</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>93.86</t>
+          <t>93.9</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>97.05</t>
+          <t>96.8</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>102.91</t>
+          <t>102.75</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>96.17</t>
+          <t>96.39</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-11.98</t>
+          <t>-5.06</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-127.83</t>
+          <t>-128.18</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,41 +7564,41 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>356936222.4610389</t>
+          <t>356637749.5785303</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>140181204.0</t>
+          <t>135185330.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>137059889.8</t>
+          <t>126336486.8</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>221562336.5</t>
+          <t>216135889.2</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>538168556.64</t>
+          <t>501408648.9</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-84502446</t>
+          <t>-89799402</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-28065906.14552652</t>
+          <t>-28801605.93323361</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>-32918284.49</v>
+        <v>-32847954.77</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>15.01</t>
+          <t>16.48</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7662,7 +7662,7 @@
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
@@ -7672,12 +7672,12 @@
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>22.49</t>
+          <t>22.24</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>18453</t>
+          <t>18243</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>95.3</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1504.164</t>
+          <t>1479.927</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,7 +7799,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-8.0</t>
+          <t>-8.09</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -7809,7 +7809,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-34.56</t>
+          <t>-38.14</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-11.68</t>
+          <t>-12.62</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>7.27</t>
+          <t>7.15</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,77 +7905,77 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>1638</t>
+          <t>1153</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>7.89</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>19.17</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-3.11</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-5.57</t>
+          <t>-5.69</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>7.35</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>94.24</t>
+          <t>93.86</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>97.26</t>
+          <t>97.05</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>102.91</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>95.95</t>
+          <t>96.17</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-14.81</t>
+          <t>-11.98</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-126.99</t>
+          <t>-127.83</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,41 +7995,41 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>356936222.4610389</t>
+          <t>356637749.5785303</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>143008503.0</t>
+          <t>140181204.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>152789337.4</t>
+          <t>137059889.8</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>233463581.9</t>
+          <t>221562336.5</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>553861277.88</t>
+          <t>538168556.64</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-80674244</t>
+          <t>-84502446</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-27183655.53719378</t>
+          <t>-28065906.14552652</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>-32378374.72</v>
+        <v>-32918284.49</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>16.24</t>
+          <t>15.01</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8093,7 +8093,7 @@
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
@@ -8103,12 +8103,12 @@
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>22.49</t>
+          <t>22.24</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>18453</t>
+          <t>18243</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,22 +8158,22 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>96.5</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1012.26</t>
+          <t>1504.164</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>93.2</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,7 +8230,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-6.51</t>
+          <t>-9.25</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -8240,7 +8240,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-18.35</t>
+          <t>-34.56</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-12.90</t>
+          <t>-11.68</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>7.27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,77 +8336,77 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>1638</t>
+          <t>1153</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>19.17</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-3.11</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-5.57</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>7.68</t>
+          <t>7.35</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>94.66</t>
+          <t>94.24</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>97.62</t>
+          <t>97.26</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>103.01</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>95.66</t>
+          <t>95.95</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-22.08</t>
+          <t>-14.81</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-125.99</t>
+          <t>-126.99</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,41 +8426,41 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>356936222.4610389</t>
+          <t>356637749.5785303</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>94658594.0</t>
+          <t>143008503.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>222851108.2</t>
+          <t>152789337.4</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>272945780.2</t>
+          <t>233463581.9</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>561353465.26</t>
+          <t>553861277.88</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-50094672</t>
+          <t>-80674244</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-26239161.13943687</t>
+          <t>-27183655.53719378</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>-30753629.43</v>
+        <v>-32378374.72</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>14.64</t>
+          <t>16.24</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>22.49</t>
+          <t>22.24</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>18453</t>
+          <t>18243</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,22 +8589,22 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>93.7</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>95.3</t>
+          <t>96.5</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>92.8</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>93.2</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1267.489</t>
+          <t>1012.26</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>93.6</t>
+          <t>93.2</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,7 +8661,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-6.97</t>
+          <t>-7.75</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -8671,7 +8671,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-4.29</t>
+          <t>-18.35</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-12.52</t>
+          <t>-12.90</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>6.13</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,77 +8767,77 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>1638</t>
+          <t>1153</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>22.33</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>8.01</t>
+          <t>7.68</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>95.42</t>
+          <t>94.66</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>98.18</t>
+          <t>97.62</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>103.03</t>
+          <t>103.01</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>95.39</t>
+          <t>95.66</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-23.72</t>
+          <t>-22.08</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-124.56</t>
+          <t>-125.99</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,41 +8857,41 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>356936222.4610389</t>
+          <t>356637749.5785303</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>118648803.0</t>
+          <t>94658594.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>265570385.8</t>
+          <t>222851108.2</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>277478761.0</t>
+          <t>272945780.2</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>570658631.0</t>
+          <t>561353465.26</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-11908375</t>
+          <t>-50094672</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-25418348.72380762</t>
+          <t>-26239161.13943687</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>-22153873.41</v>
+        <v>-30753629.43</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>15.13</t>
+          <t>14.64</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8955,22 +8955,22 @@
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>22.49</t>
+          <t>22.24</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>18453</t>
+          <t>18243</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,12 +9020,12 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>93.7</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>95.3</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
@@ -9035,7 +9035,7 @@
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>93.6</t>
+          <t>93.2</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1991.474</t>
+          <t>1267.489</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>93.6</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,7 +9092,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-8.0</t>
+          <t>-8.21</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -9102,7 +9102,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>9.77</t>
+          <t>-4.29</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-11.68</t>
+          <t>-12.52</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>9.63</t>
+          <t>6.13</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,77 +9198,77 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>1638</t>
+          <t>1153</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>22.33</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-2.78</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-4.12</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>8.29</t>
+          <t>8.01</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>95.42</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>98.75</t>
+          <t>98.18</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>102.99</t>
+          <t>103.03</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>95.11</t>
+          <t>95.39</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-24.59</t>
+          <t>-23.72</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-123.10</t>
+          <t>-124.56</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,41 +9288,41 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>356936222.4610389</t>
+          <t>356637749.5785303</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>188802345.0</t>
+          <t>118648803.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>305935291.6</t>
+          <t>265570385.8</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>278708338.6</t>
+          <t>277478761.0</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>581698082.72</t>
+          <t>570658631.0</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>27226953</t>
+          <t>-11908375</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-26011889.68977666</t>
+          <t>-25418348.72380762</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>-11647677.45</v>
+        <v>-22153873.41</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>16.24</t>
+          <t>15.13</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>22.49</t>
+          <t>22.24</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>18453</t>
+          <t>18243</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,22 +9451,22 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>97.1</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>93.2</t>
+          <t>92.8</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>93.6</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2312.284</t>
+          <t>1991.474</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>95.4</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,7 +9523,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-9.03</t>
+          <t>-9.25</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -9533,7 +9533,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>9.77</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-10.84</t>
+          <t>-11.68</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11.18</t>
+          <t>9.63</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,77 +9629,77 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>1638</t>
+          <t>1153</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>-2.78</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-3.41</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>8.52</t>
+          <t>8.29</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>95.7</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>99.4</t>
+          <t>98.75</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>102.9</t>
+          <t>102.99</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>94.83</t>
+          <t>95.11</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-27.28</t>
+          <t>-24.59</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-121.68</t>
+          <t>-123.10</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>356936222.4610389</t>
+          <t>356637749.5785303</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>218828442.0</t>
+          <t>188802345.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>306064783.2</t>
+          <t>305935291.6</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>278240578.4</t>
+          <t>278708338.6</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>594226537.62</t>
+          <t>581698082.72</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>27824204</t>
+          <t>27226953</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-28623564.64298534</t>
+          <t>-26011889.68977666</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>-3739288.52</v>
+        <v>-11647677.45</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>17.34</t>
+          <t>16.24</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9827,12 +9827,12 @@
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>22.49</t>
+          <t>22.24</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>18453</t>
+          <t>18243</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,22 +9882,22 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>95.1</t>
+          <t>96.3</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>97.1</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>93.2</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>95.4</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>4980.394</t>
+          <t>2312.284</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>95.4</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,7 +9954,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-10.4</t>
+          <t>-10.29</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -9964,7 +9964,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-9.72</t>
+          <t>-10.84</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>24.07</t>
+          <t>11.18</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-5.49</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,77 +10060,77 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>1638</t>
+          <t>1153</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>42.32</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-2.9</t>
+          <t>-3.41</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>8.78</t>
+          <t>8.52</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>95.52000000000001</t>
+          <t>95.7</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>99.83</t>
+          <t>99.4</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>102.81</t>
+          <t>102.9</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>94.52</t>
+          <t>94.83</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-33.42</t>
+          <t>-27.28</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-120.20</t>
+          <t>-121.68</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>356936222.4610389</t>
+          <t>356637749.5785303</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>493317357.0</t>
+          <t>218828442.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>314137826.4</t>
+          <t>306064783.2</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>296369265.5</t>
+          <t>278240578.4</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>598741786.76</t>
+          <t>594226537.62</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>17768560</t>
+          <t>27824204</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-33147978.48379749</t>
+          <t>-28623564.64298534</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>4474874.15</v>
+        <v>-3739288.52</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>18.82</t>
+          <t>17.34</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10258,12 +10258,12 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>22.49</t>
+          <t>22.24</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>18453</t>
+          <t>18243</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,22 +10313,22 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>95.1</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>96.5</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>95.4</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/電鍍材料.xlsx
+++ b/Result/checksun_type/電鍍材料.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>685.0</t>
+          <t>670.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>44.95</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,97 +908,97 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
+          <t>24.67</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2025-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2025-10-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2025-08-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2025-08-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>45.6</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>44.45</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>52.5</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>47.6</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>1.12</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
           <t>-4.20</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2025-10-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2025-10-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2025-08-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2025-08-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>45.6</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>44.45</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>52.5</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>47.6</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>1.24</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>-4.20</t>
-        </is>
-      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16.81</t>
+          <t>16.44</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,270 +1014,270 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>670</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>98.77</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>75.04</t>
+          <t>94.23</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>42.73999999999999</t>
+          <t>43.31</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>43.61</t>
+          <t>43.58</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>44.12</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
+          <t>45.01</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>56.72</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>-0.17</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>-0.39</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>2.77</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>-114.07</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>2025/11/19</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>28280.49712230216</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>30506.0</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>23927.2</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>19193.0</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>13522.88</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>4734</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>927.631088724425</t>
+        </is>
+      </c>
+      <c r="BC2" t="n">
+        <v>1721.62</v>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>49.9</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>2025/08/12</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>-9.92</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>匯鑽科</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>匯鑽科</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>0.77</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>-10.56465687102404</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>-13.69932964657055</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>7.80229574004913</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>6.59</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>8.25%</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>-14.21%</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>42.77</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>1995</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>加工業務99.90%、勞務0.10% (2024年)</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>匯鑽科-其他電子業-上櫃</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>其他電子業右下上櫃</t>
+        </is>
+      </c>
+      <c r="CC2" t="inlineStr">
+        <is>
+          <t>45.5</t>
+        </is>
+      </c>
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>46.55</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>44.8</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
           <t>44.95</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>24.64</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>-0.34</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>-0.45</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>2.77</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>-116.07</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>2025/11/19</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>28255.31195965418</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>30695.0</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>18788.8</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>19613.1</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>13049.74</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>-824</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>783.2701283472239</t>
-        </is>
-      </c>
-      <c r="BC2" t="n">
-        <v>1149.94</v>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>49.9</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>2025/08/12</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>-9.82</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>匯鑽科</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>匯鑽科</t>
-        </is>
-      </c>
-      <c r="BJ2" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>0.78</t>
-        </is>
-      </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>-10.56465687102404</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
-        <is>
-          <t>-13.69932964657055</t>
-        </is>
-      </c>
-      <c r="BO2" t="inlineStr">
-        <is>
-          <t>7.80229574004913</t>
-        </is>
-      </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
-        </is>
-      </c>
-      <c r="BQ2" t="inlineStr">
-        <is>
-          <t>價漲量增</t>
-        </is>
-      </c>
-      <c r="BR2" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
-      </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="BT2" t="inlineStr">
-        <is>
-          <t>6.59</t>
-        </is>
-      </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BV2" t="inlineStr">
-        <is>
-          <t>8.25%</t>
-        </is>
-      </c>
-      <c r="BW2" t="inlineStr">
-        <is>
-          <t>-14.21%</t>
-        </is>
-      </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>41.96</t>
-        </is>
-      </c>
-      <c r="BY2" t="inlineStr">
-        <is>
-          <t>1998</t>
-        </is>
-      </c>
-      <c r="BZ2" t="inlineStr">
-        <is>
-          <t>加工業務99.90%、勞務0.10% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA2" t="inlineStr">
-        <is>
-          <t>匯鑽科-其他電子業-上櫃</t>
-        </is>
-      </c>
-      <c r="CB2" t="inlineStr">
-        <is>
-          <t>其他電子業右下上櫃</t>
-        </is>
-      </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>43.55</t>
-        </is>
-      </c>
-      <c r="CD2" t="inlineStr">
-        <is>
-          <t>45.55</t>
-        </is>
-      </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>43.3</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>45.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>655.0</t>
+          <t>685.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-32.14</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>16.81</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1445,72 +1445,72 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>670</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>83.93</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>75.04</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>42.22000000000001</t>
+          <t>42.73999999999999</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>43.61</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>44.15</t>
+          <t>44.12</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>44.89</t>
+          <t>44.95</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-16.05</t>
+          <t>24.64</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-117.06</t>
+          <t>-116.07</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>28255.31195965418</t>
+          <t>28280.49712230216</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>28225.0</t>
+          <t>30695.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>13738.6</t>
+          <t>18788.8</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>20246.9</t>
+          <t>19613.1</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>12733.2</t>
+          <t>13049.74</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-6508</t>
+          <t>-824</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>716.6020020198885</t>
+          <t>783.2701283472239</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>271.95</v>
+        <v>1149.94</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-13.23</t>
+          <t>-9.82</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1628,17 +1628,17 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>42.77</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>42.35</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>369.0</t>
+          <t>655.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>42.35</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>5.89</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-43.86</t>
+          <t>-32.14</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-4.72</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>9.06</t>
+          <t>16.07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1876,72 +1876,72 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>670</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>41.18</t>
+          <t>83.93</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>14.84</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>42.22000000000001</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>43.53</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>44.23</t>
+          <t>44.15</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>44.87</t>
+          <t>44.89</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-40.91</t>
+          <t>-16.05</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-116.38</t>
+          <t>-117.06</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>28255.31195965418</t>
+          <t>28280.49712230216</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>15453.0</t>
+          <t>28225.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>11783.2</t>
+          <t>13738.6</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>20989.4</t>
+          <t>20246.9</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>12346.96</t>
+          <t>12733.2</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-9206</t>
+          <t>-6508</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>797.4475068096988</t>
+          <t>716.6020020198885</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-727.39</v>
+        <v>271.95</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-15.13</t>
+          <t>-13.23</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>42.77</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>42.7</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>42.35</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>42.35</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>358.0</t>
+          <t>369.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>42.35</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>5.78</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-27.59</t>
+          <t>-43.86</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-7.87</t>
+          <t>-4.72</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>8.79</t>
+          <t>9.06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2307,72 +2307,72 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>670</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>41.18</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>14.84</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-3.31</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>42.04000000000001</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>43.48</t>
+          <t>43.53</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>44.31</t>
+          <t>44.23</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>44.85</t>
+          <t>44.87</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-59.38</t>
+          <t>-40.91</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-114.70</t>
+          <t>-116.38</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>28255.31195965418</t>
+          <t>28280.49712230216</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>14757.0</t>
+          <t>15453.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>15111.8</t>
+          <t>11783.2</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>20870.2</t>
+          <t>20989.4</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>12172.68</t>
+          <t>12346.96</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-5758</t>
+          <t>-9206</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>1074.691386655718</t>
+          <t>797.4475068096988</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-760.62</v>
+        <v>-727.39</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-17.94</t>
+          <t>-15.13</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>42.77</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>42.45</t>
+          <t>42.7</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2570,7 +2570,7 @@
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>42.35</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>358.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6.44</t>
+          <t>8.9</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-29.63</t>
+          <t>-27.59</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-5.29</t>
+          <t>-7.87</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>8.79</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2738,12 +2738,12 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>670</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -2753,57 +2753,57 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-3.31</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>42.55</t>
+          <t>42.04000000000001</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.48</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>44.42</t>
+          <t>44.31</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>44.84</t>
+          <t>44.85</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-46.96</t>
+          <t>-59.38</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-112.52</t>
+          <t>-114.70</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>28255.31195965418</t>
+          <t>28280.49712230216</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>4814.0</t>
+          <t>14757.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>14458.8</t>
+          <t>15111.8</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>20545.5</t>
+          <t>20870.2</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>12162.98</t>
+          <t>12172.68</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-6086</t>
+          <t>-5758</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>1408.384988086925</t>
+          <t>1074.691386655718</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-706.36</v>
+        <v>-760.62</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-15.63</t>
+          <t>-17.94</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>42.77</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
+          <t>42.1</t>
+        </is>
+      </c>
+      <c r="CD6" t="inlineStr">
+        <is>
           <t>42.45</t>
         </is>
       </c>
-      <c r="CD6" t="inlineStr">
-        <is>
-          <t>42.7</t>
-        </is>
-      </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>41.95</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>114.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>42.4</t>
+          <t>42.1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5.78</t>
+          <t>6.34</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-7.97</t>
+          <t>-29.63</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-4.61</t>
+          <t>-5.29</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3169,72 +3169,72 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>670</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>42.88</t>
+          <t>42.55</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>43.46</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>44.54</t>
+          <t>44.42</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>44.81</t>
+          <t>44.84</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-44.19</t>
+          <t>-46.96</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-111.05</t>
+          <t>-112.52</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>28255.31195965418</t>
+          <t>28280.49712230216</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>5444.0</t>
+          <t>4814.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>20437.4</t>
+          <t>14458.8</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>22206.9</t>
+          <t>20545.5</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>13085.46</t>
+          <t>12162.98</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-1769</t>
+          <t>-6086</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>1792.883660776302</t>
+          <t>1408.384988086925</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>461.71</v>
+        <v>-706.36</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-15.03</t>
+          <t>-15.63</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -3352,17 +3352,17 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>42.77</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>42.45</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>42.7</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>41.95</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>42.4</t>
+          <t>42.1</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>441.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>42.4</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>15.49</t>
+          <t>-7.97</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-5.51</t>
+          <t>-4.61</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10.82</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3600,42 +3600,42 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>670</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>43.27</t>
+          <t>42.88</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -3645,27 +3645,27 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>44.68</t>
+          <t>44.54</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>44.79</t>
+          <t>44.81</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-38.94</t>
+          <t>-44.19</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-109.83</t>
+          <t>-111.05</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>28255.31195965418</t>
+          <t>28280.49712230216</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>18448.0</t>
+          <t>5444.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>26755.2</t>
+          <t>20437.4</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>23167.0</t>
+          <t>22206.9</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>14024.46</t>
+          <t>13085.46</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>3588</t>
+          <t>-1769</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>2034.914649979622</t>
+          <t>1792.883660776302</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>2046.4</v>
+        <v>461.71</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-15.83</t>
+          <t>-15.03</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>42.77</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>42.85</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>42.4</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>441.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>42.75</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>6.56</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>30.99</t>
+          <t>15.49</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-3.82</t>
+          <t>-5.51</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>18.40</t>
+          <t>10.82</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>670</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4046,57 +4046,57 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>43.87</t>
+          <t>43.27</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>43.52</t>
+          <t>43.46</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>44.87</t>
+          <t>44.68</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>44.77</t>
+          <t>44.79</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-38.94</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-108.87</t>
+          <t>-109.83</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>28255.31195965418</t>
+          <t>28280.49712230216</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>32096.0</t>
+          <t>18448.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>30195.6</t>
+          <t>26755.2</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>23051.9</t>
+          <t>23167.0</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>14111.94</t>
+          <t>14024.46</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>7143</t>
+          <t>3588</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>2032.827091412444</t>
+          <t>2034.914649979622</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>2843.86</v>
+        <v>2046.4</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-14.33</t>
+          <t>-15.83</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4224,7 +4224,7 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>42.77</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>42.85</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>42.75</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>266.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>42.75</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>22.62</t>
+          <t>30.99</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-3.82</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>6.53</t>
+          <t>18.40</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>670</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4472,62 +4472,62 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>15.28</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>44.17999999999999</t>
+          <t>43.87</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>43.52</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>44.87</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>44.74</t>
+          <t>44.77</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>33.46</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-108.82</t>
+          <t>-108.87</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>28255.31195965418</t>
+          <t>28280.49712230216</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>11492.0</t>
+          <t>32096.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>26628.6</t>
+          <t>30195.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>21717.1</t>
+          <t>23051.9</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>13933.04</t>
+          <t>14111.94</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>4911</t>
+          <t>7143</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>1885.366964693159</t>
+          <t>2032.827091412444</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>2419.24</v>
+        <v>2843.86</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-12.83</t>
+          <t>-14.33</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>42.77</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>43.8</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>42.65</t>
+          <t>42.1</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>42.75</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>791.0</t>
+          <t>266.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>43.75</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>22.13</t>
+          <t>22.62</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>19.41</t>
+          <t>6.53</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4893,7 +4893,7 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>670</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4903,62 +4903,62 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>36.33</t>
+          <t>15.28</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-3.47</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>44.27999999999999</t>
+          <t>44.17999999999999</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>43.65</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>45.22</t>
+          <t>45.05</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>44.69</t>
+          <t>44.74</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>53.56</t>
+          <t>33.46</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-109.56</t>
+          <t>-108.82</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>28255.31195965418</t>
+          <t>28280.49712230216</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>34707.0</t>
+          <t>11492.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>26632.2</t>
+          <t>26628.6</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>21806.1</t>
+          <t>21717.1</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>14945.28</t>
+          <t>13933.04</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>4826</t>
+          <t>4911</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>1788.299770372915</t>
+          <t>1885.366964693159</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>3933.8</v>
+        <v>2419.24</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-12.32</t>
+          <t>-12.83</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>42.77</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>44.85</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>43.8</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>42.75</t>
+          <t>42.65</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>43.75</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>827.0</t>
+          <t>791.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>44.35</t>
+          <t>43.75</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>12.85</t>
+          <t>22.13</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>20.29</t>
+          <t>19.41</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5324,72 +5324,72 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>670</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>45.83</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>36.33</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-3.47</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>44.33</t>
+          <t>44.27999999999999</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>43.69</t>
+          <t>43.65</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>45.34</t>
+          <t>45.22</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>44.65</t>
+          <t>44.69</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>67.99</t>
+          <t>53.56</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-110.84</t>
+          <t>-109.56</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>28255.31195965418</t>
+          <t>28280.49712230216</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>37033.0</t>
+          <t>34707.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>23976.4</t>
+          <t>26632.2</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>21246.9</t>
+          <t>21806.1</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>14725.58</t>
+          <t>14945.28</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>2729</t>
+          <t>4826</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>1398.207935072465</t>
+          <t>1788.299770372915</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>3469.66</v>
+        <v>3933.8</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-11.12</t>
+          <t>-12.32</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>42.77</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>44.85</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>43.95</t>
+          <t>42.75</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>44.35</t>
+          <t>43.75</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1153.082</t>
+          <t>710.084</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-19.16</t>
+          <t>-17.57</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,77 +5750,77 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>1153</t>
+          <t>710</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.73</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.91</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-3.74</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-5.54</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-7.14</t>
+          <t>-7.34</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>89.86</t>
+          <t>88.56</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>94.36</t>
+          <t>93.75</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>101.62</t>
+          <t>101.18</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>96.9</t>
+          <t>97.04</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-27.21</t>
+          <t>-22.39</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-2.48</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-134.50</t>
+          <t>-136.55</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,41 +5840,41 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>356637749.5785303</t>
+          <t>356260067.1431655</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>99864028.0</t>
+          <t>62765638.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>138609938.8</t>
+          <t>124126000.4</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>137834914.3</t>
+          <t>125231243.6</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>443270959.36</t>
+          <t>399636300.16</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>775024</t>
+          <t>-1105243</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-28391852.12934346</t>
+          <t>-28835218.6887616</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>-28094189.89</v>
+        <v>-31273734.77</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>6.40</t>
+          <t>8.49</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BM13" t="inlineStr">
@@ -5938,22 +5938,22 @@
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>22.24</t>
+          <t>22.67</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>33.81</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>18243</t>
+          <t>18601</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>88.6</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
+          <t>89.4</t>
+        </is>
+      </c>
+      <c r="CE13" t="inlineStr">
+        <is>
           <t>87.9</t>
         </is>
       </c>
-      <c r="CE13" t="inlineStr">
-        <is>
-          <t>85.9</t>
-        </is>
-      </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1638.11</t>
+          <t>1153.082</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-18.22</t>
+          <t>-19.16</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>7.92</t>
+          <t>5.57</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-2.40</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,12 +6181,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>1153</t>
+          <t>710</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6201,57 +6201,57 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-4.12</t>
+          <t>-3.74</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-4.10</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-6.67</t>
+          <t>-7.14</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>91.26</t>
+          <t>89.86</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>95.16</t>
+          <t>94.36</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>101.96</t>
+          <t>101.62</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>96.8</t>
+          <t>96.9</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-23.67</t>
+          <t>-27.21</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-2.86</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-132.15</t>
+          <t>-134.50</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,41 +6271,41 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>356637749.5785303</t>
+          <t>356260067.1431655</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>144178661.0</t>
+          <t>99864028.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>146673374.0</t>
+          <t>138609938.8</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>149731355.7</t>
+          <t>137834914.3</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>454484548.46</t>
+          <t>443270959.36</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-3057981</t>
+          <t>775024</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-28445972.53673498</t>
+          <t>-28391852.12934346</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>-26523446.5</v>
+        <v>-28094189.89</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>7.63</t>
+          <t>6.40</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BM14" t="inlineStr">
@@ -6379,12 +6379,12 @@
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>22.24</t>
+          <t>22.67</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>33.81</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>18243</t>
+          <t>18601</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>89.9</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>85.9</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1631.485</t>
+          <t>1638.11</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,17 +6506,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-20.69</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-16.26</t>
+          <t>-18.22</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>7.89</t>
+          <t>7.92</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-2.40</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,12 +6612,12 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>1153</t>
+          <t>710</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6627,62 +6627,62 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>13.16</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-3.30</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>-4.10</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-6.3</t>
+          <t>-6.67</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>5.78</t>
+          <t>5.33</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>92.66</t>
+          <t>91.26</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>95.84</t>
+          <t>95.16</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>102.28</t>
+          <t>101.96</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>96.69</t>
+          <t>96.8</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-16.84</t>
+          <t>-23.67</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-2.86</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-130.25</t>
+          <t>-132.15</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,41 +6702,41 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>356637749.5785303</t>
+          <t>356260067.1431655</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>147034386.0</t>
+          <t>144178661.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>146439342.4</t>
+          <t>146673374.0</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>184645225.3</t>
+          <t>149731355.7</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>461884050.18</t>
+          <t>454484548.46</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-38205882</t>
+          <t>-3057981</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-28795522.72575311</t>
+          <t>-28445972.53673498</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>-28080257.81</v>
+        <v>-26523446.5</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>10.21</t>
+          <t>7.63</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BM15" t="inlineStr">
@@ -6800,7 +6800,7 @@
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>22.24</t>
+          <t>22.67</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>33.81</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>18243</t>
+          <t>18601</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>89.9</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>89.4</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-4.0</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1815.561</t>
+          <t>1631.485</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-5.2</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-32.28</t>
+          <t>-20.69</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-14.95</t>
+          <t>-16.26</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>8.78</t>
+          <t>7.89</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,12 +7043,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>1153</t>
+          <t>710</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7058,62 +7058,62 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>15.79</t>
+          <t>13.16</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-3.30</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-3.32</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-6.05</t>
+          <t>-6.3</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>6.20</t>
+          <t>5.78</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>93.38</t>
+          <t>92.66</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>96.32</t>
+          <t>95.84</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>102.52</t>
+          <t>102.28</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>96.53</t>
+          <t>96.69</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-10.98</t>
+          <t>-16.84</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-128.98</t>
+          <t>-130.25</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,41 +7133,41 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>356637749.5785303</t>
+          <t>356260067.1431655</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>166787289.0</t>
+          <t>147034386.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>135964184.0</t>
+          <t>146439342.4</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>200767284.9</t>
+          <t>184645225.3</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>481289771.06</t>
+          <t>461884050.18</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-64803100</t>
+          <t>-38205882</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-28925570.89173124</t>
+          <t>-28795522.72575311</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>-29607378.16</v>
+        <v>-28080257.81</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>11.93</t>
+          <t>10.21</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BM16" t="inlineStr">
@@ -7231,22 +7231,22 @@
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>22.24</t>
+          <t>22.67</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>33.81</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>18243</t>
+          <t>18601</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>89.4</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1433.749</t>
+          <t>1815.561</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>94.7</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-9.48</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-41.55</t>
+          <t>-32.28</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-11.50</t>
+          <t>-14.95</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>8.78</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,77 +7474,77 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>1153</t>
+          <t>710</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>39.47</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>28.29</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-5.8</t>
+          <t>-6.05</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>6.60</t>
+          <t>6.20</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>93.9</t>
+          <t>93.38</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>96.8</t>
+          <t>96.32</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>102.75</t>
+          <t>102.52</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>96.39</t>
+          <t>96.53</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-5.06</t>
+          <t>-10.98</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-128.18</t>
+          <t>-128.98</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,41 +7564,41 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>356637749.5785303</t>
+          <t>356260067.1431655</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>135185330.0</t>
+          <t>166787289.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>126336486.8</t>
+          <t>135964184.0</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>216135889.2</t>
+          <t>200767284.9</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>501408648.9</t>
+          <t>481289771.06</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-89799402</t>
+          <t>-64803100</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-28801605.93323361</t>
+          <t>-28925570.89173124</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>-32847954.77</v>
+        <v>-29607378.16</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>16.48</t>
+          <t>11.93</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7642,7 +7642,7 @@
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BM17" t="inlineStr">
@@ -7662,22 +7662,22 @@
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>22.24</t>
+          <t>22.67</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>33.81</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>18243</t>
+          <t>18601</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>95.3</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>94.7</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1479.927</t>
+          <t>1433.749</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-8.09</t>
+          <t>-7.37</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-38.14</t>
+          <t>-41.55</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-12.62</t>
+          <t>-11.50</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>7.15</t>
+          <t>6.93</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,77 +7905,77 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>1153</t>
+          <t>710</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>7.89</t>
+          <t>39.47</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>28.29</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-5.69</t>
+          <t>-5.8</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>6.60</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>93.86</t>
+          <t>93.9</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>97.05</t>
+          <t>96.8</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>102.91</t>
+          <t>102.75</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>96.17</t>
+          <t>96.39</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-11.98</t>
+          <t>-5.06</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-127.83</t>
+          <t>-128.18</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,41 +7995,41 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>356637749.5785303</t>
+          <t>356260067.1431655</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>140181204.0</t>
+          <t>135185330.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>137059889.8</t>
+          <t>126336486.8</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>221562336.5</t>
+          <t>216135889.2</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>538168556.64</t>
+          <t>501408648.9</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-84502446</t>
+          <t>-89799402</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-28065906.14552652</t>
+          <t>-28801605.93323361</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>-32918284.49</v>
+        <v>-32847954.77</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>15.01</t>
+          <t>16.48</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BM18" t="inlineStr">
@@ -8093,7 +8093,7 @@
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
@@ -8103,12 +8103,12 @@
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>22.24</t>
+          <t>22.67</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>33.81</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>18243</t>
+          <t>18601</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,22 +8158,22 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>95.3</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1504.164</t>
+          <t>1479.927</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-9.25</t>
+          <t>-6.01</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-34.56</t>
+          <t>-38.14</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-11.68</t>
+          <t>-12.62</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>7.27</t>
+          <t>7.15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,77 +8336,77 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>1153</t>
+          <t>710</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>7.89</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>19.17</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-3.11</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-5.57</t>
+          <t>-5.69</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>7.35</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>94.24</t>
+          <t>93.86</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>97.26</t>
+          <t>97.05</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>102.91</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>95.95</t>
+          <t>96.17</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-14.81</t>
+          <t>-11.98</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-126.99</t>
+          <t>-127.83</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,41 +8426,41 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>356637749.5785303</t>
+          <t>356260067.1431655</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>143008503.0</t>
+          <t>140181204.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>152789337.4</t>
+          <t>137059889.8</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>233463581.9</t>
+          <t>221562336.5</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>553861277.88</t>
+          <t>538168556.64</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-80674244</t>
+          <t>-84502446</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-27183655.53719378</t>
+          <t>-28065906.14552652</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>-32378374.72</v>
+        <v>-32918284.49</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>16.24</t>
+          <t>15.01</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BM19" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>22.24</t>
+          <t>22.67</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>33.81</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>18243</t>
+          <t>18601</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,22 +8589,22 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>96.5</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1012.26</t>
+          <t>1504.164</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>93.2</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-7.75</t>
+          <t>-7.14</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-18.35</t>
+          <t>-34.56</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-12.90</t>
+          <t>-11.68</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>7.27</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,77 +8767,77 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>1153</t>
+          <t>710</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>19.17</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-3.11</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-5.57</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>7.68</t>
+          <t>7.35</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>94.66</t>
+          <t>94.24</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>97.62</t>
+          <t>97.26</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>103.01</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>95.66</t>
+          <t>95.95</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-22.08</t>
+          <t>-14.81</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-125.99</t>
+          <t>-126.99</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,41 +8857,41 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>356637749.5785303</t>
+          <t>356260067.1431655</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>94658594.0</t>
+          <t>143008503.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>222851108.2</t>
+          <t>152789337.4</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>272945780.2</t>
+          <t>233463581.9</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>561353465.26</t>
+          <t>553861277.88</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-50094672</t>
+          <t>-80674244</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-26239161.13943687</t>
+          <t>-27183655.53719378</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>-30753629.43</v>
+        <v>-32378374.72</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>14.64</t>
+          <t>16.24</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BM20" t="inlineStr">
@@ -8955,7 +8955,7 @@
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
@@ -8965,12 +8965,12 @@
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>22.24</t>
+          <t>22.67</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>33.81</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>18243</t>
+          <t>18601</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>93.7</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>95.3</t>
+          <t>96.5</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>92.8</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>93.2</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1267.489</t>
+          <t>1012.26</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>93.6</t>
+          <t>93.2</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-8.21</t>
+          <t>-5.67</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-4.29</t>
+          <t>-18.35</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-12.52</t>
+          <t>-12.90</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>6.13</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,77 +9198,77 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>1153</t>
+          <t>710</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>22.33</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>8.01</t>
+          <t>7.68</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>95.42</t>
+          <t>94.66</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>98.18</t>
+          <t>97.62</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>103.03</t>
+          <t>103.01</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>95.39</t>
+          <t>95.66</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-23.72</t>
+          <t>-22.08</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-124.56</t>
+          <t>-125.99</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,41 +9288,41 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>356637749.5785303</t>
+          <t>356260067.1431655</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>118648803.0</t>
+          <t>94658594.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>265570385.8</t>
+          <t>222851108.2</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>277478761.0</t>
+          <t>272945780.2</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>570658631.0</t>
+          <t>561353465.26</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-11908375</t>
+          <t>-50094672</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-25418348.72380762</t>
+          <t>-26239161.13943687</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>-22153873.41</v>
+        <v>-30753629.43</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>15.13</t>
+          <t>14.64</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BM21" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>22.24</t>
+          <t>22.67</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>33.81</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>18243</t>
+          <t>18601</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>93.7</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>95.3</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
@@ -9466,7 +9466,7 @@
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>93.6</t>
+          <t>93.2</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.96</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1991.474</t>
+          <t>1267.489</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>93.6</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-9.25</t>
+          <t>-6.12</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>9.77</t>
+          <t>-4.29</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-11.68</t>
+          <t>-12.52</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>9.63</t>
+          <t>6.13</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,77 +9629,77 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>1153</t>
+          <t>710</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>22.33</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-2.78</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-4.12</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>8.29</t>
+          <t>8.01</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>95.42</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>98.75</t>
+          <t>98.18</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>102.99</t>
+          <t>103.03</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>95.11</t>
+          <t>95.39</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-24.59</t>
+          <t>-23.72</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-2.07</t>
+          <t>-2.19</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-123.10</t>
+          <t>-124.56</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>356637749.5785303</t>
+          <t>356260067.1431655</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>188802345.0</t>
+          <t>118648803.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>305935291.6</t>
+          <t>265570385.8</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>278708338.6</t>
+          <t>277478761.0</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>581698082.72</t>
+          <t>570658631.0</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>27226953</t>
+          <t>-11908375</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-26011889.68977666</t>
+          <t>-25418348.72380762</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>-11647677.45</v>
+        <v>-22153873.41</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>16.24</t>
+          <t>15.13</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9797,7 +9797,7 @@
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BM22" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9827,12 +9827,12 @@
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>22.24</t>
+          <t>22.67</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>33.81</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>18243</t>
+          <t>18601</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,22 +9882,22 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>97.1</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>93.2</t>
+          <t>92.8</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>93.6</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2312.284</t>
+          <t>1991.474</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>95.4</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-10.29</t>
+          <t>-7.14</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>9.77</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-10.84</t>
+          <t>-11.68</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11.18</t>
+          <t>9.63</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,77 +10060,77 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>1153</t>
+          <t>710</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>-2.78</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-3.41</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>8.52</t>
+          <t>8.29</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>95.7</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>99.4</t>
+          <t>98.75</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>102.9</t>
+          <t>102.99</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>94.83</t>
+          <t>95.11</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-27.28</t>
+          <t>-24.59</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>-2.07</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-121.68</t>
+          <t>-123.10</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>356637749.5785303</t>
+          <t>356260067.1431655</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>218828442.0</t>
+          <t>188802345.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>306064783.2</t>
+          <t>305935291.6</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>278240578.4</t>
+          <t>278708338.6</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>594226537.62</t>
+          <t>581698082.72</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>27824204</t>
+          <t>27226953</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-28623564.64298534</t>
+          <t>-26011889.68977666</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-3739288.52</v>
+        <v>-11647677.45</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>17.34</t>
+          <t>16.24</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="BM23" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10258,12 +10258,12 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>22.24</t>
+          <t>22.67</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>33.81</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>18243</t>
+          <t>18601</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,22 +10313,22 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>95.1</t>
+          <t>96.3</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>97.1</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>93.2</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>95.4</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/電鍍材料.xlsx
+++ b/Result/checksun_type/電鍍材料.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-4.49</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>42.95</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>20.84</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>5.89</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,77 +1014,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>153</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>49.38</t>
+          <t>50.62</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>82.72</t>
+          <t>66.26</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>43.71</t>
+          <t>43.84</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.45</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>44.03</t>
+          <t>43.97</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>45.06</t>
+          <t>45.12</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>44.24</t>
+          <t>34.76</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-112.67</t>
+          <t>-111.66</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>28262.4073275862</t>
+          <t>28236.11621233859</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>10460.0</t>
+          <t>6625.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>23067.8</t>
+          <t>21302.2</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>19089.8</t>
+          <t>16542.7</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>13602.9</t>
+          <t>13576.72</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>3978</t>
+          <t>4759</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>873.4256973645256</t>
+          <t>657.6470386350882</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>575.296044885079</t>
+          <t>-529.1355843768179</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>10460</v>
+        <v>6625</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-13.93</t>
+          <t>-13.83</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1207,22 +1207,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>42.08</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>1909</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>42.8</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>42.95</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>670.0</t>
+          <t>240.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>44.95</t>
+          <t>42.95</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-4.66</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>24.67</t>
+          <t>20.84</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16.44</t>
+          <t>5.89</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,77 +1450,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>153</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>98.77</t>
+          <t>49.38</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>94.23</t>
+          <t>82.72</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>43.31</t>
+          <t>43.71</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>43.58</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>44.03</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>45.01</t>
+          <t>45.06</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>56.72</t>
+          <t>44.24</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-114.07</t>
+          <t>-112.67</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>28262.4073275862</t>
+          <t>28236.11621233859</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>30506.0</t>
+          <t>10460.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>23927.2</t>
+          <t>23067.8</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>19193.0</t>
+          <t>19089.8</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>13522.88</t>
+          <t>13602.9</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>4734</t>
+          <t>3978</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>927.631088724425</t>
+          <t>873.4256973645256</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>1721.616370799031</t>
+          <t>575.296044885079</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>30506</v>
+        <v>10460</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-9.92</t>
+          <t>-13.93</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1643,22 +1643,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>42.08</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>1909</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>46.55</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>44.95</t>
+          <t>42.95</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>685.0</t>
+          <t>670.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>44.95</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,102 +1780,102 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-4.53</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
+          <t>24.67</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>-95.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-10-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-08-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-08-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>45.6</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>44.45</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>52.5</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>47.6</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>1.12</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
           <t>-4.20</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>-95.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2025-10-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2025-10-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-08-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-08-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>45.6</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>44.45</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>52.5</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>47.6</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>1.24</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>-4.20</t>
-        </is>
-      </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16.81</t>
+          <t>16.44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,280 +1886,280 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>153</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>98.77</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>75.04</t>
+          <t>94.23</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>42.73999999999999</t>
+          <t>43.31</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>43.61</t>
+          <t>43.58</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>44.12</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
+          <t>45.01</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>56.72</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>-0.17</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>-0.39</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>2.77</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>-114.07</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>2025/11/19</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>28236.11621233859</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>30506.0</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>23927.2</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>19193.0</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>13522.88</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>4734</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>927.631088724425</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>1721.616370799031</t>
+        </is>
+      </c>
+      <c r="BD4" t="n">
+        <v>30506</v>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>49.9</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>2025/08/12</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>-9.92</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>匯鑽科</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>匯鑽科</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>0.77</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>-10.56465687102404</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr">
+        <is>
+          <t>-13.69932964657055</t>
+        </is>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>7.80229574004913</t>
+        </is>
+      </c>
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="BT4" t="inlineStr">
+        <is>
+          <t>2.61</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
+          <t>6.59</t>
+        </is>
+      </c>
+      <c r="BV4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
+          <t>8.25%</t>
+        </is>
+      </c>
+      <c r="BX4" t="inlineStr">
+        <is>
+          <t>-14.21%</t>
+        </is>
+      </c>
+      <c r="BY4" t="inlineStr">
+        <is>
+          <t>42.08</t>
+        </is>
+      </c>
+      <c r="BZ4" t="inlineStr">
+        <is>
+          <t>1909</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
+          <t>加工業務99.90%、勞務0.10% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>匯鑽科-其他電子業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC4" t="inlineStr">
+        <is>
+          <t>其他電子業右下上櫃</t>
+        </is>
+      </c>
+      <c r="CD4" t="inlineStr">
+        <is>
+          <t>45.5</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
+          <t>46.55</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
+          <t>44.8</t>
+        </is>
+      </c>
+      <c r="CG4" t="inlineStr">
+        <is>
           <t>44.95</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>24.64</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>-0.34</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>-0.45</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>2.77</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>-116.07</t>
-        </is>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>2025/11/19</t>
-        </is>
-      </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>28262.4073275862</t>
-        </is>
-      </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>30695.0</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>18788.8</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>19613.1</t>
-        </is>
-      </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>13049.74</t>
-        </is>
-      </c>
-      <c r="BA4" t="inlineStr">
-        <is>
-          <t>-824</t>
-        </is>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>783.2701283472239</t>
-        </is>
-      </c>
-      <c r="BC4" t="inlineStr">
-        <is>
-          <t>1149.944823147569</t>
-        </is>
-      </c>
-      <c r="BD4" t="n">
-        <v>30695</v>
-      </c>
-      <c r="BE4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>49.9</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>2025/08/12</t>
-        </is>
-      </c>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>-9.82</t>
-        </is>
-      </c>
-      <c r="BI4" t="inlineStr">
-        <is>
-          <t>匯鑽科</t>
-        </is>
-      </c>
-      <c r="BJ4" t="inlineStr">
-        <is>
-          <t>匯鑽科</t>
-        </is>
-      </c>
-      <c r="BK4" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BL4" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM4" t="inlineStr">
-        <is>
-          <t>0.78</t>
-        </is>
-      </c>
-      <c r="BN4" t="inlineStr">
-        <is>
-          <t>-10.56465687102404</t>
-        </is>
-      </c>
-      <c r="BO4" t="inlineStr">
-        <is>
-          <t>-13.69932964657055</t>
-        </is>
-      </c>
-      <c r="BP4" t="inlineStr">
-        <is>
-          <t>7.80229574004913</t>
-        </is>
-      </c>
-      <c r="BQ4" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
-        </is>
-      </c>
-      <c r="BR4" t="inlineStr">
-        <is>
-          <t>價漲量增</t>
-        </is>
-      </c>
-      <c r="BS4" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
-      </c>
-      <c r="BT4" t="inlineStr">
-        <is>
-          <t>2.62</t>
-        </is>
-      </c>
-      <c r="BU4" t="inlineStr">
-        <is>
-          <t>6.59</t>
-        </is>
-      </c>
-      <c r="BV4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BW4" t="inlineStr">
-        <is>
-          <t>8.25%</t>
-        </is>
-      </c>
-      <c r="BX4" t="inlineStr">
-        <is>
-          <t>-14.21%</t>
-        </is>
-      </c>
-      <c r="BY4" t="inlineStr">
-        <is>
-          <t>41.57</t>
-        </is>
-      </c>
-      <c r="BZ4" t="inlineStr">
-        <is>
-          <t>1907</t>
-        </is>
-      </c>
-      <c r="CA4" t="inlineStr">
-        <is>
-          <t>加工業務99.90%、勞務0.10% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB4" t="inlineStr">
-        <is>
-          <t>匯鑽科-其他電子業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC4" t="inlineStr">
-        <is>
-          <t>其他電子業右下上櫃</t>
-        </is>
-      </c>
-      <c r="CD4" t="inlineStr">
-        <is>
-          <t>43.55</t>
-        </is>
-      </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>45.55</t>
-        </is>
-      </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>43.3</t>
-        </is>
-      </c>
-      <c r="CG4" t="inlineStr">
-        <is>
-          <t>45.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>655.0</t>
+          <t>685.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-4.65</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-32.14</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>16.81</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,77 +2322,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>153</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>83.93</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>75.04</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>42.22000000000001</t>
+          <t>42.73999999999999</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>43.61</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>44.15</t>
+          <t>44.12</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>44.89</t>
+          <t>44.95</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-16.05</t>
+          <t>24.64</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-117.06</t>
+          <t>-116.07</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>28262.4073275862</t>
+          <t>28236.11621233859</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>28225.0</t>
+          <t>30695.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>13738.6</t>
+          <t>18788.8</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>20246.9</t>
+          <t>19613.1</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>12733.2</t>
+          <t>13049.74</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-6508</t>
+          <t>-824</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>716.6020020198885</t>
+          <t>783.2701283472239</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>271.9517256759318</t>
+          <t>1149.944823147569</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>28225</v>
+        <v>30695</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-13.23</t>
+          <t>-9.82</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2515,22 +2515,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>42.08</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>1909</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>42.35</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>369.0</t>
+          <t>655.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>42.35</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-43.86</t>
+          <t>-32.14</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-4.72</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>9.06</t>
+          <t>16.07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,77 +2758,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>153</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>41.18</t>
+          <t>83.93</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>14.84</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>42.22000000000001</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>43.53</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>44.23</t>
+          <t>44.15</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>44.87</t>
+          <t>44.89</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-40.91</t>
+          <t>-16.05</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-116.38</t>
+          <t>-117.06</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>28262.4073275862</t>
+          <t>28236.11621233859</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>15453.0</t>
+          <t>28225.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>11783.2</t>
+          <t>13738.6</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>20989.4</t>
+          <t>20246.9</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>12346.96</t>
+          <t>12733.2</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-9206</t>
+          <t>-6508</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>797.4475068096988</t>
+          <t>716.6020020198885</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-727.3938323434086</t>
+          <t>271.9517256759318</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>15453</v>
+        <v>28225</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-15.13</t>
+          <t>-13.23</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>42.08</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>1909</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>42.7</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>42.35</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>42.35</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>358.0</t>
+          <t>369.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>42.35</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4.66</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-27.59</t>
+          <t>-43.86</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-7.87</t>
+          <t>-4.72</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>8.79</t>
+          <t>9.06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,77 +3194,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>153</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>41.18</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>14.84</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-3.31</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>42.04000000000001</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>43.48</t>
+          <t>43.53</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>44.31</t>
+          <t>44.23</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>44.85</t>
+          <t>44.87</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-59.38</t>
+          <t>-40.91</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-114.70</t>
+          <t>-116.38</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>28262.4073275862</t>
+          <t>28236.11621233859</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>14757.0</t>
+          <t>15453.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>15111.8</t>
+          <t>11783.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>20870.2</t>
+          <t>20989.4</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>12172.68</t>
+          <t>12346.96</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-5758</t>
+          <t>-9206</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>1074.691386655718</t>
+          <t>797.4475068096988</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-760.6234212159197</t>
+          <t>-727.3938323434086</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>14757</v>
+        <v>15453</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-17.94</t>
+          <t>-15.13</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3392,17 +3392,17 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>42.08</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>1909</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>42.45</t>
+          <t>42.7</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
@@ -3467,7 +3467,7 @@
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>42.35</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>358.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>4.77</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-29.63</t>
+          <t>-27.59</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-5.29</t>
+          <t>-7.87</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>8.79</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,17 +3630,17 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>153</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -3650,57 +3650,57 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-3.31</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>42.55</t>
+          <t>42.04000000000001</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.48</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>44.42</t>
+          <t>44.31</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>44.84</t>
+          <t>44.85</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-46.96</t>
+          <t>-59.38</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-112.52</t>
+          <t>-114.70</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>28262.4073275862</t>
+          <t>28236.11621233859</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>4814.0</t>
+          <t>14757.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>14458.8</t>
+          <t>15111.8</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>20545.5</t>
+          <t>20870.2</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>12162.98</t>
+          <t>12172.68</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-6086</t>
+          <t>-5758</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>1408.384988086925</t>
+          <t>1074.691386655718</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-706.357711704648</t>
+          <t>-760.6234212159197</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>4814</v>
+        <v>14757</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-15.63</t>
+          <t>-17.94</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3828,17 +3828,17 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>42.08</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>1909</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
+          <t>42.1</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
           <t>42.45</t>
         </is>
       </c>
-      <c r="CE8" t="inlineStr">
-        <is>
-          <t>42.7</t>
-        </is>
-      </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>41.95</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>114.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>42.4</t>
+          <t>42.1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-7.97</t>
+          <t>-29.63</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-4.61</t>
+          <t>-5.29</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,77 +4066,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>153</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>42.88</t>
+          <t>42.55</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>43.46</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>44.54</t>
+          <t>44.42</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>44.81</t>
+          <t>44.84</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-44.19</t>
+          <t>-46.96</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-111.05</t>
+          <t>-112.52</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>28262.4073275862</t>
+          <t>28236.11621233859</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>5444.0</t>
+          <t>4814.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>20437.4</t>
+          <t>14458.8</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>22206.9</t>
+          <t>20545.5</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>13085.46</t>
+          <t>12162.98</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-1769</t>
+          <t>-6086</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>1792.883660776302</t>
+          <t>1408.384988086925</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>461.7132201580425</t>
+          <t>-706.357711704648</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>5444</v>
+        <v>4814</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-15.03</t>
+          <t>-15.63</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4259,22 +4259,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>42.08</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>1909</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>42.45</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>42.7</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>41.95</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>42.4</t>
+          <t>42.1</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>441.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>42.4</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>15.49</t>
+          <t>-7.97</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-5.51</t>
+          <t>-4.61</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10.82</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,47 +4502,47 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>153</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>43.27</t>
+          <t>42.88</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -4552,27 +4552,27 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>44.68</t>
+          <t>44.54</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>44.79</t>
+          <t>44.81</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-38.94</t>
+          <t>-44.19</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-109.83</t>
+          <t>-111.05</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>28262.4073275862</t>
+          <t>28236.11621233859</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>18448.0</t>
+          <t>5444.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>26755.2</t>
+          <t>20437.4</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>23167.0</t>
+          <t>22206.9</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>14024.46</t>
+          <t>13085.46</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>3588</t>
+          <t>-1769</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>2034.914649979622</t>
+          <t>1792.883660776302</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>2046.396222099105</t>
+          <t>461.7132201580425</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>18448</v>
+        <v>5444</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-15.83</t>
+          <t>-15.03</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4695,22 +4695,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>42.08</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>1909</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>42.85</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>42.4</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>441.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>42.75</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>30.99</t>
+          <t>15.49</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-3.82</t>
+          <t>-5.51</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18.40</t>
+          <t>10.82</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,12 +4938,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>153</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4958,57 +4958,57 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>43.87</t>
+          <t>43.27</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>43.52</t>
+          <t>43.46</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>44.87</t>
+          <t>44.68</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>44.77</t>
+          <t>44.79</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-38.94</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-108.87</t>
+          <t>-109.83</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>28262.4073275862</t>
+          <t>28236.11621233859</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>32096.0</t>
+          <t>18448.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>30195.6</t>
+          <t>26755.2</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>23051.9</t>
+          <t>23167.0</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>14111.94</t>
+          <t>14024.46</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>7143</t>
+          <t>3588</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>2032.827091412444</t>
+          <t>2034.914649979622</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>2843.85778836851</t>
+          <t>2046.396222099105</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>32096</v>
+        <v>18448</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-14.33</t>
+          <t>-15.83</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>42.08</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>1909</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>42.85</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>42.75</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>266.0</t>
+          <t>750.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>42.75</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>22.62</t>
+          <t>30.99</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-3.82</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>6.53</t>
+          <t>18.40</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,12 +5374,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>240</t>
+          <t>153</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5389,62 +5389,62 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>15.28</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>44.17999999999999</t>
+          <t>43.87</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>43.52</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>44.87</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>44.74</t>
+          <t>44.77</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>33.46</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-108.82</t>
+          <t>-108.87</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>28262.4073275862</t>
+          <t>28236.11621233859</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>11492.0</t>
+          <t>32096.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>26628.6</t>
+          <t>30195.6</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>21717.1</t>
+          <t>23051.9</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>13933.04</t>
+          <t>14111.94</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>4911</t>
+          <t>7143</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>1885.366964693159</t>
+          <t>2032.827091412444</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>2419.236533454499</t>
+          <t>2843.85778836851</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>11492</v>
+        <v>32096</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-12.83</t>
+          <t>-14.33</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>42.08</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>1909</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>43.8</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>42.65</t>
+          <t>42.1</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>42.75</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-3.11</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1197.387</t>
+          <t>797.916</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>86.1</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-3.32</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-9.98</t>
+          <t>-21.02</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5724,7 +5724,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-20.09</t>
+          <t>-19.53</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>5.79</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5810,77 +5810,77 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>1197</t>
+          <t>798</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>6.91</t>
+          <t>9.08</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-5.99</t>
+          <t>-6.01</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-7.53</t>
+          <t>-7.68</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>87.46000000000001</t>
+          <t>86.75999999999999</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>93.03</t>
+          <t>92.31</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>100.61</t>
+          <t>99.99</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>97.09</t>
+          <t>97.16</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-23.35</t>
+          <t>-20.19</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>-3.53</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-138.81</t>
+          <t>-140.87</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5900,46 +5900,46 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>355969373.6659483</t>
+          <t>355605937.846485</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>102624938.0</t>
+          <t>68436405.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>111293530.2</t>
+          <t>95573934.0</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>123628857.1</t>
+          <t>121006638.2</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>366752945.54</t>
+          <t>336619552.5</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-12335326</t>
+          <t>-25432704</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-28972588.9382186</t>
+          <t>-29202519.18368434</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-29728125.31023213</t>
+          <t>-30467135.53374588</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>102624938</v>
+        <v>68436405</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>5.17</t>
+          <t>5.90</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>4.06</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>21.98</t>
+          <t>22.13</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>32.63</t>
+          <t>32.66</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>18032</t>
+          <t>18158</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6063,27 +6063,27 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>電子零組件業平上市</t>
+          <t>電子零組件業右上上市</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>86.1</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>-3.11</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>710.084</t>
+          <t>1197.387</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6140,17 +6140,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-3.32</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-9.98</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6160,7 +6160,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-17.57</t>
+          <t>-20.09</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6225,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>5.79</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6246,17 +6246,17 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>1197</t>
+          <t>798</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>20.73</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
@@ -6266,57 +6266,57 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-5.54</t>
+          <t>-5.99</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-7.34</t>
+          <t>-7.53</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>88.56</t>
+          <t>87.46000000000001</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>93.75</t>
+          <t>93.03</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>101.18</t>
+          <t>100.61</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>97.04</t>
+          <t>97.09</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-22.39</t>
+          <t>-23.35</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-136.55</t>
+          <t>-138.81</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6336,46 +6336,46 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>355969373.6659483</t>
+          <t>355605937.846485</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>62765638.0</t>
+          <t>102624938.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>124126000.4</t>
+          <t>111293530.2</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>125231243.6</t>
+          <t>123628857.1</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>399636300.16</t>
+          <t>366752945.54</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-1105243</t>
+          <t>-12335326</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-28835218.6887616</t>
+          <t>-28972588.9382186</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-31273734.76556134</t>
+          <t>-29728125.31023213</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>62765638</v>
+        <v>102624938</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>8.49</t>
+          <t>5.17</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6439,22 +6439,22 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>4.06</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>21.98</t>
+          <t>22.13</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>32.63</t>
+          <t>32.66</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>18032</t>
+          <t>18158</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6499,27 +6499,27 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>電子零組件業平上市</t>
+          <t>電子零組件業右上上市</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>89.4</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1153.082</t>
+          <t>710.084</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6576,17 +6576,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-3.32</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6596,7 +6596,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-19.16</t>
+          <t>-17.57</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6682,77 +6682,77 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>1197</t>
+          <t>798</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.73</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.91</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-3.74</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-5.54</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-7.14</t>
+          <t>-7.34</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>89.86</t>
+          <t>88.56</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>94.36</t>
+          <t>93.75</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>101.62</t>
+          <t>101.18</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>96.9</t>
+          <t>97.04</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-27.21</t>
+          <t>-22.39</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-2.48</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-134.50</t>
+          <t>-136.55</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6772,46 +6772,46 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>355969373.6659483</t>
+          <t>355605937.846485</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>99864028.0</t>
+          <t>62765638.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>138609938.8</t>
+          <t>124126000.4</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>137834914.3</t>
+          <t>125231243.6</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>443270959.36</t>
+          <t>399636300.16</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>775024</t>
+          <t>-1105243</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-28391852.12934346</t>
+          <t>-28835218.6887616</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-28094189.88869017</t>
+          <t>-31273734.76556134</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>99864028</v>
+        <v>62765638</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>6.40</t>
+          <t>8.49</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6875,22 +6875,22 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>4.06</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6900,7 +6900,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>21.98</t>
+          <t>22.13</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>32.63</t>
+          <t>32.66</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>18032</t>
+          <t>18158</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6935,27 +6935,27 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>電子零組件業平上市</t>
+          <t>電子零組件業右上上市</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>88.6</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
+          <t>89.4</t>
+        </is>
+      </c>
+      <c r="CF15" t="inlineStr">
+        <is>
           <t>87.9</t>
         </is>
       </c>
-      <c r="CF15" t="inlineStr">
-        <is>
-          <t>85.9</t>
-        </is>
-      </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1638.11</t>
+          <t>1153.082</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7012,17 +7012,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-2.34</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-3.32</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7032,7 +7032,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-18.22</t>
+          <t>-19.16</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7097,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>7.92</t>
+          <t>5.57</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-2.40</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7118,12 +7118,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>1197</t>
+          <t>798</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7138,57 +7138,57 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-4.12</t>
+          <t>-3.74</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-4.10</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-6.67</t>
+          <t>-7.14</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>91.26</t>
+          <t>89.86</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>95.16</t>
+          <t>94.36</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>101.96</t>
+          <t>101.62</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>96.8</t>
+          <t>96.9</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-23.67</t>
+          <t>-27.21</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-2.86</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-132.15</t>
+          <t>-134.50</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7208,46 +7208,46 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>355969373.6659483</t>
+          <t>355605937.846485</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>144178661.0</t>
+          <t>99864028.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>146673374.0</t>
+          <t>138609938.8</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>149731355.7</t>
+          <t>137834914.3</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>454484548.46</t>
+          <t>443270959.36</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-3057981</t>
+          <t>775024</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-28445972.53673498</t>
+          <t>-28391852.12934346</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-26523446.49713525</t>
+          <t>-28094189.88869017</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>144178661</v>
+        <v>99864028</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>7.63</t>
+          <t>6.40</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7321,12 +7321,12 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>4.06</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>21.98</t>
+          <t>22.13</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>32.63</t>
+          <t>32.66</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>18032</t>
+          <t>18158</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7371,27 +7371,27 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>電子零組件業平上市</t>
+          <t>電子零組件業右上上市</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>89.9</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>85.9</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1631.485</t>
+          <t>1638.11</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7448,17 +7448,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-4.8</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-3.32</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-20.69</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7468,7 +7468,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-16.26</t>
+          <t>-18.22</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7533,17 +7533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>7.89</t>
+          <t>7.92</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-2.40</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7554,12 +7554,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>1197</t>
+          <t>798</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7569,62 +7569,62 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>13.16</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-3.30</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>-4.10</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-6.3</t>
+          <t>-6.67</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>5.78</t>
+          <t>5.33</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>92.66</t>
+          <t>91.26</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>95.84</t>
+          <t>95.16</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>102.28</t>
+          <t>101.96</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>96.69</t>
+          <t>96.8</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-16.84</t>
+          <t>-23.67</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-2.86</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-130.25</t>
+          <t>-132.15</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7644,46 +7644,46 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>355969373.6659483</t>
+          <t>355605937.846485</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>147034386.0</t>
+          <t>144178661.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>146439342.4</t>
+          <t>146673374.0</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>184645225.3</t>
+          <t>149731355.7</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>461884050.18</t>
+          <t>454484548.46</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-38205882</t>
+          <t>-3057981</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-28795522.72575311</t>
+          <t>-28445972.53673498</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-28080257.81287342</t>
+          <t>-26523446.49713525</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>147034386</v>
+        <v>144178661</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>10.21</t>
+          <t>7.63</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>4.06</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>21.98</t>
+          <t>22.13</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>32.63</t>
+          <t>32.66</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>18032</t>
+          <t>18158</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7807,27 +7807,27 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>電子零組件業平上市</t>
+          <t>電子零組件業右上上市</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>89.9</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>89.4</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-4.0</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1815.561</t>
+          <t>1631.485</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-6.43</t>
+          <t>-4.07</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-3.32</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-32.28</t>
+          <t>-20.69</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7904,7 +7904,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -7959,7 +7959,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-14.95</t>
+          <t>-16.26</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7969,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>8.78</t>
+          <t>7.89</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7990,12 +7990,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>1197</t>
+          <t>798</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -8005,62 +8005,62 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>15.79</t>
+          <t>13.16</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-3.30</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-3.32</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-6.05</t>
+          <t>-6.3</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>6.20</t>
+          <t>5.78</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>93.38</t>
+          <t>92.66</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>96.32</t>
+          <t>95.84</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>102.52</t>
+          <t>102.28</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>96.53</t>
+          <t>96.69</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-10.98</t>
+          <t>-16.84</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-128.98</t>
+          <t>-130.25</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -8080,46 +8080,46 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>355969373.6659483</t>
+          <t>355605937.846485</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>166787289.0</t>
+          <t>147034386.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>135964184.0</t>
+          <t>146439342.4</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>200767284.9</t>
+          <t>184645225.3</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>481289771.06</t>
+          <t>461884050.18</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-64803100</t>
+          <t>-38205882</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-28925570.89173124</t>
+          <t>-28795522.72575311</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-29607378.16346818</t>
+          <t>-28080257.81287342</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>166787289</v>
+        <v>147034386</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>11.93</t>
+          <t>10.21</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8183,22 +8183,22 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>4.06</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>21.98</t>
+          <t>22.13</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>32.63</t>
+          <t>32.66</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>18032</t>
+          <t>18158</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8243,27 +8243,27 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>電子零組件業平上市</t>
+          <t>電子零組件業右上上市</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>89.4</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1433.749</t>
+          <t>1815.561</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>94.7</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8320,17 +8320,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-10.76</t>
+          <t>-5.69</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-3.32</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-41.55</t>
+          <t>-32.28</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8340,7 +8340,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-11.50</t>
+          <t>-14.95</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>8.78</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8426,77 +8426,77 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>1197</t>
+          <t>798</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>39.47</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>28.29</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-5.8</t>
+          <t>-6.05</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>6.60</t>
+          <t>6.20</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>93.9</t>
+          <t>93.38</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>96.8</t>
+          <t>96.32</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>102.75</t>
+          <t>102.52</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>96.39</t>
+          <t>96.53</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-5.06</t>
+          <t>-10.98</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-128.18</t>
+          <t>-128.98</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8516,46 +8516,46 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>355969373.6659483</t>
+          <t>355605937.846485</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>135185330.0</t>
+          <t>166787289.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>126336486.8</t>
+          <t>135964184.0</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>216135889.2</t>
+          <t>200767284.9</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>501408648.9</t>
+          <t>481289771.06</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-89799402</t>
+          <t>-64803100</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-28801605.93323361</t>
+          <t>-28925570.89173124</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-32847954.76562259</t>
+          <t>-29607378.16346818</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>135185330</v>
+        <v>166787289</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>16.48</t>
+          <t>11.93</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8619,22 +8619,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>4.06</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>21.98</t>
+          <t>22.13</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>32.63</t>
+          <t>32.66</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>18032</t>
+          <t>18158</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8679,27 +8679,27 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>電子零組件業平上市</t>
+          <t>電子零組件業右上上市</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>95.3</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>94.7</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1479.927</t>
+          <t>1433.749</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8756,17 +8756,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-9.36</t>
+          <t>-9.99</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-3.32</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-38.14</t>
+          <t>-41.55</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8776,7 +8776,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-12.62</t>
+          <t>-11.50</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>7.15</t>
+          <t>6.93</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8862,77 +8862,77 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>1197</t>
+          <t>798</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>7.89</t>
+          <t>39.47</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>28.29</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-5.69</t>
+          <t>-5.8</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>6.60</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>93.86</t>
+          <t>93.9</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>97.05</t>
+          <t>96.8</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>102.91</t>
+          <t>102.75</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>96.17</t>
+          <t>96.39</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-11.98</t>
+          <t>-5.06</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-127.83</t>
+          <t>-128.18</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8952,46 +8952,46 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>355969373.6659483</t>
+          <t>355605937.846485</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>140181204.0</t>
+          <t>135185330.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>137059889.8</t>
+          <t>126336486.8</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>221562336.5</t>
+          <t>216135889.2</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>538168556.64</t>
+          <t>501408648.9</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-84502446</t>
+          <t>-89799402</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-28065906.14552652</t>
+          <t>-28801605.93323361</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-32918284.49135661</t>
+          <t>-32847954.76562259</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>140181204</v>
+        <v>135185330</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>15.01</t>
+          <t>16.48</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -9055,7 +9055,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -9065,12 +9065,12 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>4.06</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -9080,7 +9080,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>21.98</t>
+          <t>22.13</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>32.63</t>
+          <t>32.66</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>18032</t>
+          <t>18158</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9115,27 +9115,27 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>電子零組件業平上市</t>
+          <t>電子零組件業右上上市</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>95.3</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1504.164</t>
+          <t>1479.927</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9192,17 +9192,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-10.53</t>
+          <t>-8.59</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-3.32</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-34.56</t>
+          <t>-38.14</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9212,7 +9212,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-11.68</t>
+          <t>-12.62</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9277,17 +9277,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>7.27</t>
+          <t>7.15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9298,77 +9298,77 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>1197</t>
+          <t>798</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>7.89</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>19.17</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-3.11</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-5.57</t>
+          <t>-5.69</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>7.35</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>94.24</t>
+          <t>93.86</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>97.26</t>
+          <t>97.05</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>102.91</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>95.95</t>
+          <t>96.17</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-14.81</t>
+          <t>-11.98</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-126.99</t>
+          <t>-127.83</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9388,46 +9388,46 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>355969373.6659483</t>
+          <t>355605937.846485</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>143008503.0</t>
+          <t>140181204.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>152789337.4</t>
+          <t>137059889.8</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>233463581.9</t>
+          <t>221562336.5</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>553861277.88</t>
+          <t>538168556.64</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-80674244</t>
+          <t>-84502446</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-27183655.53719378</t>
+          <t>-28065906.14552652</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-32378374.72485676</t>
+          <t>-32918284.49135661</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>143008503</v>
+        <v>140181204</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>16.24</t>
+          <t>15.01</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9501,12 +9501,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>4.06</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>21.98</t>
+          <t>22.13</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>32.63</t>
+          <t>32.66</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>18032</t>
+          <t>18158</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9551,27 +9551,27 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>電子零組件業平上市</t>
+          <t>電子零組件業右上上市</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>96.5</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1012.26</t>
+          <t>1504.164</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>93.2</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9628,17 +9628,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-9.01</t>
+          <t>-9.76</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-3.32</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-18.35</t>
+          <t>-34.56</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9648,7 +9648,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-12.90</t>
+          <t>-11.68</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9713,17 +9713,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>7.27</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9734,77 +9734,77 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>1197</t>
+          <t>798</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>19.17</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-3.11</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-5.57</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>7.68</t>
+          <t>7.35</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>94.66</t>
+          <t>94.24</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>97.62</t>
+          <t>97.26</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>103.01</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>95.66</t>
+          <t>95.95</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-22.08</t>
+          <t>-14.81</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-125.99</t>
+          <t>-126.99</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9824,46 +9824,46 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>355969373.6659483</t>
+          <t>355605937.846485</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>94658594.0</t>
+          <t>143008503.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>222851108.2</t>
+          <t>152789337.4</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>272945780.2</t>
+          <t>233463581.9</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>561353465.26</t>
+          <t>553861277.88</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-50094672</t>
+          <t>-80674244</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-26239161.13943687</t>
+          <t>-27183655.53719378</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-30753629.42539778</t>
+          <t>-32378374.72485676</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>94658594</v>
+        <v>143008503</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>14.64</t>
+          <t>16.24</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>4.06</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>21.98</t>
+          <t>22.13</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>32.63</t>
+          <t>32.66</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>18032</t>
+          <t>18158</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9987,27 +9987,27 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>電子零組件業平上市</t>
+          <t>電子零組件業右上上市</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>93.7</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>95.3</t>
+          <t>96.5</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>92.8</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>93.2</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.96</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1267.489</t>
+          <t>1012.26</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>93.6</t>
+          <t>93.2</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -10064,17 +10064,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-9.47</t>
+          <t>-8.25</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-3.32</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-4.29</t>
+          <t>-18.35</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10084,7 +10084,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-12.52</t>
+          <t>-12.90</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10149,17 +10149,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>6.13</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10170,77 +10170,77 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>1197</t>
+          <t>798</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>22.33</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-3.03</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>-5.24</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>8.01</t>
+          <t>7.68</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>95.42</t>
+          <t>94.66</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>98.18</t>
+          <t>97.62</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>103.03</t>
+          <t>103.01</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>95.39</t>
+          <t>95.66</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-23.72</t>
+          <t>-22.08</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-2.28</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-1.77</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-124.56</t>
+          <t>-125.99</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10260,46 +10260,46 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>355969373.6659483</t>
+          <t>355605937.846485</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>118648803.0</t>
+          <t>94658594.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>265570385.8</t>
+          <t>222851108.2</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>277478761.0</t>
+          <t>272945780.2</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>570658631.0</t>
+          <t>561353465.26</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-11908375</t>
+          <t>-50094672</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-25418348.72380762</t>
+          <t>-26239161.13943687</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-22153873.41097793</t>
+          <t>-30753629.42539778</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>118648803</v>
+        <v>94658594</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>15.13</t>
+          <t>14.64</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>4.09</t>
+          <t>4.06</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>21.98</t>
+          <t>22.13</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>32.63</t>
+          <t>32.66</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>18032</t>
+          <t>18158</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10423,17 +10423,17 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>電子零組件業平上市</t>
+          <t>電子零組件業右上上市</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>93.7</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>95.3</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>93.6</t>
+          <t>93.2</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/電鍍材料.xlsx
+++ b/Result/checksun_type/電鍍材料.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>118.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>28.77</t>
+          <t>9.71</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,280 +1014,280 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>118</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>50.62</t>
+          <t>65.43</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>66.26</t>
+          <t>55.14</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.1</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>43.84</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
+          <t>43.44</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>43.92</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>45.19</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>41.21</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>-0.17</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>-0.29</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>2.77</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>-110.57</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>2025/11/19</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>28206.79083094556</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>5178.0</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>16692.8</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>15215.7</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>13519.76</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>1477</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>341.4652888065019</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>-1397.534335250723</t>
+        </is>
+      </c>
+      <c r="BD2" t="n">
+        <v>5178</v>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>49.9</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>2025/08/12</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>-12.63</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>匯鑽科</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>匯鑽科</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>0.78</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>-10.56465687102404</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>-13.69932964657055</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>7.80229574004913</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>價-量縮</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>2.33</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>2.58</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>6.59</t>
+        </is>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>8.25%</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>-14.21%</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>42.67</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>1935</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>加工業務99.90%、勞務0.10% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>匯鑽科-其他電子業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC2" t="inlineStr">
+        <is>
+          <t>其他電子業右下上櫃</t>
+        </is>
+      </c>
+      <c r="CD2" t="inlineStr">
+        <is>
           <t>43.45</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>43.97</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>45.12</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>34.76</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>-0.21</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>-0.32</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>2.77</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>-111.66</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>2025/11/19</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>28236.11621233859</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>6625.0</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>21302.2</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>16542.7</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>13576.72</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>4759</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>657.6470386350882</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>-529.1355843768179</t>
-        </is>
-      </c>
-      <c r="BD2" t="n">
-        <v>6625</v>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>49.9</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>2025/08/12</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>-13.83</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>匯鑽科</t>
-        </is>
-      </c>
-      <c r="BJ2" t="inlineStr">
-        <is>
-          <t>匯鑽科</t>
-        </is>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>0.77</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
-        <is>
-          <t>-10.56465687102404</t>
-        </is>
-      </c>
-      <c r="BO2" t="inlineStr">
-        <is>
-          <t>-13.69932964657055</t>
-        </is>
-      </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>7.80229574004913</t>
-        </is>
-      </c>
-      <c r="BQ2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR2" t="inlineStr">
-        <is>
-          <t>價跌量縮</t>
-        </is>
-      </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
-      </c>
-      <c r="BT2" t="inlineStr">
-        <is>
-          <t>2.61</t>
-        </is>
-      </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>6.59</t>
-        </is>
-      </c>
-      <c r="BV2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BW2" t="inlineStr">
-        <is>
-          <t>8.25%</t>
-        </is>
-      </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>-14.21%</t>
-        </is>
-      </c>
-      <c r="BY2" t="inlineStr">
-        <is>
-          <t>42.08</t>
-        </is>
-      </c>
-      <c r="BZ2" t="inlineStr">
-        <is>
-          <t>1909</t>
-        </is>
-      </c>
-      <c r="CA2" t="inlineStr">
-        <is>
-          <t>加工業務99.90%、勞務0.10% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB2" t="inlineStr">
-        <is>
-          <t>匯鑽科-其他電子業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>其他電子業右下上櫃</t>
-        </is>
-      </c>
-      <c r="CD2" t="inlineStr">
-        <is>
-          <t>43.1</t>
-        </is>
-      </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>42.8</t>
+          <t>43.45</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-4.49</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>42.95</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>20.84</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>5.89</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,77 +1450,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>118</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>49.38</t>
+          <t>50.62</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>82.72</t>
+          <t>66.26</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>43.71</t>
+          <t>43.84</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.45</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>44.03</t>
+          <t>43.97</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>45.06</t>
+          <t>45.12</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>44.24</t>
+          <t>34.76</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-112.67</t>
+          <t>-111.66</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>28236.11621233859</t>
+          <t>28206.79083094556</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>10460.0</t>
+          <t>6625.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>23067.8</t>
+          <t>21302.2</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>19089.8</t>
+          <t>16542.7</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>13602.9</t>
+          <t>13576.72</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>3978</t>
+          <t>4759</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>873.4256973645256</t>
+          <t>657.6470386350882</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>575.296044885079</t>
+          <t>-529.1355843768179</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>10460</v>
+        <v>6625</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-13.93</t>
+          <t>-13.83</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1643,22 +1643,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>42.08</t>
+          <t>42.67</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1909</t>
+          <t>1935</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>42.8</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>42.95</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>670.0</t>
+          <t>240.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>44.95</t>
+          <t>42.95</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-4.53</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>24.67</t>
+          <t>20.84</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16.44</t>
+          <t>5.89</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,77 +1886,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>118</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>98.77</t>
+          <t>49.38</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>94.23</t>
+          <t>82.72</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>43.31</t>
+          <t>43.71</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>43.58</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>44.03</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>45.01</t>
+          <t>45.06</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>56.72</t>
+          <t>44.24</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-114.07</t>
+          <t>-112.67</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>28236.11621233859</t>
+          <t>28206.79083094556</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>30506.0</t>
+          <t>10460.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>23927.2</t>
+          <t>23067.8</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>19193.0</t>
+          <t>19089.8</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>13522.88</t>
+          <t>13602.9</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>4734</t>
+          <t>3978</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>927.631088724425</t>
+          <t>873.4256973645256</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>1721.616370799031</t>
+          <t>575.296044885079</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>30506</v>
+        <v>10460</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-9.92</t>
+          <t>-13.93</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2079,22 +2079,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>42.08</t>
+          <t>42.67</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1909</t>
+          <t>1935</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>46.55</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>44.95</t>
+          <t>42.95</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>685.0</t>
+          <t>670.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>44.95</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,102 +2216,102 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-4.65</t>
+          <t>-3.1</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
+          <t>24.67</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>-95.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-10-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2025-08-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2025-08-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>45.6</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>44.45</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>52.5</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>47.6</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>1.12</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
           <t>-4.20</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>-95.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2025-10-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2025-10-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-08-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-08-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>45.6</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>44.45</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>52.5</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>47.6</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>1.24</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>-4.20</t>
-        </is>
-      </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16.81</t>
+          <t>16.44</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,280 +2322,280 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>118</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>98.77</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>75.04</t>
+          <t>94.23</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>42.73999999999999</t>
+          <t>43.31</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>43.61</t>
+          <t>43.58</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>44.12</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
+          <t>45.01</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>56.72</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>-0.17</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>-0.39</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>2.77</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>-114.07</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>2025/11/19</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>28206.79083094556</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>30506.0</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>23927.2</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>19193.0</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>13522.88</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>4734</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>927.631088724425</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>1721.616370799031</t>
+        </is>
+      </c>
+      <c r="BD5" t="n">
+        <v>30506</v>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>49.9</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>2025/08/12</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>-9.92</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>匯鑽科</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>匯鑽科</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>0.78</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
+          <t>-10.56465687102404</t>
+        </is>
+      </c>
+      <c r="BO5" t="inlineStr">
+        <is>
+          <t>-13.69932964657055</t>
+        </is>
+      </c>
+      <c r="BP5" t="inlineStr">
+        <is>
+          <t>7.80229574004913</t>
+        </is>
+      </c>
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS5" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="BT5" t="inlineStr">
+        <is>
+          <t>2.58</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
+          <t>6.59</t>
+        </is>
+      </c>
+      <c r="BV5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
+          <t>8.25%</t>
+        </is>
+      </c>
+      <c r="BX5" t="inlineStr">
+        <is>
+          <t>-14.21%</t>
+        </is>
+      </c>
+      <c r="BY5" t="inlineStr">
+        <is>
+          <t>42.67</t>
+        </is>
+      </c>
+      <c r="BZ5" t="inlineStr">
+        <is>
+          <t>1935</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
+          <t>加工業務99.90%、勞務0.10% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>匯鑽科-其他電子業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC5" t="inlineStr">
+        <is>
+          <t>其他電子業右下上櫃</t>
+        </is>
+      </c>
+      <c r="CD5" t="inlineStr">
+        <is>
+          <t>45.5</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
+          <t>46.55</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
+          <t>44.8</t>
+        </is>
+      </c>
+      <c r="CG5" t="inlineStr">
+        <is>
           <t>44.95</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>24.64</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>-0.34</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>-0.45</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>2.77</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr">
-        <is>
-          <t>-116.07</t>
-        </is>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>2025/11/19</t>
-        </is>
-      </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>28236.11621233859</t>
-        </is>
-      </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>30695.0</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>18788.8</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>19613.1</t>
-        </is>
-      </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>13049.74</t>
-        </is>
-      </c>
-      <c r="BA5" t="inlineStr">
-        <is>
-          <t>-824</t>
-        </is>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>783.2701283472239</t>
-        </is>
-      </c>
-      <c r="BC5" t="inlineStr">
-        <is>
-          <t>1149.944823147569</t>
-        </is>
-      </c>
-      <c r="BD5" t="n">
-        <v>30695</v>
-      </c>
-      <c r="BE5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>49.9</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>2025/08/12</t>
-        </is>
-      </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>-9.82</t>
-        </is>
-      </c>
-      <c r="BI5" t="inlineStr">
-        <is>
-          <t>匯鑽科</t>
-        </is>
-      </c>
-      <c r="BJ5" t="inlineStr">
-        <is>
-          <t>匯鑽科</t>
-        </is>
-      </c>
-      <c r="BK5" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BL5" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM5" t="inlineStr">
-        <is>
-          <t>0.77</t>
-        </is>
-      </c>
-      <c r="BN5" t="inlineStr">
-        <is>
-          <t>-10.56465687102404</t>
-        </is>
-      </c>
-      <c r="BO5" t="inlineStr">
-        <is>
-          <t>-13.69932964657055</t>
-        </is>
-      </c>
-      <c r="BP5" t="inlineStr">
-        <is>
-          <t>7.80229574004913</t>
-        </is>
-      </c>
-      <c r="BQ5" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
-        </is>
-      </c>
-      <c r="BR5" t="inlineStr">
-        <is>
-          <t>價漲量增</t>
-        </is>
-      </c>
-      <c r="BS5" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
-      </c>
-      <c r="BT5" t="inlineStr">
-        <is>
-          <t>2.61</t>
-        </is>
-      </c>
-      <c r="BU5" t="inlineStr">
-        <is>
-          <t>6.59</t>
-        </is>
-      </c>
-      <c r="BV5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BW5" t="inlineStr">
-        <is>
-          <t>8.25%</t>
-        </is>
-      </c>
-      <c r="BX5" t="inlineStr">
-        <is>
-          <t>-14.21%</t>
-        </is>
-      </c>
-      <c r="BY5" t="inlineStr">
-        <is>
-          <t>42.08</t>
-        </is>
-      </c>
-      <c r="BZ5" t="inlineStr">
-        <is>
-          <t>1909</t>
-        </is>
-      </c>
-      <c r="CA5" t="inlineStr">
-        <is>
-          <t>加工業務99.90%、勞務0.10% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB5" t="inlineStr">
-        <is>
-          <t>匯鑽科-其他電子業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC5" t="inlineStr">
-        <is>
-          <t>其他電子業右下上櫃</t>
-        </is>
-      </c>
-      <c r="CD5" t="inlineStr">
-        <is>
-          <t>43.55</t>
-        </is>
-      </c>
-      <c r="CE5" t="inlineStr">
-        <is>
-          <t>45.55</t>
-        </is>
-      </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>43.3</t>
-        </is>
-      </c>
-      <c r="CG5" t="inlineStr">
-        <is>
-          <t>45.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>655.0</t>
+          <t>685.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-32.14</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>16.81</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,77 +2758,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>118</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>83.93</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>75.04</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>42.22000000000001</t>
+          <t>42.73999999999999</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>43.61</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>44.15</t>
+          <t>44.12</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>44.89</t>
+          <t>44.95</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-16.05</t>
+          <t>24.64</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-117.06</t>
+          <t>-116.07</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>28236.11621233859</t>
+          <t>28206.79083094556</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>28225.0</t>
+          <t>30695.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>13738.6</t>
+          <t>18788.8</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>20246.9</t>
+          <t>19613.1</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>12733.2</t>
+          <t>13049.74</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-6508</t>
+          <t>-824</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>716.6020020198885</t>
+          <t>783.2701283472239</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>271.9517256759318</t>
+          <t>1149.944823147569</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>28225</v>
+        <v>30695</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-13.23</t>
+          <t>-9.82</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2951,22 +2951,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>42.08</t>
+          <t>42.67</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>1909</t>
+          <t>1935</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>42.35</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>369.0</t>
+          <t>655.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>42.35</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-43.86</t>
+          <t>-32.14</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-4.72</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>9.06</t>
+          <t>16.07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,77 +3194,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>118</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>41.18</t>
+          <t>83.93</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>14.84</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>42.22000000000001</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>43.53</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>44.23</t>
+          <t>44.15</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>44.87</t>
+          <t>44.89</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-40.91</t>
+          <t>-16.05</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-116.38</t>
+          <t>-117.06</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>28236.11621233859</t>
+          <t>28206.79083094556</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>15453.0</t>
+          <t>28225.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>11783.2</t>
+          <t>13738.6</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>20989.4</t>
+          <t>20246.9</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>12346.96</t>
+          <t>12733.2</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-9206</t>
+          <t>-6508</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>797.4475068096988</t>
+          <t>716.6020020198885</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-727.3938323434086</t>
+          <t>271.9517256759318</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>15453</v>
+        <v>28225</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-15.13</t>
+          <t>-13.23</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3387,7 +3387,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>42.08</t>
+          <t>42.67</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>1909</t>
+          <t>1935</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>42.7</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>42.35</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>42.35</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>358.0</t>
+          <t>369.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>42.35</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-27.59</t>
+          <t>-43.86</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-7.87</t>
+          <t>-4.72</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>8.79</t>
+          <t>9.06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,77 +3630,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>118</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>41.18</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>14.84</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-3.31</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>42.04000000000001</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>43.48</t>
+          <t>43.53</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>44.31</t>
+          <t>44.23</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>44.85</t>
+          <t>44.87</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-59.38</t>
+          <t>-40.91</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-114.70</t>
+          <t>-116.38</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>28236.11621233859</t>
+          <t>28206.79083094556</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>14757.0</t>
+          <t>15453.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>15111.8</t>
+          <t>11783.2</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>20870.2</t>
+          <t>20989.4</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>12172.68</t>
+          <t>12346.96</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-5758</t>
+          <t>-9206</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>1074.691386655718</t>
+          <t>797.4475068096988</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-760.6234212159197</t>
+          <t>-727.3938323434086</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>14757</v>
+        <v>15453</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-17.94</t>
+          <t>-15.13</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3828,17 +3828,17 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>42.08</t>
+          <t>42.67</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>1909</t>
+          <t>1935</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,12 +3888,12 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>42.45</t>
+          <t>42.7</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
@@ -3903,7 +3903,7 @@
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>42.35</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>358.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>6.08</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-29.63</t>
+          <t>-27.59</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-5.29</t>
+          <t>-7.87</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>8.79</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,17 +4066,17 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>118</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -4086,57 +4086,57 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-3.31</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>42.55</t>
+          <t>42.04000000000001</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>43.48</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>44.42</t>
+          <t>44.31</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>44.84</t>
+          <t>44.85</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-46.96</t>
+          <t>-59.38</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-112.52</t>
+          <t>-114.70</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>28236.11621233859</t>
+          <t>28206.79083094556</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>4814.0</t>
+          <t>14757.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>14458.8</t>
+          <t>15111.8</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>20545.5</t>
+          <t>20870.2</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>12162.98</t>
+          <t>12172.68</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-6086</t>
+          <t>-5758</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>1408.384988086925</t>
+          <t>1074.691386655718</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-706.357711704648</t>
+          <t>-760.6234212159197</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>4814</v>
+        <v>14757</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-15.63</t>
+          <t>-17.94</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4264,17 +4264,17 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>42.08</t>
+          <t>42.67</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>1909</t>
+          <t>1935</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
+          <t>42.1</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
           <t>42.45</t>
         </is>
       </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>42.7</t>
-        </is>
-      </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>41.95</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>114.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>42.4</t>
+          <t>42.1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-7.97</t>
+          <t>-29.63</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-4.61</t>
+          <t>-5.29</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,77 +4502,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>118</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>42.88</t>
+          <t>42.55</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>43.46</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>44.54</t>
+          <t>44.42</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>44.81</t>
+          <t>44.84</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-44.19</t>
+          <t>-46.96</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-111.05</t>
+          <t>-112.52</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>28236.11621233859</t>
+          <t>28206.79083094556</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>5444.0</t>
+          <t>4814.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>20437.4</t>
+          <t>14458.8</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>22206.9</t>
+          <t>20545.5</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>13085.46</t>
+          <t>12162.98</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-1769</t>
+          <t>-6086</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>1792.883660776302</t>
+          <t>1408.384988086925</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>461.7132201580425</t>
+          <t>-706.357711704648</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>5444</v>
+        <v>4814</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-15.03</t>
+          <t>-15.63</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4705,12 +4705,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>42.08</t>
+          <t>42.67</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>1909</t>
+          <t>1935</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>42.45</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>42.7</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>41.95</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>42.4</t>
+          <t>42.1</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>441.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>42.4</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>15.49</t>
+          <t>-7.97</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-5.51</t>
+          <t>-4.61</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10.82</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,47 +4938,47 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>118</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.33</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>43.27</t>
+          <t>42.88</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -4988,27 +4988,27 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>44.68</t>
+          <t>44.54</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>44.79</t>
+          <t>44.81</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-38.94</t>
+          <t>-44.19</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.27</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-109.83</t>
+          <t>-111.05</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>28236.11621233859</t>
+          <t>28206.79083094556</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>18448.0</t>
+          <t>5444.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>26755.2</t>
+          <t>20437.4</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>23167.0</t>
+          <t>22206.9</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>14024.46</t>
+          <t>13085.46</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>3588</t>
+          <t>-1769</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>2034.914649979622</t>
+          <t>1792.883660776302</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>2046.396222099105</t>
+          <t>461.7132201580425</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>18448</v>
+        <v>5444</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-15.83</t>
+          <t>-15.03</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>42.08</t>
+          <t>42.67</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1909</t>
+          <t>1935</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>42.85</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>42.4</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>750.0</t>
+          <t>441.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>42.75</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>30.99</t>
+          <t>15.49</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-3.82</t>
+          <t>-5.51</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>18.40</t>
+          <t>10.82</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,12 +5374,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>118</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5394,57 +5394,57 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>43.87</t>
+          <t>43.27</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>43.52</t>
+          <t>43.46</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>44.87</t>
+          <t>44.68</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>44.77</t>
+          <t>44.79</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-38.94</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>-0.27</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-108.87</t>
+          <t>-109.83</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>28236.11621233859</t>
+          <t>28206.79083094556</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>32096.0</t>
+          <t>18448.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>30195.6</t>
+          <t>26755.2</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>23051.9</t>
+          <t>23167.0</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>14111.94</t>
+          <t>14024.46</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>7143</t>
+          <t>3588</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>2032.827091412444</t>
+          <t>2034.914649979622</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>2843.85778836851</t>
+          <t>2046.396222099105</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>32096</v>
+        <v>18448</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-14.33</t>
+          <t>-15.83</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>42.08</t>
+          <t>42.67</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1909</t>
+          <t>1935</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>42.85</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>42.75</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>797.916</t>
+          <t>557.755</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>86.1</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-21.02</t>
+          <t>-31.49</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-19.53</t>
+          <t>-19.07</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5810,157 +5810,157 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>558</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
+          <t>11.96</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>6.16</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>-5.79</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>-7.52</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>86.58</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>91.9</t>
+        </is>
+      </c>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>99.37</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>97.25</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>-15.28</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>-3.52</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>-3.06</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>7.19</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr">
+        <is>
+          <t>-142.50</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>2025/07/15</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>355200475.5730659</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>48395514.0</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>76417304.6</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>111545339.3</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>319430807.84</t>
+        </is>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>-35128034</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>-29590721.02109627</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>-31725831.12686187</t>
+        </is>
+      </c>
+      <c r="BD13" t="n">
+        <v>48395514</v>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
+          <t>81.3</t>
+        </is>
+      </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>2025/07/28</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
           <t>6.52</t>
         </is>
       </c>
-      <c r="AG13" t="inlineStr">
-        <is>
-          <t>9.08</t>
-        </is>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>-0.76</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>-6.01</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>-7.68</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>2.91</t>
-        </is>
-      </c>
-      <c r="AL13" t="inlineStr">
-        <is>
-          <t>86.75999999999999</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>92.31</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>99.99</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>97.16</t>
-        </is>
-      </c>
-      <c r="AP13" t="inlineStr">
-        <is>
-          <t>-20.19</t>
-        </is>
-      </c>
-      <c r="AQ13" t="inlineStr">
-        <is>
-          <t>-3.53</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>-2.94</t>
-        </is>
-      </c>
-      <c r="AS13" t="inlineStr">
-        <is>
-          <t>7.19</t>
-        </is>
-      </c>
-      <c r="AT13" t="inlineStr">
-        <is>
-          <t>-140.87</t>
-        </is>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>2025/07/15</t>
-        </is>
-      </c>
-      <c r="AV13" t="inlineStr">
-        <is>
-          <t>355605937.846485</t>
-        </is>
-      </c>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>68436405.0</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>95573934.0</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>121006638.2</t>
-        </is>
-      </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>336619552.5</t>
-        </is>
-      </c>
-      <c r="BA13" t="inlineStr">
-        <is>
-          <t>-25432704</t>
-        </is>
-      </c>
-      <c r="BB13" t="inlineStr">
-        <is>
-          <t>-29202519.18368434</t>
-        </is>
-      </c>
-      <c r="BC13" t="inlineStr">
-        <is>
-          <t>-30467135.53374588</t>
-        </is>
-      </c>
-      <c r="BD13" t="n">
-        <v>68436405</v>
-      </c>
-      <c r="BE13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF13" t="inlineStr">
-        <is>
-          <t>81.3</t>
-        </is>
-      </c>
-      <c r="BG13" t="inlineStr">
-        <is>
-          <t>2025/07/28</t>
-        </is>
-      </c>
-      <c r="BH13" t="inlineStr">
-        <is>
-          <t>5.90</t>
-        </is>
-      </c>
       <c r="BI13" t="inlineStr">
         <is>
           <t>鉅祥</t>
@@ -6003,7 +6003,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>22.13</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>32.66</t>
+          <t>33.24</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>18158</t>
+          <t>18264</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6068,22 +6068,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>85.1</t>
+          <t>85.9</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>86.1</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-3.11</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1197.387</t>
+          <t>797.916</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>86.1</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6140,17 +6140,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-9.98</t>
+          <t>-21.02</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-20.09</t>
+          <t>-19.53</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6225,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>5.79</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6246,77 +6246,77 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>558</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>6.91</t>
+          <t>9.08</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-5.99</t>
+          <t>-6.01</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-7.53</t>
+          <t>-7.68</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>87.46000000000001</t>
+          <t>86.75999999999999</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>93.03</t>
+          <t>92.31</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>100.61</t>
+          <t>99.99</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>97.09</t>
+          <t>97.16</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-23.35</t>
+          <t>-20.19</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>-3.53</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-138.81</t>
+          <t>-140.87</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6336,46 +6336,46 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>355605937.846485</t>
+          <t>355200475.5730659</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>102624938.0</t>
+          <t>68436405.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>111293530.2</t>
+          <t>95573934.0</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>123628857.1</t>
+          <t>121006638.2</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>366752945.54</t>
+          <t>336619552.5</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-12335326</t>
+          <t>-25432704</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-28972588.9382186</t>
+          <t>-29202519.18368434</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-29728125.31023213</t>
+          <t>-30467135.53374588</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>102624938</v>
+        <v>68436405</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>5.17</t>
+          <t>5.90</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6449,12 +6449,12 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>22.13</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>32.66</t>
+          <t>33.24</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>18158</t>
+          <t>18264</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6504,22 +6504,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>86.1</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>-3.11</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>710.084</t>
+          <t>1197.387</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6576,17 +6576,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-9.98</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-17.57</t>
+          <t>-20.09</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>5.79</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6682,17 +6682,17 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>558</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>20.73</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
@@ -6702,57 +6702,57 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-5.54</t>
+          <t>-5.99</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-7.34</t>
+          <t>-7.53</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>88.56</t>
+          <t>87.46000000000001</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>93.75</t>
+          <t>93.03</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>101.18</t>
+          <t>100.61</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>97.04</t>
+          <t>97.09</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-22.39</t>
+          <t>-23.35</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-136.55</t>
+          <t>-138.81</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6772,46 +6772,46 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>355605937.846485</t>
+          <t>355200475.5730659</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>62765638.0</t>
+          <t>102624938.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>124126000.4</t>
+          <t>111293530.2</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>125231243.6</t>
+          <t>123628857.1</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>399636300.16</t>
+          <t>366752945.54</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-1105243</t>
+          <t>-12335326</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-28835218.6887616</t>
+          <t>-28972588.9382186</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-31273734.76556134</t>
+          <t>-29728125.31023213</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>62765638</v>
+        <v>102624938</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>8.49</t>
+          <t>5.17</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6875,22 +6875,22 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6900,7 +6900,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>22.13</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>32.66</t>
+          <t>33.24</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>18158</t>
+          <t>18264</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6940,22 +6940,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>89.4</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1153.082</t>
+          <t>710.084</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7012,17 +7012,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-19.16</t>
+          <t>-17.57</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7097,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7118,77 +7118,77 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>558</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.73</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.91</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-3.74</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-5.54</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-7.14</t>
+          <t>-7.34</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>89.86</t>
+          <t>88.56</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>94.36</t>
+          <t>93.75</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>101.62</t>
+          <t>101.18</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>96.9</t>
+          <t>97.04</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-27.21</t>
+          <t>-22.39</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-2.48</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-134.50</t>
+          <t>-136.55</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7208,46 +7208,46 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>355605937.846485</t>
+          <t>355200475.5730659</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>99864028.0</t>
+          <t>62765638.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>138609938.8</t>
+          <t>124126000.4</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>137834914.3</t>
+          <t>125231243.6</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>443270959.36</t>
+          <t>399636300.16</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>775024</t>
+          <t>-1105243</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-28391852.12934346</t>
+          <t>-28835218.6887616</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-28094189.88869017</t>
+          <t>-31273734.76556134</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>99864028</v>
+        <v>62765638</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>6.40</t>
+          <t>8.49</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7311,22 +7311,22 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>22.13</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>32.66</t>
+          <t>33.24</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>18158</t>
+          <t>18264</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7376,22 +7376,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>88.6</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
+          <t>89.4</t>
+        </is>
+      </c>
+      <c r="CF16" t="inlineStr">
+        <is>
           <t>87.9</t>
         </is>
       </c>
-      <c r="CF16" t="inlineStr">
-        <is>
-          <t>85.9</t>
-        </is>
-      </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1638.11</t>
+          <t>1153.082</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7448,17 +7448,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-18.22</t>
+          <t>-19.16</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7533,17 +7533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>7.92</t>
+          <t>5.57</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-2.40</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7554,12 +7554,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>558</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7574,57 +7574,57 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-4.12</t>
+          <t>-3.74</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-4.10</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-6.67</t>
+          <t>-7.14</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>91.26</t>
+          <t>89.86</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>95.16</t>
+          <t>94.36</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>101.96</t>
+          <t>101.62</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>96.8</t>
+          <t>96.9</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-23.67</t>
+          <t>-27.21</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-2.86</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-132.15</t>
+          <t>-134.50</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7644,46 +7644,46 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>355605937.846485</t>
+          <t>355200475.5730659</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>144178661.0</t>
+          <t>99864028.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>146673374.0</t>
+          <t>138609938.8</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>149731355.7</t>
+          <t>137834914.3</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>454484548.46</t>
+          <t>443270959.36</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-3057981</t>
+          <t>775024</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-28445972.53673498</t>
+          <t>-28391852.12934346</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-26523446.49713525</t>
+          <t>-28094189.88869017</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>144178661</v>
+        <v>99864028</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>7.63</t>
+          <t>6.40</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>22.13</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>32.66</t>
+          <t>33.24</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>18158</t>
+          <t>18264</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7812,22 +7812,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>89.9</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>85.9</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1631.485</t>
+          <t>1638.11</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-4.07</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-20.69</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7959,7 +7959,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-16.26</t>
+          <t>-18.22</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7969,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>7.89</t>
+          <t>7.92</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-2.40</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7990,12 +7990,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>558</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -8005,62 +8005,62 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>13.16</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-3.30</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>-4.10</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-6.3</t>
+          <t>-6.67</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>5.78</t>
+          <t>5.33</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>92.66</t>
+          <t>91.26</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>95.84</t>
+          <t>95.16</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>102.28</t>
+          <t>101.96</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>96.69</t>
+          <t>96.8</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-16.84</t>
+          <t>-23.67</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-2.86</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-130.25</t>
+          <t>-132.15</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -8080,46 +8080,46 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>355605937.846485</t>
+          <t>355200475.5730659</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>147034386.0</t>
+          <t>144178661.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>146439342.4</t>
+          <t>146673374.0</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>184645225.3</t>
+          <t>149731355.7</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>461884050.18</t>
+          <t>454484548.46</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-38205882</t>
+          <t>-3057981</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-28795522.72575311</t>
+          <t>-28445972.53673498</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-28080257.81287342</t>
+          <t>-26523446.49713525</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>147034386</v>
+        <v>144178661</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>10.21</t>
+          <t>7.63</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8183,7 +8183,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>22.13</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>32.66</t>
+          <t>33.24</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>18158</t>
+          <t>18264</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8248,22 +8248,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>89.9</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>89.4</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-4.0</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1815.561</t>
+          <t>1631.485</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8320,17 +8320,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-5.69</t>
+          <t>-3.46</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-32.28</t>
+          <t>-20.69</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-14.95</t>
+          <t>-16.26</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>8.78</t>
+          <t>7.89</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8426,12 +8426,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>558</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8441,62 +8441,62 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>15.79</t>
+          <t>13.16</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-3.30</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-3.32</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-6.05</t>
+          <t>-6.3</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>6.20</t>
+          <t>5.78</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>93.38</t>
+          <t>92.66</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>96.32</t>
+          <t>95.84</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>102.52</t>
+          <t>102.28</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>96.53</t>
+          <t>96.69</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-10.98</t>
+          <t>-16.84</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-128.98</t>
+          <t>-130.25</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8516,46 +8516,46 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>355605937.846485</t>
+          <t>355200475.5730659</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>166787289.0</t>
+          <t>147034386.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>135964184.0</t>
+          <t>146439342.4</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>200767284.9</t>
+          <t>184645225.3</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>481289771.06</t>
+          <t>461884050.18</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-64803100</t>
+          <t>-38205882</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-28925570.89173124</t>
+          <t>-28795522.72575311</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-29607378.16346818</t>
+          <t>-28080257.81287342</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>166787289</v>
+        <v>147034386</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>11.93</t>
+          <t>10.21</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8619,22 +8619,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>22.13</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>32.66</t>
+          <t>33.24</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>18158</t>
+          <t>18264</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8684,22 +8684,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>89.4</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1433.749</t>
+          <t>1815.561</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>94.7</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8756,17 +8756,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-9.99</t>
+          <t>-5.08</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-41.55</t>
+          <t>-32.28</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-11.50</t>
+          <t>-14.95</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>8.78</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8862,77 +8862,77 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>558</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>39.47</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>28.29</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-5.8</t>
+          <t>-6.05</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>6.60</t>
+          <t>6.20</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>93.9</t>
+          <t>93.38</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>96.8</t>
+          <t>96.32</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>102.75</t>
+          <t>102.52</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>96.39</t>
+          <t>96.53</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-5.06</t>
+          <t>-10.98</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-128.18</t>
+          <t>-128.98</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8952,46 +8952,46 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>355605937.846485</t>
+          <t>355200475.5730659</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>135185330.0</t>
+          <t>166787289.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>126336486.8</t>
+          <t>135964184.0</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>216135889.2</t>
+          <t>200767284.9</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>501408648.9</t>
+          <t>481289771.06</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-89799402</t>
+          <t>-64803100</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-28801605.93323361</t>
+          <t>-28925570.89173124</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-32847954.76562259</t>
+          <t>-29607378.16346818</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>135185330</v>
+        <v>166787289</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>16.48</t>
+          <t>11.93</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -9055,22 +9055,22 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -9080,7 +9080,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>22.13</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>32.66</t>
+          <t>33.24</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>18158</t>
+          <t>18264</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9120,22 +9120,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>95.3</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>94.7</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1479.927</t>
+          <t>1433.749</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9192,17 +9192,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-8.59</t>
+          <t>-9.35</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-38.14</t>
+          <t>-41.55</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-12.62</t>
+          <t>-11.50</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9277,17 +9277,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>7.15</t>
+          <t>6.93</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9298,77 +9298,77 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>558</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>7.89</t>
+          <t>39.47</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>28.29</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-5.69</t>
+          <t>-5.8</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>6.60</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>93.86</t>
+          <t>93.9</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>97.05</t>
+          <t>96.8</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>102.91</t>
+          <t>102.75</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>96.17</t>
+          <t>96.39</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-11.98</t>
+          <t>-5.06</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-2.13</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-127.83</t>
+          <t>-128.18</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9388,46 +9388,46 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>355605937.846485</t>
+          <t>355200475.5730659</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>140181204.0</t>
+          <t>135185330.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>137059889.8</t>
+          <t>126336486.8</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>221562336.5</t>
+          <t>216135889.2</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>538168556.64</t>
+          <t>501408648.9</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-84502446</t>
+          <t>-89799402</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-28065906.14552652</t>
+          <t>-28801605.93323361</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-32918284.49135661</t>
+          <t>-32847954.76562259</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>140181204</v>
+        <v>135185330</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>15.01</t>
+          <t>16.48</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9501,12 +9501,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>22.13</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>32.66</t>
+          <t>33.24</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>18158</t>
+          <t>18264</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9556,22 +9556,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>95.3</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>94.7</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1504.164</t>
+          <t>1479.927</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9628,17 +9628,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-9.76</t>
+          <t>-7.97</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-34.56</t>
+          <t>-38.14</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-11.68</t>
+          <t>-12.62</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9713,17 +9713,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>7.27</t>
+          <t>7.15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-0.83</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9734,77 +9734,77 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>558</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>7.89</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>19.17</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-3.11</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-5.57</t>
+          <t>-5.69</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>7.35</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>94.24</t>
+          <t>93.86</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>97.26</t>
+          <t>97.05</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>102.91</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>95.95</t>
+          <t>96.17</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-14.81</t>
+          <t>-11.98</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-1.94</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-126.99</t>
+          <t>-127.83</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9824,46 +9824,46 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>355605937.846485</t>
+          <t>355200475.5730659</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>143008503.0</t>
+          <t>140181204.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>152789337.4</t>
+          <t>137059889.8</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>233463581.9</t>
+          <t>221562336.5</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>553861277.88</t>
+          <t>538168556.64</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-80674244</t>
+          <t>-84502446</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-27183655.53719378</t>
+          <t>-28065906.14552652</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-32378374.72485676</t>
+          <t>-32918284.49135661</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>143008503</v>
+        <v>140181204</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>16.24</t>
+          <t>15.01</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>22.13</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>32.66</t>
+          <t>33.24</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>18158</t>
+          <t>18264</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9992,22 +9992,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>96.5</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1012.26</t>
+          <t>1504.164</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>93.2</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -10064,17 +10064,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-8.25</t>
+          <t>-9.12</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-18.35</t>
+          <t>-34.56</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-12.90</t>
+          <t>-11.68</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10149,17 +10149,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>7.27</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>-0.83</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10170,77 +10170,77 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>558</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>19.17</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-3.03</t>
+          <t>-3.11</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-5.24</t>
+          <t>-5.57</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>7.68</t>
+          <t>7.35</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>94.66</t>
+          <t>94.24</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>97.62</t>
+          <t>97.26</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>103.01</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>95.66</t>
+          <t>95.95</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-22.08</t>
+          <t>-14.81</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-2.28</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-1.94</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-125.99</t>
+          <t>-126.99</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10260,46 +10260,46 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>355605937.846485</t>
+          <t>355200475.5730659</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>94658594.0</t>
+          <t>143008503.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>222851108.2</t>
+          <t>152789337.4</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>272945780.2</t>
+          <t>233463581.9</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>561353465.26</t>
+          <t>553861277.88</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-50094672</t>
+          <t>-80674244</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-26239161.13943687</t>
+          <t>-27183655.53719378</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-30753629.42539778</t>
+          <t>-32378374.72485676</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>94658594</v>
+        <v>143008503</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>14.64</t>
+          <t>16.24</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>4.04</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>22.13</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>32.66</t>
+          <t>33.24</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>18158</t>
+          <t>18264</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10428,22 +10428,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>93.7</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>95.3</t>
+          <t>96.5</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>92.8</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>93.2</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/電鍍材料.xlsx
+++ b/Result/checksun_type/電鍍材料.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>43.92</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>43.47</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>43.94</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>43.47</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>43.94</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>13560.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>13265.8</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>13265.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>16027.3</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>13521.82</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>13521.82</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-1341.825102481189</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>13560</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>13560.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>43.9</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>43.44</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>43.92</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>43.44</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>43.92</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>5178.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>16692.8</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>16692.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>15215.7</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>13519.76</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>13519.76</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-1397.534335250723</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>5178</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>5178.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>43.84</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>43.45</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>43.97</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>43.45</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>43.97</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>6625.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>21302.2</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>21302.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>16542.7</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>13576.72</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>13576.72</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-529.1355843768179</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>6625</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>6625.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>43.71</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>43.5</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>44.03</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>44.03</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>10460.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>23067.8</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>23067.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>19089.8</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>13602.9</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>13602.9</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>575.296044885079</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>10460</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>10460.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>43.31</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>43.58</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>44.1</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>43.58</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>44.1</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>30506.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>23927.2</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>23927.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>19193.0</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>13522.88</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>13522.88</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>1721.616370799031</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>30506</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>30506.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>42.73999999999999</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>43.61</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>44.12</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>43.61</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>44.12</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>30695.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>18788.8</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>18788.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>19613.1</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>13049.74</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>13049.74</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>1149.944823147569</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>30695</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>30695.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>42.22000000000001</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>43.6</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>44.15</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>44.15</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>28225.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>13738.6</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>13738.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>20246.9</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>12733.2</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>12733.2</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>271.9517256759318</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>28225</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>28225.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>41.96</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>43.53</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>44.23</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>43.53</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>44.23</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>15453.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>11783.2</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>11783.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>20989.4</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>12346.96</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>12346.96</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-727.3938323434086</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>15453</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>15453.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>42.04000000000001</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>43.48</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>44.31</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>43.48</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>44.31</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>14757.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>15111.8</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>15111.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>20870.2</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>12172.68</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>12172.68</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-760.6234212159197</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>14757</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>14757.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>42.55</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>43.5</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>44.42</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>44.42</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>4814.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>14458.8</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>14458.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>20545.5</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>12162.98</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>12162.98</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-706.357711704648</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>4814</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>4814.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>42.88</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>43.46</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>44.54</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>43.46</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>44.54</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>5444.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>20437.4</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>20437.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>22206.9</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>13085.46</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>13085.46</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>461.7132201580425</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>5444</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>5444.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5667,11 +5601,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
           <t>2476</t>
@@ -5853,41 +5783,37 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
+      <c r="AM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO13" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AN13" t="inlineStr">
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AP13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AS13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AT13" t="inlineStr">
         <is>
           <t>0</t>
@@ -5908,20 +5834,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>0</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>0</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5860,10 @@
           <t>0</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>0</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>

--- a/Result/checksun_type/電鍍材料.xlsx
+++ b/Result/checksun_type/電鍍材料.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CJ13"/>
+  <dimension ref="A1:CJ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>302.0</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>44.45</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-17.23</t>
+          <t>-48.61</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1019,68 +1019,68 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>123</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>76.36</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>72.02</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>43.92</t>
+          <t>43.82000000000001</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>43.47</v>
+        <v>43.49</v>
       </c>
       <c r="AN2" t="n">
         <v>43.94</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>45.23</t>
+          <t>45.21</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>91.47</t>
+          <t>125.94</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-108.60</t>
+          <t>-106.54</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>28195.53648068669</t>
+          <t>28167.14142857143</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>13560.0</t>
+          <t>5546.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>13265.8</v>
+        <v>8273.799999999999</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>16027.3</t>
+          <t>16100.5</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>13521.82</v>
+        <v>13310.48</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-2761</t>
+          <t>-7826</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>82.49753630070325</t>
+          <t>-217.9379326656332</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-1341.825102481189</t>
+          <t>-1870.333011980483</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>13560.0</t>
+          <t>5546.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-9.62</t>
+          <t>-10.92</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>1973</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>44.45</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>44.45</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>118.0</t>
+          <t>302.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>9.71</t>
+          <t>-17.23</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1449,68 +1449,68 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>123</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>65.43</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>55.14</t>
+          <t>72.02</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.1</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.80</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>43.92</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>43.44</v>
+        <v>43.47</v>
       </c>
       <c r="AN3" t="n">
-        <v>43.92</v>
+        <v>43.94</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>45.19</t>
+          <t>45.23</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>41.21</t>
+          <t>91.47</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-110.57</t>
+          <t>-108.60</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>28195.53648068669</t>
+          <t>28167.14142857143</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>5178.0</t>
+          <t>13560.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>16692.8</v>
+        <v>13265.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>15215.7</t>
+          <t>16027.3</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>13519.76</v>
+        <v>13521.82</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>-2761</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>341.4652888065019</t>
+          <t>82.49753630070325</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-1397.534335250723</t>
+          <t>-1341.825102481189</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>5178.0</t>
+          <t>13560.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-12.63</t>
+          <t>-9.62</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>1973</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>43.45</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>43.45</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>118.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4.66</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>28.77</t>
+          <t>9.71</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1879,68 +1879,68 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>123</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>50.62</t>
+          <t>65.43</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>66.26</t>
+          <t>55.14</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.1</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>43.84</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>43.45</v>
+        <v>43.44</v>
       </c>
       <c r="AN4" t="n">
-        <v>43.97</v>
+        <v>43.92</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>45.12</t>
+          <t>45.19</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>34.76</t>
+          <t>41.21</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-111.66</t>
+          <t>-110.57</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>28195.53648068669</t>
+          <t>28167.14142857143</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>6625.0</t>
+          <t>5178.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>21302.2</v>
+        <v>16692.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>16542.7</t>
+          <t>15215.7</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>13576.72</v>
+        <v>13519.76</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>4759</t>
+          <t>1477</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>657.6470386350882</t>
+          <t>341.4652888065019</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-529.1355843768179</t>
+          <t>-1397.534335250723</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>6625.0</t>
+          <t>5178.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-13.83</t>
+          <t>-12.63</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>1973</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>43.45</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>42.8</t>
+          <t>43.45</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-4.49</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>42.95</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>3.26</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>20.84</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5.89</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2309,68 +2309,68 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>123</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>49.38</t>
+          <t>50.62</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>82.72</t>
+          <t>66.26</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>43.71</t>
+          <t>43.84</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>43.5</v>
+        <v>43.45</v>
       </c>
       <c r="AN5" t="n">
-        <v>44.03</v>
+        <v>43.97</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>45.06</t>
+          <t>45.12</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>44.24</t>
+          <t>34.76</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-112.67</t>
+          <t>-111.66</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>28195.53648068669</t>
+          <t>28167.14142857143</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>10460.0</t>
+          <t>6625.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>23067.8</v>
+        <v>21302.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>19089.8</t>
+          <t>16542.7</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>13602.9</v>
+        <v>13576.72</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>3978</t>
+          <t>4759</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>873.4256973645256</t>
+          <t>657.6470386350882</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>575.296044885079</t>
+          <t>-529.1355843768179</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>10460.0</t>
+          <t>6625.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-13.93</t>
+          <t>-13.83</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>1973</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>42.8</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>42.95</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>670.0</t>
+          <t>240.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>44.95</t>
+          <t>42.95</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>24.67</t>
+          <t>20.84</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16.44</t>
+          <t>5.89</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2739,68 +2739,68 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>123</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>98.77</t>
+          <t>49.38</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>94.23</t>
+          <t>82.72</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>43.31</t>
+          <t>43.71</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>43.58</v>
+        <v>43.5</v>
       </c>
       <c r="AN6" t="n">
-        <v>44.1</v>
+        <v>44.03</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>45.01</t>
+          <t>45.06</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>56.72</t>
+          <t>44.24</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-114.07</t>
+          <t>-112.67</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>28195.53648068669</t>
+          <t>28167.14142857143</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>30506.0</t>
+          <t>10460.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>23927.2</v>
+        <v>23067.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>19193.0</t>
+          <t>19089.8</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>13522.88</v>
+        <v>13602.9</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>4734</t>
+          <t>3978</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>927.631088724425</t>
+          <t>873.4256973645256</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>1721.616370799031</t>
+          <t>575.296044885079</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>30506.0</t>
+          <t>10460.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-9.92</t>
+          <t>-13.93</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>1973</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>46.55</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>44.95</t>
+          <t>42.95</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>685.0</t>
+          <t>670.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>44.95</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,102 +3058,102 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
+          <t>24.67</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2025-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-10-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2025-08-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2025-08-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>45.6</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>44.45</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>52.5</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>47.6</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>1.12</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
           <t>-4.20</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2025-10-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2025-10-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2025-08-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2025-08-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>45.6</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>44.45</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>52.5</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>47.6</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>1.24</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>-4.20</t>
-        </is>
-      </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16.81</t>
+          <t>16.44</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3169,269 +3169,269 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>123</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>98.77</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>75.04</t>
+          <t>94.23</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>42.73999999999999</t>
+          <t>43.31</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>43.61</v>
+        <v>43.58</v>
       </c>
       <c r="AN7" t="n">
-        <v>44.12</v>
+        <v>44.1</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
+          <t>45.01</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>56.72</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>-0.17</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>-0.39</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>2.77</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>-114.07</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>2025/11/19</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>28167.14142857143</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>30506.0</t>
+        </is>
+      </c>
+      <c r="AX7" t="n">
+        <v>23927.2</v>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>19193.0</t>
+        </is>
+      </c>
+      <c r="AZ7" t="n">
+        <v>13522.88</v>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>4734</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>927.631088724425</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>1721.616370799031</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>30506.0</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>49.9</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>2025/08/12</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>-9.92</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>匯鑽科</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>匯鑽科</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>0.78</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
+          <t>-10.56465687102404</t>
+        </is>
+      </c>
+      <c r="BO7" t="inlineStr">
+        <is>
+          <t>-13.69932964657055</t>
+        </is>
+      </c>
+      <c r="BP7" t="inlineStr">
+        <is>
+          <t>7.80229574004913</t>
+        </is>
+      </c>
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS7" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="BT7" t="inlineStr">
+        <is>
+          <t>2.53</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
+          <t>6.59</t>
+        </is>
+      </c>
+      <c r="BV7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
+          <t>8.25%</t>
+        </is>
+      </c>
+      <c r="BX7" t="inlineStr">
+        <is>
+          <t>-14.21%</t>
+        </is>
+      </c>
+      <c r="BY7" t="inlineStr">
+        <is>
+          <t>43.4</t>
+        </is>
+      </c>
+      <c r="BZ7" t="inlineStr">
+        <is>
+          <t>1973</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
+          <t>加工業務99.90%、勞務0.10% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>匯鑽科-其他電子業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC7" t="inlineStr">
+        <is>
+          <t>其他電子業右下上櫃</t>
+        </is>
+      </c>
+      <c r="CD7" t="inlineStr">
+        <is>
+          <t>45.5</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
+          <t>46.55</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
+          <t>44.8</t>
+        </is>
+      </c>
+      <c r="CG7" t="inlineStr">
+        <is>
           <t>44.95</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>24.64</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>-0.34</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>-0.45</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>2.77</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr">
-        <is>
-          <t>-116.07</t>
-        </is>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>2025/11/19</t>
-        </is>
-      </c>
-      <c r="AV7" t="inlineStr">
-        <is>
-          <t>28195.53648068669</t>
-        </is>
-      </c>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>30695.0</t>
-        </is>
-      </c>
-      <c r="AX7" t="n">
-        <v>18788.8</v>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>19613.1</t>
-        </is>
-      </c>
-      <c r="AZ7" t="n">
-        <v>13049.74</v>
-      </c>
-      <c r="BA7" t="inlineStr">
-        <is>
-          <t>-824</t>
-        </is>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>783.2701283472239</t>
-        </is>
-      </c>
-      <c r="BC7" t="inlineStr">
-        <is>
-          <t>1149.944823147569</t>
-        </is>
-      </c>
-      <c r="BD7" t="inlineStr">
-        <is>
-          <t>30695.0</t>
-        </is>
-      </c>
-      <c r="BE7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF7" t="inlineStr">
-        <is>
-          <t>49.9</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>2025/08/12</t>
-        </is>
-      </c>
-      <c r="BH7" t="inlineStr">
-        <is>
-          <t>-9.82</t>
-        </is>
-      </c>
-      <c r="BI7" t="inlineStr">
-        <is>
-          <t>匯鑽科</t>
-        </is>
-      </c>
-      <c r="BJ7" t="inlineStr">
-        <is>
-          <t>匯鑽科</t>
-        </is>
-      </c>
-      <c r="BK7" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BL7" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM7" t="inlineStr">
-        <is>
-          <t>0.78</t>
-        </is>
-      </c>
-      <c r="BN7" t="inlineStr">
-        <is>
-          <t>-10.56465687102404</t>
-        </is>
-      </c>
-      <c r="BO7" t="inlineStr">
-        <is>
-          <t>-13.69932964657055</t>
-        </is>
-      </c>
-      <c r="BP7" t="inlineStr">
-        <is>
-          <t>7.80229574004913</t>
-        </is>
-      </c>
-      <c r="BQ7" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
-        </is>
-      </c>
-      <c r="BR7" t="inlineStr">
-        <is>
-          <t>價漲量增</t>
-        </is>
-      </c>
-      <c r="BS7" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
-      </c>
-      <c r="BT7" t="inlineStr">
-        <is>
-          <t>2.49</t>
-        </is>
-      </c>
-      <c r="BU7" t="inlineStr">
-        <is>
-          <t>6.59</t>
-        </is>
-      </c>
-      <c r="BV7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BW7" t="inlineStr">
-        <is>
-          <t>8.25%</t>
-        </is>
-      </c>
-      <c r="BX7" t="inlineStr">
-        <is>
-          <t>-14.21%</t>
-        </is>
-      </c>
-      <c r="BY7" t="inlineStr">
-        <is>
-          <t>43.25</t>
-        </is>
-      </c>
-      <c r="BZ7" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
-      </c>
-      <c r="CA7" t="inlineStr">
-        <is>
-          <t>加工業務99.90%、勞務0.10% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB7" t="inlineStr">
-        <is>
-          <t>匯鑽科-其他電子業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC7" t="inlineStr">
-        <is>
-          <t>其他電子業右下上櫃</t>
-        </is>
-      </c>
-      <c r="CD7" t="inlineStr">
-        <is>
-          <t>43.55</t>
-        </is>
-      </c>
-      <c r="CE7" t="inlineStr">
-        <is>
-          <t>45.55</t>
-        </is>
-      </c>
-      <c r="CF7" t="inlineStr">
-        <is>
-          <t>43.3</t>
-        </is>
-      </c>
-      <c r="CG7" t="inlineStr">
-        <is>
-          <t>45.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3453,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>655.0</t>
+          <t>685.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-32.14</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>16.81</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3599,68 +3599,68 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>123</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>83.93</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>75.04</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>42.22000000000001</t>
+          <t>42.73999999999999</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>43.6</v>
+        <v>43.61</v>
       </c>
       <c r="AN8" t="n">
-        <v>44.15</v>
+        <v>44.12</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>44.89</t>
+          <t>44.95</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-16.05</t>
+          <t>24.64</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-117.06</t>
+          <t>-116.07</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>28195.53648068669</t>
+          <t>28167.14142857143</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>28225.0</t>
+          <t>30695.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>13738.6</v>
+        <v>18788.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>20246.9</t>
+          <t>19613.1</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>12733.2</v>
+        <v>13049.74</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-6508</t>
+          <t>-824</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>716.6020020198885</t>
+          <t>783.2701283472239</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>271.9517256759318</t>
+          <t>1149.944823147569</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>28225.0</t>
+          <t>30695.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-13.23</t>
+          <t>-9.82</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>1973</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>42.35</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>369.0</t>
+          <t>655.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>42.35</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-43.86</t>
+          <t>-32.14</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-4.72</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>9.06</t>
+          <t>16.07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4029,68 +4029,68 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>123</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>41.18</t>
+          <t>83.93</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>14.84</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>42.22000000000001</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>43.53</v>
+        <v>43.6</v>
       </c>
       <c r="AN9" t="n">
-        <v>44.23</v>
+        <v>44.15</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>44.87</t>
+          <t>44.89</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-40.91</t>
+          <t>-16.05</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-116.38</t>
+          <t>-117.06</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>28195.53648068669</t>
+          <t>28167.14142857143</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>15453.0</t>
+          <t>28225.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>11783.2</v>
+        <v>13738.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>20989.4</t>
+          <t>20246.9</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>12346.96</v>
+        <v>12733.2</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-9206</t>
+          <t>-6508</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>797.4475068096988</t>
+          <t>716.6020020198885</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-727.3938323434086</t>
+          <t>271.9517256759318</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>15453.0</t>
+          <t>28225.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-15.13</t>
+          <t>-13.23</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>1973</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>42.7</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>42.35</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>42.35</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>358.0</t>
+          <t>369.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>42.35</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>4.72</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-27.59</t>
+          <t>-43.86</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-7.87</t>
+          <t>-4.72</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>8.79</t>
+          <t>9.06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4459,68 +4459,68 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>123</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>41.18</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>14.84</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-3.31</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>42.04000000000001</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>43.48</v>
+        <v>43.53</v>
       </c>
       <c r="AN10" t="n">
-        <v>44.31</v>
+        <v>44.23</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>44.85</t>
+          <t>44.87</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-59.38</t>
+          <t>-40.91</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-114.70</t>
+          <t>-116.38</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>28195.53648068669</t>
+          <t>28167.14142857143</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>14757.0</t>
+          <t>15453.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>15111.8</v>
+        <v>11783.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>20870.2</t>
+          <t>20989.4</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>12172.68</v>
+        <v>12346.96</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-5758</t>
+          <t>-9206</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>1074.691386655718</t>
+          <t>797.4475068096988</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-760.6234212159197</t>
+          <t>-727.3938323434086</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>14757.0</t>
+          <t>15453.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-17.94</t>
+          <t>-15.13</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>1973</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,12 +4706,12 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>42.45</t>
+          <t>42.7</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>42.35</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>358.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6.65</t>
+          <t>7.87</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-29.63</t>
+          <t>-27.59</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-5.29</t>
+          <t>-7.87</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>8.79</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>123</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -4904,53 +4904,53 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-3.31</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>42.55</t>
+          <t>42.04000000000001</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>43.5</v>
+        <v>43.48</v>
       </c>
       <c r="AN11" t="n">
-        <v>44.42</v>
+        <v>44.31</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>44.84</t>
+          <t>44.85</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-46.96</t>
+          <t>-59.38</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-112.52</t>
+          <t>-114.70</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>28195.53648068669</t>
+          <t>28167.14142857143</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>4814.0</t>
+          <t>14757.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>14458.8</v>
+        <v>15111.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>20545.5</t>
+          <t>20870.2</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>12162.98</v>
+        <v>12172.68</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-6086</t>
+          <t>-5758</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>1408.384988086925</t>
+          <t>1074.691386655718</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-706.357711704648</t>
+          <t>-760.6234212159197</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>4814.0</t>
+          <t>14757.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-15.63</t>
+          <t>-17.94</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>1973</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
+          <t>42.1</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
           <t>42.45</t>
         </is>
       </c>
-      <c r="CE11" t="inlineStr">
-        <is>
-          <t>42.7</t>
-        </is>
-      </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>41.95</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>114.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>42.4</t>
+          <t>42.1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5.99</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-7.97</t>
+          <t>-29.63</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-4.61</t>
+          <t>-5.29</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,68 +5319,68 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>123</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>42.88</t>
+          <t>42.55</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>43.46</v>
+        <v>43.5</v>
       </c>
       <c r="AN12" t="n">
-        <v>44.54</v>
+        <v>44.42</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>44.81</t>
+          <t>44.84</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-44.19</t>
+          <t>-46.96</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-111.05</t>
+          <t>-112.52</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>28195.53648068669</t>
+          <t>28167.14142857143</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>5444.0</t>
+          <t>4814.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>20437.4</v>
+        <v>14458.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>22206.9</t>
+          <t>20545.5</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>13085.46</v>
+        <v>12162.98</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-1769</t>
+          <t>-6086</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>1792.883660776302</t>
+          <t>1408.384988086925</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>461.7132201580425</t>
+          <t>-706.357711704648</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>5444.0</t>
+          <t>4814.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-15.03</t>
+          <t>-15.63</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>1973</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>42.45</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>42.7</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>41.95</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>42.4</t>
+          <t>42.1</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5601,7 +5601,11 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
           <t>2476</t>
@@ -5609,42 +5613,42 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>-0.91</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>630.229</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>87.1</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.7</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-29.59</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5654,37 +5658,37 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-07-23 00:00:00</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-09-16 00:00:00</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-06 00:00:00</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-03-07 00:00:00</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -5694,12 +5698,12 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>95.8</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>92.1</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -5709,318 +5713,4618 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-18.60</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-15.09</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>714</t>
+          <t>630</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
+          <t>39.02</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>31.54</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>0.53</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>-5.08</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>-7.16</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>0.90</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>86.64</t>
+        </is>
+      </c>
+      <c r="AM13" t="n">
+        <v>91.28</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>98.31</v>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>97.43</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>-4.05</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>-3.28</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>-3.15</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>7.19</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr">
+        <is>
+          <t>-143.82</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>2025/07/15</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>354437913.0685714</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>55246132.0</t>
+        </is>
+      </c>
+      <c r="AX13" t="n">
+        <v>67438997.8</v>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>95782499.1</t>
+        </is>
+      </c>
+      <c r="AZ13" t="n">
+        <v>275665355.36</v>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>-28343501</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>-29782766.16711858</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>-29852555.79943146</t>
+        </is>
+      </c>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>55246132.0</t>
+        </is>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
+          <t>81.3</t>
+        </is>
+      </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>2025/07/28</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>7.13</t>
+        </is>
+      </c>
+      <c r="BI13" t="inlineStr">
+        <is>
+          <t>鉅祥</t>
+        </is>
+      </c>
+      <c r="BJ13" t="inlineStr">
+        <is>
+          <t>鉅祥</t>
+        </is>
+      </c>
+      <c r="BK13" t="inlineStr">
+        <is>
+          <t>電子零組件業</t>
+        </is>
+      </c>
+      <c r="BL13" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM13" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="BN13" t="inlineStr">
+        <is>
+          <t>-7.291353668658945</t>
+        </is>
+      </c>
+      <c r="BO13" t="inlineStr">
+        <is>
+          <t>11.64963320584363</t>
+        </is>
+      </c>
+      <c r="BP13" t="inlineStr">
+        <is>
+          <t>10.65346457950322</t>
+        </is>
+      </c>
+      <c r="BQ13" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR13" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS13" t="inlineStr">
+        <is>
+          <t>2.29</t>
+        </is>
+      </c>
+      <c r="BT13" t="inlineStr">
+        <is>
+          <t>4.02</t>
+        </is>
+      </c>
+      <c r="BU13" t="inlineStr">
+        <is>
+          <t>9.36</t>
+        </is>
+      </c>
+      <c r="BV13" t="inlineStr">
+        <is>
+          <t>22.39</t>
+        </is>
+      </c>
+      <c r="BW13" t="inlineStr">
+        <is>
+          <t>29.60%</t>
+        </is>
+      </c>
+      <c r="BX13" t="inlineStr">
+        <is>
+          <t>15.93%</t>
+        </is>
+      </c>
+      <c r="BY13" t="inlineStr">
+        <is>
+          <t>34.43</t>
+        </is>
+      </c>
+      <c r="BZ13" t="inlineStr">
+        <is>
+          <t>18369</t>
+        </is>
+      </c>
+      <c r="CA13" t="inlineStr">
+        <is>
+          <t>部品95.14%、模具3.09%、商品銷售1.03%、治具0.75% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB13" t="inlineStr">
+        <is>
+          <t>鉅祥-電子零組件業-上市</t>
+        </is>
+      </c>
+      <c r="CC13" t="inlineStr">
+        <is>
+          <t>電子零組件業右上上市</t>
+        </is>
+      </c>
+      <c r="CD13" t="inlineStr">
+        <is>
+          <t>87.9</t>
+        </is>
+      </c>
+      <c r="CE13" t="inlineStr">
+        <is>
+          <t>88.5</t>
+        </is>
+      </c>
+      <c r="CF13" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="CG13" t="inlineStr">
+        <is>
+          <t>87.1</t>
+        </is>
+      </c>
+      <c r="CH13" t="inlineStr">
+        <is>
+          <t>38.04</t>
+        </is>
+      </c>
+      <c r="CI13" t="inlineStr">
+        <is>
+          <t>** 平面顯示器 - 其他零組件** 通信網路 - 主/被動元件、塑膠/金屬機殼** 連接器 - 金屬材料、電鍍材料、塑膠材料** 醫療器材 - 塑化材料</t>
+        </is>
+      </c>
+      <c r="CJ13" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2476</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>713.512</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>87.9</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-0.92</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>-2.7</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>-33.57</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2025-07-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2025-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2025-03-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2025-03-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>78.2</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>107.0</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>95.8</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>92.1</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>-17.85</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>-15.09</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>0.80</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>43.64</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>20.7</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>1.20</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>-5.14</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>-7.33</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>86.85999999999999</t>
+        </is>
+      </c>
+      <c r="AM14" t="n">
+        <v>91.56999999999999</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>98.81999999999999</v>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>97.34</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>-8.10</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>-3.37</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>-3.12</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>7.19</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>-143.38</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>2025/07/15</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>354437913.0685714</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>62492000.0</t>
+        </is>
+      </c>
+      <c r="AX14" t="n">
+        <v>68942899</v>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>103776418.9</t>
+        </is>
+      </c>
+      <c r="AZ14" t="n">
+        <v>296624289.38</v>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>-34833519</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>-29770077.14306169</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>-30756535.8138715</t>
+        </is>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>62492000.0</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>81.3</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>2025/07/28</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>8.12</t>
+        </is>
+      </c>
+      <c r="BI14" t="inlineStr">
+        <is>
+          <t>鉅祥</t>
+        </is>
+      </c>
+      <c r="BJ14" t="inlineStr">
+        <is>
+          <t>鉅祥</t>
+        </is>
+      </c>
+      <c r="BK14" t="inlineStr">
+        <is>
+          <t>電子零組件業</t>
+        </is>
+      </c>
+      <c r="BL14" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM14" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="BN14" t="inlineStr">
+        <is>
+          <t>-7.291353668658945</t>
+        </is>
+      </c>
+      <c r="BO14" t="inlineStr">
+        <is>
+          <t>11.64963320584363</t>
+        </is>
+      </c>
+      <c r="BP14" t="inlineStr">
+        <is>
+          <t>10.65346457950322</t>
+        </is>
+      </c>
+      <c r="BQ14" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR14" t="inlineStr">
+        <is>
+          <t>價漲量-</t>
+        </is>
+      </c>
+      <c r="BS14" t="inlineStr">
+        <is>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="BT14" t="inlineStr">
+        <is>
+          <t>4.02</t>
+        </is>
+      </c>
+      <c r="BU14" t="inlineStr">
+        <is>
+          <t>9.36</t>
+        </is>
+      </c>
+      <c r="BV14" t="inlineStr">
+        <is>
+          <t>22.39</t>
+        </is>
+      </c>
+      <c r="BW14" t="inlineStr">
+        <is>
+          <t>29.60%</t>
+        </is>
+      </c>
+      <c r="BX14" t="inlineStr">
+        <is>
+          <t>15.93%</t>
+        </is>
+      </c>
+      <c r="BY14" t="inlineStr">
+        <is>
+          <t>34.43</t>
+        </is>
+      </c>
+      <c r="BZ14" t="inlineStr">
+        <is>
+          <t>18369</t>
+        </is>
+      </c>
+      <c r="CA14" t="inlineStr">
+        <is>
+          <t>部品95.14%、模具3.09%、商品銷售1.03%、治具0.75% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB14" t="inlineStr">
+        <is>
+          <t>鉅祥-電子零組件業-上市</t>
+        </is>
+      </c>
+      <c r="CC14" t="inlineStr">
+        <is>
+          <t>電子零組件業右上上市</t>
+        </is>
+      </c>
+      <c r="CD14" t="inlineStr">
+        <is>
+          <t>87.2</t>
+        </is>
+      </c>
+      <c r="CE14" t="inlineStr">
+        <is>
+          <t>87.9</t>
+        </is>
+      </c>
+      <c r="CF14" t="inlineStr">
+        <is>
+          <t>87.2</t>
+        </is>
+      </c>
+      <c r="CG14" t="inlineStr">
+        <is>
+          <t>87.9</t>
+        </is>
+      </c>
+      <c r="CH14" t="inlineStr">
+        <is>
+          <t>38.04</t>
+        </is>
+      </c>
+      <c r="CI14" t="inlineStr">
+        <is>
+          <t>** 平面顯示器 - 其他零組件** 通信網路 - 主/被動元件、塑膠/金屬機殼** 連接器 - 金屬材料、電鍍材料、塑膠材料** 醫療器材 - 塑化材料</t>
+        </is>
+      </c>
+      <c r="CJ14" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2476</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0.57</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>557.755</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>86.6</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0.57</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>-2.7</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>-31.49</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2025-07-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2025-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2025-03-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2025-03-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>78.2</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>107.0</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>95.8</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>92.1</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>-19.07</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>-15.09</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>-0.46</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>11.96</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>6.16</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>-5.79</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>-7.52</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>86.58</t>
+        </is>
+      </c>
+      <c r="AM15" t="n">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>99.37</v>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>97.25</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>-15.28</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>-3.52</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>-3.06</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>7.19</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr">
+        <is>
+          <t>-142.50</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>2025/07/15</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>354437913.0685714</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>48395514.0</t>
+        </is>
+      </c>
+      <c r="AX15" t="n">
+        <v>76417304.59999999</v>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>111545339.3</t>
+        </is>
+      </c>
+      <c r="AZ15" t="n">
+        <v>319430807.84</v>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>-35128034</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>-29590721.02109627</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>-31725831.12686187</t>
+        </is>
+      </c>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>48395514.0</t>
+        </is>
+      </c>
+      <c r="BE15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF15" t="inlineStr">
+        <is>
+          <t>81.3</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>2025/07/28</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>6.52</t>
+        </is>
+      </c>
+      <c r="BI15" t="inlineStr">
+        <is>
+          <t>鉅祥</t>
+        </is>
+      </c>
+      <c r="BJ15" t="inlineStr">
+        <is>
+          <t>鉅祥</t>
+        </is>
+      </c>
+      <c r="BK15" t="inlineStr">
+        <is>
+          <t>電子零組件業</t>
+        </is>
+      </c>
+      <c r="BL15" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM15" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="BN15" t="inlineStr">
+        <is>
+          <t>-7.291353668658945</t>
+        </is>
+      </c>
+      <c r="BO15" t="inlineStr">
+        <is>
+          <t>11.64963320584363</t>
+        </is>
+      </c>
+      <c r="BP15" t="inlineStr">
+        <is>
+          <t>10.65346457950322</t>
+        </is>
+      </c>
+      <c r="BQ15" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR15" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS15" t="inlineStr">
+        <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="BT15" t="inlineStr">
+        <is>
+          <t>4.02</t>
+        </is>
+      </c>
+      <c r="BU15" t="inlineStr">
+        <is>
+          <t>9.36</t>
+        </is>
+      </c>
+      <c r="BV15" t="inlineStr">
+        <is>
+          <t>22.39</t>
+        </is>
+      </c>
+      <c r="BW15" t="inlineStr">
+        <is>
+          <t>29.60%</t>
+        </is>
+      </c>
+      <c r="BX15" t="inlineStr">
+        <is>
+          <t>15.93%</t>
+        </is>
+      </c>
+      <c r="BY15" t="inlineStr">
+        <is>
+          <t>34.43</t>
+        </is>
+      </c>
+      <c r="BZ15" t="inlineStr">
+        <is>
+          <t>18369</t>
+        </is>
+      </c>
+      <c r="CA15" t="inlineStr">
+        <is>
+          <t>部品95.14%、模具3.09%、商品銷售1.03%、治具0.75% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB15" t="inlineStr">
+        <is>
+          <t>鉅祥-電子零組件業-上市</t>
+        </is>
+      </c>
+      <c r="CC15" t="inlineStr">
+        <is>
+          <t>電子零組件業右上上市</t>
+        </is>
+      </c>
+      <c r="CD15" t="inlineStr">
+        <is>
+          <t>87.7</t>
+        </is>
+      </c>
+      <c r="CE15" t="inlineStr">
+        <is>
+          <t>87.7</t>
+        </is>
+      </c>
+      <c r="CF15" t="inlineStr">
+        <is>
+          <t>85.9</t>
+        </is>
+      </c>
+      <c r="CG15" t="inlineStr">
+        <is>
+          <t>86.6</t>
+        </is>
+      </c>
+      <c r="CH15" t="inlineStr">
+        <is>
+          <t>38.04</t>
+        </is>
+      </c>
+      <c r="CI15" t="inlineStr">
+        <is>
+          <t>** 平面顯示器 - 其他零組件** 通信網路 - 主/被動元件、塑膠/金屬機殼** 連接器 - 金屬材料、電鍍材料、塑膠材料** 醫療器材 - 塑化材料</t>
+        </is>
+      </c>
+      <c r="CJ15" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2476</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>797.916</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>86.1</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>1.15</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>-2.7</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>-21.02</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2025-07-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2025-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2025-03-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2025-03-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>78.2</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>107.0</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>95.8</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>92.1</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>-19.53</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>-15.09</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>3.86</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>0.94</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>6.52</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>9.08</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>-0.76</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>-6.01</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>-7.68</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>2.91</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>86.75999999999999</t>
+        </is>
+      </c>
+      <c r="AM16" t="n">
+        <v>92.31</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>99.98999999999999</v>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>97.16</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>-20.19</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>-3.53</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>-2.94</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>7.19</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr">
+        <is>
+          <t>-140.87</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>2025/07/15</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>354437913.0685714</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>68436405.0</t>
+        </is>
+      </c>
+      <c r="AX16" t="n">
+        <v>95573934</v>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>121006638.2</t>
+        </is>
+      </c>
+      <c r="AZ16" t="n">
+        <v>336619552.5</v>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>-25432704</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>-29202519.18368434</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>-30467135.53374588</t>
+        </is>
+      </c>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>68436405.0</t>
+        </is>
+      </c>
+      <c r="BE16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF16" t="inlineStr">
+        <is>
+          <t>81.3</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>2025/07/28</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>5.90</t>
+        </is>
+      </c>
+      <c r="BI16" t="inlineStr">
+        <is>
+          <t>鉅祥</t>
+        </is>
+      </c>
+      <c r="BJ16" t="inlineStr">
+        <is>
+          <t>鉅祥</t>
+        </is>
+      </c>
+      <c r="BK16" t="inlineStr">
+        <is>
+          <t>電子零組件業</t>
+        </is>
+      </c>
+      <c r="BL16" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM16" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="BN16" t="inlineStr">
+        <is>
+          <t>-7.291353668658945</t>
+        </is>
+      </c>
+      <c r="BO16" t="inlineStr">
+        <is>
+          <t>11.64963320584363</t>
+        </is>
+      </c>
+      <c r="BP16" t="inlineStr">
+        <is>
+          <t>10.65346457950322</t>
+        </is>
+      </c>
+      <c r="BQ16" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR16" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS16" t="inlineStr">
+        <is>
+          <t>2.26</t>
+        </is>
+      </c>
+      <c r="BT16" t="inlineStr">
+        <is>
+          <t>4.02</t>
+        </is>
+      </c>
+      <c r="BU16" t="inlineStr">
+        <is>
+          <t>9.36</t>
+        </is>
+      </c>
+      <c r="BV16" t="inlineStr">
+        <is>
+          <t>22.39</t>
+        </is>
+      </c>
+      <c r="BW16" t="inlineStr">
+        <is>
+          <t>29.60%</t>
+        </is>
+      </c>
+      <c r="BX16" t="inlineStr">
+        <is>
+          <t>15.93%</t>
+        </is>
+      </c>
+      <c r="BY16" t="inlineStr">
+        <is>
+          <t>34.43</t>
+        </is>
+      </c>
+      <c r="BZ16" t="inlineStr">
+        <is>
+          <t>18369</t>
+        </is>
+      </c>
+      <c r="CA16" t="inlineStr">
+        <is>
+          <t>部品95.14%、模具3.09%、商品銷售1.03%、治具0.75% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB16" t="inlineStr">
+        <is>
+          <t>鉅祥-電子零組件業-上市</t>
+        </is>
+      </c>
+      <c r="CC16" t="inlineStr">
+        <is>
+          <t>電子零組件業右上上市</t>
+        </is>
+      </c>
+      <c r="CD16" t="inlineStr">
+        <is>
+          <t>86.3</t>
+        </is>
+      </c>
+      <c r="CE16" t="inlineStr">
+        <is>
+          <t>86.3</t>
+        </is>
+      </c>
+      <c r="CF16" t="inlineStr">
+        <is>
+          <t>85.1</t>
+        </is>
+      </c>
+      <c r="CG16" t="inlineStr">
+        <is>
+          <t>86.1</t>
+        </is>
+      </c>
+      <c r="CH16" t="inlineStr">
+        <is>
+          <t>38.04</t>
+        </is>
+      </c>
+      <c r="CI16" t="inlineStr">
+        <is>
+          <t>** 平面顯示器 - 其他零組件** 通信網路 - 主/被動元件、塑膠/金屬機殼** 連接器 - 金屬材料、電鍍材料、塑膠材料** 醫療器材 - 塑化材料</t>
+        </is>
+      </c>
+      <c r="CJ16" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2476</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>-3.11</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>1197.387</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>85.5</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>-2.7</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>-9.98</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2025-07-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2025-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>2025-03-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2025-03-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>78.2</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>107.0</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>95.8</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>92.1</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>-20.09</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>-15.09</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>5.79</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>-1.27</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AG13" t="inlineStr">
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>6.91</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>-2.24</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>-5.99</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>-7.53</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>3.62</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>87.46000000000001</t>
+        </is>
+      </c>
+      <c r="AM17" t="n">
+        <v>93.03</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>100.61</v>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>97.09</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>-23.35</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>-3.44</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>-2.79</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>7.19</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr">
+        <is>
+          <t>-138.81</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>2025/07/15</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>354437913.0685714</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>102624938.0</t>
+        </is>
+      </c>
+      <c r="AX17" t="n">
+        <v>111293530.2</v>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>123628857.1</t>
+        </is>
+      </c>
+      <c r="AZ17" t="n">
+        <v>366752945.54</v>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>-12335326</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>-28972588.9382186</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>-29728125.31023213</t>
+        </is>
+      </c>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>102624938.0</t>
+        </is>
+      </c>
+      <c r="BE17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF17" t="inlineStr">
+        <is>
+          <t>81.3</t>
+        </is>
+      </c>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>2025/07/28</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>5.17</t>
+        </is>
+      </c>
+      <c r="BI17" t="inlineStr">
+        <is>
+          <t>鉅祥</t>
+        </is>
+      </c>
+      <c r="BJ17" t="inlineStr">
+        <is>
+          <t>鉅祥</t>
+        </is>
+      </c>
+      <c r="BK17" t="inlineStr">
+        <is>
+          <t>電子零組件業</t>
+        </is>
+      </c>
+      <c r="BL17" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM17" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="BN17" t="inlineStr">
+        <is>
+          <t>-7.291353668658945</t>
+        </is>
+      </c>
+      <c r="BO17" t="inlineStr">
+        <is>
+          <t>11.64963320584363</t>
+        </is>
+      </c>
+      <c r="BP17" t="inlineStr">
+        <is>
+          <t>10.65346457950322</t>
+        </is>
+      </c>
+      <c r="BQ17" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR17" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS17" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="BT17" t="inlineStr">
+        <is>
+          <t>4.02</t>
+        </is>
+      </c>
+      <c r="BU17" t="inlineStr">
+        <is>
+          <t>9.36</t>
+        </is>
+      </c>
+      <c r="BV17" t="inlineStr">
+        <is>
+          <t>22.39</t>
+        </is>
+      </c>
+      <c r="BW17" t="inlineStr">
+        <is>
+          <t>29.60%</t>
+        </is>
+      </c>
+      <c r="BX17" t="inlineStr">
+        <is>
+          <t>15.93%</t>
+        </is>
+      </c>
+      <c r="BY17" t="inlineStr">
+        <is>
+          <t>34.43</t>
+        </is>
+      </c>
+      <c r="BZ17" t="inlineStr">
+        <is>
+          <t>18369</t>
+        </is>
+      </c>
+      <c r="CA17" t="inlineStr">
+        <is>
+          <t>部品95.14%、模具3.09%、商品銷售1.03%、治具0.75% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB17" t="inlineStr">
+        <is>
+          <t>鉅祥-電子零組件業-上市</t>
+        </is>
+      </c>
+      <c r="CC17" t="inlineStr">
+        <is>
+          <t>電子零組件業右上上市</t>
+        </is>
+      </c>
+      <c r="CD17" t="inlineStr">
+        <is>
+          <t>86.7</t>
+        </is>
+      </c>
+      <c r="CE17" t="inlineStr">
+        <is>
+          <t>87.6</t>
+        </is>
+      </c>
+      <c r="CF17" t="inlineStr">
+        <is>
+          <t>84.5</t>
+        </is>
+      </c>
+      <c r="CG17" t="inlineStr">
+        <is>
+          <t>85.5</t>
+        </is>
+      </c>
+      <c r="CH17" t="inlineStr">
+        <is>
+          <t>38.04</t>
+        </is>
+      </c>
+      <c r="CI17" t="inlineStr">
+        <is>
+          <t>** 平面顯示器 - 其他零組件** 通信網路 - 主/被動元件、塑膠/金屬機殼** 連接器 - 金屬材料、電鍍材料、塑膠材料** 醫療器材 - 塑化材料</t>
+        </is>
+      </c>
+      <c r="CJ17" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2476</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>710.084</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>88.2</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-1.26</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-2.7</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>-0.88</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2025-07-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2025-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>2025-03-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2025-03-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>78.2</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>107.0</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>95.8</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>92.1</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>-17.57</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>-15.09</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>3.43</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>-1.02</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>20.73</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>6.91</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>-0.41</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>-5.54</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>-7.34</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>4.27</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>88.56</t>
+        </is>
+      </c>
+      <c r="AM18" t="n">
+        <v>93.75</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>101.18</v>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>97.04</t>
+        </is>
+      </c>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>-22.39</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>-3.22</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>-2.63</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>7.19</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr">
+        <is>
+          <t>-136.55</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>2025/07/15</t>
+        </is>
+      </c>
+      <c r="AV18" t="inlineStr">
+        <is>
+          <t>354437913.0685714</t>
+        </is>
+      </c>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>62765638.0</t>
+        </is>
+      </c>
+      <c r="AX18" t="n">
+        <v>124126000.4</v>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>125231243.6</t>
+        </is>
+      </c>
+      <c r="AZ18" t="n">
+        <v>399636300.16</v>
+      </c>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>-1105243</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>-28835218.6887616</t>
+        </is>
+      </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>-31273734.76556134</t>
+        </is>
+      </c>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>62765638.0</t>
+        </is>
+      </c>
+      <c r="BE18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF18" t="inlineStr">
+        <is>
+          <t>81.3</t>
+        </is>
+      </c>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>2025/07/28</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>8.49</t>
+        </is>
+      </c>
+      <c r="BI18" t="inlineStr">
+        <is>
+          <t>鉅祥</t>
+        </is>
+      </c>
+      <c r="BJ18" t="inlineStr">
+        <is>
+          <t>鉅祥</t>
+        </is>
+      </c>
+      <c r="BK18" t="inlineStr">
+        <is>
+          <t>電子零組件業</t>
+        </is>
+      </c>
+      <c r="BL18" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM18" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="BN18" t="inlineStr">
+        <is>
+          <t>-7.291353668658945</t>
+        </is>
+      </c>
+      <c r="BO18" t="inlineStr">
+        <is>
+          <t>11.64963320584363</t>
+        </is>
+      </c>
+      <c r="BP18" t="inlineStr">
+        <is>
+          <t>10.65346457950322</t>
+        </is>
+      </c>
+      <c r="BQ18" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR18" t="inlineStr">
+        <is>
+          <t>價漲量-</t>
+        </is>
+      </c>
+      <c r="BS18" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="BT18" t="inlineStr">
+        <is>
+          <t>4.02</t>
+        </is>
+      </c>
+      <c r="BU18" t="inlineStr">
+        <is>
+          <t>9.36</t>
+        </is>
+      </c>
+      <c r="BV18" t="inlineStr">
+        <is>
+          <t>22.39</t>
+        </is>
+      </c>
+      <c r="BW18" t="inlineStr">
+        <is>
+          <t>29.60%</t>
+        </is>
+      </c>
+      <c r="BX18" t="inlineStr">
+        <is>
+          <t>15.93%</t>
+        </is>
+      </c>
+      <c r="BY18" t="inlineStr">
+        <is>
+          <t>34.43</t>
+        </is>
+      </c>
+      <c r="BZ18" t="inlineStr">
+        <is>
+          <t>18369</t>
+        </is>
+      </c>
+      <c r="CA18" t="inlineStr">
+        <is>
+          <t>部品95.14%、模具3.09%、商品銷售1.03%、治具0.75% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB18" t="inlineStr">
+        <is>
+          <t>鉅祥-電子零組件業-上市</t>
+        </is>
+      </c>
+      <c r="CC18" t="inlineStr">
+        <is>
+          <t>電子零組件業右上上市</t>
+        </is>
+      </c>
+      <c r="CD18" t="inlineStr">
+        <is>
+          <t>88.6</t>
+        </is>
+      </c>
+      <c r="CE18" t="inlineStr">
+        <is>
+          <t>89.4</t>
+        </is>
+      </c>
+      <c r="CF18" t="inlineStr">
+        <is>
+          <t>87.9</t>
+        </is>
+      </c>
+      <c r="CG18" t="inlineStr">
+        <is>
+          <t>88.2</t>
+        </is>
+      </c>
+      <c r="CH18" t="inlineStr">
+        <is>
+          <t>38.04</t>
+        </is>
+      </c>
+      <c r="CI18" t="inlineStr">
+        <is>
+          <t>** 平面顯示器 - 其他零組件** 通信網路 - 主/被動元件、塑膠/金屬機殼** 連接器 - 金屬材料、電鍍材料、塑膠材料** 醫療器材 - 塑化材料</t>
+        </is>
+      </c>
+      <c r="CJ18" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2476</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>-1.14</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>1153.082</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>86.5</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0.69</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>-2.7</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2025-07-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2025-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>2025-03-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2025-03-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>78.2</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>107.0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>95.8</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>92.1</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>-19.16</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>-15.09</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>5.57</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>-0.92</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
+      <c r="AG19" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AM13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO13" t="inlineStr">
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>-3.74</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>-4.77</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>-7.14</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>4.87</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>89.86</t>
+        </is>
+      </c>
+      <c r="AM19" t="n">
+        <v>94.36</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>101.62</v>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>96.9</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>-27.21</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>-3.16</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>-2.48</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>7.19</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr">
+        <is>
+          <t>-134.50</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>2025/07/15</t>
+        </is>
+      </c>
+      <c r="AV19" t="inlineStr">
+        <is>
+          <t>354437913.0685714</t>
+        </is>
+      </c>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>99864028.0</t>
+        </is>
+      </c>
+      <c r="AX19" t="n">
+        <v>138609938.8</v>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>137834914.3</t>
+        </is>
+      </c>
+      <c r="AZ19" t="n">
+        <v>443270959.36</v>
+      </c>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>775024</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>-28391852.12934346</t>
+        </is>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>-28094189.88869017</t>
+        </is>
+      </c>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>99864028.0</t>
+        </is>
+      </c>
+      <c r="BE19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF19" t="inlineStr">
+        <is>
+          <t>81.3</t>
+        </is>
+      </c>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>2025/07/28</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>6.40</t>
+        </is>
+      </c>
+      <c r="BI19" t="inlineStr">
+        <is>
+          <t>鉅祥</t>
+        </is>
+      </c>
+      <c r="BJ19" t="inlineStr">
+        <is>
+          <t>鉅祥</t>
+        </is>
+      </c>
+      <c r="BK19" t="inlineStr">
+        <is>
+          <t>電子零組件業</t>
+        </is>
+      </c>
+      <c r="BL19" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM19" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="BN19" t="inlineStr">
+        <is>
+          <t>-7.291353668658945</t>
+        </is>
+      </c>
+      <c r="BO19" t="inlineStr">
+        <is>
+          <t>11.64963320584363</t>
+        </is>
+      </c>
+      <c r="BP19" t="inlineStr">
+        <is>
+          <t>10.65346457950322</t>
+        </is>
+      </c>
+      <c r="BQ19" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BR19" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS19" t="inlineStr">
+        <is>
+          <t>2.27</t>
+        </is>
+      </c>
+      <c r="BT19" t="inlineStr">
+        <is>
+          <t>4.02</t>
+        </is>
+      </c>
+      <c r="BU19" t="inlineStr">
+        <is>
+          <t>9.36</t>
+        </is>
+      </c>
+      <c r="BV19" t="inlineStr">
+        <is>
+          <t>22.39</t>
+        </is>
+      </c>
+      <c r="BW19" t="inlineStr">
+        <is>
+          <t>29.60%</t>
+        </is>
+      </c>
+      <c r="BX19" t="inlineStr">
+        <is>
+          <t>15.93%</t>
+        </is>
+      </c>
+      <c r="BY19" t="inlineStr">
+        <is>
+          <t>34.43</t>
+        </is>
+      </c>
+      <c r="BZ19" t="inlineStr">
+        <is>
+          <t>18369</t>
+        </is>
+      </c>
+      <c r="CA19" t="inlineStr">
+        <is>
+          <t>部品95.14%、模具3.09%、商品銷售1.03%、治具0.75% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB19" t="inlineStr">
+        <is>
+          <t>鉅祥-電子零組件業-上市</t>
+        </is>
+      </c>
+      <c r="CC19" t="inlineStr">
+        <is>
+          <t>電子零組件業右上上市</t>
+        </is>
+      </c>
+      <c r="CD19" t="inlineStr">
+        <is>
+          <t>87.7</t>
+        </is>
+      </c>
+      <c r="CE19" t="inlineStr">
+        <is>
+          <t>87.9</t>
+        </is>
+      </c>
+      <c r="CF19" t="inlineStr">
+        <is>
+          <t>85.9</t>
+        </is>
+      </c>
+      <c r="CG19" t="inlineStr">
+        <is>
+          <t>86.5</t>
+        </is>
+      </c>
+      <c r="CH19" t="inlineStr">
+        <is>
+          <t>38.04</t>
+        </is>
+      </c>
+      <c r="CI19" t="inlineStr">
+        <is>
+          <t>** 平面顯示器 - 其他零組件** 通信網路 - 主/被動元件、塑膠/金屬機殼** 連接器 - 金屬材料、電鍍材料、塑膠材料** 醫療器材 - 塑化材料</t>
+        </is>
+      </c>
+      <c r="CJ19" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2476</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>-2.36</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1638.11</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>87.5</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-0.46</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>-2.7</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>-2.04</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2025-07-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>2025-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>2025-03-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2025-03-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>78.2</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>107.0</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>95.8</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>92.1</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>-18.22</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>-15.09</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>7.92</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>-2.40</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AP13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AS13" t="inlineStr">
+      <c r="AG20" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AT13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AV13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BB13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BC13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BD13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BG13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BH13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BI13" t="inlineStr">
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>-4.12</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>-4.10</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>-6.67</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>5.33</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>91.26</t>
+        </is>
+      </c>
+      <c r="AM20" t="n">
+        <v>95.16</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>101.96</v>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>96.8</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>-23.67</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>-2.86</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>-2.31</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>7.19</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr">
+        <is>
+          <t>-132.15</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>2025/07/15</t>
+        </is>
+      </c>
+      <c r="AV20" t="inlineStr">
+        <is>
+          <t>354437913.0685714</t>
+        </is>
+      </c>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>144178661.0</t>
+        </is>
+      </c>
+      <c r="AX20" t="n">
+        <v>146673374</v>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>149731355.7</t>
+        </is>
+      </c>
+      <c r="AZ20" t="n">
+        <v>454484548.46</v>
+      </c>
+      <c r="BA20" t="inlineStr">
+        <is>
+          <t>-3057981</t>
+        </is>
+      </c>
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>-28445972.53673498</t>
+        </is>
+      </c>
+      <c r="BC20" t="inlineStr">
+        <is>
+          <t>-26523446.49713525</t>
+        </is>
+      </c>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>144178661.0</t>
+        </is>
+      </c>
+      <c r="BE20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF20" t="inlineStr">
+        <is>
+          <t>81.3</t>
+        </is>
+      </c>
+      <c r="BG20" t="inlineStr">
+        <is>
+          <t>2025/07/28</t>
+        </is>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>7.63</t>
+        </is>
+      </c>
+      <c r="BI20" t="inlineStr">
         <is>
           <t>鉅祥</t>
         </is>
       </c>
-      <c r="BJ13" t="inlineStr">
+      <c r="BJ20" t="inlineStr">
         <is>
           <t>鉅祥</t>
         </is>
       </c>
-      <c r="BK13" t="inlineStr">
+      <c r="BK20" t="inlineStr">
         <is>
           <t>電子零組件業</t>
         </is>
       </c>
-      <c r="BL13" t="inlineStr">
+      <c r="BL20" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BM13" t="inlineStr">
-        <is>
-          <t>1.03</t>
-        </is>
-      </c>
-      <c r="BN13" t="inlineStr">
+      <c r="BM20" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="BN20" t="inlineStr">
         <is>
           <t>-7.291353668658945</t>
         </is>
       </c>
-      <c r="BO13" t="inlineStr">
+      <c r="BO20" t="inlineStr">
         <is>
           <t>11.64963320584363</t>
         </is>
       </c>
-      <c r="BP13" t="inlineStr">
+      <c r="BP20" t="inlineStr">
         <is>
           <t>10.65346457950322</t>
         </is>
       </c>
-      <c r="BQ13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BR13" t="inlineStr">
+      <c r="BQ20" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BR20" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BS13" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="BT13" t="inlineStr">
-        <is>
-          <t>3.98</t>
-        </is>
-      </c>
-      <c r="BU13" t="inlineStr">
+      <c r="BS20" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="BT20" t="inlineStr">
+        <is>
+          <t>4.02</t>
+        </is>
+      </c>
+      <c r="BU20" t="inlineStr">
         <is>
           <t>9.36</t>
         </is>
       </c>
-      <c r="BV13" t="inlineStr">
-        <is>
-          <t>22.6</t>
-        </is>
-      </c>
-      <c r="BW13" t="inlineStr">
+      <c r="BV20" t="inlineStr">
+        <is>
+          <t>22.39</t>
+        </is>
+      </c>
+      <c r="BW20" t="inlineStr">
         <is>
           <t>29.60%</t>
         </is>
       </c>
-      <c r="BX13" t="inlineStr">
+      <c r="BX20" t="inlineStr">
         <is>
           <t>15.93%</t>
         </is>
       </c>
-      <c r="BY13" t="inlineStr">
-        <is>
-          <t>33.62</t>
-        </is>
-      </c>
-      <c r="BZ13" t="inlineStr">
-        <is>
-          <t>18538</t>
-        </is>
-      </c>
-      <c r="CA13" t="inlineStr">
+      <c r="BY20" t="inlineStr">
+        <is>
+          <t>34.43</t>
+        </is>
+      </c>
+      <c r="BZ20" t="inlineStr">
+        <is>
+          <t>18369</t>
+        </is>
+      </c>
+      <c r="CA20" t="inlineStr">
         <is>
           <t>部品95.14%、模具3.09%、商品銷售1.03%、治具0.75% (2024年)</t>
         </is>
       </c>
-      <c r="CB13" t="inlineStr">
+      <c r="CB20" t="inlineStr">
         <is>
           <t>鉅祥-電子零組件業-上市</t>
         </is>
       </c>
-      <c r="CC13" t="inlineStr">
-        <is>
-          <t>電子零組件業右下上市</t>
-        </is>
-      </c>
-      <c r="CD13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CE13" t="inlineStr">
+      <c r="CC20" t="inlineStr">
+        <is>
+          <t>電子零組件業右上上市</t>
+        </is>
+      </c>
+      <c r="CD20" t="inlineStr">
+        <is>
+          <t>88.8</t>
+        </is>
+      </c>
+      <c r="CE20" t="inlineStr">
+        <is>
+          <t>89.9</t>
+        </is>
+      </c>
+      <c r="CF20" t="inlineStr">
+        <is>
+          <t>87.2</t>
+        </is>
+      </c>
+      <c r="CG20" t="inlineStr">
+        <is>
+          <t>87.5</t>
+        </is>
+      </c>
+      <c r="CH20" t="inlineStr">
+        <is>
+          <t>38.04</t>
+        </is>
+      </c>
+      <c r="CI20" t="inlineStr">
+        <is>
+          <t>** 平面顯示器 - 其他零組件** 通信網路 - 主/被動元件、塑膠/金屬機殼** 連接器 - 金屬材料、電鍍材料、塑膠材料** 醫療器材 - 塑化材料</t>
+        </is>
+      </c>
+      <c r="CJ20" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2476</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>-1.56</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>1631.485</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>89.6</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-2.87</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>-2.7</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>-20.69</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2025-07-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>2025-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>2025-03-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2025-03-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>78.2</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>107.0</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>95.8</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>92.1</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>-16.26</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>-15.09</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>7.89</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>-1.90</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="CF13" t="inlineStr">
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>13.16</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>-3.30</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>-3.32</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>-6.3</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>5.78</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>92.66</t>
+        </is>
+      </c>
+      <c r="AM21" t="n">
+        <v>95.84</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>102.28</v>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>96.69</t>
+        </is>
+      </c>
+      <c r="AP21" t="inlineStr">
+        <is>
+          <t>-16.84</t>
+        </is>
+      </c>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>-2.54</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>-2.18</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>7.19</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr">
+        <is>
+          <t>-130.25</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>2025/07/15</t>
+        </is>
+      </c>
+      <c r="AV21" t="inlineStr">
+        <is>
+          <t>354437913.0685714</t>
+        </is>
+      </c>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>147034386.0</t>
+        </is>
+      </c>
+      <c r="AX21" t="n">
+        <v>146439342.4</v>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>184645225.3</t>
+        </is>
+      </c>
+      <c r="AZ21" t="n">
+        <v>461884050.18</v>
+      </c>
+      <c r="BA21" t="inlineStr">
+        <is>
+          <t>-38205882</t>
+        </is>
+      </c>
+      <c r="BB21" t="inlineStr">
+        <is>
+          <t>-28795522.72575311</t>
+        </is>
+      </c>
+      <c r="BC21" t="inlineStr">
+        <is>
+          <t>-28080257.81287342</t>
+        </is>
+      </c>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>147034386.0</t>
+        </is>
+      </c>
+      <c r="BE21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF21" t="inlineStr">
+        <is>
+          <t>81.3</t>
+        </is>
+      </c>
+      <c r="BG21" t="inlineStr">
+        <is>
+          <t>2025/07/28</t>
+        </is>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>10.21</t>
+        </is>
+      </c>
+      <c r="BI21" t="inlineStr">
+        <is>
+          <t>鉅祥</t>
+        </is>
+      </c>
+      <c r="BJ21" t="inlineStr">
+        <is>
+          <t>鉅祥</t>
+        </is>
+      </c>
+      <c r="BK21" t="inlineStr">
+        <is>
+          <t>電子零組件業</t>
+        </is>
+      </c>
+      <c r="BL21" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM21" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="BN21" t="inlineStr">
+        <is>
+          <t>-7.291353668658945</t>
+        </is>
+      </c>
+      <c r="BO21" t="inlineStr">
+        <is>
+          <t>11.64963320584363</t>
+        </is>
+      </c>
+      <c r="BP21" t="inlineStr">
+        <is>
+          <t>10.65346457950322</t>
+        </is>
+      </c>
+      <c r="BQ21" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR21" t="inlineStr">
+        <is>
+          <t>價跌量增</t>
+        </is>
+      </c>
+      <c r="BS21" t="inlineStr">
+        <is>
+          <t>2.36</t>
+        </is>
+      </c>
+      <c r="BT21" t="inlineStr">
+        <is>
+          <t>4.02</t>
+        </is>
+      </c>
+      <c r="BU21" t="inlineStr">
+        <is>
+          <t>9.36</t>
+        </is>
+      </c>
+      <c r="BV21" t="inlineStr">
+        <is>
+          <t>22.39</t>
+        </is>
+      </c>
+      <c r="BW21" t="inlineStr">
+        <is>
+          <t>29.60%</t>
+        </is>
+      </c>
+      <c r="BX21" t="inlineStr">
+        <is>
+          <t>15.93%</t>
+        </is>
+      </c>
+      <c r="BY21" t="inlineStr">
+        <is>
+          <t>34.43</t>
+        </is>
+      </c>
+      <c r="BZ21" t="inlineStr">
+        <is>
+          <t>18369</t>
+        </is>
+      </c>
+      <c r="CA21" t="inlineStr">
+        <is>
+          <t>部品95.14%、模具3.09%、商品銷售1.03%、治具0.75% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB21" t="inlineStr">
+        <is>
+          <t>鉅祥-電子零組件業-上市</t>
+        </is>
+      </c>
+      <c r="CC21" t="inlineStr">
+        <is>
+          <t>電子零組件業右上上市</t>
+        </is>
+      </c>
+      <c r="CD21" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="CE21" t="inlineStr">
+        <is>
+          <t>91.5</t>
+        </is>
+      </c>
+      <c r="CF21" t="inlineStr">
+        <is>
+          <t>89.4</t>
+        </is>
+      </c>
+      <c r="CG21" t="inlineStr">
+        <is>
+          <t>89.6</t>
+        </is>
+      </c>
+      <c r="CH21" t="inlineStr">
+        <is>
+          <t>38.04</t>
+        </is>
+      </c>
+      <c r="CI21" t="inlineStr">
+        <is>
+          <t>** 平面顯示器 - 其他零組件** 通信網路 - 主/被動元件、塑膠/金屬機殼** 連接器 - 金屬材料、電鍍材料、塑膠材料** 醫療器材 - 塑化材料</t>
+        </is>
+      </c>
+      <c r="CJ21" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2476</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>-4.0</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>1815.561</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-4.48</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>-2.7</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>-32.28</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2025-07-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>2025-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>2025-03-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2025-03-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>78.2</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>107.0</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>95.8</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>92.1</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>-14.95</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>-15.09</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>8.78</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>-2.53</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="CG13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="CH13" t="inlineStr">
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>15.79</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>-2.55</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>-3.05</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>-6.05</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>6.20</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>93.38</t>
+        </is>
+      </c>
+      <c r="AM22" t="n">
+        <v>96.31999999999999</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>102.52</v>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>96.53</t>
+        </is>
+      </c>
+      <c r="AP22" t="inlineStr">
+        <is>
+          <t>-10.98</t>
+        </is>
+      </c>
+      <c r="AQ22" t="inlineStr">
+        <is>
+          <t>-2.31</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>-2.08</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>7.19</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr">
+        <is>
+          <t>-128.98</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>2025/07/15</t>
+        </is>
+      </c>
+      <c r="AV22" t="inlineStr">
+        <is>
+          <t>354437913.0685714</t>
+        </is>
+      </c>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>166787289.0</t>
+        </is>
+      </c>
+      <c r="AX22" t="n">
+        <v>135964184</v>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>200767284.9</t>
+        </is>
+      </c>
+      <c r="AZ22" t="n">
+        <v>481289771.06</v>
+      </c>
+      <c r="BA22" t="inlineStr">
+        <is>
+          <t>-64803100</t>
+        </is>
+      </c>
+      <c r="BB22" t="inlineStr">
+        <is>
+          <t>-28925570.89173124</t>
+        </is>
+      </c>
+      <c r="BC22" t="inlineStr">
+        <is>
+          <t>-29607378.16346818</t>
+        </is>
+      </c>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>166787289.0</t>
+        </is>
+      </c>
+      <c r="BE22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF22" t="inlineStr">
+        <is>
+          <t>81.3</t>
+        </is>
+      </c>
+      <c r="BG22" t="inlineStr">
+        <is>
+          <t>2025/07/28</t>
+        </is>
+      </c>
+      <c r="BH22" t="inlineStr">
+        <is>
+          <t>11.93</t>
+        </is>
+      </c>
+      <c r="BI22" t="inlineStr">
+        <is>
+          <t>鉅祥</t>
+        </is>
+      </c>
+      <c r="BJ22" t="inlineStr">
+        <is>
+          <t>鉅祥</t>
+        </is>
+      </c>
+      <c r="BK22" t="inlineStr">
+        <is>
+          <t>電子零組件業</t>
+        </is>
+      </c>
+      <c r="BL22" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM22" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="BN22" t="inlineStr">
+        <is>
+          <t>-7.291353668658945</t>
+        </is>
+      </c>
+      <c r="BO22" t="inlineStr">
+        <is>
+          <t>11.64963320584363</t>
+        </is>
+      </c>
+      <c r="BP22" t="inlineStr">
+        <is>
+          <t>10.65346457950322</t>
+        </is>
+      </c>
+      <c r="BQ22" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR22" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS22" t="inlineStr">
+        <is>
+          <t>2.39</t>
+        </is>
+      </c>
+      <c r="BT22" t="inlineStr">
+        <is>
+          <t>4.02</t>
+        </is>
+      </c>
+      <c r="BU22" t="inlineStr">
+        <is>
+          <t>9.36</t>
+        </is>
+      </c>
+      <c r="BV22" t="inlineStr">
+        <is>
+          <t>22.39</t>
+        </is>
+      </c>
+      <c r="BW22" t="inlineStr">
+        <is>
+          <t>29.60%</t>
+        </is>
+      </c>
+      <c r="BX22" t="inlineStr">
+        <is>
+          <t>15.93%</t>
+        </is>
+      </c>
+      <c r="BY22" t="inlineStr">
+        <is>
+          <t>34.43</t>
+        </is>
+      </c>
+      <c r="BZ22" t="inlineStr">
+        <is>
+          <t>18369</t>
+        </is>
+      </c>
+      <c r="CA22" t="inlineStr">
+        <is>
+          <t>部品95.14%、模具3.09%、商品銷售1.03%、治具0.75% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB22" t="inlineStr">
+        <is>
+          <t>鉅祥-電子零組件業-上市</t>
+        </is>
+      </c>
+      <c r="CC22" t="inlineStr">
+        <is>
+          <t>電子零組件業右上上市</t>
+        </is>
+      </c>
+      <c r="CD22" t="inlineStr">
+        <is>
+          <t>92.5</t>
+        </is>
+      </c>
+      <c r="CE22" t="inlineStr">
+        <is>
+          <t>93.3</t>
+        </is>
+      </c>
+      <c r="CF22" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="CG22" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="CH22" t="inlineStr">
         <is>
           <t>38.04</t>
         </is>
       </c>
-      <c r="CI13" t="inlineStr">
+      <c r="CI22" t="inlineStr">
         <is>
           <t>** 平面顯示器 - 其他零組件** 通信網路 - 主/被動元件、塑膠/金屬機殼** 連接器 - 金屬材料、電鍍材料、塑膠材料** 醫療器材 - 塑化材料</t>
         </is>
       </c>
-      <c r="CJ13" t="inlineStr">
+      <c r="CJ22" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2476</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1.28</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>1433.749</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>94.7</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-8.73</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>-2.7</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>-41.55</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>50.0</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2025-07-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>2025-09-16 00:00:00</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>2025-03-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2025-03-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>78.2</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>107.0</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>95.8</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>92.1</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>-11.50</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>-15.09</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>6.93</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>39.47</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>28.29</t>
+        </is>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>0.85</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>-2.99</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>-5.8</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>6.60</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>93.9</t>
+        </is>
+      </c>
+      <c r="AM23" t="n">
+        <v>96.8</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>102.75</v>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>96.39</t>
+        </is>
+      </c>
+      <c r="AP23" t="inlineStr">
+        <is>
+          <t>-5.06</t>
+        </is>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>-2.13</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>-2.03</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>7.19</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr">
+        <is>
+          <t>-128.18</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>2025/07/15</t>
+        </is>
+      </c>
+      <c r="AV23" t="inlineStr">
+        <is>
+          <t>354437913.0685714</t>
+        </is>
+      </c>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>135185330.0</t>
+        </is>
+      </c>
+      <c r="AX23" t="n">
+        <v>126336486.8</v>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>216135889.2</t>
+        </is>
+      </c>
+      <c r="AZ23" t="n">
+        <v>501408648.9</v>
+      </c>
+      <c r="BA23" t="inlineStr">
+        <is>
+          <t>-89799402</t>
+        </is>
+      </c>
+      <c r="BB23" t="inlineStr">
+        <is>
+          <t>-28801605.93323361</t>
+        </is>
+      </c>
+      <c r="BC23" t="inlineStr">
+        <is>
+          <t>-32847954.76562259</t>
+        </is>
+      </c>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>135185330.0</t>
+        </is>
+      </c>
+      <c r="BE23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF23" t="inlineStr">
+        <is>
+          <t>81.3</t>
+        </is>
+      </c>
+      <c r="BG23" t="inlineStr">
+        <is>
+          <t>2025/07/28</t>
+        </is>
+      </c>
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>16.48</t>
+        </is>
+      </c>
+      <c r="BI23" t="inlineStr">
+        <is>
+          <t>鉅祥</t>
+        </is>
+      </c>
+      <c r="BJ23" t="inlineStr">
+        <is>
+          <t>鉅祥</t>
+        </is>
+      </c>
+      <c r="BK23" t="inlineStr">
+        <is>
+          <t>電子零組件業</t>
+        </is>
+      </c>
+      <c r="BL23" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM23" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="BN23" t="inlineStr">
+        <is>
+          <t>-7.291353668658945</t>
+        </is>
+      </c>
+      <c r="BO23" t="inlineStr">
+        <is>
+          <t>11.64963320584363</t>
+        </is>
+      </c>
+      <c r="BP23" t="inlineStr">
+        <is>
+          <t>10.65346457950322</t>
+        </is>
+      </c>
+      <c r="BQ23" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR23" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS23" t="inlineStr">
+        <is>
+          <t>2.49</t>
+        </is>
+      </c>
+      <c r="BT23" t="inlineStr">
+        <is>
+          <t>4.02</t>
+        </is>
+      </c>
+      <c r="BU23" t="inlineStr">
+        <is>
+          <t>9.36</t>
+        </is>
+      </c>
+      <c r="BV23" t="inlineStr">
+        <is>
+          <t>22.39</t>
+        </is>
+      </c>
+      <c r="BW23" t="inlineStr">
+        <is>
+          <t>29.60%</t>
+        </is>
+      </c>
+      <c r="BX23" t="inlineStr">
+        <is>
+          <t>15.93%</t>
+        </is>
+      </c>
+      <c r="BY23" t="inlineStr">
+        <is>
+          <t>34.43</t>
+        </is>
+      </c>
+      <c r="BZ23" t="inlineStr">
+        <is>
+          <t>18369</t>
+        </is>
+      </c>
+      <c r="CA23" t="inlineStr">
+        <is>
+          <t>部品95.14%、模具3.09%、商品銷售1.03%、治具0.75% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB23" t="inlineStr">
+        <is>
+          <t>鉅祥-電子零組件業-上市</t>
+        </is>
+      </c>
+      <c r="CC23" t="inlineStr">
+        <is>
+          <t>電子零組件業右上上市</t>
+        </is>
+      </c>
+      <c r="CD23" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="CE23" t="inlineStr">
+        <is>
+          <t>95.3</t>
+        </is>
+      </c>
+      <c r="CF23" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="CG23" t="inlineStr">
+        <is>
+          <t>94.7</t>
+        </is>
+      </c>
+      <c r="CH23" t="inlineStr">
+        <is>
+          <t>38.04</t>
+        </is>
+      </c>
+      <c r="CI23" t="inlineStr">
+        <is>
+          <t>** 平面顯示器 - 其他零組件** 通信網路 - 主/被動元件、塑膠/金屬機殼** 連接器 - 金屬材料、電鍍材料、塑膠材料** 醫療器材 - 塑化材料</t>
+        </is>
+      </c>
+      <c r="CJ23" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/電鍍材料.xlsx
+++ b/Result/checksun_type/電鍍材料.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>197.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,69 +898,69 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>44.65</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>-48.71</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2025-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2025-10-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2025-08-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2025-08-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>45.6</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
           <t>44.45</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>-0.12</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>-48.61</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2025-10-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2025-10-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2025-08-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2025-08-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>45.6</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>44.45</t>
-        </is>
-      </c>
       <c r="S2" t="inlineStr">
         <is>
           <t>0</t>
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1019,32 +1019,32 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>197</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>76.36</t>
+          <t>79.07</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>85.14</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
@@ -1054,33 +1054,33 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>43.82000000000001</t>
+          <t>44.16</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>43.49</v>
+        <v>43.52</v>
       </c>
       <c r="AN2" t="n">
-        <v>43.94</v>
+        <v>43.95</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>45.21</t>
+          <t>45.23</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>125.94</t>
+          <t>194.44</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-106.54</t>
+          <t>-104.40</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>28167.14142857143</t>
+          <t>28145.93580599144</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>5546.0</t>
+          <t>8868.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>8273.799999999999</v>
+        <v>7955.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>16100.5</t>
+          <t>15511.6</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>13310.48</v>
+        <v>13262.22</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-7826</t>
+          <t>-7556</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-217.9379326656332</t>
+          <t>-483.5444389217631</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-1870.333011980483</t>
+          <t>-1944.380223330478</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>5546.0</t>
+          <t>8868.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-10.92</t>
+          <t>-10.52</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>44.86</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1973</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>44.45</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>44.45</t>
+          <t>44.65</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>302.0</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>44.45</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-17.23</t>
+          <t>-48.61</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1449,68 +1449,68 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>197</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>76.36</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>72.02</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>43.92</t>
+          <t>43.82000000000001</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>43.47</v>
+        <v>43.49</v>
       </c>
       <c r="AN3" t="n">
         <v>43.94</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>45.23</t>
+          <t>45.21</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>91.47</t>
+          <t>125.94</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-108.60</t>
+          <t>-106.54</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>28167.14142857143</t>
+          <t>28145.93580599144</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>13560.0</t>
+          <t>5546.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>13265.8</v>
+        <v>8273.799999999999</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>16027.3</t>
+          <t>16100.5</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>13521.82</v>
+        <v>13310.48</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-2761</t>
+          <t>-7826</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>82.49753630070325</t>
+          <t>-217.9379326656332</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-1341.825102481189</t>
+          <t>-1870.333011980483</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>13560.0</t>
+          <t>5546.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-9.62</t>
+          <t>-10.92</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>44.86</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1973</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>44.45</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>44.45</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>118.0</t>
+          <t>302.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>9.71</t>
+          <t>-17.23</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1879,68 +1879,68 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>197</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>65.43</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>55.14</t>
+          <t>72.02</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.1</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.80</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>43.92</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>43.44</v>
+        <v>43.47</v>
       </c>
       <c r="AN4" t="n">
-        <v>43.92</v>
+        <v>43.94</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>45.19</t>
+          <t>45.23</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>41.21</t>
+          <t>91.47</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-110.57</t>
+          <t>-108.60</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>28167.14142857143</t>
+          <t>28145.93580599144</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>5178.0</t>
+          <t>13560.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>16692.8</v>
+        <v>13265.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>15215.7</t>
+          <t>16027.3</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>13519.76</v>
+        <v>13521.82</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>-2761</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>341.4652888065019</t>
+          <t>82.49753630070325</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-1397.534335250723</t>
+          <t>-1341.825102481189</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>5178.0</t>
+          <t>13560.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-12.63</t>
+          <t>-9.62</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>44.86</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1973</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>43.45</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>43.45</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>118.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>28.77</t>
+          <t>9.71</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2309,68 +2309,68 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>197</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>50.62</t>
+          <t>65.43</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>66.26</t>
+          <t>55.14</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>43.84</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>43.45</v>
+        <v>43.44</v>
       </c>
       <c r="AN5" t="n">
-        <v>43.97</v>
+        <v>43.92</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>45.12</t>
+          <t>45.19</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>34.76</t>
+          <t>41.21</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-111.66</t>
+          <t>-110.57</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>28167.14142857143</t>
+          <t>28145.93580599144</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>6625.0</t>
+          <t>5178.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>21302.2</v>
+        <v>16692.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>16542.7</t>
+          <t>15215.7</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>13576.72</v>
+        <v>13519.76</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>4759</t>
+          <t>1477</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>657.6470386350882</t>
+          <t>341.4652888065019</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-529.1355843768179</t>
+          <t>-1397.534335250723</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>6625.0</t>
+          <t>5178.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-13.83</t>
+          <t>-12.63</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>44.86</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>1973</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>43.45</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>42.8</t>
+          <t>43.45</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-4.49</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>42.95</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>20.84</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>5.89</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2739,68 +2739,68 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>197</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>49.38</t>
+          <t>50.62</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>82.72</t>
+          <t>66.26</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>43.71</t>
+          <t>43.84</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>43.5</v>
+        <v>43.45</v>
       </c>
       <c r="AN6" t="n">
-        <v>44.03</v>
+        <v>43.97</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>45.06</t>
+          <t>45.12</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>44.24</t>
+          <t>34.76</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-112.67</t>
+          <t>-111.66</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>28167.14142857143</t>
+          <t>28145.93580599144</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>10460.0</t>
+          <t>6625.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>23067.8</v>
+        <v>21302.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>19089.8</t>
+          <t>16542.7</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>13602.9</v>
+        <v>13576.72</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>3978</t>
+          <t>4759</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>873.4256973645256</t>
+          <t>657.6470386350882</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>575.296044885079</t>
+          <t>-529.1355843768179</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>10460.0</t>
+          <t>6625.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-13.93</t>
+          <t>-13.83</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>44.86</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>1973</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>42.8</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>42.95</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>670.0</t>
+          <t>240.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>44.95</t>
+          <t>42.95</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>3.81</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>24.67</t>
+          <t>20.84</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16.44</t>
+          <t>5.89</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3169,68 +3169,68 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>197</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>98.77</t>
+          <t>49.38</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>94.23</t>
+          <t>82.72</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>43.31</t>
+          <t>43.71</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>43.58</v>
+        <v>43.5</v>
       </c>
       <c r="AN7" t="n">
-        <v>44.1</v>
+        <v>44.03</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>45.01</t>
+          <t>45.06</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>56.72</t>
+          <t>44.24</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-114.07</t>
+          <t>-112.67</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>28167.14142857143</t>
+          <t>28145.93580599144</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>30506.0</t>
+          <t>10460.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>23927.2</v>
+        <v>23067.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>19193.0</t>
+          <t>19089.8</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>13522.88</v>
+        <v>13602.9</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>4734</t>
+          <t>3978</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>927.631088724425</t>
+          <t>873.4256973645256</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>1721.616370799031</t>
+          <t>575.296044885079</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>30506.0</t>
+          <t>10460.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-9.92</t>
+          <t>-13.93</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>44.86</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>1973</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>46.55</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>44.95</t>
+          <t>42.95</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>685.0</t>
+          <t>670.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>44.95</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,102 +3488,102 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
+          <t>24.67</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2025-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2025-10-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2025-08-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2025-08-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>45.6</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>44.45</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>52.5</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>47.6</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>1.12</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
           <t>-4.20</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>2025-10-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2025-10-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2025-08-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2025-08-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>45.6</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>44.45</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>52.5</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>47.6</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>1.24</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>-4.20</t>
-        </is>
-      </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16.81</t>
+          <t>16.44</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3599,269 +3599,269 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>197</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>98.77</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>75.04</t>
+          <t>94.23</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>42.73999999999999</t>
+          <t>43.31</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>43.61</v>
+        <v>43.58</v>
       </c>
       <c r="AN8" t="n">
-        <v>44.12</v>
+        <v>44.1</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
+          <t>45.01</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>56.72</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>-0.17</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>-0.39</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>2.77</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>-114.07</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>2025/11/19</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>28145.93580599144</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>30506.0</t>
+        </is>
+      </c>
+      <c r="AX8" t="n">
+        <v>23927.2</v>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>19193.0</t>
+        </is>
+      </c>
+      <c r="AZ8" t="n">
+        <v>13522.88</v>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>4734</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>927.631088724425</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>1721.616370799031</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>30506.0</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>49.9</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>2025/08/12</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>-9.92</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>匯鑽科</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>匯鑽科</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>0.78</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
+          <t>-10.56465687102404</t>
+        </is>
+      </c>
+      <c r="BO8" t="inlineStr">
+        <is>
+          <t>-13.69932964657055</t>
+        </is>
+      </c>
+      <c r="BP8" t="inlineStr">
+        <is>
+          <t>7.80229574004913</t>
+        </is>
+      </c>
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS8" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="BT8" t="inlineStr">
+        <is>
+          <t>2.52</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
+          <t>6.59</t>
+        </is>
+      </c>
+      <c r="BV8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
+          <t>8.25%</t>
+        </is>
+      </c>
+      <c r="BX8" t="inlineStr">
+        <is>
+          <t>-14.21%</t>
+        </is>
+      </c>
+      <c r="BY8" t="inlineStr">
+        <is>
+          <t>44.86</t>
+        </is>
+      </c>
+      <c r="BZ8" t="inlineStr">
+        <is>
+          <t>1982</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
+          <t>加工業務99.90%、勞務0.10% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>匯鑽科-其他電子業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC8" t="inlineStr">
+        <is>
+          <t>其他電子業右下上櫃</t>
+        </is>
+      </c>
+      <c r="CD8" t="inlineStr">
+        <is>
+          <t>45.5</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
+          <t>46.55</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
+          <t>44.8</t>
+        </is>
+      </c>
+      <c r="CG8" t="inlineStr">
+        <is>
           <t>44.95</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>24.64</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>-0.34</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>-0.45</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>2.77</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>-116.07</t>
-        </is>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>2025/11/19</t>
-        </is>
-      </c>
-      <c r="AV8" t="inlineStr">
-        <is>
-          <t>28167.14142857143</t>
-        </is>
-      </c>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>30695.0</t>
-        </is>
-      </c>
-      <c r="AX8" t="n">
-        <v>18788.8</v>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>19613.1</t>
-        </is>
-      </c>
-      <c r="AZ8" t="n">
-        <v>13049.74</v>
-      </c>
-      <c r="BA8" t="inlineStr">
-        <is>
-          <t>-824</t>
-        </is>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>783.2701283472239</t>
-        </is>
-      </c>
-      <c r="BC8" t="inlineStr">
-        <is>
-          <t>1149.944823147569</t>
-        </is>
-      </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>30695.0</t>
-        </is>
-      </c>
-      <c r="BE8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>49.9</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>2025/08/12</t>
-        </is>
-      </c>
-      <c r="BH8" t="inlineStr">
-        <is>
-          <t>-9.82</t>
-        </is>
-      </c>
-      <c r="BI8" t="inlineStr">
-        <is>
-          <t>匯鑽科</t>
-        </is>
-      </c>
-      <c r="BJ8" t="inlineStr">
-        <is>
-          <t>匯鑽科</t>
-        </is>
-      </c>
-      <c r="BK8" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BL8" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM8" t="inlineStr">
-        <is>
-          <t>0.78</t>
-        </is>
-      </c>
-      <c r="BN8" t="inlineStr">
-        <is>
-          <t>-10.56465687102404</t>
-        </is>
-      </c>
-      <c r="BO8" t="inlineStr">
-        <is>
-          <t>-13.69932964657055</t>
-        </is>
-      </c>
-      <c r="BP8" t="inlineStr">
-        <is>
-          <t>7.80229574004913</t>
-        </is>
-      </c>
-      <c r="BQ8" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
-        </is>
-      </c>
-      <c r="BR8" t="inlineStr">
-        <is>
-          <t>價漲量增</t>
-        </is>
-      </c>
-      <c r="BS8" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
-      </c>
-      <c r="BT8" t="inlineStr">
-        <is>
-          <t>2.53</t>
-        </is>
-      </c>
-      <c r="BU8" t="inlineStr">
-        <is>
-          <t>6.59</t>
-        </is>
-      </c>
-      <c r="BV8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BW8" t="inlineStr">
-        <is>
-          <t>8.25%</t>
-        </is>
-      </c>
-      <c r="BX8" t="inlineStr">
-        <is>
-          <t>-14.21%</t>
-        </is>
-      </c>
-      <c r="BY8" t="inlineStr">
-        <is>
-          <t>43.4</t>
-        </is>
-      </c>
-      <c r="BZ8" t="inlineStr">
-        <is>
-          <t>1973</t>
-        </is>
-      </c>
-      <c r="CA8" t="inlineStr">
-        <is>
-          <t>加工業務99.90%、勞務0.10% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB8" t="inlineStr">
-        <is>
-          <t>匯鑽科-其他電子業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC8" t="inlineStr">
-        <is>
-          <t>其他電子業右下上櫃</t>
-        </is>
-      </c>
-      <c r="CD8" t="inlineStr">
-        <is>
-          <t>43.55</t>
-        </is>
-      </c>
-      <c r="CE8" t="inlineStr">
-        <is>
-          <t>45.55</t>
-        </is>
-      </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>43.3</t>
-        </is>
-      </c>
-      <c r="CG8" t="inlineStr">
-        <is>
-          <t>45.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3883,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>655.0</t>
+          <t>685.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-32.14</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>16.81</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4029,68 +4029,68 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>197</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>83.93</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>75.04</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>42.22000000000001</t>
+          <t>42.73999999999999</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>43.6</v>
+        <v>43.61</v>
       </c>
       <c r="AN9" t="n">
-        <v>44.15</v>
+        <v>44.12</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>44.89</t>
+          <t>44.95</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-16.05</t>
+          <t>24.64</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-117.06</t>
+          <t>-116.07</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>28167.14142857143</t>
+          <t>28145.93580599144</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>28225.0</t>
+          <t>30695.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>13738.6</v>
+        <v>18788.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>20246.9</t>
+          <t>19613.1</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>12733.2</v>
+        <v>13049.74</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-6508</t>
+          <t>-824</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>716.6020020198885</t>
+          <t>783.2701283472239</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>271.9517256759318</t>
+          <t>1149.944823147569</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>28225.0</t>
+          <t>30695.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-13.23</t>
+          <t>-9.82</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>44.86</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>1973</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>42.35</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>369.0</t>
+          <t>655.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>42.35</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4.72</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-43.86</t>
+          <t>-32.14</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-4.72</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>9.06</t>
+          <t>16.07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4459,68 +4459,68 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>197</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>41.18</t>
+          <t>83.93</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>14.84</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>42.22000000000001</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>43.53</v>
+        <v>43.6</v>
       </c>
       <c r="AN10" t="n">
-        <v>44.23</v>
+        <v>44.15</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>44.87</t>
+          <t>44.89</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-40.91</t>
+          <t>-16.05</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-116.38</t>
+          <t>-117.06</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>28167.14142857143</t>
+          <t>28145.93580599144</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>15453.0</t>
+          <t>28225.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>11783.2</v>
+        <v>13738.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>20989.4</t>
+          <t>20246.9</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>12346.96</v>
+        <v>12733.2</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-9206</t>
+          <t>-6508</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>797.4475068096988</t>
+          <t>716.6020020198885</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-727.3938323434086</t>
+          <t>271.9517256759318</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>15453.0</t>
+          <t>28225.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-15.13</t>
+          <t>-13.23</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>44.86</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>1973</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>42.7</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>42.35</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>42.35</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>358.0</t>
+          <t>369.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>42.35</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>7.87</t>
+          <t>5.15</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-27.59</t>
+          <t>-43.86</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-7.87</t>
+          <t>-4.72</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>8.79</t>
+          <t>9.06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4889,68 +4889,68 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>197</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>41.18</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>14.84</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-3.31</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>42.04000000000001</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>43.48</v>
+        <v>43.53</v>
       </c>
       <c r="AN11" t="n">
-        <v>44.31</v>
+        <v>44.23</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>44.85</t>
+          <t>44.87</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-59.38</t>
+          <t>-40.91</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-114.70</t>
+          <t>-116.38</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>28167.14142857143</t>
+          <t>28145.93580599144</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>14757.0</t>
+          <t>15453.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>15111.8</v>
+        <v>11783.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>20870.2</t>
+          <t>20989.4</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>12172.68</v>
+        <v>12346.96</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-5758</t>
+          <t>-9206</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>1074.691386655718</t>
+          <t>797.4475068096988</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-760.6234212159197</t>
+          <t>-727.3938323434086</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>14757.0</t>
+          <t>15453.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-17.94</t>
+          <t>-15.13</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>44.86</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1973</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>42.45</t>
+          <t>42.7</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>42.35</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>358.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>8.29</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-29.63</t>
+          <t>-27.59</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-5.29</t>
+          <t>-7.87</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>8.79</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,12 +5319,12 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>197</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
@@ -5334,53 +5334,53 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-3.31</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>-1.88</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>42.55</t>
+          <t>42.04000000000001</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>43.5</v>
+        <v>43.48</v>
       </c>
       <c r="AN12" t="n">
-        <v>44.42</v>
+        <v>44.31</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>44.84</t>
+          <t>44.85</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-46.96</t>
+          <t>-59.38</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-112.52</t>
+          <t>-114.70</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>28167.14142857143</t>
+          <t>28145.93580599144</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>4814.0</t>
+          <t>14757.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>14458.8</v>
+        <v>15111.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>20545.5</t>
+          <t>20870.2</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>12162.98</v>
+        <v>12172.68</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-6086</t>
+          <t>-5758</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>1408.384988086925</t>
+          <t>1074.691386655718</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-706.357711704648</t>
+          <t>-760.6234212159197</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>4814.0</t>
+          <t>14757.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-15.63</t>
+          <t>-17.94</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>44.86</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1973</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
+          <t>42.1</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
           <t>42.45</t>
         </is>
       </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>42.7</t>
-        </is>
-      </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>41.95</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5603,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>630.229</t>
+          <t>461.141</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-2.7</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-29.59</t>
+          <t>-33.87</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-18.60</t>
+          <t>-17.94</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,73 +5744,73 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>461</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>39.02</t>
+          <t>85.19</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>31.54</t>
+          <t>55.95</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-5.08</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-7.16</t>
+          <t>-7.23</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>86.64</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>91.28</v>
+        <v>90.84</v>
       </c>
       <c r="AN13" t="n">
-        <v>98.31</v>
+        <v>97.92</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>97.43</t>
+          <t>97.54</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-3.11</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-3.15</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,53 +5820,53 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-143.82</t>
+          <t>-143.71</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>2025/07/15</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>354437913.0685714</t>
+          <t>354018572.6854494</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>55246132.0</t>
+          <t>40320203.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>67438997.8</v>
+        <v>54978050.8</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>95782499.1</t>
+          <t>83135790.5</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>275665355.36</v>
+        <v>260959475.16</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-28343501</t>
+          <t>-28157739</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-29782766.16711858</t>
+          <t>-29753556.07515229</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-29852555.79943146</t>
+          <t>-29592900.56933765</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>55246132.0</t>
+          <t>40320203.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>7.13</t>
+          <t>8.00</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>22.39</t>
+          <t>22.57</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>34.43</t>
+          <t>34.84</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>18369</t>
+          <t>18517</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6001,17 +6001,17 @@
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.9</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>713.512</t>
+          <t>630.229</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-2.7</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-33.57</t>
+          <t>-29.59</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-17.85</t>
+          <t>-18.60</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,73 +6174,73 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>461</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>43.64</t>
+          <t>39.02</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>31.54</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-5.14</t>
+          <t>-5.08</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-7.33</t>
+          <t>-7.16</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>86.85999999999999</t>
+          <t>86.64</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>91.56999999999999</v>
+        <v>91.28</v>
       </c>
       <c r="AN14" t="n">
-        <v>98.81999999999999</v>
+        <v>98.31</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>97.34</t>
+          <t>97.43</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-8.10</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-3.12</t>
+          <t>-3.15</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,53 +6250,53 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-143.38</t>
+          <t>-143.82</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>2025/07/15</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>354437913.0685714</t>
+          <t>354018572.6854494</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>62492000.0</t>
+          <t>55246132.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>68942899</v>
+        <v>67438997.8</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>103776418.9</t>
+          <t>95782499.1</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>296624289.38</v>
+        <v>275665355.36</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-34833519</t>
+          <t>-28343501</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-29770077.14306169</t>
+          <t>-29782766.16711858</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-30756535.8138715</t>
+          <t>-29852555.79943146</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>62492000.0</t>
+          <t>55246132.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>7.13</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6361,22 +6361,22 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>22.39</t>
+          <t>22.57</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>34.43</t>
+          <t>34.84</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>18369</t>
+          <t>18517</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>557.755</t>
+          <t>713.512</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-2.7</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-31.49</t>
+          <t>-33.57</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-19.07</t>
+          <t>-17.85</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,73 +6604,73 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>461</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>11.96</t>
+          <t>43.64</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>6.16</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-5.79</t>
+          <t>-5.14</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-7.52</t>
+          <t>-7.33</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>86.58</t>
+          <t>86.85999999999999</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>91.90000000000001</v>
+        <v>91.56999999999999</v>
       </c>
       <c r="AN15" t="n">
-        <v>99.37</v>
+        <v>98.81999999999999</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>97.25</t>
+          <t>97.34</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-15.28</t>
+          <t>-8.10</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-3.12</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,53 +6680,53 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-142.50</t>
+          <t>-143.38</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>2025/07/15</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>354437913.0685714</t>
+          <t>354018572.6854494</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>48395514.0</t>
+          <t>62492000.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>76417304.59999999</v>
+        <v>68942899</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>111545339.3</t>
+          <t>103776418.9</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>319430807.84</v>
+        <v>296624289.38</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-35128034</t>
+          <t>-34833519</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-29590721.02109627</t>
+          <t>-29770077.14306169</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-31725831.12686187</t>
+          <t>-30756535.8138715</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>48395514.0</t>
+          <t>62492000.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>8.12</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6791,22 +6791,22 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>22.39</t>
+          <t>22.57</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>34.43</t>
+          <t>34.84</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>18369</t>
+          <t>18517</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>797.916</t>
+          <t>557.755</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>86.1</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-2.7</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-21.02</t>
+          <t>-31.49</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-19.53</t>
+          <t>-19.07</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,151 +7034,151 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>461</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
+          <t>11.96</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>6.16</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>-5.79</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>-7.52</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>86.58</t>
+        </is>
+      </c>
+      <c r="AM16" t="n">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>99.37</v>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>97.25</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>-15.28</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>-3.52</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>-3.06</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>7.19</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr">
+        <is>
+          <t>-142.50</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>2025/11/28</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>354018572.6854494</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>48395514.0</t>
+        </is>
+      </c>
+      <c r="AX16" t="n">
+        <v>76417304.59999999</v>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>111545339.3</t>
+        </is>
+      </c>
+      <c r="AZ16" t="n">
+        <v>319430807.84</v>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>-35128034</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>-29590721.02109627</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>-31725831.12686187</t>
+        </is>
+      </c>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>48395514.0</t>
+        </is>
+      </c>
+      <c r="BE16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF16" t="inlineStr">
+        <is>
+          <t>81.3</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>2025/07/28</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
           <t>6.52</t>
         </is>
       </c>
-      <c r="AG16" t="inlineStr">
-        <is>
-          <t>9.08</t>
-        </is>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>-0.76</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>-6.01</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>-7.68</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>2.91</t>
-        </is>
-      </c>
-      <c r="AL16" t="inlineStr">
-        <is>
-          <t>86.75999999999999</t>
-        </is>
-      </c>
-      <c r="AM16" t="n">
-        <v>92.31</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>99.98999999999999</v>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>97.16</t>
-        </is>
-      </c>
-      <c r="AP16" t="inlineStr">
-        <is>
-          <t>-20.19</t>
-        </is>
-      </c>
-      <c r="AQ16" t="inlineStr">
-        <is>
-          <t>-3.53</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>-2.94</t>
-        </is>
-      </c>
-      <c r="AS16" t="inlineStr">
-        <is>
-          <t>7.19</t>
-        </is>
-      </c>
-      <c r="AT16" t="inlineStr">
-        <is>
-          <t>-140.87</t>
-        </is>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>2025/07/15</t>
-        </is>
-      </c>
-      <c r="AV16" t="inlineStr">
-        <is>
-          <t>354437913.0685714</t>
-        </is>
-      </c>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>68436405.0</t>
-        </is>
-      </c>
-      <c r="AX16" t="n">
-        <v>95573934</v>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>121006638.2</t>
-        </is>
-      </c>
-      <c r="AZ16" t="n">
-        <v>336619552.5</v>
-      </c>
-      <c r="BA16" t="inlineStr">
-        <is>
-          <t>-25432704</t>
-        </is>
-      </c>
-      <c r="BB16" t="inlineStr">
-        <is>
-          <t>-29202519.18368434</t>
-        </is>
-      </c>
-      <c r="BC16" t="inlineStr">
-        <is>
-          <t>-30467135.53374588</t>
-        </is>
-      </c>
-      <c r="BD16" t="inlineStr">
-        <is>
-          <t>68436405.0</t>
-        </is>
-      </c>
-      <c r="BE16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF16" t="inlineStr">
-        <is>
-          <t>81.3</t>
-        </is>
-      </c>
-      <c r="BG16" t="inlineStr">
-        <is>
-          <t>2025/07/28</t>
-        </is>
-      </c>
-      <c r="BH16" t="inlineStr">
-        <is>
-          <t>5.90</t>
-        </is>
-      </c>
       <c r="BI16" t="inlineStr">
         <is>
           <t>鉅祥</t>
@@ -7221,7 +7221,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>22.39</t>
+          <t>22.57</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>34.43</t>
+          <t>34.84</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>18369</t>
+          <t>18517</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>85.1</t>
+          <t>85.9</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>86.1</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-3.11</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1197.387</t>
+          <t>797.916</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>86.1</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-2.7</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-9.98</t>
+          <t>-21.02</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-20.09</t>
+          <t>-19.53</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>5.79</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,73 +7464,73 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>461</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>6.91</t>
+          <t>9.08</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-5.99</t>
+          <t>-6.01</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-7.53</t>
+          <t>-7.68</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>87.46000000000001</t>
+          <t>86.75999999999999</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>93.03</v>
+        <v>92.31</v>
       </c>
       <c r="AN17" t="n">
-        <v>100.61</v>
+        <v>99.98999999999999</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>97.09</t>
+          <t>97.16</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-23.35</t>
+          <t>-20.19</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>-3.53</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,53 +7540,53 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-138.81</t>
+          <t>-140.87</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>2025/07/15</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>354437913.0685714</t>
+          <t>354018572.6854494</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>102624938.0</t>
+          <t>68436405.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>111293530.2</v>
+        <v>95573934</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>123628857.1</t>
+          <t>121006638.2</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>366752945.54</v>
+        <v>336619552.5</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-12335326</t>
+          <t>-25432704</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-28972588.9382186</t>
+          <t>-29202519.18368434</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-29728125.31023213</t>
+          <t>-30467135.53374588</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>102624938.0</t>
+          <t>68436405.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>5.17</t>
+          <t>5.90</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7661,12 +7661,12 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>22.39</t>
+          <t>22.57</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>34.43</t>
+          <t>34.84</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>18369</t>
+          <t>18517</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>86.1</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>-3.11</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>710.084</t>
+          <t>1197.387</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-2.7</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-9.98</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-17.57</t>
+          <t>-20.09</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>5.79</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,17 +7894,17 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>461</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>20.73</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
@@ -7914,53 +7914,53 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-5.54</t>
+          <t>-5.99</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-7.34</t>
+          <t>-7.53</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>88.56</t>
+          <t>87.46000000000001</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>93.75</v>
+        <v>93.03</v>
       </c>
       <c r="AN18" t="n">
-        <v>101.18</v>
+        <v>100.61</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>97.04</t>
+          <t>97.09</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-22.39</t>
+          <t>-23.35</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,53 +7970,53 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-136.55</t>
+          <t>-138.81</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>2025/07/15</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>354437913.0685714</t>
+          <t>354018572.6854494</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>62765638.0</t>
+          <t>102624938.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>124126000.4</v>
+        <v>111293530.2</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>125231243.6</t>
+          <t>123628857.1</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>399636300.16</v>
+        <v>366752945.54</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-1105243</t>
+          <t>-12335326</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-28835218.6887616</t>
+          <t>-28972588.9382186</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-31273734.76556134</t>
+          <t>-29728125.31023213</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>62765638.0</t>
+          <t>102624938.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>8.49</t>
+          <t>5.17</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,22 +8081,22 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>22.39</t>
+          <t>22.57</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>34.43</t>
+          <t>34.84</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>18369</t>
+          <t>18517</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>89.4</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1153.082</t>
+          <t>710.084</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-2.7</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-19.16</t>
+          <t>-17.57</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,73 +8324,73 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>461</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.73</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.91</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-3.74</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-5.54</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-7.14</t>
+          <t>-7.34</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>89.86</t>
+          <t>88.56</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>94.36</v>
+        <v>93.75</v>
       </c>
       <c r="AN19" t="n">
-        <v>101.62</v>
+        <v>101.18</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>96.9</t>
+          <t>97.04</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-27.21</t>
+          <t>-22.39</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-2.48</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,53 +8400,53 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-134.50</t>
+          <t>-136.55</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>2025/07/15</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>354437913.0685714</t>
+          <t>354018572.6854494</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>99864028.0</t>
+          <t>62765638.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>138609938.8</v>
+        <v>124126000.4</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>137834914.3</t>
+          <t>125231243.6</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>443270959.36</v>
+        <v>399636300.16</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>775024</t>
+          <t>-1105243</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-28391852.12934346</t>
+          <t>-28835218.6887616</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-28094189.88869017</t>
+          <t>-31273734.76556134</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>99864028.0</t>
+          <t>62765638.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>6.40</t>
+          <t>8.49</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,22 +8511,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>22.39</t>
+          <t>22.57</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>34.43</t>
+          <t>34.84</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>18369</t>
+          <t>18517</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>88.6</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
+          <t>89.4</t>
+        </is>
+      </c>
+      <c r="CF19" t="inlineStr">
+        <is>
           <t>87.9</t>
         </is>
       </c>
-      <c r="CF19" t="inlineStr">
-        <is>
-          <t>85.9</t>
-        </is>
-      </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1638.11</t>
+          <t>1153.082</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-2.7</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-18.22</t>
+          <t>-19.16</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>7.92</t>
+          <t>5.57</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-2.40</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,12 +8754,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>461</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8774,53 +8774,53 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-4.12</t>
+          <t>-3.74</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-4.10</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-6.67</t>
+          <t>-7.14</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>91.26</t>
+          <t>89.86</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>95.16</v>
+        <v>94.36</v>
       </c>
       <c r="AN20" t="n">
-        <v>101.96</v>
+        <v>101.62</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>96.8</t>
+          <t>96.9</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-23.67</t>
+          <t>-27.21</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-2.86</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,53 +8830,53 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-132.15</t>
+          <t>-134.50</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>2025/07/15</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>354437913.0685714</t>
+          <t>354018572.6854494</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>144178661.0</t>
+          <t>99864028.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>146673374</v>
+        <v>138609938.8</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>149731355.7</t>
+          <t>137834914.3</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>454484548.46</v>
+        <v>443270959.36</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-3057981</t>
+          <t>775024</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-28445972.53673498</t>
+          <t>-28391852.12934346</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-26523446.49713525</t>
+          <t>-28094189.88869017</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>144178661.0</t>
+          <t>99864028.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>7.63</t>
+          <t>6.40</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8951,12 +8951,12 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>22.39</t>
+          <t>22.57</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>34.43</t>
+          <t>34.84</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>18369</t>
+          <t>18517</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>89.9</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>85.9</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1631.485</t>
+          <t>1638.11</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-2.7</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-20.69</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-16.26</t>
+          <t>-18.22</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>7.89</t>
+          <t>7.92</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-2.40</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,12 +9184,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>461</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9199,58 +9199,58 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>13.16</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-3.30</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>-4.10</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-6.3</t>
+          <t>-6.67</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>5.78</t>
+          <t>5.33</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>92.66</t>
+          <t>91.26</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>95.84</v>
+        <v>95.16</v>
       </c>
       <c r="AN21" t="n">
-        <v>102.28</v>
+        <v>101.96</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>96.69</t>
+          <t>96.8</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-16.84</t>
+          <t>-23.67</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-2.86</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,53 +9260,53 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-130.25</t>
+          <t>-132.15</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>2025/07/15</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>354437913.0685714</t>
+          <t>354018572.6854494</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>147034386.0</t>
+          <t>144178661.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>146439342.4</v>
+        <v>146673374</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>184645225.3</t>
+          <t>149731355.7</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>461884050.18</v>
+        <v>454484548.46</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-38205882</t>
+          <t>-3057981</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-28795522.72575311</t>
+          <t>-28445972.53673498</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-28080257.81287342</t>
+          <t>-26523446.49713525</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>147034386.0</t>
+          <t>144178661.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>10.21</t>
+          <t>7.63</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9381,12 +9381,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>22.39</t>
+          <t>22.57</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>34.43</t>
+          <t>34.84</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>18369</t>
+          <t>18517</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>89.9</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>89.4</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-4.0</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1815.561</t>
+          <t>1631.485</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-4.48</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-2.7</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-32.28</t>
+          <t>-20.69</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-14.95</t>
+          <t>-16.26</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>8.78</t>
+          <t>7.89</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,12 +9614,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>461</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9629,58 +9629,58 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>15.79</t>
+          <t>13.16</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-3.30</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-3.32</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-6.05</t>
+          <t>-6.3</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>6.20</t>
+          <t>5.78</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>93.38</t>
+          <t>92.66</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>96.31999999999999</v>
+        <v>95.84</v>
       </c>
       <c r="AN22" t="n">
-        <v>102.52</v>
+        <v>102.28</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>96.53</t>
+          <t>96.69</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-10.98</t>
+          <t>-16.84</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,53 +9690,53 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-128.98</t>
+          <t>-130.25</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>2025/07/15</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>354437913.0685714</t>
+          <t>354018572.6854494</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>166787289.0</t>
+          <t>147034386.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>135964184</v>
+        <v>146439342.4</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>200767284.9</t>
+          <t>184645225.3</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>481289771.06</v>
+        <v>461884050.18</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-64803100</t>
+          <t>-38205882</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-28925570.89173124</t>
+          <t>-28795522.72575311</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-29607378.16346818</t>
+          <t>-28080257.81287342</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>166787289.0</t>
+          <t>147034386.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>11.93</t>
+          <t>10.21</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>22.39</t>
+          <t>22.57</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>34.43</t>
+          <t>34.84</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>18369</t>
+          <t>18517</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>89.4</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1433.749</t>
+          <t>1815.561</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>94.7</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-8.73</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-2.7</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-41.55</t>
+          <t>-32.28</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-11.50</t>
+          <t>-14.95</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>8.78</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>-2.53</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,73 +10044,73 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>461</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>39.47</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>28.29</t>
+          <t>15.79</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-5.8</t>
+          <t>-6.05</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>6.60</t>
+          <t>6.20</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>93.9</t>
+          <t>93.38</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>96.8</v>
+        <v>96.31999999999999</v>
       </c>
       <c r="AN23" t="n">
-        <v>102.75</v>
+        <v>102.52</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>96.39</t>
+          <t>96.53</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-5.06</t>
+          <t>-10.98</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-2.13</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,53 +10120,53 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-128.18</t>
+          <t>-128.98</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>2025/07/15</t>
+          <t>2025/11/28</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>354437913.0685714</t>
+          <t>354018572.6854494</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>135185330.0</t>
+          <t>166787289.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>126336486.8</v>
+        <v>135964184</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>216135889.2</t>
+          <t>200767284.9</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>501408648.9</v>
+        <v>481289771.06</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-89799402</t>
+          <t>-64803100</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-28801605.93323361</t>
+          <t>-28925570.89173124</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-32847954.76562259</t>
+          <t>-29607378.16346818</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>135185330.0</t>
+          <t>166787289.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>16.48</t>
+          <t>11.93</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>22.39</t>
+          <t>22.57</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>34.43</t>
+          <t>34.84</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>18369</t>
+          <t>18517</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>95.3</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>94.7</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/電鍍材料.xlsx
+++ b/Result/checksun_type/電鍍材料.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>197.0</t>
+          <t>318.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>44.65</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-48.71</t>
+          <t>-38.19</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>7.80</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1019,12 +1019,12 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>318</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>79.07</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -1034,53 +1034,53 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-2.90</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>44.16</t>
+          <t>44.62</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>43.52</v>
+        <v>43.57</v>
       </c>
       <c r="AN2" t="n">
         <v>43.95</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>45.23</t>
+          <t>45.26</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>194.44</t>
+          <t>507.74</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-104.40</t>
+          <t>-101.94</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>28145.93580599144</t>
+          <t>28136.79700854701</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>8868.0</t>
+          <t>14487.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>7955.4</v>
+        <v>9527.799999999999</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>15511.6</t>
+          <t>15415.0</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>13262.22</v>
+        <v>13104.9</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-7556</t>
+          <t>-5887</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-483.5444389217631</t>
+          <t>-643.9497199633709</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-1944.380223330478</t>
+          <t>-1526.178765692213</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>8868.0</t>
+          <t>14487.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-10.52</t>
+          <t>-9.22</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
+          <t>46.0</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
+          <t>45.1</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
+        <is>
           <t>45.3</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>44.4</t>
-        </is>
-      </c>
-      <c r="CG2" t="inlineStr">
-        <is>
-          <t>44.65</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>197.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,94 +1328,94 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>44.65</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2.49</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-48.71</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-10-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-08-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-08-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>45.6</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
           <t>44.45</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>52.5</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>47.6</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>0.45</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>-48.61</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-10-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-10-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-08-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-08-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>45.6</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>44.45</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>52.5</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>47.6</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
       <c r="X3" t="inlineStr">
         <is>
           <t>-4.20</t>
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1449,32 +1449,32 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>318</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>76.36</t>
+          <t>79.07</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>85.14</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1484,33 +1484,33 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>43.82000000000001</t>
+          <t>44.16</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>43.49</v>
+        <v>43.52</v>
       </c>
       <c r="AN3" t="n">
-        <v>43.94</v>
+        <v>43.95</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>45.21</t>
+          <t>45.23</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>125.94</t>
+          <t>194.44</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-106.54</t>
+          <t>-104.40</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>28145.93580599144</t>
+          <t>28136.79700854701</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>5546.0</t>
+          <t>8868.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>8273.799999999999</v>
+        <v>7955.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>16100.5</t>
+          <t>15511.6</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>13310.48</v>
+        <v>13262.22</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-7826</t>
+          <t>-7556</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-217.9379326656332</t>
+          <t>-483.5444389217631</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-1870.333011980483</t>
+          <t>-1944.380223330478</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>5546.0</t>
+          <t>8868.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-10.92</t>
+          <t>-10.52</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>44.45</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>44.45</t>
+          <t>44.65</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>302.0</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>44.45</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-17.23</t>
+          <t>-48.61</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1879,68 +1879,68 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>318</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>76.36</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>72.02</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>43.92</t>
+          <t>43.82000000000001</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>43.47</v>
+        <v>43.49</v>
       </c>
       <c r="AN4" t="n">
         <v>43.94</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>45.23</t>
+          <t>45.21</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>91.47</t>
+          <t>125.94</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-108.60</t>
+          <t>-106.54</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>28145.93580599144</t>
+          <t>28136.79700854701</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>13560.0</t>
+          <t>5546.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>13265.8</v>
+        <v>8273.799999999999</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>16027.3</t>
+          <t>16100.5</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>13521.82</v>
+        <v>13310.48</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-2761</t>
+          <t>-7826</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>82.49753630070325</t>
+          <t>-217.9379326656332</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-1341.825102481189</t>
+          <t>-1870.333011980483</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>13560.0</t>
+          <t>5546.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-9.62</t>
+          <t>-10.92</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>44.45</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>44.45</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>118.0</t>
+          <t>302.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>9.71</t>
+          <t>-17.23</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2309,68 +2309,68 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>318</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>65.43</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>55.14</t>
+          <t>72.02</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.1</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.80</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>43.92</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>43.44</v>
+        <v>43.47</v>
       </c>
       <c r="AN5" t="n">
-        <v>43.92</v>
+        <v>43.94</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>45.19</t>
+          <t>45.23</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>41.21</t>
+          <t>91.47</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-110.57</t>
+          <t>-108.60</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>28145.93580599144</t>
+          <t>28136.79700854701</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>5178.0</t>
+          <t>13560.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>16692.8</v>
+        <v>13265.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>15215.7</t>
+          <t>16027.3</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>13519.76</v>
+        <v>13521.82</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>-2761</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>341.4652888065019</t>
+          <t>82.49753630070325</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-1397.534335250723</t>
+          <t>-1341.825102481189</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>5178.0</t>
+          <t>13560.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-12.63</t>
+          <t>-9.62</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>43.45</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>43.45</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>118.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>28.77</t>
+          <t>9.71</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2739,68 +2739,68 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>318</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>50.62</t>
+          <t>65.43</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>66.26</t>
+          <t>55.14</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.1</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>43.84</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>43.45</v>
+        <v>43.44</v>
       </c>
       <c r="AN6" t="n">
-        <v>43.97</v>
+        <v>43.92</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>45.12</t>
+          <t>45.19</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>34.76</t>
+          <t>41.21</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-111.66</t>
+          <t>-110.57</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>28145.93580599144</t>
+          <t>28136.79700854701</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>6625.0</t>
+          <t>5178.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>21302.2</v>
+        <v>16692.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>16542.7</t>
+          <t>15215.7</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>13576.72</v>
+        <v>13519.76</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>4759</t>
+          <t>1477</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>657.6470386350882</t>
+          <t>341.4652888065019</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-529.1355843768179</t>
+          <t>-1397.534335250723</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>6625.0</t>
+          <t>5178.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-13.83</t>
+          <t>-12.63</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>43.45</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>42.8</t>
+          <t>43.45</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-4.49</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>42.95</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>5.08</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>20.84</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>5.89</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3169,68 +3169,68 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>318</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>49.38</t>
+          <t>50.62</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>82.72</t>
+          <t>66.26</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>43.71</t>
+          <t>43.84</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>43.5</v>
+        <v>43.45</v>
       </c>
       <c r="AN7" t="n">
-        <v>44.03</v>
+        <v>43.97</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>45.06</t>
+          <t>45.12</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>44.24</t>
+          <t>34.76</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-112.67</t>
+          <t>-111.66</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>28145.93580599144</t>
+          <t>28136.79700854701</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>10460.0</t>
+          <t>6625.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>23067.8</v>
+        <v>21302.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>19089.8</t>
+          <t>16542.7</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>13602.9</v>
+        <v>13576.72</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>3978</t>
+          <t>4759</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>873.4256973645256</t>
+          <t>657.6470386350882</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>575.296044885079</t>
+          <t>-529.1355843768179</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>10460.0</t>
+          <t>6625.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-13.93</t>
+          <t>-13.83</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>42.8</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>42.95</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>670.0</t>
+          <t>240.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>44.95</t>
+          <t>42.95</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>5.19</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>24.67</t>
+          <t>20.84</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16.44</t>
+          <t>5.89</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3599,68 +3599,68 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>318</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>98.77</t>
+          <t>49.38</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>94.23</t>
+          <t>82.72</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>43.31</t>
+          <t>43.71</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>43.58</v>
+        <v>43.5</v>
       </c>
       <c r="AN8" t="n">
-        <v>44.1</v>
+        <v>44.03</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>45.01</t>
+          <t>45.06</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>56.72</t>
+          <t>44.24</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-114.07</t>
+          <t>-112.67</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>28145.93580599144</t>
+          <t>28136.79700854701</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>30506.0</t>
+          <t>10460.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>23927.2</v>
+        <v>23067.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>19193.0</t>
+          <t>19089.8</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>13522.88</v>
+        <v>13602.9</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>4734</t>
+          <t>3978</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>927.631088724425</t>
+          <t>873.4256973645256</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>1721.616370799031</t>
+          <t>575.296044885079</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>30506.0</t>
+          <t>10460.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-9.92</t>
+          <t>-13.93</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>46.55</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>44.95</t>
+          <t>42.95</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>685.0</t>
+          <t>670.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>44.95</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,102 +3918,102 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
+          <t>24.67</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2025-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2025-10-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2025-08-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2025-08-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>45.6</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>44.45</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>52.5</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>47.6</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>1.12</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
           <t>-4.20</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>2025-10-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2025-10-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2025-08-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2025-08-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>45.6</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>44.45</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>52.5</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>47.6</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>1.24</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>-4.20</t>
-        </is>
-      </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16.81</t>
+          <t>16.44</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4029,269 +4029,269 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>318</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>98.77</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>75.04</t>
+          <t>94.23</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>42.73999999999999</t>
+          <t>43.31</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>43.61</v>
+        <v>43.58</v>
       </c>
       <c r="AN9" t="n">
-        <v>44.12</v>
+        <v>44.1</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
+          <t>45.01</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>56.72</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>-0.17</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>-0.39</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>2.77</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>-114.07</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>2025/11/19</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>28136.79700854701</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>30506.0</t>
+        </is>
+      </c>
+      <c r="AX9" t="n">
+        <v>23927.2</v>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>19193.0</t>
+        </is>
+      </c>
+      <c r="AZ9" t="n">
+        <v>13522.88</v>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>4734</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>927.631088724425</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>1721.616370799031</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>30506.0</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>49.9</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>2025/08/12</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>-9.92</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>匯鑽科</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>匯鑽科</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>0.78</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
+          <t>-10.56465687102404</t>
+        </is>
+      </c>
+      <c r="BO9" t="inlineStr">
+        <is>
+          <t>-13.69932964657055</t>
+        </is>
+      </c>
+      <c r="BP9" t="inlineStr">
+        <is>
+          <t>7.80229574004913</t>
+        </is>
+      </c>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="BT9" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
+          <t>6.59</t>
+        </is>
+      </c>
+      <c r="BV9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
+          <t>8.25%</t>
+        </is>
+      </c>
+      <c r="BX9" t="inlineStr">
+        <is>
+          <t>-14.21%</t>
+        </is>
+      </c>
+      <c r="BY9" t="inlineStr">
+        <is>
+          <t>44.93</t>
+        </is>
+      </c>
+      <c r="BZ9" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
+          <t>加工業務99.90%、勞務0.10% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>匯鑽科-其他電子業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC9" t="inlineStr">
+        <is>
+          <t>其他電子業右下上櫃</t>
+        </is>
+      </c>
+      <c r="CD9" t="inlineStr">
+        <is>
+          <t>45.5</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
+          <t>46.55</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
+          <t>44.8</t>
+        </is>
+      </c>
+      <c r="CG9" t="inlineStr">
+        <is>
           <t>44.95</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>24.64</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>-0.34</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>-0.45</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>2.77</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>-116.07</t>
-        </is>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>2025/11/19</t>
-        </is>
-      </c>
-      <c r="AV9" t="inlineStr">
-        <is>
-          <t>28145.93580599144</t>
-        </is>
-      </c>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>30695.0</t>
-        </is>
-      </c>
-      <c r="AX9" t="n">
-        <v>18788.8</v>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>19613.1</t>
-        </is>
-      </c>
-      <c r="AZ9" t="n">
-        <v>13049.74</v>
-      </c>
-      <c r="BA9" t="inlineStr">
-        <is>
-          <t>-824</t>
-        </is>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>783.2701283472239</t>
-        </is>
-      </c>
-      <c r="BC9" t="inlineStr">
-        <is>
-          <t>1149.944823147569</t>
-        </is>
-      </c>
-      <c r="BD9" t="inlineStr">
-        <is>
-          <t>30695.0</t>
-        </is>
-      </c>
-      <c r="BE9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF9" t="inlineStr">
-        <is>
-          <t>49.9</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>2025/08/12</t>
-        </is>
-      </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>-9.82</t>
-        </is>
-      </c>
-      <c r="BI9" t="inlineStr">
-        <is>
-          <t>匯鑽科</t>
-        </is>
-      </c>
-      <c r="BJ9" t="inlineStr">
-        <is>
-          <t>匯鑽科</t>
-        </is>
-      </c>
-      <c r="BK9" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BL9" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM9" t="inlineStr">
-        <is>
-          <t>0.78</t>
-        </is>
-      </c>
-      <c r="BN9" t="inlineStr">
-        <is>
-          <t>-10.56465687102404</t>
-        </is>
-      </c>
-      <c r="BO9" t="inlineStr">
-        <is>
-          <t>-13.69932964657055</t>
-        </is>
-      </c>
-      <c r="BP9" t="inlineStr">
-        <is>
-          <t>7.80229574004913</t>
-        </is>
-      </c>
-      <c r="BQ9" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
-        </is>
-      </c>
-      <c r="BR9" t="inlineStr">
-        <is>
-          <t>價漲量增</t>
-        </is>
-      </c>
-      <c r="BS9" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
-      </c>
-      <c r="BT9" t="inlineStr">
-        <is>
-          <t>2.52</t>
-        </is>
-      </c>
-      <c r="BU9" t="inlineStr">
-        <is>
-          <t>6.59</t>
-        </is>
-      </c>
-      <c r="BV9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BW9" t="inlineStr">
-        <is>
-          <t>8.25%</t>
-        </is>
-      </c>
-      <c r="BX9" t="inlineStr">
-        <is>
-          <t>-14.21%</t>
-        </is>
-      </c>
-      <c r="BY9" t="inlineStr">
-        <is>
-          <t>44.86</t>
-        </is>
-      </c>
-      <c r="BZ9" t="inlineStr">
-        <is>
-          <t>1982</t>
-        </is>
-      </c>
-      <c r="CA9" t="inlineStr">
-        <is>
-          <t>加工業務99.90%、勞務0.10% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB9" t="inlineStr">
-        <is>
-          <t>匯鑽科-其他電子業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC9" t="inlineStr">
-        <is>
-          <t>其他電子業右下上櫃</t>
-        </is>
-      </c>
-      <c r="CD9" t="inlineStr">
-        <is>
-          <t>43.55</t>
-        </is>
-      </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>45.55</t>
-        </is>
-      </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>43.3</t>
-        </is>
-      </c>
-      <c r="CG9" t="inlineStr">
-        <is>
-          <t>45.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4313,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>655.0</t>
+          <t>685.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-32.14</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>16.81</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4459,68 +4459,68 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>318</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>83.93</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>75.04</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>42.22000000000001</t>
+          <t>42.73999999999999</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>43.6</v>
+        <v>43.61</v>
       </c>
       <c r="AN10" t="n">
-        <v>44.15</v>
+        <v>44.12</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>44.89</t>
+          <t>44.95</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-16.05</t>
+          <t>24.64</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-117.06</t>
+          <t>-116.07</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>28145.93580599144</t>
+          <t>28136.79700854701</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>28225.0</t>
+          <t>30695.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>13738.6</v>
+        <v>18788.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>20246.9</t>
+          <t>19613.1</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>12733.2</v>
+        <v>13049.74</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-6508</t>
+          <t>-824</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>716.6020020198885</t>
+          <t>783.2701283472239</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>271.9517256759318</t>
+          <t>1149.944823147569</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>28225.0</t>
+          <t>30695.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-13.23</t>
+          <t>-9.82</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,22 +4641,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>42.35</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>369.0</t>
+          <t>655.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>42.35</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>4.42</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-43.86</t>
+          <t>-32.14</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-4.72</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>9.06</t>
+          <t>16.07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4889,68 +4889,68 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>318</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>41.18</t>
+          <t>83.93</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>14.84</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>42.22000000000001</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>43.53</v>
+        <v>43.6</v>
       </c>
       <c r="AN11" t="n">
-        <v>44.23</v>
+        <v>44.15</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>44.87</t>
+          <t>44.89</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-40.91</t>
+          <t>-16.05</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-116.38</t>
+          <t>-117.06</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>28145.93580599144</t>
+          <t>28136.79700854701</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>15453.0</t>
+          <t>28225.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>11783.2</v>
+        <v>13738.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>20989.4</t>
+          <t>20246.9</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>12346.96</v>
+        <v>12733.2</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-9206</t>
+          <t>-6508</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>797.4475068096988</t>
+          <t>716.6020020198885</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-727.3938323434086</t>
+          <t>271.9517256759318</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>15453.0</t>
+          <t>28225.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-15.13</t>
+          <t>-13.23</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>42.7</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>42.35</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>42.35</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-2.73</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>358.0</t>
+          <t>369.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>42.35</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>8.29</t>
+          <t>6.51</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-27.59</t>
+          <t>-43.86</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-7.87</t>
+          <t>-4.72</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>8.79</t>
+          <t>9.06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,68 +5319,68 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>318</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>41.18</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>14.84</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-3.31</t>
+          <t>-3.61</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.88</t>
+          <t>-1.58</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>42.04000000000001</t>
+          <t>41.96</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>43.48</v>
+        <v>43.53</v>
       </c>
       <c r="AN12" t="n">
-        <v>44.31</v>
+        <v>44.23</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>44.85</t>
+          <t>44.87</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-59.38</t>
+          <t>-40.91</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-114.70</t>
+          <t>-116.38</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>28145.93580599144</t>
+          <t>28136.79700854701</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>14757.0</t>
+          <t>15453.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>15111.8</v>
+        <v>11783.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>20870.2</t>
+          <t>20989.4</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>12172.68</v>
+        <v>12346.96</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-5758</t>
+          <t>-9206</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>1074.691386655718</t>
+          <t>797.4475068096988</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-760.6234212159197</t>
+          <t>-727.3938323434086</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>14757.0</t>
+          <t>15453.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-17.94</t>
+          <t>-15.13</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>44.86</t>
+          <t>44.93</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>1982</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,12 +5566,12 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>41.1</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>42.45</t>
+          <t>42.7</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
@@ -5581,7 +5581,7 @@
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>42.35</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>461.141</t>
+          <t>1014.23</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>87.8</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-2.97</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-33.87</t>
+          <t>-23.60</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-17.94</t>
+          <t>-18.60</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>4.90</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,274 +5744,274 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>1014</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>85.19</t>
+          <t>59.26</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>55.95</t>
+          <t>61.16</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-4.12</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-7.23</t>
+          <t>-7.36</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
+          <t>87.29999999999998</t>
+        </is>
+      </c>
+      <c r="AM13" t="n">
+        <v>90.34</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>97.52</v>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>97.62</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>3.61</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>-3.00</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>-3.12</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>7.19</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr">
+        <is>
+          <t>-143.32</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>2025/11/28</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>353704340.7735043</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>88951847.0</t>
+        </is>
+      </c>
+      <c r="AX13" t="n">
+        <v>59081139.2</v>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>77327536.6</t>
+        </is>
+      </c>
+      <c r="AZ13" t="n">
+        <v>250820460.68</v>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>-18246397</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>-29025923.77036555</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>-25023946.09403855</t>
+        </is>
+      </c>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>88951847.0</t>
+        </is>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
+          <t>81.3</t>
+        </is>
+      </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>2025/07/28</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>7.13</t>
+        </is>
+      </c>
+      <c r="BI13" t="inlineStr">
+        <is>
+          <t>鉅祥</t>
+        </is>
+      </c>
+      <c r="BJ13" t="inlineStr">
+        <is>
+          <t>鉅祥</t>
+        </is>
+      </c>
+      <c r="BK13" t="inlineStr">
+        <is>
+          <t>電子零組件業</t>
+        </is>
+      </c>
+      <c r="BL13" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM13" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="BN13" t="inlineStr">
+        <is>
+          <t>-7.291353668658945</t>
+        </is>
+      </c>
+      <c r="BO13" t="inlineStr">
+        <is>
+          <t>11.64963320584363</t>
+        </is>
+      </c>
+      <c r="BP13" t="inlineStr">
+        <is>
+          <t>10.65346457950322</t>
+        </is>
+      </c>
+      <c r="BQ13" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR13" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS13" t="inlineStr">
+        <is>
+          <t>2.29</t>
+        </is>
+      </c>
+      <c r="BT13" t="inlineStr">
+        <is>
+          <t>4.02</t>
+        </is>
+      </c>
+      <c r="BU13" t="inlineStr">
+        <is>
+          <t>9.36</t>
+        </is>
+      </c>
+      <c r="BV13" t="inlineStr">
+        <is>
+          <t>22.39</t>
+        </is>
+      </c>
+      <c r="BW13" t="inlineStr">
+        <is>
+          <t>29.60%</t>
+        </is>
+      </c>
+      <c r="BX13" t="inlineStr">
+        <is>
+          <t>15.93%</t>
+        </is>
+      </c>
+      <c r="BY13" t="inlineStr">
+        <is>
+          <t>34.7</t>
+        </is>
+      </c>
+      <c r="BZ13" t="inlineStr">
+        <is>
+          <t>18369</t>
+        </is>
+      </c>
+      <c r="CA13" t="inlineStr">
+        <is>
+          <t>部品95.14%、模具3.09%、商品銷售1.03%、治具0.75% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB13" t="inlineStr">
+        <is>
+          <t>鉅祥-電子零組件業-上市</t>
+        </is>
+      </c>
+      <c r="CC13" t="inlineStr">
+        <is>
+          <t>電子零組件業右上上市</t>
+        </is>
+      </c>
+      <c r="CD13" t="inlineStr">
+        <is>
+          <t>87.5</t>
+        </is>
+      </c>
+      <c r="CE13" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="CF13" t="inlineStr">
+        <is>
+          <t>86.8</t>
+        </is>
+      </c>
+      <c r="CG13" t="inlineStr">
+        <is>
           <t>87.1</t>
-        </is>
-      </c>
-      <c r="AM13" t="n">
-        <v>90.84</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>97.92</v>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>97.54</t>
-        </is>
-      </c>
-      <c r="AP13" t="inlineStr">
-        <is>
-          <t>0.98</t>
-        </is>
-      </c>
-      <c r="AQ13" t="inlineStr">
-        <is>
-          <t>-3.11</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>-3.14</t>
-        </is>
-      </c>
-      <c r="AS13" t="inlineStr">
-        <is>
-          <t>7.19</t>
-        </is>
-      </c>
-      <c r="AT13" t="inlineStr">
-        <is>
-          <t>-143.71</t>
-        </is>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>2025/11/28</t>
-        </is>
-      </c>
-      <c r="AV13" t="inlineStr">
-        <is>
-          <t>354018572.6854494</t>
-        </is>
-      </c>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>40320203.0</t>
-        </is>
-      </c>
-      <c r="AX13" t="n">
-        <v>54978050.8</v>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>83135790.5</t>
-        </is>
-      </c>
-      <c r="AZ13" t="n">
-        <v>260959475.16</v>
-      </c>
-      <c r="BA13" t="inlineStr">
-        <is>
-          <t>-28157739</t>
-        </is>
-      </c>
-      <c r="BB13" t="inlineStr">
-        <is>
-          <t>-29753556.07515229</t>
-        </is>
-      </c>
-      <c r="BC13" t="inlineStr">
-        <is>
-          <t>-29592900.56933765</t>
-        </is>
-      </c>
-      <c r="BD13" t="inlineStr">
-        <is>
-          <t>40320203.0</t>
-        </is>
-      </c>
-      <c r="BE13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF13" t="inlineStr">
-        <is>
-          <t>81.3</t>
-        </is>
-      </c>
-      <c r="BG13" t="inlineStr">
-        <is>
-          <t>2025/07/28</t>
-        </is>
-      </c>
-      <c r="BH13" t="inlineStr">
-        <is>
-          <t>8.00</t>
-        </is>
-      </c>
-      <c r="BI13" t="inlineStr">
-        <is>
-          <t>鉅祥</t>
-        </is>
-      </c>
-      <c r="BJ13" t="inlineStr">
-        <is>
-          <t>鉅祥</t>
-        </is>
-      </c>
-      <c r="BK13" t="inlineStr">
-        <is>
-          <t>電子零組件業</t>
-        </is>
-      </c>
-      <c r="BL13" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM13" t="inlineStr">
-        <is>
-          <t>1.02</t>
-        </is>
-      </c>
-      <c r="BN13" t="inlineStr">
-        <is>
-          <t>-7.291353668658945</t>
-        </is>
-      </c>
-      <c r="BO13" t="inlineStr">
-        <is>
-          <t>11.64963320584363</t>
-        </is>
-      </c>
-      <c r="BP13" t="inlineStr">
-        <is>
-          <t>10.65346457950322</t>
-        </is>
-      </c>
-      <c r="BQ13" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR13" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS13" t="inlineStr">
-        <is>
-          <t>2.31</t>
-        </is>
-      </c>
-      <c r="BT13" t="inlineStr">
-        <is>
-          <t>3.98</t>
-        </is>
-      </c>
-      <c r="BU13" t="inlineStr">
-        <is>
-          <t>9.36</t>
-        </is>
-      </c>
-      <c r="BV13" t="inlineStr">
-        <is>
-          <t>22.57</t>
-        </is>
-      </c>
-      <c r="BW13" t="inlineStr">
-        <is>
-          <t>29.60%</t>
-        </is>
-      </c>
-      <c r="BX13" t="inlineStr">
-        <is>
-          <t>15.93%</t>
-        </is>
-      </c>
-      <c r="BY13" t="inlineStr">
-        <is>
-          <t>34.84</t>
-        </is>
-      </c>
-      <c r="BZ13" t="inlineStr">
-        <is>
-          <t>18517</t>
-        </is>
-      </c>
-      <c r="CA13" t="inlineStr">
-        <is>
-          <t>部品95.14%、模具3.09%、商品銷售1.03%、治具0.75% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB13" t="inlineStr">
-        <is>
-          <t>鉅祥-電子零組件業-上市</t>
-        </is>
-      </c>
-      <c r="CC13" t="inlineStr">
-        <is>
-          <t>電子零組件業右上上市</t>
-        </is>
-      </c>
-      <c r="CD13" t="inlineStr">
-        <is>
-          <t>87.9</t>
-        </is>
-      </c>
-      <c r="CE13" t="inlineStr">
-        <is>
-          <t>87.9</t>
-        </is>
-      </c>
-      <c r="CF13" t="inlineStr">
-        <is>
-          <t>86.9</t>
-        </is>
-      </c>
-      <c r="CG13" t="inlineStr">
-        <is>
-          <t>87.8</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6033,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>630.229</t>
+          <t>461.141</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-2.97</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-29.59</t>
+          <t>-33.87</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-18.60</t>
+          <t>-17.94</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,73 +6174,73 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>1014</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>39.02</t>
+          <t>85.19</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>31.54</t>
+          <t>55.95</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-5.08</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-7.16</t>
+          <t>-7.23</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>86.64</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>91.28</v>
+        <v>90.84</v>
       </c>
       <c r="AN14" t="n">
-        <v>98.31</v>
+        <v>97.92</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>97.43</t>
+          <t>97.54</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-3.11</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-3.15</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-143.82</t>
+          <t>-143.71</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>354018572.6854494</t>
+          <t>353704340.7735043</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>55246132.0</t>
+          <t>40320203.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>67438997.8</v>
+        <v>54978050.8</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>95782499.1</t>
+          <t>83135790.5</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>275665355.36</v>
+        <v>260959475.16</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-28343501</t>
+          <t>-28157739</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-29782766.16711858</t>
+          <t>-29753556.07515229</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-29852555.79943146</t>
+          <t>-29592900.56933765</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>55246132.0</t>
+          <t>40320203.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>7.13</t>
+          <t>8.00</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>22.57</t>
+          <t>22.39</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>34.84</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>18517</t>
+          <t>18369</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6431,17 +6431,17 @@
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.9</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>713.512</t>
+          <t>630.229</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-2.97</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-33.57</t>
+          <t>-29.59</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-17.85</t>
+          <t>-18.60</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,73 +6604,73 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>1014</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>43.64</t>
+          <t>39.02</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>31.54</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-5.14</t>
+          <t>-5.08</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-7.33</t>
+          <t>-7.16</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>86.85999999999999</t>
+          <t>86.64</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>91.56999999999999</v>
+        <v>91.28</v>
       </c>
       <c r="AN15" t="n">
-        <v>98.81999999999999</v>
+        <v>98.31</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>97.34</t>
+          <t>97.43</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-8.10</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-3.12</t>
+          <t>-3.15</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-143.38</t>
+          <t>-143.82</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>354018572.6854494</t>
+          <t>353704340.7735043</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>62492000.0</t>
+          <t>55246132.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>68942899</v>
+        <v>67438997.8</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>103776418.9</t>
+          <t>95782499.1</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>296624289.38</v>
+        <v>275665355.36</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-34833519</t>
+          <t>-28343501</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-29770077.14306169</t>
+          <t>-29782766.16711858</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-30756535.8138715</t>
+          <t>-29852555.79943146</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>62492000.0</t>
+          <t>55246132.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>7.13</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6791,22 +6791,22 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>22.57</t>
+          <t>22.39</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>34.84</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>18517</t>
+          <t>18369</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>557.755</t>
+          <t>713.512</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-2.97</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-31.49</t>
+          <t>-33.57</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-19.07</t>
+          <t>-17.85</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,73 +7034,73 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>1014</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>11.96</t>
+          <t>43.64</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>6.16</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-5.79</t>
+          <t>-5.14</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-7.52</t>
+          <t>-7.33</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>86.58</t>
+          <t>86.85999999999999</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>91.90000000000001</v>
+        <v>91.56999999999999</v>
       </c>
       <c r="AN16" t="n">
-        <v>99.37</v>
+        <v>98.81999999999999</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>97.25</t>
+          <t>97.34</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-15.28</t>
+          <t>-8.10</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-3.12</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-142.50</t>
+          <t>-143.38</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>354018572.6854494</t>
+          <t>353704340.7735043</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>48395514.0</t>
+          <t>62492000.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>76417304.59999999</v>
+        <v>68942899</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>111545339.3</t>
+          <t>103776418.9</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>319430807.84</v>
+        <v>296624289.38</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-35128034</t>
+          <t>-34833519</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-29590721.02109627</t>
+          <t>-29770077.14306169</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-31725831.12686187</t>
+          <t>-30756535.8138715</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>48395514.0</t>
+          <t>62492000.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>8.12</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,22 +7221,22 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>22.57</t>
+          <t>22.39</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>34.84</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>18517</t>
+          <t>18369</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>797.916</t>
+          <t>557.755</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>86.1</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-2.97</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-21.02</t>
+          <t>-31.49</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-19.53</t>
+          <t>-19.07</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,151 +7464,151 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>1014</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
+          <t>11.96</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>6.16</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>-5.79</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>-7.52</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>86.58</t>
+        </is>
+      </c>
+      <c r="AM17" t="n">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>99.37</v>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>97.25</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>-15.28</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>-3.52</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>-3.06</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>7.19</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr">
+        <is>
+          <t>-142.50</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>2025/11/28</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>353704340.7735043</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>48395514.0</t>
+        </is>
+      </c>
+      <c r="AX17" t="n">
+        <v>76417304.59999999</v>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>111545339.3</t>
+        </is>
+      </c>
+      <c r="AZ17" t="n">
+        <v>319430807.84</v>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>-35128034</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>-29590721.02109627</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>-31725831.12686187</t>
+        </is>
+      </c>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>48395514.0</t>
+        </is>
+      </c>
+      <c r="BE17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF17" t="inlineStr">
+        <is>
+          <t>81.3</t>
+        </is>
+      </c>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>2025/07/28</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
           <t>6.52</t>
         </is>
       </c>
-      <c r="AG17" t="inlineStr">
-        <is>
-          <t>9.08</t>
-        </is>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>-0.76</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>-6.01</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>-7.68</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>2.91</t>
-        </is>
-      </c>
-      <c r="AL17" t="inlineStr">
-        <is>
-          <t>86.75999999999999</t>
-        </is>
-      </c>
-      <c r="AM17" t="n">
-        <v>92.31</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>99.98999999999999</v>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>97.16</t>
-        </is>
-      </c>
-      <c r="AP17" t="inlineStr">
-        <is>
-          <t>-20.19</t>
-        </is>
-      </c>
-      <c r="AQ17" t="inlineStr">
-        <is>
-          <t>-3.53</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>-2.94</t>
-        </is>
-      </c>
-      <c r="AS17" t="inlineStr">
-        <is>
-          <t>7.19</t>
-        </is>
-      </c>
-      <c r="AT17" t="inlineStr">
-        <is>
-          <t>-140.87</t>
-        </is>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>2025/11/28</t>
-        </is>
-      </c>
-      <c r="AV17" t="inlineStr">
-        <is>
-          <t>354018572.6854494</t>
-        </is>
-      </c>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>68436405.0</t>
-        </is>
-      </c>
-      <c r="AX17" t="n">
-        <v>95573934</v>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>121006638.2</t>
-        </is>
-      </c>
-      <c r="AZ17" t="n">
-        <v>336619552.5</v>
-      </c>
-      <c r="BA17" t="inlineStr">
-        <is>
-          <t>-25432704</t>
-        </is>
-      </c>
-      <c r="BB17" t="inlineStr">
-        <is>
-          <t>-29202519.18368434</t>
-        </is>
-      </c>
-      <c r="BC17" t="inlineStr">
-        <is>
-          <t>-30467135.53374588</t>
-        </is>
-      </c>
-      <c r="BD17" t="inlineStr">
-        <is>
-          <t>68436405.0</t>
-        </is>
-      </c>
-      <c r="BE17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF17" t="inlineStr">
-        <is>
-          <t>81.3</t>
-        </is>
-      </c>
-      <c r="BG17" t="inlineStr">
-        <is>
-          <t>2025/07/28</t>
-        </is>
-      </c>
-      <c r="BH17" t="inlineStr">
-        <is>
-          <t>5.90</t>
-        </is>
-      </c>
       <c r="BI17" t="inlineStr">
         <is>
           <t>鉅祥</t>
@@ -7651,7 +7651,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7661,12 +7661,12 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>22.57</t>
+          <t>22.39</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>34.84</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>18517</t>
+          <t>18369</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>85.1</t>
+          <t>85.9</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>86.1</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-3.11</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1197.387</t>
+          <t>797.916</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>86.1</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-2.97</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-9.98</t>
+          <t>-21.02</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-20.09</t>
+          <t>-19.53</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>5.79</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,73 +7894,73 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>1014</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>6.91</t>
+          <t>9.08</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-5.99</t>
+          <t>-6.01</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-7.53</t>
+          <t>-7.68</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>87.46000000000001</t>
+          <t>86.75999999999999</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>93.03</v>
+        <v>92.31</v>
       </c>
       <c r="AN18" t="n">
-        <v>100.61</v>
+        <v>99.98999999999999</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>97.09</t>
+          <t>97.16</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-23.35</t>
+          <t>-20.19</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>-3.53</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-138.81</t>
+          <t>-140.87</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>354018572.6854494</t>
+          <t>353704340.7735043</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>102624938.0</t>
+          <t>68436405.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>111293530.2</v>
+        <v>95573934</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>123628857.1</t>
+          <t>121006638.2</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>366752945.54</v>
+        <v>336619552.5</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-12335326</t>
+          <t>-25432704</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-28972588.9382186</t>
+          <t>-29202519.18368434</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-29728125.31023213</t>
+          <t>-30467135.53374588</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>102624938.0</t>
+          <t>68436405.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>5.17</t>
+          <t>5.90</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>22.57</t>
+          <t>22.39</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>34.84</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>18517</t>
+          <t>18369</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>86.1</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>-3.11</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>710.084</t>
+          <t>1197.387</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-2.97</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-9.98</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-17.57</t>
+          <t>-20.09</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>5.79</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,17 +8324,17 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>1014</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>20.73</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
@@ -8344,53 +8344,53 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-5.54</t>
+          <t>-5.99</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-7.34</t>
+          <t>-7.53</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>88.56</t>
+          <t>87.46000000000001</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>93.75</v>
+        <v>93.03</v>
       </c>
       <c r="AN19" t="n">
-        <v>101.18</v>
+        <v>100.61</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>97.04</t>
+          <t>97.09</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-22.39</t>
+          <t>-23.35</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-136.55</t>
+          <t>-138.81</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>354018572.6854494</t>
+          <t>353704340.7735043</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>62765638.0</t>
+          <t>102624938.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>124126000.4</v>
+        <v>111293530.2</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>125231243.6</t>
+          <t>123628857.1</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>399636300.16</v>
+        <v>366752945.54</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-1105243</t>
+          <t>-12335326</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-28835218.6887616</t>
+          <t>-28972588.9382186</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-31273734.76556134</t>
+          <t>-29728125.31023213</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>62765638.0</t>
+          <t>102624938.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>8.49</t>
+          <t>5.17</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,22 +8511,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>22.57</t>
+          <t>22.39</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>34.84</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>18517</t>
+          <t>18369</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>89.4</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1153.082</t>
+          <t>710.084</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-2.97</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-19.16</t>
+          <t>-17.57</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,73 +8754,73 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>1014</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.73</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.91</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-3.74</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-5.54</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-7.14</t>
+          <t>-7.34</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>89.86</t>
+          <t>88.56</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>94.36</v>
+        <v>93.75</v>
       </c>
       <c r="AN20" t="n">
-        <v>101.62</v>
+        <v>101.18</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>96.9</t>
+          <t>97.04</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-27.21</t>
+          <t>-22.39</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-2.48</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-134.50</t>
+          <t>-136.55</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>354018572.6854494</t>
+          <t>353704340.7735043</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>99864028.0</t>
+          <t>62765638.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>138609938.8</v>
+        <v>124126000.4</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>137834914.3</t>
+          <t>125231243.6</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>443270959.36</v>
+        <v>399636300.16</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>775024</t>
+          <t>-1105243</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-28391852.12934346</t>
+          <t>-28835218.6887616</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-28094189.88869017</t>
+          <t>-31273734.76556134</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>99864028.0</t>
+          <t>62765638.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>6.40</t>
+          <t>8.49</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8941,22 +8941,22 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>22.57</t>
+          <t>22.39</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>34.84</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>18517</t>
+          <t>18369</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>88.6</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
+          <t>89.4</t>
+        </is>
+      </c>
+      <c r="CF20" t="inlineStr">
+        <is>
           <t>87.9</t>
         </is>
       </c>
-      <c r="CF20" t="inlineStr">
-        <is>
-          <t>85.9</t>
-        </is>
-      </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1638.11</t>
+          <t>1153.082</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-2.97</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-18.22</t>
+          <t>-19.16</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>7.92</t>
+          <t>5.57</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-2.40</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,12 +9184,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>1014</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9204,53 +9204,53 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-4.12</t>
+          <t>-3.74</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-4.10</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-6.67</t>
+          <t>-7.14</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>91.26</t>
+          <t>89.86</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>95.16</v>
+        <v>94.36</v>
       </c>
       <c r="AN21" t="n">
-        <v>101.96</v>
+        <v>101.62</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>96.8</t>
+          <t>96.9</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-23.67</t>
+          <t>-27.21</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-2.86</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-132.15</t>
+          <t>-134.50</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>354018572.6854494</t>
+          <t>353704340.7735043</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>144178661.0</t>
+          <t>99864028.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>146673374</v>
+        <v>138609938.8</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>149731355.7</t>
+          <t>137834914.3</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>454484548.46</v>
+        <v>443270959.36</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-3057981</t>
+          <t>775024</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-28445972.53673498</t>
+          <t>-28391852.12934346</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-26523446.49713525</t>
+          <t>-28094189.88869017</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>144178661.0</t>
+          <t>99864028.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>7.63</t>
+          <t>6.40</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9381,12 +9381,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>22.57</t>
+          <t>22.39</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>34.84</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>18517</t>
+          <t>18369</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>89.9</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>85.9</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1631.485</t>
+          <t>1638.11</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-2.05</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-2.97</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-20.69</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-16.26</t>
+          <t>-18.22</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>7.89</t>
+          <t>7.92</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-2.40</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,12 +9614,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>1014</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9629,58 +9629,58 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>13.16</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-3.30</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>-4.10</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-6.3</t>
+          <t>-6.67</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>5.78</t>
+          <t>5.33</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>92.66</t>
+          <t>91.26</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>95.84</v>
+        <v>95.16</v>
       </c>
       <c r="AN22" t="n">
-        <v>102.28</v>
+        <v>101.96</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>96.69</t>
+          <t>96.8</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-16.84</t>
+          <t>-23.67</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-2.86</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-130.25</t>
+          <t>-132.15</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>354018572.6854494</t>
+          <t>353704340.7735043</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>147034386.0</t>
+          <t>144178661.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>146439342.4</v>
+        <v>146673374</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>184645225.3</t>
+          <t>149731355.7</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>461884050.18</v>
+        <v>454484548.46</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-38205882</t>
+          <t>-3057981</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-28795522.72575311</t>
+          <t>-28445972.53673498</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-28080257.81287342</t>
+          <t>-26523446.49713525</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>147034386.0</t>
+          <t>144178661.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>10.21</t>
+          <t>7.63</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>22.57</t>
+          <t>22.39</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>34.84</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>18517</t>
+          <t>18369</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>89.9</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>89.4</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-4.0</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1815.561</t>
+          <t>1631.485</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-2.97</t>
+          <t>-1.43</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-32.28</t>
+          <t>-20.69</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-14.95</t>
+          <t>-16.26</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>8.78</t>
+          <t>7.89</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-2.53</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,12 +10044,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>1014</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10059,58 +10059,58 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>15.79</t>
+          <t>13.16</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-3.30</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-3.32</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-6.05</t>
+          <t>-6.3</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>6.20</t>
+          <t>5.78</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>93.38</t>
+          <t>92.66</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>96.31999999999999</v>
+        <v>95.84</v>
       </c>
       <c r="AN23" t="n">
-        <v>102.52</v>
+        <v>102.28</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>96.53</t>
+          <t>96.69</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-10.98</t>
+          <t>-16.84</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-2.54</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-128.98</t>
+          <t>-130.25</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>354018572.6854494</t>
+          <t>353704340.7735043</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>166787289.0</t>
+          <t>147034386.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>135964184</v>
+        <v>146439342.4</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>200767284.9</t>
+          <t>184645225.3</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>481289771.06</v>
+        <v>461884050.18</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-64803100</t>
+          <t>-38205882</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-28925570.89173124</t>
+          <t>-28795522.72575311</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-29607378.16346818</t>
+          <t>-28080257.81287342</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>166787289.0</t>
+          <t>147034386.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>11.93</t>
+          <t>10.21</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>22.57</t>
+          <t>22.39</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>34.84</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>18517</t>
+          <t>18369</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>89.4</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/電鍍材料.xlsx
+++ b/Result/checksun_type/電鍍材料.xlsx
@@ -883,127 +883,127 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>0.88</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>151.0</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>45.7</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-0.88</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>-25.69</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2025-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2025-10-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2025-08-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2025-08-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>45.6</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>44.45</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>52.5</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>47.6</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>2.81</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>-4.20</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>3.71</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
           <t>1.44</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>318.0</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>45.3</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2.49</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>-38.19</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2025-10-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2025-10-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2025-08-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2025-08-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>45.6</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>44.45</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>52.5</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>47.6</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>-4.20</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>7.80</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>-1.10</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1029,58 +1029,58 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>85.14</t>
+          <t>93.02</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.90</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>44.62</t>
+          <t>45.04</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>43.57</v>
+        <v>43.61</v>
       </c>
       <c r="AN2" t="n">
-        <v>43.95</v>
+        <v>43.98</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>45.26</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>507.74</t>
+          <t>1334.55</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-101.94</t>
+          <t>-99.17</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>28136.79700854701</t>
+          <t>28111.46159317212</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>14487.0</t>
+          <t>6884.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>9527.799999999999</v>
+        <v>9869</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>15415.0</t>
+          <t>13280.9</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>13104.9</v>
+        <v>13072.58</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-5887</t>
+          <t>-3411</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-643.9497199633709</t>
+          <t>-816.4971901541018</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-1526.178765692213</t>
+          <t>-1765.508276203122</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>14487.0</t>
+          <t>6884.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-9.22</t>
+          <t>-8.42</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>45.05</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>197.0</t>
+          <t>318.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>44.65</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-48.71</t>
+          <t>-38.19</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>7.80</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>79.07</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -1464,53 +1464,53 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-2.90</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>44.16</t>
+          <t>44.62</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>43.52</v>
+        <v>43.57</v>
       </c>
       <c r="AN3" t="n">
         <v>43.95</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>45.23</t>
+          <t>45.26</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>194.44</t>
+          <t>507.74</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-104.40</t>
+          <t>-101.94</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>28136.79700854701</t>
+          <t>28111.46159317212</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>8868.0</t>
+          <t>14487.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>7955.4</v>
+        <v>9527.799999999999</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>15511.6</t>
+          <t>15415.0</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>13262.22</v>
+        <v>13104.9</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-7556</t>
+          <t>-5887</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-483.5444389217631</t>
+          <t>-643.9497199633709</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-1944.380223330478</t>
+          <t>-1526.178765692213</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>8868.0</t>
+          <t>14487.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-10.52</t>
+          <t>-9.22</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
+          <t>46.0</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
+          <t>45.1</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
           <t>45.3</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>44.4</t>
-        </is>
-      </c>
-      <c r="CG3" t="inlineStr">
-        <is>
-          <t>44.65</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>197.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,69 +1758,69 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>44.65</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>-48.71</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-10-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-08-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-08-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>45.6</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
           <t>44.45</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>1.88</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2.49</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>-48.61</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2025-10-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2025-10-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-08-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-08-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>45.6</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>44.45</t>
-        </is>
-      </c>
       <c r="S4" t="inlineStr">
         <is>
           <t>0</t>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1884,27 +1884,27 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>76.36</t>
+          <t>79.07</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>85.14</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1914,33 +1914,33 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>43.82000000000001</t>
+          <t>44.16</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>43.49</v>
+        <v>43.52</v>
       </c>
       <c r="AN4" t="n">
-        <v>43.94</v>
+        <v>43.95</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>45.21</t>
+          <t>45.23</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>125.94</t>
+          <t>194.44</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-106.54</t>
+          <t>-104.40</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>28136.79700854701</t>
+          <t>28111.46159317212</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>5546.0</t>
+          <t>8868.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>8273.799999999999</v>
+        <v>7955.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>16100.5</t>
+          <t>15511.6</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>13310.48</v>
+        <v>13262.22</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-7826</t>
+          <t>-7556</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-217.9379326656332</t>
+          <t>-483.5444389217631</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-1870.333011980483</t>
+          <t>-1944.380223330478</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>5546.0</t>
+          <t>8868.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-10.92</t>
+          <t>-10.52</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2071,12 +2071,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>44.45</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>44.45</t>
+          <t>44.65</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>302.0</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>44.45</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-17.23</t>
+          <t>-48.61</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2314,63 +2314,63 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>76.36</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>72.02</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>43.92</t>
+          <t>43.82000000000001</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>43.47</v>
+        <v>43.49</v>
       </c>
       <c r="AN5" t="n">
         <v>43.94</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>45.23</t>
+          <t>45.21</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>91.47</t>
+          <t>125.94</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-108.60</t>
+          <t>-106.54</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>28136.79700854701</t>
+          <t>28111.46159317212</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>13560.0</t>
+          <t>5546.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>13265.8</v>
+        <v>8273.799999999999</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>16027.3</t>
+          <t>16100.5</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>13521.82</v>
+        <v>13310.48</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-2761</t>
+          <t>-7826</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>82.49753630070325</t>
+          <t>-217.9379326656332</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-1341.825102481189</t>
+          <t>-1870.333011980483</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>13560.0</t>
+          <t>5546.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-9.62</t>
+          <t>-10.92</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>44.45</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>44.45</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>118.0</t>
+          <t>302.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>9.71</t>
+          <t>-17.23</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2744,63 +2744,63 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>65.43</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>55.14</t>
+          <t>72.02</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.1</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-2.80</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>43.92</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>43.44</v>
+        <v>43.47</v>
       </c>
       <c r="AN6" t="n">
-        <v>43.92</v>
+        <v>43.94</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>45.19</t>
+          <t>45.23</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>41.21</t>
+          <t>91.47</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-110.57</t>
+          <t>-108.60</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>28136.79700854701</t>
+          <t>28111.46159317212</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>5178.0</t>
+          <t>13560.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>16692.8</v>
+        <v>13265.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>15215.7</t>
+          <t>16027.3</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>13519.76</v>
+        <v>13521.82</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>-2761</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>341.4652888065019</t>
+          <t>82.49753630070325</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-1397.534335250723</t>
+          <t>-1341.825102481189</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>5178.0</t>
+          <t>13560.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-12.63</t>
+          <t>-9.62</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>43.45</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>43.45</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>118.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5.08</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>28.77</t>
+          <t>9.71</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3174,63 +3174,63 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>50.62</t>
+          <t>65.43</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>66.26</t>
+          <t>55.14</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>43.84</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>43.45</v>
+        <v>43.44</v>
       </c>
       <c r="AN7" t="n">
-        <v>43.97</v>
+        <v>43.92</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>45.12</t>
+          <t>45.19</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>34.76</t>
+          <t>41.21</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-111.66</t>
+          <t>-110.57</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>28136.79700854701</t>
+          <t>28111.46159317212</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>6625.0</t>
+          <t>5178.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>21302.2</v>
+        <v>16692.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>16542.7</t>
+          <t>15215.7</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>13576.72</v>
+        <v>13519.76</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>4759</t>
+          <t>1477</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>657.6470386350882</t>
+          <t>341.4652888065019</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-529.1355843768179</t>
+          <t>-1397.534335250723</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>6625.0</t>
+          <t>5178.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-13.83</t>
+          <t>-12.63</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>43.45</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>42.8</t>
+          <t>43.45</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-4.49</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>42.95</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5.19</t>
+          <t>5.08</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>20.84</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>5.89</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3604,63 +3604,63 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>49.38</t>
+          <t>50.62</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>82.72</t>
+          <t>66.26</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>43.71</t>
+          <t>43.84</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>43.5</v>
+        <v>43.45</v>
       </c>
       <c r="AN8" t="n">
-        <v>44.03</v>
+        <v>43.97</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>45.06</t>
+          <t>45.12</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>44.24</t>
+          <t>34.76</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-112.67</t>
+          <t>-111.66</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>28136.79700854701</t>
+          <t>28111.46159317212</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>10460.0</t>
+          <t>6625.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>23067.8</v>
+        <v>21302.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>19089.8</t>
+          <t>16542.7</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>13602.9</v>
+        <v>13576.72</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>3978</t>
+          <t>4759</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>873.4256973645256</t>
+          <t>657.6470386350882</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>575.296044885079</t>
+          <t>-529.1355843768179</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>10460.0</t>
+          <t>6625.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-13.93</t>
+          <t>-13.83</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>42.8</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>42.95</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>670.0</t>
+          <t>240.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>44.95</t>
+          <t>42.95</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>5.19</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>24.67</t>
+          <t>20.84</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16.44</t>
+          <t>5.89</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4034,63 +4034,63 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>98.77</t>
+          <t>49.38</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>94.23</t>
+          <t>82.72</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>43.31</t>
+          <t>43.71</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>43.58</v>
+        <v>43.5</v>
       </c>
       <c r="AN9" t="n">
-        <v>44.1</v>
+        <v>44.03</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>45.01</t>
+          <t>45.06</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>56.72</t>
+          <t>44.24</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-114.07</t>
+          <t>-112.67</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>28136.79700854701</t>
+          <t>28111.46159317212</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>30506.0</t>
+          <t>10460.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>23927.2</v>
+        <v>23067.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>19193.0</t>
+          <t>19089.8</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>13522.88</v>
+        <v>13602.9</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>4734</t>
+          <t>3978</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>927.631088724425</t>
+          <t>873.4256973645256</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>1721.616370799031</t>
+          <t>575.296044885079</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>30506.0</t>
+          <t>10460.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-9.92</t>
+          <t>-13.93</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>46.55</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>44.95</t>
+          <t>42.95</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>685.0</t>
+          <t>670.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>44.95</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,102 +4348,102 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
+          <t>24.67</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2025-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2025-10-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2025-08-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2025-08-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>45.6</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>44.45</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>52.5</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>47.6</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>1.12</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
           <t>-4.20</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2025-10-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2025-10-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2025-08-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2025-08-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>45.6</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>44.45</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>52.5</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>47.6</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>1.24</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>-4.20</t>
-        </is>
-      </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16.81</t>
+          <t>16.44</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4464,264 +4464,264 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>98.77</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>75.04</t>
+          <t>94.23</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>42.73999999999999</t>
+          <t>43.31</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>43.61</v>
+        <v>43.58</v>
       </c>
       <c r="AN10" t="n">
-        <v>44.12</v>
+        <v>44.1</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
+          <t>45.01</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>56.72</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>-0.17</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>-0.39</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>2.77</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>-114.07</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>2025/11/19</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>28111.46159317212</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>30506.0</t>
+        </is>
+      </c>
+      <c r="AX10" t="n">
+        <v>23927.2</v>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>19193.0</t>
+        </is>
+      </c>
+      <c r="AZ10" t="n">
+        <v>13522.88</v>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>4734</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>927.631088724425</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>1721.616370799031</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>30506.0</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>49.9</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>2025/08/12</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>-9.92</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>匯鑽科</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>匯鑽科</t>
+        </is>
+      </c>
+      <c r="BK10" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL10" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM10" t="inlineStr">
+        <is>
+          <t>0.78</t>
+        </is>
+      </c>
+      <c r="BN10" t="inlineStr">
+        <is>
+          <t>-10.56465687102404</t>
+        </is>
+      </c>
+      <c r="BO10" t="inlineStr">
+        <is>
+          <t>-13.69932964657055</t>
+        </is>
+      </c>
+      <c r="BP10" t="inlineStr">
+        <is>
+          <t>7.80229574004913</t>
+        </is>
+      </c>
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
+          <t>價漲量增</t>
+        </is>
+      </c>
+      <c r="BS10" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="BT10" t="inlineStr">
+        <is>
+          <t>2.46</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
+          <t>6.59</t>
+        </is>
+      </c>
+      <c r="BV10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr">
+        <is>
+          <t>8.25%</t>
+        </is>
+      </c>
+      <c r="BX10" t="inlineStr">
+        <is>
+          <t>-14.21%</t>
+        </is>
+      </c>
+      <c r="BY10" t="inlineStr">
+        <is>
+          <t>44.93</t>
+        </is>
+      </c>
+      <c r="BZ10" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
+        <is>
+          <t>加工業務99.90%、勞務0.10% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>匯鑽科-其他電子業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC10" t="inlineStr">
+        <is>
+          <t>其他電子業右下上櫃</t>
+        </is>
+      </c>
+      <c r="CD10" t="inlineStr">
+        <is>
+          <t>45.5</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
+          <t>46.55</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
+          <t>44.8</t>
+        </is>
+      </c>
+      <c r="CG10" t="inlineStr">
+        <is>
           <t>44.95</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>24.64</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>-0.34</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>-0.45</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>2.77</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr">
-        <is>
-          <t>-116.07</t>
-        </is>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>2025/11/19</t>
-        </is>
-      </c>
-      <c r="AV10" t="inlineStr">
-        <is>
-          <t>28136.79700854701</t>
-        </is>
-      </c>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>30695.0</t>
-        </is>
-      </c>
-      <c r="AX10" t="n">
-        <v>18788.8</v>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>19613.1</t>
-        </is>
-      </c>
-      <c r="AZ10" t="n">
-        <v>13049.74</v>
-      </c>
-      <c r="BA10" t="inlineStr">
-        <is>
-          <t>-824</t>
-        </is>
-      </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>783.2701283472239</t>
-        </is>
-      </c>
-      <c r="BC10" t="inlineStr">
-        <is>
-          <t>1149.944823147569</t>
-        </is>
-      </c>
-      <c r="BD10" t="inlineStr">
-        <is>
-          <t>30695.0</t>
-        </is>
-      </c>
-      <c r="BE10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF10" t="inlineStr">
-        <is>
-          <t>49.9</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>2025/08/12</t>
-        </is>
-      </c>
-      <c r="BH10" t="inlineStr">
-        <is>
-          <t>-9.82</t>
-        </is>
-      </c>
-      <c r="BI10" t="inlineStr">
-        <is>
-          <t>匯鑽科</t>
-        </is>
-      </c>
-      <c r="BJ10" t="inlineStr">
-        <is>
-          <t>匯鑽科</t>
-        </is>
-      </c>
-      <c r="BK10" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BL10" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM10" t="inlineStr">
-        <is>
-          <t>0.78</t>
-        </is>
-      </c>
-      <c r="BN10" t="inlineStr">
-        <is>
-          <t>-10.56465687102404</t>
-        </is>
-      </c>
-      <c r="BO10" t="inlineStr">
-        <is>
-          <t>-13.69932964657055</t>
-        </is>
-      </c>
-      <c r="BP10" t="inlineStr">
-        <is>
-          <t>7.80229574004913</t>
-        </is>
-      </c>
-      <c r="BQ10" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
-        </is>
-      </c>
-      <c r="BR10" t="inlineStr">
-        <is>
-          <t>價漲量增</t>
-        </is>
-      </c>
-      <c r="BS10" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
-      </c>
-      <c r="BT10" t="inlineStr">
-        <is>
-          <t>2.48</t>
-        </is>
-      </c>
-      <c r="BU10" t="inlineStr">
-        <is>
-          <t>6.59</t>
-        </is>
-      </c>
-      <c r="BV10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BW10" t="inlineStr">
-        <is>
-          <t>8.25%</t>
-        </is>
-      </c>
-      <c r="BX10" t="inlineStr">
-        <is>
-          <t>-14.21%</t>
-        </is>
-      </c>
-      <c r="BY10" t="inlineStr">
-        <is>
-          <t>44.93</t>
-        </is>
-      </c>
-      <c r="BZ10" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
-      </c>
-      <c r="CA10" t="inlineStr">
-        <is>
-          <t>加工業務99.90%、勞務0.10% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB10" t="inlineStr">
-        <is>
-          <t>匯鑽科-其他電子業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC10" t="inlineStr">
-        <is>
-          <t>其他電子業右下上櫃</t>
-        </is>
-      </c>
-      <c r="CD10" t="inlineStr">
-        <is>
-          <t>43.55</t>
-        </is>
-      </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>45.55</t>
-        </is>
-      </c>
-      <c r="CF10" t="inlineStr">
-        <is>
-          <t>43.3</t>
-        </is>
-      </c>
-      <c r="CG10" t="inlineStr">
-        <is>
-          <t>45.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4743,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>655.0</t>
+          <t>685.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4.42</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-32.14</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>16.81</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4894,63 +4894,63 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>83.93</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>75.04</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>42.22000000000001</t>
+          <t>42.73999999999999</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>43.6</v>
+        <v>43.61</v>
       </c>
       <c r="AN11" t="n">
-        <v>44.15</v>
+        <v>44.12</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>44.89</t>
+          <t>44.95</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-16.05</t>
+          <t>24.64</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-117.06</t>
+          <t>-116.07</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>28136.79700854701</t>
+          <t>28111.46159317212</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>28225.0</t>
+          <t>30695.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>13738.6</v>
+        <v>18788.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>20246.9</t>
+          <t>19613.1</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>12733.2</v>
+        <v>13049.74</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-6508</t>
+          <t>-824</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>716.6020020198885</t>
+          <t>783.2701283472239</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>271.9517256759318</t>
+          <t>1149.944823147569</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>28225.0</t>
+          <t>30695.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-13.23</t>
+          <t>-9.82</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>42.35</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>369.0</t>
+          <t>655.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>42.35</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>6.51</t>
+          <t>4.42</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-43.86</t>
+          <t>-32.14</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-4.72</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>9.06</t>
+          <t>16.07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5324,63 +5324,63 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>41.18</t>
+          <t>83.93</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>14.84</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-3.61</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.58</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>42.22000000000001</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>43.53</v>
+        <v>43.6</v>
       </c>
       <c r="AN12" t="n">
-        <v>44.23</v>
+        <v>44.15</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>44.87</t>
+          <t>44.89</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-40.91</t>
+          <t>-16.05</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-116.38</t>
+          <t>-117.06</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>28136.79700854701</t>
+          <t>28111.46159317212</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>15453.0</t>
+          <t>28225.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>11783.2</v>
+        <v>13738.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>20989.4</t>
+          <t>20246.9</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>12346.96</v>
+        <v>12733.2</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-9206</t>
+          <t>-6508</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>797.4475068096988</t>
+          <t>716.6020020198885</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-727.3938323434086</t>
+          <t>271.9517256759318</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>15453.0</t>
+          <t>28225.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-15.13</t>
+          <t>-13.23</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>41.1</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>42.7</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>42.35</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>42.35</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1014.23</t>
+          <t>739.811</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-23.60</t>
+          <t>-10.13</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>4.90</t>
+          <t>3.58</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,12 +5744,12 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>1014</t>
+          <t>740</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5759,58 +5759,58 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>61.16</t>
+          <t>67.9</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-7.36</t>
+          <t>-7.48</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>87.29999999999998</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>90.34</v>
+        <v>89.87</v>
       </c>
       <c r="AN13" t="n">
-        <v>97.52</v>
+        <v>97.14</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>97.62</t>
+          <t>97.67</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>6.07</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-3.00</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-3.12</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-143.32</t>
+          <t>-142.67</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>353704340.7735043</t>
+          <t>353339499.4032717</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>88951847.0</t>
+          <t>64813905.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>59081139.2</v>
+        <v>62364817.4</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>77327536.6</t>
+          <t>69391061.0</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>250820460.68</v>
+        <v>243715090.02</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-18246397</t>
+          <t>-7026243</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-29025923.77036555</t>
+          <t>-28100462.4147675</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-25023946.09403855</t>
+          <t>-23010424.95897819</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>88951847.0</t>
+          <t>64813905.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5971,7 +5971,7 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>34.53</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>88.9</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>461.141</t>
+          <t>1014.23</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>87.8</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-33.87</t>
+          <t>-23.60</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-17.94</t>
+          <t>-18.60</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>4.90</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,274 +6174,274 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>1014</t>
+          <t>740</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>85.19</t>
+          <t>59.26</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>55.95</t>
+          <t>61.16</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-4.12</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-7.23</t>
+          <t>-7.36</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
+          <t>87.29999999999998</t>
+        </is>
+      </c>
+      <c r="AM14" t="n">
+        <v>90.34</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>97.52</v>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>97.62</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>3.61</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>-3.00</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>-3.12</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>7.19</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>-143.32</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>2025/11/28</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>353339499.4032717</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>88951847.0</t>
+        </is>
+      </c>
+      <c r="AX14" t="n">
+        <v>59081139.2</v>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>77327536.6</t>
+        </is>
+      </c>
+      <c r="AZ14" t="n">
+        <v>250820460.68</v>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>-18246397</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>-29025923.77036555</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>-25023946.09403855</t>
+        </is>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>88951847.0</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>81.3</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>2025/07/28</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>7.13</t>
+        </is>
+      </c>
+      <c r="BI14" t="inlineStr">
+        <is>
+          <t>鉅祥</t>
+        </is>
+      </c>
+      <c r="BJ14" t="inlineStr">
+        <is>
+          <t>鉅祥</t>
+        </is>
+      </c>
+      <c r="BK14" t="inlineStr">
+        <is>
+          <t>電子零組件業</t>
+        </is>
+      </c>
+      <c r="BL14" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM14" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="BN14" t="inlineStr">
+        <is>
+          <t>-7.291353668658945</t>
+        </is>
+      </c>
+      <c r="BO14" t="inlineStr">
+        <is>
+          <t>11.64963320584363</t>
+        </is>
+      </c>
+      <c r="BP14" t="inlineStr">
+        <is>
+          <t>10.65346457950322</t>
+        </is>
+      </c>
+      <c r="BQ14" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR14" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS14" t="inlineStr">
+        <is>
+          <t>2.29</t>
+        </is>
+      </c>
+      <c r="BT14" t="inlineStr">
+        <is>
+          <t>4.02</t>
+        </is>
+      </c>
+      <c r="BU14" t="inlineStr">
+        <is>
+          <t>9.36</t>
+        </is>
+      </c>
+      <c r="BV14" t="inlineStr">
+        <is>
+          <t>22.39</t>
+        </is>
+      </c>
+      <c r="BW14" t="inlineStr">
+        <is>
+          <t>29.60%</t>
+        </is>
+      </c>
+      <c r="BX14" t="inlineStr">
+        <is>
+          <t>15.93%</t>
+        </is>
+      </c>
+      <c r="BY14" t="inlineStr">
+        <is>
+          <t>34.53</t>
+        </is>
+      </c>
+      <c r="BZ14" t="inlineStr">
+        <is>
+          <t>18369</t>
+        </is>
+      </c>
+      <c r="CA14" t="inlineStr">
+        <is>
+          <t>部品95.14%、模具3.09%、商品銷售1.03%、治具0.75% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB14" t="inlineStr">
+        <is>
+          <t>鉅祥-電子零組件業-上市</t>
+        </is>
+      </c>
+      <c r="CC14" t="inlineStr">
+        <is>
+          <t>電子零組件業右上上市</t>
+        </is>
+      </c>
+      <c r="CD14" t="inlineStr">
+        <is>
+          <t>87.5</t>
+        </is>
+      </c>
+      <c r="CE14" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="CF14" t="inlineStr">
+        <is>
+          <t>86.8</t>
+        </is>
+      </c>
+      <c r="CG14" t="inlineStr">
+        <is>
           <t>87.1</t>
-        </is>
-      </c>
-      <c r="AM14" t="n">
-        <v>90.84</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>97.92</v>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>97.54</t>
-        </is>
-      </c>
-      <c r="AP14" t="inlineStr">
-        <is>
-          <t>0.98</t>
-        </is>
-      </c>
-      <c r="AQ14" t="inlineStr">
-        <is>
-          <t>-3.11</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>-3.14</t>
-        </is>
-      </c>
-      <c r="AS14" t="inlineStr">
-        <is>
-          <t>7.19</t>
-        </is>
-      </c>
-      <c r="AT14" t="inlineStr">
-        <is>
-          <t>-143.71</t>
-        </is>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>2025/11/28</t>
-        </is>
-      </c>
-      <c r="AV14" t="inlineStr">
-        <is>
-          <t>353704340.7735043</t>
-        </is>
-      </c>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>40320203.0</t>
-        </is>
-      </c>
-      <c r="AX14" t="n">
-        <v>54978050.8</v>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>83135790.5</t>
-        </is>
-      </c>
-      <c r="AZ14" t="n">
-        <v>260959475.16</v>
-      </c>
-      <c r="BA14" t="inlineStr">
-        <is>
-          <t>-28157739</t>
-        </is>
-      </c>
-      <c r="BB14" t="inlineStr">
-        <is>
-          <t>-29753556.07515229</t>
-        </is>
-      </c>
-      <c r="BC14" t="inlineStr">
-        <is>
-          <t>-29592900.56933765</t>
-        </is>
-      </c>
-      <c r="BD14" t="inlineStr">
-        <is>
-          <t>40320203.0</t>
-        </is>
-      </c>
-      <c r="BE14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF14" t="inlineStr">
-        <is>
-          <t>81.3</t>
-        </is>
-      </c>
-      <c r="BG14" t="inlineStr">
-        <is>
-          <t>2025/07/28</t>
-        </is>
-      </c>
-      <c r="BH14" t="inlineStr">
-        <is>
-          <t>8.00</t>
-        </is>
-      </c>
-      <c r="BI14" t="inlineStr">
-        <is>
-          <t>鉅祥</t>
-        </is>
-      </c>
-      <c r="BJ14" t="inlineStr">
-        <is>
-          <t>鉅祥</t>
-        </is>
-      </c>
-      <c r="BK14" t="inlineStr">
-        <is>
-          <t>電子零組件業</t>
-        </is>
-      </c>
-      <c r="BL14" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM14" t="inlineStr">
-        <is>
-          <t>1.02</t>
-        </is>
-      </c>
-      <c r="BN14" t="inlineStr">
-        <is>
-          <t>-7.291353668658945</t>
-        </is>
-      </c>
-      <c r="BO14" t="inlineStr">
-        <is>
-          <t>11.64963320584363</t>
-        </is>
-      </c>
-      <c r="BP14" t="inlineStr">
-        <is>
-          <t>10.65346457950322</t>
-        </is>
-      </c>
-      <c r="BQ14" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR14" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS14" t="inlineStr">
-        <is>
-          <t>2.31</t>
-        </is>
-      </c>
-      <c r="BT14" t="inlineStr">
-        <is>
-          <t>4.02</t>
-        </is>
-      </c>
-      <c r="BU14" t="inlineStr">
-        <is>
-          <t>9.36</t>
-        </is>
-      </c>
-      <c r="BV14" t="inlineStr">
-        <is>
-          <t>22.39</t>
-        </is>
-      </c>
-      <c r="BW14" t="inlineStr">
-        <is>
-          <t>29.60%</t>
-        </is>
-      </c>
-      <c r="BX14" t="inlineStr">
-        <is>
-          <t>15.93%</t>
-        </is>
-      </c>
-      <c r="BY14" t="inlineStr">
-        <is>
-          <t>34.7</t>
-        </is>
-      </c>
-      <c r="BZ14" t="inlineStr">
-        <is>
-          <t>18369</t>
-        </is>
-      </c>
-      <c r="CA14" t="inlineStr">
-        <is>
-          <t>部品95.14%、模具3.09%、商品銷售1.03%、治具0.75% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB14" t="inlineStr">
-        <is>
-          <t>鉅祥-電子零組件業-上市</t>
-        </is>
-      </c>
-      <c r="CC14" t="inlineStr">
-        <is>
-          <t>電子零組件業右上上市</t>
-        </is>
-      </c>
-      <c r="CD14" t="inlineStr">
-        <is>
-          <t>87.9</t>
-        </is>
-      </c>
-      <c r="CE14" t="inlineStr">
-        <is>
-          <t>87.9</t>
-        </is>
-      </c>
-      <c r="CF14" t="inlineStr">
-        <is>
-          <t>86.9</t>
-        </is>
-      </c>
-      <c r="CG14" t="inlineStr">
-        <is>
-          <t>87.8</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6463,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>630.229</t>
+          <t>461.141</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-29.59</t>
+          <t>-33.87</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-18.60</t>
+          <t>-17.94</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,73 +6604,73 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>1014</t>
+          <t>740</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>39.02</t>
+          <t>85.19</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>31.54</t>
+          <t>55.95</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-5.08</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-7.16</t>
+          <t>-7.23</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>86.64</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>91.28</v>
+        <v>90.84</v>
       </c>
       <c r="AN15" t="n">
-        <v>98.31</v>
+        <v>97.92</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>97.43</t>
+          <t>97.54</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-3.11</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-3.15</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-143.82</t>
+          <t>-143.71</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>353704340.7735043</t>
+          <t>353339499.4032717</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>55246132.0</t>
+          <t>40320203.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>67438997.8</v>
+        <v>54978050.8</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>95782499.1</t>
+          <t>83135790.5</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>275665355.36</v>
+        <v>260959475.16</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-28343501</t>
+          <t>-28157739</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-29782766.16711858</t>
+          <t>-29753556.07515229</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-29852555.79943146</t>
+          <t>-29592900.56933765</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>55246132.0</t>
+          <t>40320203.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>7.13</t>
+          <t>8.00</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>34.53</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6861,17 +6861,17 @@
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.9</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>713.512</t>
+          <t>630.229</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-33.57</t>
+          <t>-29.59</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-17.85</t>
+          <t>-18.60</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,73 +7034,73 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>1014</t>
+          <t>740</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>43.64</t>
+          <t>39.02</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>31.54</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-5.14</t>
+          <t>-5.08</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-7.33</t>
+          <t>-7.16</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>86.85999999999999</t>
+          <t>86.64</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>91.56999999999999</v>
+        <v>91.28</v>
       </c>
       <c r="AN16" t="n">
-        <v>98.81999999999999</v>
+        <v>98.31</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>97.34</t>
+          <t>97.43</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-8.10</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-3.12</t>
+          <t>-3.15</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-143.38</t>
+          <t>-143.82</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>353704340.7735043</t>
+          <t>353339499.4032717</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>62492000.0</t>
+          <t>55246132.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>68942899</v>
+        <v>67438997.8</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>103776418.9</t>
+          <t>95782499.1</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>296624289.38</v>
+        <v>275665355.36</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-34833519</t>
+          <t>-28343501</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-29770077.14306169</t>
+          <t>-29782766.16711858</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-30756535.8138715</t>
+          <t>-29852555.79943146</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>62492000.0</t>
+          <t>55246132.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>7.13</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,17 +7221,17 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7261,7 +7261,7 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>34.53</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>557.755</t>
+          <t>713.512</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-31.49</t>
+          <t>-33.57</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-19.07</t>
+          <t>-17.85</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,73 +7464,73 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>1014</t>
+          <t>740</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>11.96</t>
+          <t>43.64</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>6.16</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-5.79</t>
+          <t>-5.14</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-7.52</t>
+          <t>-7.33</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>86.58</t>
+          <t>86.85999999999999</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>91.90000000000001</v>
+        <v>91.56999999999999</v>
       </c>
       <c r="AN17" t="n">
-        <v>99.37</v>
+        <v>98.81999999999999</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>97.25</t>
+          <t>97.34</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-15.28</t>
+          <t>-8.10</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-3.12</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-142.50</t>
+          <t>-143.38</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>353704340.7735043</t>
+          <t>353339499.4032717</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>48395514.0</t>
+          <t>62492000.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>76417304.59999999</v>
+        <v>68942899</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>111545339.3</t>
+          <t>103776418.9</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>319430807.84</v>
+        <v>296624289.38</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-35128034</t>
+          <t>-34833519</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-29590721.02109627</t>
+          <t>-29770077.14306169</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-31725831.12686187</t>
+          <t>-30756535.8138715</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>48395514.0</t>
+          <t>62492000.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>8.12</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,17 +7651,17 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>34.53</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>797.916</t>
+          <t>557.755</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>86.1</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-21.02</t>
+          <t>-31.49</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-19.53</t>
+          <t>-19.07</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,151 +7894,151 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>1014</t>
+          <t>740</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
+          <t>11.96</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>6.16</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>-5.79</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>-7.52</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>86.58</t>
+        </is>
+      </c>
+      <c r="AM18" t="n">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>99.37</v>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>97.25</t>
+        </is>
+      </c>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>-15.28</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>-3.52</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>-3.06</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>7.19</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr">
+        <is>
+          <t>-142.50</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>2025/11/28</t>
+        </is>
+      </c>
+      <c r="AV18" t="inlineStr">
+        <is>
+          <t>353339499.4032717</t>
+        </is>
+      </c>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>48395514.0</t>
+        </is>
+      </c>
+      <c r="AX18" t="n">
+        <v>76417304.59999999</v>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>111545339.3</t>
+        </is>
+      </c>
+      <c r="AZ18" t="n">
+        <v>319430807.84</v>
+      </c>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>-35128034</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>-29590721.02109627</t>
+        </is>
+      </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>-31725831.12686187</t>
+        </is>
+      </c>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>48395514.0</t>
+        </is>
+      </c>
+      <c r="BE18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF18" t="inlineStr">
+        <is>
+          <t>81.3</t>
+        </is>
+      </c>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>2025/07/28</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
           <t>6.52</t>
         </is>
       </c>
-      <c r="AG18" t="inlineStr">
-        <is>
-          <t>9.08</t>
-        </is>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>-0.76</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>-6.01</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>-7.68</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>2.91</t>
-        </is>
-      </c>
-      <c r="AL18" t="inlineStr">
-        <is>
-          <t>86.75999999999999</t>
-        </is>
-      </c>
-      <c r="AM18" t="n">
-        <v>92.31</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>99.98999999999999</v>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>97.16</t>
-        </is>
-      </c>
-      <c r="AP18" t="inlineStr">
-        <is>
-          <t>-20.19</t>
-        </is>
-      </c>
-      <c r="AQ18" t="inlineStr">
-        <is>
-          <t>-3.53</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>-2.94</t>
-        </is>
-      </c>
-      <c r="AS18" t="inlineStr">
-        <is>
-          <t>7.19</t>
-        </is>
-      </c>
-      <c r="AT18" t="inlineStr">
-        <is>
-          <t>-140.87</t>
-        </is>
-      </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>2025/11/28</t>
-        </is>
-      </c>
-      <c r="AV18" t="inlineStr">
-        <is>
-          <t>353704340.7735043</t>
-        </is>
-      </c>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>68436405.0</t>
-        </is>
-      </c>
-      <c r="AX18" t="n">
-        <v>95573934</v>
-      </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>121006638.2</t>
-        </is>
-      </c>
-      <c r="AZ18" t="n">
-        <v>336619552.5</v>
-      </c>
-      <c r="BA18" t="inlineStr">
-        <is>
-          <t>-25432704</t>
-        </is>
-      </c>
-      <c r="BB18" t="inlineStr">
-        <is>
-          <t>-29202519.18368434</t>
-        </is>
-      </c>
-      <c r="BC18" t="inlineStr">
-        <is>
-          <t>-30467135.53374588</t>
-        </is>
-      </c>
-      <c r="BD18" t="inlineStr">
-        <is>
-          <t>68436405.0</t>
-        </is>
-      </c>
-      <c r="BE18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF18" t="inlineStr">
-        <is>
-          <t>81.3</t>
-        </is>
-      </c>
-      <c r="BG18" t="inlineStr">
-        <is>
-          <t>2025/07/28</t>
-        </is>
-      </c>
-      <c r="BH18" t="inlineStr">
-        <is>
-          <t>5.90</t>
-        </is>
-      </c>
       <c r="BI18" t="inlineStr">
         <is>
           <t>鉅祥</t>
@@ -8081,7 +8081,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>34.53</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>85.1</t>
+          <t>85.9</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>86.1</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-3.11</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1197.387</t>
+          <t>797.916</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>86.1</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-9.98</t>
+          <t>-21.02</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-20.09</t>
+          <t>-19.53</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>5.79</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,73 +8324,73 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>1014</t>
+          <t>740</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>6.91</t>
+          <t>9.08</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-5.99</t>
+          <t>-6.01</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-7.53</t>
+          <t>-7.68</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>87.46000000000001</t>
+          <t>86.75999999999999</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>93.03</v>
+        <v>92.31</v>
       </c>
       <c r="AN19" t="n">
-        <v>100.61</v>
+        <v>99.98999999999999</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>97.09</t>
+          <t>97.16</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-23.35</t>
+          <t>-20.19</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>-3.53</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-138.81</t>
+          <t>-140.87</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>353704340.7735043</t>
+          <t>353339499.4032717</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>102624938.0</t>
+          <t>68436405.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>111293530.2</v>
+        <v>95573934</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>123628857.1</t>
+          <t>121006638.2</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>366752945.54</v>
+        <v>336619552.5</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-12335326</t>
+          <t>-25432704</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-28972588.9382186</t>
+          <t>-29202519.18368434</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-29728125.31023213</t>
+          <t>-30467135.53374588</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>102624938.0</t>
+          <t>68436405.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>5.17</t>
+          <t>5.90</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8521,7 +8521,7 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8551,7 +8551,7 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>34.53</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>86.1</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>-3.11</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>710.084</t>
+          <t>1197.387</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-9.98</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-17.57</t>
+          <t>-20.09</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>5.79</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,17 +8754,17 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>1014</t>
+          <t>740</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>20.73</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
@@ -8774,53 +8774,53 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-5.54</t>
+          <t>-5.99</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-7.34</t>
+          <t>-7.53</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>88.56</t>
+          <t>87.46000000000001</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>93.75</v>
+        <v>93.03</v>
       </c>
       <c r="AN20" t="n">
-        <v>101.18</v>
+        <v>100.61</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>97.04</t>
+          <t>97.09</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-22.39</t>
+          <t>-23.35</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-136.55</t>
+          <t>-138.81</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>353704340.7735043</t>
+          <t>353339499.4032717</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>62765638.0</t>
+          <t>102624938.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>124126000.4</v>
+        <v>111293530.2</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>125231243.6</t>
+          <t>123628857.1</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>399636300.16</v>
+        <v>366752945.54</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-1105243</t>
+          <t>-12335326</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-28835218.6887616</t>
+          <t>-28972588.9382186</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-31273734.76556134</t>
+          <t>-29728125.31023213</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>62765638.0</t>
+          <t>102624938.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>8.49</t>
+          <t>5.17</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8941,17 +8941,17 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8981,7 +8981,7 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>34.53</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>89.4</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1153.082</t>
+          <t>710.084</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-19.16</t>
+          <t>-17.57</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,73 +9184,73 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>1014</t>
+          <t>740</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.73</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.91</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-3.74</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-5.54</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-7.14</t>
+          <t>-7.34</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>89.86</t>
+          <t>88.56</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>94.36</v>
+        <v>93.75</v>
       </c>
       <c r="AN21" t="n">
-        <v>101.62</v>
+        <v>101.18</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>96.9</t>
+          <t>97.04</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-27.21</t>
+          <t>-22.39</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-2.48</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-134.50</t>
+          <t>-136.55</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>353704340.7735043</t>
+          <t>353339499.4032717</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>99864028.0</t>
+          <t>62765638.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>138609938.8</v>
+        <v>124126000.4</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>137834914.3</t>
+          <t>125231243.6</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>443270959.36</v>
+        <v>399636300.16</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>775024</t>
+          <t>-1105243</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-28391852.12934346</t>
+          <t>-28835218.6887616</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-28094189.88869017</t>
+          <t>-31273734.76556134</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>99864028.0</t>
+          <t>62765638.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>6.40</t>
+          <t>8.49</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9371,17 +9371,17 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>34.53</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>88.6</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
+          <t>89.4</t>
+        </is>
+      </c>
+      <c r="CF21" t="inlineStr">
+        <is>
           <t>87.9</t>
         </is>
       </c>
-      <c r="CF21" t="inlineStr">
-        <is>
-          <t>85.9</t>
-        </is>
-      </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1638.11</t>
+          <t>1153.082</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>0.69</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-18.22</t>
+          <t>-19.16</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>7.92</t>
+          <t>5.57</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-2.40</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,12 +9614,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>1014</t>
+          <t>740</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9634,53 +9634,53 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-4.12</t>
+          <t>-3.74</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-4.10</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-6.67</t>
+          <t>-7.14</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>91.26</t>
+          <t>89.86</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>95.16</v>
+        <v>94.36</v>
       </c>
       <c r="AN22" t="n">
-        <v>101.96</v>
+        <v>101.62</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>96.8</t>
+          <t>96.9</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-23.67</t>
+          <t>-27.21</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-2.86</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-132.15</t>
+          <t>-134.50</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>353704340.7735043</t>
+          <t>353339499.4032717</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>144178661.0</t>
+          <t>99864028.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>146673374</v>
+        <v>138609938.8</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>149731355.7</t>
+          <t>137834914.3</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>454484548.46</v>
+        <v>443270959.36</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-3057981</t>
+          <t>775024</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-28445972.53673498</t>
+          <t>-28391852.12934346</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-26523446.49713525</t>
+          <t>-28094189.88869017</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>144178661.0</t>
+          <t>99864028.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>7.63</t>
+          <t>6.40</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9841,7 +9841,7 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>34.53</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>89.9</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>85.9</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1631.485</t>
+          <t>1638.11</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-1.43</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-20.69</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-16.26</t>
+          <t>-18.22</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>7.89</t>
+          <t>7.92</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>-2.40</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,12 +10044,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>1014</t>
+          <t>740</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10059,58 +10059,58 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>13.16</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-3.30</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>-4.10</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-6.3</t>
+          <t>-6.67</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>5.78</t>
+          <t>5.33</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>92.66</t>
+          <t>91.26</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>95.84</v>
+        <v>95.16</v>
       </c>
       <c r="AN23" t="n">
-        <v>102.28</v>
+        <v>101.96</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>96.69</t>
+          <t>96.8</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-16.84</t>
+          <t>-23.67</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-2.54</t>
+          <t>-2.86</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-2.31</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-130.25</t>
+          <t>-132.15</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>353704340.7735043</t>
+          <t>353339499.4032717</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>147034386.0</t>
+          <t>144178661.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>146439342.4</v>
+        <v>146673374</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>184645225.3</t>
+          <t>149731355.7</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>461884050.18</v>
+        <v>454484548.46</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-38205882</t>
+          <t>-3057981</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-28795522.72575311</t>
+          <t>-28445972.53673498</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-28080257.81287342</t>
+          <t>-26523446.49713525</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>147034386.0</t>
+          <t>144178661.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>10.21</t>
+          <t>7.63</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10271,7 +10271,7 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>34.53</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>89.9</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>89.4</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/電鍍材料.xlsx
+++ b/Result/checksun_type/電鍍材料.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>1537.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>48.45</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,17 +908,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-6.02</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-25.69</t>
+          <t>24.37</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>9.00</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>37.72</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>151</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,58 +1029,58 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>93.02</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>5.99</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-2.95</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>45.04</t>
+          <t>45.71</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>43.61</v>
+        <v>43.81</v>
       </c>
       <c r="AN2" t="n">
-        <v>43.98</v>
+        <v>44.04</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>45.38</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>1334.55</t>
+          <t>336.50</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-99.17</t>
+          <t>-94.77</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>28111.46159317212</t>
+          <t>28227.69034090909</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>6884.0</t>
+          <t>73291.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>9869</v>
+        <v>21815.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>13280.9</t>
+          <t>17540.5</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>13072.58</v>
+        <v>14449.18</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-3411</t>
+          <t>4274</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-816.4971901541018</t>
+          <t>-215.247811154344</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-1765.508276203122</t>
+          <t>3091.623773344323</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>6884.0</t>
+          <t>73291.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-8.42</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2029</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>48.45</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,127 +1313,127 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>0.88</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>151.0</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>45.7</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3.38</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-25.69</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-10-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-08-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-08-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>45.6</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>44.45</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>52.5</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>47.6</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>2.81</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>-4.20</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>3.71</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
           <t>1.44</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>318.0</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>45.3</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>-38.19</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-10-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-10-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-08-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-08-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>45.6</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>44.45</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>52.5</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>47.6</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>-4.20</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>7.80</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>-1.10</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,12 +1444,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>151</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1459,58 +1459,58 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>85.14</t>
+          <t>93.02</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.90</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>44.62</t>
+          <t>45.04</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>43.57</v>
+        <v>43.61</v>
       </c>
       <c r="AN3" t="n">
-        <v>43.95</v>
+        <v>43.98</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>45.26</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>507.74</t>
+          <t>1334.55</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-101.94</t>
+          <t>-99.17</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>28111.46159317212</t>
+          <t>28227.69034090909</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>14487.0</t>
+          <t>6884.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>9527.799999999999</v>
+        <v>9869</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>15415.0</t>
+          <t>13280.9</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>13104.9</v>
+        <v>13072.58</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-5887</t>
+          <t>-3411</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-643.9497199633709</t>
+          <t>-816.4971901541018</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-1526.178765692213</t>
+          <t>-1765.508276203122</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>14487.0</t>
+          <t>6884.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-9.22</t>
+          <t>-8.42</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2029</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>45.05</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>197.0</t>
+          <t>318.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>44.65</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-48.71</t>
+          <t>-38.19</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>7.80</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,17 +1874,17 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>151</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>79.07</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1894,53 +1894,53 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-2.90</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>44.16</t>
+          <t>44.62</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>43.52</v>
+        <v>43.57</v>
       </c>
       <c r="AN4" t="n">
         <v>43.95</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>45.23</t>
+          <t>45.26</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>194.44</t>
+          <t>507.74</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-104.40</t>
+          <t>-101.94</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>28111.46159317212</t>
+          <t>28227.69034090909</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>8868.0</t>
+          <t>14487.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>7955.4</v>
+        <v>9527.799999999999</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>15511.6</t>
+          <t>15415.0</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>13262.22</v>
+        <v>13104.9</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-7556</t>
+          <t>-5887</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-483.5444389217631</t>
+          <t>-643.9497199633709</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-1944.380223330478</t>
+          <t>-1526.178765692213</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>8868.0</t>
+          <t>14487.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-10.52</t>
+          <t>-9.22</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2071,12 +2071,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2029</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
+          <t>46.0</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
+          <t>45.1</t>
+        </is>
+      </c>
+      <c r="CG4" t="inlineStr">
+        <is>
           <t>45.3</t>
-        </is>
-      </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>44.4</t>
-        </is>
-      </c>
-      <c r="CG4" t="inlineStr">
-        <is>
-          <t>44.65</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>197.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,69 +2188,69 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>44.65</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>3.38</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>-48.71</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-10-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2025-08-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2025-08-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>45.6</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
           <t>44.45</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>1.88</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>-48.61</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2025-10-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2025-10-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-08-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-08-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>45.6</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>44.45</t>
-        </is>
-      </c>
       <c r="S5" t="inlineStr">
         <is>
           <t>0</t>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,37 +2304,37 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>151</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>76.36</t>
+          <t>79.07</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>85.14</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -2344,33 +2344,33 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>43.82000000000001</t>
+          <t>44.16</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>43.49</v>
+        <v>43.52</v>
       </c>
       <c r="AN5" t="n">
-        <v>43.94</v>
+        <v>43.95</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>45.21</t>
+          <t>45.23</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>125.94</t>
+          <t>194.44</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-106.54</t>
+          <t>-104.40</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>28111.46159317212</t>
+          <t>28227.69034090909</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>5546.0</t>
+          <t>8868.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>8273.799999999999</v>
+        <v>7955.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>16100.5</t>
+          <t>15511.6</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>13310.48</v>
+        <v>13262.22</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-7826</t>
+          <t>-7556</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-217.9379326656332</t>
+          <t>-483.5444389217631</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-1870.333011980483</t>
+          <t>-1944.380223330478</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>5546.0</t>
+          <t>8868.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-10.92</t>
+          <t>-10.52</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2501,12 +2501,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2029</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>44.45</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>44.45</t>
+          <t>44.65</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>302.0</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>44.45</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>2.74</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-17.23</t>
+          <t>-48.61</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>151</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>76.36</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>72.02</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>43.92</t>
+          <t>43.82000000000001</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>43.47</v>
+        <v>43.49</v>
       </c>
       <c r="AN6" t="n">
         <v>43.94</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>45.23</t>
+          <t>45.21</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>91.47</t>
+          <t>125.94</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-108.60</t>
+          <t>-106.54</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>28111.46159317212</t>
+          <t>28227.69034090909</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>13560.0</t>
+          <t>5546.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>13265.8</v>
+        <v>8273.799999999999</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>16027.3</t>
+          <t>16100.5</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>13521.82</v>
+        <v>13310.48</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-2761</t>
+          <t>-7826</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>82.49753630070325</t>
+          <t>-217.9379326656332</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-1341.825102481189</t>
+          <t>-1870.333011980483</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>13560.0</t>
+          <t>5546.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-9.62</t>
+          <t>-10.92</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2029</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>44.45</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>44.45</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>118.0</t>
+          <t>302.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>9.71</t>
+          <t>-17.23</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>151</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>65.43</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>55.14</t>
+          <t>72.02</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.1</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-2.80</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>43.92</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>43.44</v>
+        <v>43.47</v>
       </c>
       <c r="AN7" t="n">
-        <v>43.92</v>
+        <v>43.94</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>45.19</t>
+          <t>45.23</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>41.21</t>
+          <t>91.47</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-110.57</t>
+          <t>-108.60</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>28111.46159317212</t>
+          <t>28227.69034090909</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>5178.0</t>
+          <t>13560.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>16692.8</v>
+        <v>13265.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>15215.7</t>
+          <t>16027.3</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>13519.76</v>
+        <v>13521.82</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>-2761</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>341.4652888065019</t>
+          <t>82.49753630070325</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-1397.534335250723</t>
+          <t>-1341.825102481189</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>5178.0</t>
+          <t>13560.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-12.63</t>
+          <t>-9.62</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2029</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>43.45</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>43.45</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>118.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5.08</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>28.77</t>
+          <t>9.71</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>151</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>50.62</t>
+          <t>65.43</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>66.26</t>
+          <t>55.14</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.1</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>43.84</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>43.45</v>
+        <v>43.44</v>
       </c>
       <c r="AN8" t="n">
-        <v>43.97</v>
+        <v>43.92</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>45.12</t>
+          <t>45.19</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>34.76</t>
+          <t>41.21</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-111.66</t>
+          <t>-110.57</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>28111.46159317212</t>
+          <t>28227.69034090909</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>6625.0</t>
+          <t>5178.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>21302.2</v>
+        <v>16692.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>16542.7</t>
+          <t>15215.7</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>13576.72</v>
+        <v>13519.76</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>4759</t>
+          <t>1477</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>657.6470386350882</t>
+          <t>341.4652888065019</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-529.1355843768179</t>
+          <t>-1397.534335250723</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>6625.0</t>
+          <t>5178.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-13.83</t>
+          <t>-12.63</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2029</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>43.45</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>42.8</t>
+          <t>43.45</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-4.49</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>42.95</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5.19</t>
+          <t>5.91</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>20.84</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>5.89</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>151</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>49.38</t>
+          <t>50.62</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>82.72</t>
+          <t>66.26</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>43.71</t>
+          <t>43.84</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>43.5</v>
+        <v>43.45</v>
       </c>
       <c r="AN9" t="n">
-        <v>44.03</v>
+        <v>43.97</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>45.06</t>
+          <t>45.12</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>44.24</t>
+          <t>34.76</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-112.67</t>
+          <t>-111.66</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>28111.46159317212</t>
+          <t>28227.69034090909</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>10460.0</t>
+          <t>6625.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>23067.8</v>
+        <v>21302.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>19089.8</t>
+          <t>16542.7</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>13602.9</v>
+        <v>13576.72</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>3978</t>
+          <t>4759</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>873.4256973645256</t>
+          <t>657.6470386350882</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>575.296044885079</t>
+          <t>-529.1355843768179</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>10460.0</t>
+          <t>6625.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-13.93</t>
+          <t>-13.83</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2029</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>42.8</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>42.95</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>670.0</t>
+          <t>240.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>44.95</t>
+          <t>42.95</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>24.67</t>
+          <t>20.84</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16.44</t>
+          <t>5.89</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>151</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>98.77</t>
+          <t>49.38</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>94.23</t>
+          <t>82.72</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>43.31</t>
+          <t>43.71</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>43.58</v>
+        <v>43.5</v>
       </c>
       <c r="AN10" t="n">
-        <v>44.1</v>
+        <v>44.03</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>45.01</t>
+          <t>45.06</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>56.72</t>
+          <t>44.24</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-114.07</t>
+          <t>-112.67</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>28111.46159317212</t>
+          <t>28227.69034090909</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>30506.0</t>
+          <t>10460.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>23927.2</v>
+        <v>23067.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>19193.0</t>
+          <t>19089.8</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>13522.88</v>
+        <v>13602.9</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>4734</t>
+          <t>3978</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>927.631088724425</t>
+          <t>873.4256973645256</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>1721.616370799031</t>
+          <t>575.296044885079</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>30506.0</t>
+          <t>10460.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-9.92</t>
+          <t>-13.93</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4641,22 +4641,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2029</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>46.55</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>44.95</t>
+          <t>42.95</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>685.0</t>
+          <t>670.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>44.95</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,102 +4778,102 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
+          <t>24.67</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2025-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-10-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-08-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2025-08-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>45.6</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>44.45</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>52.5</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>47.6</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>1.12</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
           <t>-4.20</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2025-10-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2025-10-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-08-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-08-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>45.6</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>44.45</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>52.5</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>47.6</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>1.24</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>-4.20</t>
-        </is>
-      </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16.81</t>
+          <t>16.44</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,274 +4884,274 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>151</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>98.77</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>75.04</t>
+          <t>94.23</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>42.73999999999999</t>
+          <t>43.31</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>43.61</v>
+        <v>43.58</v>
       </c>
       <c r="AN11" t="n">
-        <v>44.12</v>
+        <v>44.1</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
+          <t>45.01</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>56.72</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>-0.17</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>-0.39</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>2.77</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>-114.07</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>2025/11/19</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>28227.69034090909</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>30506.0</t>
+        </is>
+      </c>
+      <c r="AX11" t="n">
+        <v>23927.2</v>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>19193.0</t>
+        </is>
+      </c>
+      <c r="AZ11" t="n">
+        <v>13522.88</v>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>4734</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>927.631088724425</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>1721.616370799031</t>
+        </is>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>30506.0</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>49.9</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>2025/08/12</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>-9.92</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>匯鑽科</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>匯鑽科</t>
+        </is>
+      </c>
+      <c r="BK11" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL11" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM11" t="inlineStr">
+        <is>
+          <t>0.79</t>
+        </is>
+      </c>
+      <c r="BN11" t="inlineStr">
+        <is>
+          <t>-10.56465687102404</t>
+        </is>
+      </c>
+      <c r="BO11" t="inlineStr">
+        <is>
+          <t>-13.69932964657055</t>
+        </is>
+      </c>
+      <c r="BP11" t="inlineStr">
+        <is>
+          <t>7.80229574004913</t>
+        </is>
+      </c>
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS11" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="BT11" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
+          <t>6.59</t>
+        </is>
+      </c>
+      <c r="BV11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr">
+        <is>
+          <t>8.25%</t>
+        </is>
+      </c>
+      <c r="BX11" t="inlineStr">
+        <is>
+          <t>-14.21%</t>
+        </is>
+      </c>
+      <c r="BY11" t="inlineStr">
+        <is>
+          <t>45.09</t>
+        </is>
+      </c>
+      <c r="BZ11" t="inlineStr">
+        <is>
+          <t>2029</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
+          <t>加工業務99.90%、勞務0.10% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>匯鑽科-其他電子業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC11" t="inlineStr">
+        <is>
+          <t>其他電子業右下上櫃</t>
+        </is>
+      </c>
+      <c r="CD11" t="inlineStr">
+        <is>
+          <t>45.5</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
+          <t>46.55</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
+          <t>44.8</t>
+        </is>
+      </c>
+      <c r="CG11" t="inlineStr">
+        <is>
           <t>44.95</t>
-        </is>
-      </c>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>24.64</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>-0.34</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>-0.45</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>2.77</t>
-        </is>
-      </c>
-      <c r="AT11" t="inlineStr">
-        <is>
-          <t>-116.07</t>
-        </is>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>2025/11/19</t>
-        </is>
-      </c>
-      <c r="AV11" t="inlineStr">
-        <is>
-          <t>28111.46159317212</t>
-        </is>
-      </c>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>30695.0</t>
-        </is>
-      </c>
-      <c r="AX11" t="n">
-        <v>18788.8</v>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>19613.1</t>
-        </is>
-      </c>
-      <c r="AZ11" t="n">
-        <v>13049.74</v>
-      </c>
-      <c r="BA11" t="inlineStr">
-        <is>
-          <t>-824</t>
-        </is>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>783.2701283472239</t>
-        </is>
-      </c>
-      <c r="BC11" t="inlineStr">
-        <is>
-          <t>1149.944823147569</t>
-        </is>
-      </c>
-      <c r="BD11" t="inlineStr">
-        <is>
-          <t>30695.0</t>
-        </is>
-      </c>
-      <c r="BE11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF11" t="inlineStr">
-        <is>
-          <t>49.9</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>2025/08/12</t>
-        </is>
-      </c>
-      <c r="BH11" t="inlineStr">
-        <is>
-          <t>-9.82</t>
-        </is>
-      </c>
-      <c r="BI11" t="inlineStr">
-        <is>
-          <t>匯鑽科</t>
-        </is>
-      </c>
-      <c r="BJ11" t="inlineStr">
-        <is>
-          <t>匯鑽科</t>
-        </is>
-      </c>
-      <c r="BK11" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BL11" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM11" t="inlineStr">
-        <is>
-          <t>0.78</t>
-        </is>
-      </c>
-      <c r="BN11" t="inlineStr">
-        <is>
-          <t>-10.56465687102404</t>
-        </is>
-      </c>
-      <c r="BO11" t="inlineStr">
-        <is>
-          <t>-13.69932964657055</t>
-        </is>
-      </c>
-      <c r="BP11" t="inlineStr">
-        <is>
-          <t>7.80229574004913</t>
-        </is>
-      </c>
-      <c r="BQ11" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
-        </is>
-      </c>
-      <c r="BR11" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS11" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
-      </c>
-      <c r="BT11" t="inlineStr">
-        <is>
-          <t>2.46</t>
-        </is>
-      </c>
-      <c r="BU11" t="inlineStr">
-        <is>
-          <t>6.59</t>
-        </is>
-      </c>
-      <c r="BV11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BW11" t="inlineStr">
-        <is>
-          <t>8.25%</t>
-        </is>
-      </c>
-      <c r="BX11" t="inlineStr">
-        <is>
-          <t>-14.21%</t>
-        </is>
-      </c>
-      <c r="BY11" t="inlineStr">
-        <is>
-          <t>44.93</t>
-        </is>
-      </c>
-      <c r="BZ11" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
-      </c>
-      <c r="CA11" t="inlineStr">
-        <is>
-          <t>加工業務99.90%、勞務0.10% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB11" t="inlineStr">
-        <is>
-          <t>匯鑽科-其他電子業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC11" t="inlineStr">
-        <is>
-          <t>其他電子業右下上櫃</t>
-        </is>
-      </c>
-      <c r="CD11" t="inlineStr">
-        <is>
-          <t>43.55</t>
-        </is>
-      </c>
-      <c r="CE11" t="inlineStr">
-        <is>
-          <t>45.55</t>
-        </is>
-      </c>
-      <c r="CF11" t="inlineStr">
-        <is>
-          <t>43.3</t>
-        </is>
-      </c>
-      <c r="CG11" t="inlineStr">
-        <is>
-          <t>45.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5173,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>3.9</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>655.0</t>
+          <t>685.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4.42</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-32.14</t>
+          <t>-4.20</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16.07</t>
+          <t>16.81</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>151</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>83.93</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>75.04</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-3.18</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>42.22000000000001</t>
+          <t>42.73999999999999</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>43.6</v>
+        <v>43.61</v>
       </c>
       <c r="AN12" t="n">
-        <v>44.15</v>
+        <v>44.12</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>44.89</t>
+          <t>44.95</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-16.05</t>
+          <t>24.64</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-117.06</t>
+          <t>-116.07</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>28111.46159317212</t>
+          <t>28227.69034090909</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>28225.0</t>
+          <t>30695.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>13738.6</v>
+        <v>18788.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>20246.9</t>
+          <t>19613.1</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>12733.2</v>
+        <v>13049.74</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-6508</t>
+          <t>-824</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>716.6020020198885</t>
+          <t>783.2701283472239</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>271.9517256759318</t>
+          <t>1149.944823147569</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>28225.0</t>
+          <t>30695.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-13.23</t>
+          <t>-9.82</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>44.93</t>
+          <t>45.09</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2029</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>45.55</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>42.35</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,42 +5613,42 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>0.46</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>678.728</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>87.5</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>739.811</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>87.1</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-10.13</t>
+          <t>-5.49</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-18.60</t>
+          <t>-18.22</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,73 +5744,73 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>740</t>
+          <t>679</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>59.26</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>67.9</t>
+          <t>67.28</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-7.48</t>
+          <t>-7.49</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>87.32000000000001</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>89.87</v>
+        <v>89.48</v>
       </c>
       <c r="AN13" t="n">
-        <v>97.14</v>
+        <v>96.72</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>97.67</t>
+          <t>97.72</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>9.21</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-3.00</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-142.67</t>
+          <t>-141.71</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>353339499.4032717</t>
+          <t>352964405.0369318</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>64813905.0</t>
+          <t>59515377.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>62364817.4</v>
+        <v>61769492.8</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>69391061.0</t>
+          <t>65356195.9</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>243715090.02</v>
+        <v>234235775.26</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-7026243</t>
+          <t>-3586703</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-28100462.4147675</t>
+          <t>-27073174.21872042</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-23010424.95897819</t>
+          <t>-21423089.14046149</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>64813905.0</t>
+          <t>59515377.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>7.13</t>
+          <t>7.63</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>4</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>22.39</t>
+          <t>22.49</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>34.53</t>
+          <t>34.97</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>18369</t>
+          <t>18453</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6001,17 +6001,17 @@
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>88.9</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1014.23</t>
+          <t>739.811</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-23.60</t>
+          <t>-10.13</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>4.90</t>
+          <t>3.58</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,12 +6174,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>740</t>
+          <t>679</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6189,58 +6189,58 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>61.16</t>
+          <t>67.9</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-7.36</t>
+          <t>-7.48</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>87.29999999999998</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>90.34</v>
+        <v>89.87</v>
       </c>
       <c r="AN14" t="n">
-        <v>97.52</v>
+        <v>97.14</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>97.62</t>
+          <t>97.67</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>6.07</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-3.00</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-3.12</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-143.32</t>
+          <t>-142.67</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>353339499.4032717</t>
+          <t>352964405.0369318</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>88951847.0</t>
+          <t>64813905.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>59081139.2</v>
+        <v>62364817.4</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>77327536.6</t>
+          <t>69391061.0</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>250820460.68</v>
+        <v>243715090.02</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-18246397</t>
+          <t>-7026243</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-29025923.77036555</t>
+          <t>-28100462.4147675</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-25023946.09403855</t>
+          <t>-23010424.95897819</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>88951847.0</t>
+          <t>64813905.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>4</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>22.39</t>
+          <t>22.49</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>34.53</t>
+          <t>34.97</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>18369</t>
+          <t>18453</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>88.9</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>461.141</t>
+          <t>1014.23</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>87.8</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-33.87</t>
+          <t>-23.60</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-17.94</t>
+          <t>-18.60</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>4.90</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,274 +6604,274 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>740</t>
+          <t>679</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>85.19</t>
+          <t>59.26</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>55.95</t>
+          <t>61.16</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-4.12</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-7.23</t>
+          <t>-7.36</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
+          <t>87.29999999999998</t>
+        </is>
+      </c>
+      <c r="AM15" t="n">
+        <v>90.34</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>97.52</v>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>97.62</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>3.61</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>-3.00</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>-3.12</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>7.19</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr">
+        <is>
+          <t>-143.32</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>2025/11/28</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>352964405.0369318</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>88951847.0</t>
+        </is>
+      </c>
+      <c r="AX15" t="n">
+        <v>59081139.2</v>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>77327536.6</t>
+        </is>
+      </c>
+      <c r="AZ15" t="n">
+        <v>250820460.68</v>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>-18246397</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>-29025923.77036555</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>-25023946.09403855</t>
+        </is>
+      </c>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>88951847.0</t>
+        </is>
+      </c>
+      <c r="BE15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF15" t="inlineStr">
+        <is>
+          <t>81.3</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>2025/07/28</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>7.13</t>
+        </is>
+      </c>
+      <c r="BI15" t="inlineStr">
+        <is>
+          <t>鉅祥</t>
+        </is>
+      </c>
+      <c r="BJ15" t="inlineStr">
+        <is>
+          <t>鉅祥</t>
+        </is>
+      </c>
+      <c r="BK15" t="inlineStr">
+        <is>
+          <t>電子零組件業</t>
+        </is>
+      </c>
+      <c r="BL15" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM15" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="BN15" t="inlineStr">
+        <is>
+          <t>-7.291353668658945</t>
+        </is>
+      </c>
+      <c r="BO15" t="inlineStr">
+        <is>
+          <t>11.64963320584363</t>
+        </is>
+      </c>
+      <c r="BP15" t="inlineStr">
+        <is>
+          <t>10.65346457950322</t>
+        </is>
+      </c>
+      <c r="BQ15" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR15" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS15" t="inlineStr">
+        <is>
+          <t>2.29</t>
+        </is>
+      </c>
+      <c r="BT15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BU15" t="inlineStr">
+        <is>
+          <t>9.36</t>
+        </is>
+      </c>
+      <c r="BV15" t="inlineStr">
+        <is>
+          <t>22.49</t>
+        </is>
+      </c>
+      <c r="BW15" t="inlineStr">
+        <is>
+          <t>29.60%</t>
+        </is>
+      </c>
+      <c r="BX15" t="inlineStr">
+        <is>
+          <t>15.93%</t>
+        </is>
+      </c>
+      <c r="BY15" t="inlineStr">
+        <is>
+          <t>34.97</t>
+        </is>
+      </c>
+      <c r="BZ15" t="inlineStr">
+        <is>
+          <t>18453</t>
+        </is>
+      </c>
+      <c r="CA15" t="inlineStr">
+        <is>
+          <t>部品95.14%、模具3.09%、商品銷售1.03%、治具0.75% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB15" t="inlineStr">
+        <is>
+          <t>鉅祥-電子零組件業-上市</t>
+        </is>
+      </c>
+      <c r="CC15" t="inlineStr">
+        <is>
+          <t>電子零組件業右上上市</t>
+        </is>
+      </c>
+      <c r="CD15" t="inlineStr">
+        <is>
+          <t>87.5</t>
+        </is>
+      </c>
+      <c r="CE15" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="CF15" t="inlineStr">
+        <is>
+          <t>86.8</t>
+        </is>
+      </c>
+      <c r="CG15" t="inlineStr">
+        <is>
           <t>87.1</t>
-        </is>
-      </c>
-      <c r="AM15" t="n">
-        <v>90.84</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>97.92</v>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>97.54</t>
-        </is>
-      </c>
-      <c r="AP15" t="inlineStr">
-        <is>
-          <t>0.98</t>
-        </is>
-      </c>
-      <c r="AQ15" t="inlineStr">
-        <is>
-          <t>-3.11</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>-3.14</t>
-        </is>
-      </c>
-      <c r="AS15" t="inlineStr">
-        <is>
-          <t>7.19</t>
-        </is>
-      </c>
-      <c r="AT15" t="inlineStr">
-        <is>
-          <t>-143.71</t>
-        </is>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>2025/11/28</t>
-        </is>
-      </c>
-      <c r="AV15" t="inlineStr">
-        <is>
-          <t>353339499.4032717</t>
-        </is>
-      </c>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>40320203.0</t>
-        </is>
-      </c>
-      <c r="AX15" t="n">
-        <v>54978050.8</v>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>83135790.5</t>
-        </is>
-      </c>
-      <c r="AZ15" t="n">
-        <v>260959475.16</v>
-      </c>
-      <c r="BA15" t="inlineStr">
-        <is>
-          <t>-28157739</t>
-        </is>
-      </c>
-      <c r="BB15" t="inlineStr">
-        <is>
-          <t>-29753556.07515229</t>
-        </is>
-      </c>
-      <c r="BC15" t="inlineStr">
-        <is>
-          <t>-29592900.56933765</t>
-        </is>
-      </c>
-      <c r="BD15" t="inlineStr">
-        <is>
-          <t>40320203.0</t>
-        </is>
-      </c>
-      <c r="BE15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF15" t="inlineStr">
-        <is>
-          <t>81.3</t>
-        </is>
-      </c>
-      <c r="BG15" t="inlineStr">
-        <is>
-          <t>2025/07/28</t>
-        </is>
-      </c>
-      <c r="BH15" t="inlineStr">
-        <is>
-          <t>8.00</t>
-        </is>
-      </c>
-      <c r="BI15" t="inlineStr">
-        <is>
-          <t>鉅祥</t>
-        </is>
-      </c>
-      <c r="BJ15" t="inlineStr">
-        <is>
-          <t>鉅祥</t>
-        </is>
-      </c>
-      <c r="BK15" t="inlineStr">
-        <is>
-          <t>電子零組件業</t>
-        </is>
-      </c>
-      <c r="BL15" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM15" t="inlineStr">
-        <is>
-          <t>1.02</t>
-        </is>
-      </c>
-      <c r="BN15" t="inlineStr">
-        <is>
-          <t>-7.291353668658945</t>
-        </is>
-      </c>
-      <c r="BO15" t="inlineStr">
-        <is>
-          <t>11.64963320584363</t>
-        </is>
-      </c>
-      <c r="BP15" t="inlineStr">
-        <is>
-          <t>10.65346457950322</t>
-        </is>
-      </c>
-      <c r="BQ15" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR15" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS15" t="inlineStr">
-        <is>
-          <t>2.31</t>
-        </is>
-      </c>
-      <c r="BT15" t="inlineStr">
-        <is>
-          <t>4.02</t>
-        </is>
-      </c>
-      <c r="BU15" t="inlineStr">
-        <is>
-          <t>9.36</t>
-        </is>
-      </c>
-      <c r="BV15" t="inlineStr">
-        <is>
-          <t>22.39</t>
-        </is>
-      </c>
-      <c r="BW15" t="inlineStr">
-        <is>
-          <t>29.60%</t>
-        </is>
-      </c>
-      <c r="BX15" t="inlineStr">
-        <is>
-          <t>15.93%</t>
-        </is>
-      </c>
-      <c r="BY15" t="inlineStr">
-        <is>
-          <t>34.53</t>
-        </is>
-      </c>
-      <c r="BZ15" t="inlineStr">
-        <is>
-          <t>18369</t>
-        </is>
-      </c>
-      <c r="CA15" t="inlineStr">
-        <is>
-          <t>部品95.14%、模具3.09%、商品銷售1.03%、治具0.75% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB15" t="inlineStr">
-        <is>
-          <t>鉅祥-電子零組件業-上市</t>
-        </is>
-      </c>
-      <c r="CC15" t="inlineStr">
-        <is>
-          <t>電子零組件業右上上市</t>
-        </is>
-      </c>
-      <c r="CD15" t="inlineStr">
-        <is>
-          <t>87.9</t>
-        </is>
-      </c>
-      <c r="CE15" t="inlineStr">
-        <is>
-          <t>87.9</t>
-        </is>
-      </c>
-      <c r="CF15" t="inlineStr">
-        <is>
-          <t>86.9</t>
-        </is>
-      </c>
-      <c r="CG15" t="inlineStr">
-        <is>
-          <t>87.8</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6893,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>630.229</t>
+          <t>461.141</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-29.59</t>
+          <t>-33.87</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-18.60</t>
+          <t>-17.94</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,73 +7034,73 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>740</t>
+          <t>679</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>39.02</t>
+          <t>85.19</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>31.54</t>
+          <t>55.95</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-5.08</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-7.16</t>
+          <t>-7.23</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>86.64</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>91.28</v>
+        <v>90.84</v>
       </c>
       <c r="AN16" t="n">
-        <v>98.31</v>
+        <v>97.92</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>97.43</t>
+          <t>97.54</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-3.11</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-3.15</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-143.82</t>
+          <t>-143.71</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>353339499.4032717</t>
+          <t>352964405.0369318</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>55246132.0</t>
+          <t>40320203.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>67438997.8</v>
+        <v>54978050.8</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>95782499.1</t>
+          <t>83135790.5</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>275665355.36</v>
+        <v>260959475.16</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-28343501</t>
+          <t>-28157739</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-29782766.16711858</t>
+          <t>-29753556.07515229</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-29852555.79943146</t>
+          <t>-29592900.56933765</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>55246132.0</t>
+          <t>40320203.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>7.13</t>
+          <t>8.00</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>4</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>22.39</t>
+          <t>22.49</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>34.53</t>
+          <t>34.97</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>18369</t>
+          <t>18453</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7291,17 +7291,17 @@
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.9</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>713.512</t>
+          <t>630.229</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-33.57</t>
+          <t>-29.59</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-17.85</t>
+          <t>-18.60</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,73 +7464,73 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>740</t>
+          <t>679</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>43.64</t>
+          <t>39.02</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>31.54</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-5.14</t>
+          <t>-5.08</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-7.33</t>
+          <t>-7.16</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>86.85999999999999</t>
+          <t>86.64</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>91.56999999999999</v>
+        <v>91.28</v>
       </c>
       <c r="AN17" t="n">
-        <v>98.81999999999999</v>
+        <v>98.31</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>97.34</t>
+          <t>97.43</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-8.10</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-3.12</t>
+          <t>-3.15</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-143.38</t>
+          <t>-143.82</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>353339499.4032717</t>
+          <t>352964405.0369318</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>62492000.0</t>
+          <t>55246132.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>68942899</v>
+        <v>67438997.8</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>103776418.9</t>
+          <t>95782499.1</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>296624289.38</v>
+        <v>275665355.36</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-34833519</t>
+          <t>-28343501</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-29770077.14306169</t>
+          <t>-29782766.16711858</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-30756535.8138715</t>
+          <t>-29852555.79943146</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>62492000.0</t>
+          <t>55246132.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>7.13</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,22 +7651,22 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>4</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>22.39</t>
+          <t>22.49</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>34.53</t>
+          <t>34.97</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>18369</t>
+          <t>18453</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>557.755</t>
+          <t>713.512</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-31.49</t>
+          <t>-33.57</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-19.07</t>
+          <t>-17.85</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,73 +7894,73 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>740</t>
+          <t>679</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>11.96</t>
+          <t>43.64</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>6.16</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-5.79</t>
+          <t>-5.14</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-7.52</t>
+          <t>-7.33</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>86.58</t>
+          <t>86.85999999999999</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>91.90000000000001</v>
+        <v>91.56999999999999</v>
       </c>
       <c r="AN18" t="n">
-        <v>99.37</v>
+        <v>98.81999999999999</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>97.25</t>
+          <t>97.34</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-15.28</t>
+          <t>-8.10</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-3.12</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-142.50</t>
+          <t>-143.38</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>353339499.4032717</t>
+          <t>352964405.0369318</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>48395514.0</t>
+          <t>62492000.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>76417304.59999999</v>
+        <v>68942899</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>111545339.3</t>
+          <t>103776418.9</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>319430807.84</v>
+        <v>296624289.38</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-35128034</t>
+          <t>-34833519</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-29590721.02109627</t>
+          <t>-29770077.14306169</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-31725831.12686187</t>
+          <t>-30756535.8138715</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>48395514.0</t>
+          <t>62492000.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>8.12</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,22 +8081,22 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>4</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>22.39</t>
+          <t>22.49</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>34.53</t>
+          <t>34.97</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>18369</t>
+          <t>18453</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>797.916</t>
+          <t>557.755</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>86.1</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-21.02</t>
+          <t>-31.49</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-19.53</t>
+          <t>-19.07</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,151 +8324,151 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>740</t>
+          <t>679</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
+          <t>11.96</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>6.16</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>-5.79</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>-7.52</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>86.58</t>
+        </is>
+      </c>
+      <c r="AM19" t="n">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>99.37</v>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>97.25</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>-15.28</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>-3.52</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>-3.06</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>7.19</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr">
+        <is>
+          <t>-142.50</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>2025/11/28</t>
+        </is>
+      </c>
+      <c r="AV19" t="inlineStr">
+        <is>
+          <t>352964405.0369318</t>
+        </is>
+      </c>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>48395514.0</t>
+        </is>
+      </c>
+      <c r="AX19" t="n">
+        <v>76417304.59999999</v>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>111545339.3</t>
+        </is>
+      </c>
+      <c r="AZ19" t="n">
+        <v>319430807.84</v>
+      </c>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>-35128034</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>-29590721.02109627</t>
+        </is>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>-31725831.12686187</t>
+        </is>
+      </c>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>48395514.0</t>
+        </is>
+      </c>
+      <c r="BE19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF19" t="inlineStr">
+        <is>
+          <t>81.3</t>
+        </is>
+      </c>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>2025/07/28</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
           <t>6.52</t>
         </is>
       </c>
-      <c r="AG19" t="inlineStr">
-        <is>
-          <t>9.08</t>
-        </is>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>-0.76</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>-6.01</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>-7.68</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>2.91</t>
-        </is>
-      </c>
-      <c r="AL19" t="inlineStr">
-        <is>
-          <t>86.75999999999999</t>
-        </is>
-      </c>
-      <c r="AM19" t="n">
-        <v>92.31</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>99.98999999999999</v>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>97.16</t>
-        </is>
-      </c>
-      <c r="AP19" t="inlineStr">
-        <is>
-          <t>-20.19</t>
-        </is>
-      </c>
-      <c r="AQ19" t="inlineStr">
-        <is>
-          <t>-3.53</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>-2.94</t>
-        </is>
-      </c>
-      <c r="AS19" t="inlineStr">
-        <is>
-          <t>7.19</t>
-        </is>
-      </c>
-      <c r="AT19" t="inlineStr">
-        <is>
-          <t>-140.87</t>
-        </is>
-      </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>2025/11/28</t>
-        </is>
-      </c>
-      <c r="AV19" t="inlineStr">
-        <is>
-          <t>353339499.4032717</t>
-        </is>
-      </c>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>68436405.0</t>
-        </is>
-      </c>
-      <c r="AX19" t="n">
-        <v>95573934</v>
-      </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>121006638.2</t>
-        </is>
-      </c>
-      <c r="AZ19" t="n">
-        <v>336619552.5</v>
-      </c>
-      <c r="BA19" t="inlineStr">
-        <is>
-          <t>-25432704</t>
-        </is>
-      </c>
-      <c r="BB19" t="inlineStr">
-        <is>
-          <t>-29202519.18368434</t>
-        </is>
-      </c>
-      <c r="BC19" t="inlineStr">
-        <is>
-          <t>-30467135.53374588</t>
-        </is>
-      </c>
-      <c r="BD19" t="inlineStr">
-        <is>
-          <t>68436405.0</t>
-        </is>
-      </c>
-      <c r="BE19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF19" t="inlineStr">
-        <is>
-          <t>81.3</t>
-        </is>
-      </c>
-      <c r="BG19" t="inlineStr">
-        <is>
-          <t>2025/07/28</t>
-        </is>
-      </c>
-      <c r="BH19" t="inlineStr">
-        <is>
-          <t>5.90</t>
-        </is>
-      </c>
       <c r="BI19" t="inlineStr">
         <is>
           <t>鉅祥</t>
@@ -8511,7 +8511,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8521,12 +8521,12 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>4</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>22.39</t>
+          <t>22.49</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>34.53</t>
+          <t>34.97</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>18369</t>
+          <t>18453</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>85.1</t>
+          <t>85.9</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>86.1</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-3.11</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1197.387</t>
+          <t>797.916</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>86.1</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-9.98</t>
+          <t>-21.02</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-20.09</t>
+          <t>-19.53</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>5.79</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,73 +8754,73 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>740</t>
+          <t>679</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>6.91</t>
+          <t>9.08</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-2.24</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-5.99</t>
+          <t>-6.01</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-7.53</t>
+          <t>-7.68</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>87.46000000000001</t>
+          <t>86.75999999999999</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>93.03</v>
+        <v>92.31</v>
       </c>
       <c r="AN20" t="n">
-        <v>100.61</v>
+        <v>99.98999999999999</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>97.09</t>
+          <t>97.16</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-23.35</t>
+          <t>-20.19</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>-3.53</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-138.81</t>
+          <t>-140.87</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>353339499.4032717</t>
+          <t>352964405.0369318</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>102624938.0</t>
+          <t>68436405.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>111293530.2</v>
+        <v>95573934</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>123628857.1</t>
+          <t>121006638.2</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>366752945.54</v>
+        <v>336619552.5</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-12335326</t>
+          <t>-25432704</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-28972588.9382186</t>
+          <t>-29202519.18368434</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-29728125.31023213</t>
+          <t>-30467135.53374588</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>102624938.0</t>
+          <t>68436405.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>5.17</t>
+          <t>5.90</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8941,7 +8941,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -8951,12 +8951,12 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>4</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>22.39</t>
+          <t>22.49</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>34.53</t>
+          <t>34.97</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>18369</t>
+          <t>18453</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>85.1</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>86.1</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>-3.11</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>710.084</t>
+          <t>1197.387</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-9.98</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-17.57</t>
+          <t>-20.09</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>5.79</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,17 +9184,17 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>740</t>
+          <t>679</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>20.73</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
@@ -9204,53 +9204,53 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-2.24</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-5.54</t>
+          <t>-5.99</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-7.34</t>
+          <t>-7.53</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>3.62</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>88.56</t>
+          <t>87.46000000000001</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>93.75</v>
+        <v>93.03</v>
       </c>
       <c r="AN21" t="n">
-        <v>101.18</v>
+        <v>100.61</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>97.04</t>
+          <t>97.09</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-22.39</t>
+          <t>-23.35</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>-2.63</t>
+          <t>-2.79</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-136.55</t>
+          <t>-138.81</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>353339499.4032717</t>
+          <t>352964405.0369318</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>62765638.0</t>
+          <t>102624938.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>124126000.4</v>
+        <v>111293530.2</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>125231243.6</t>
+          <t>123628857.1</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>399636300.16</v>
+        <v>366752945.54</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-1105243</t>
+          <t>-12335326</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-28835218.6887616</t>
+          <t>-28972588.9382186</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-31273734.76556134</t>
+          <t>-29728125.31023213</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>62765638.0</t>
+          <t>102624938.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>8.49</t>
+          <t>5.17</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9381,12 +9381,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>4</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>22.39</t>
+          <t>22.49</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>34.53</t>
+          <t>34.97</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>18369</t>
+          <t>18453</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>89.4</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1153.082</t>
+          <t>710.084</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-19.16</t>
+          <t>-17.57</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>5.57</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,73 +9614,73 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>740</t>
+          <t>679</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.73</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.91</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-3.74</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-5.54</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>-7.14</t>
+          <t>-7.34</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>89.86</t>
+          <t>88.56</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>94.36</v>
+        <v>93.75</v>
       </c>
       <c r="AN22" t="n">
-        <v>101.62</v>
+        <v>101.18</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>96.9</t>
+          <t>97.04</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-27.21</t>
+          <t>-22.39</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>-2.48</t>
+          <t>-2.63</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-134.50</t>
+          <t>-136.55</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>353339499.4032717</t>
+          <t>352964405.0369318</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>99864028.0</t>
+          <t>62765638.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>138609938.8</v>
+        <v>124126000.4</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>137834914.3</t>
+          <t>125231243.6</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>443270959.36</v>
+        <v>399636300.16</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>775024</t>
+          <t>-1105243</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-28391852.12934346</t>
+          <t>-28835218.6887616</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-28094189.88869017</t>
+          <t>-31273734.76556134</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>99864028.0</t>
+          <t>62765638.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>6.40</t>
+          <t>8.49</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>4</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>22.39</t>
+          <t>22.49</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>34.53</t>
+          <t>34.97</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>18369</t>
+          <t>18453</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>88.6</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
+          <t>89.4</t>
+        </is>
+      </c>
+      <c r="CF22" t="inlineStr">
+        <is>
           <t>87.9</t>
         </is>
       </c>
-      <c r="CF22" t="inlineStr">
-        <is>
-          <t>85.9</t>
-        </is>
-      </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1638.11</t>
+          <t>1153.082</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-18.22</t>
+          <t>-19.16</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>7.92</t>
+          <t>5.57</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-2.40</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,12 +10044,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>740</t>
+          <t>679</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10064,53 +10064,53 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-4.12</t>
+          <t>-3.74</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-4.10</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>-6.67</t>
+          <t>-7.14</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>4.87</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>91.26</t>
+          <t>89.86</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>95.16</v>
+        <v>94.36</v>
       </c>
       <c r="AN23" t="n">
-        <v>101.96</v>
+        <v>101.62</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>96.8</t>
+          <t>96.9</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-23.67</t>
+          <t>-27.21</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>-2.86</t>
+          <t>-3.16</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-2.48</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-132.15</t>
+          <t>-134.50</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>353339499.4032717</t>
+          <t>352964405.0369318</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>144178661.0</t>
+          <t>99864028.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>146673374</v>
+        <v>138609938.8</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>149731355.7</t>
+          <t>137834914.3</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>454484548.46</v>
+        <v>443270959.36</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-3057981</t>
+          <t>775024</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-28445972.53673498</t>
+          <t>-28391852.12934346</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-26523446.49713525</t>
+          <t>-28094189.88869017</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>144178661.0</t>
+          <t>99864028.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>7.63</t>
+          <t>6.40</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>4</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>22.39</t>
+          <t>22.49</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>34.53</t>
+          <t>34.97</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>18369</t>
+          <t>18453</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>89.9</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>85.9</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/電鍍材料.xlsx
+++ b/Result/checksun_type/電鍍材料.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>9.01</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1537.0</t>
+          <t>1436.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>48.45</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,17 +908,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-6.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>24.37</t>
+          <t>61.38</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>9.00</t>
+          <t>8.66</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>37.72</t>
+          <t>35.24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>1436</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>97.25</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>99.08</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>5.99</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.95</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>45.71</t>
+          <t>46.48</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>43.81</v>
+        <v>44.04</v>
       </c>
       <c r="AN2" t="n">
-        <v>44.04</v>
+        <v>44.11</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>45.38</t>
+          <t>45.46</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>336.50</t>
+          <t>197.33</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-94.77</t>
+          <t>-89.68</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>28227.69034090909</t>
+          <t>28335.18723404255</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>73291.0</t>
+          <t>69342.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>21815.2</v>
+        <v>34574.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>17540.5</t>
+          <t>21424.1</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>14449.18</v>
+        <v>15776.4</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>4274</t>
+          <t>13150</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-215.247811154344</t>
+          <t>759.1211772838512</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>3091.623773344323</t>
+          <t>6118.150613693924</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>73291.0</t>
+          <t>69342.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-2.91</t>
+          <t>-3.21</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>45.09</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>47.6</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>48.45</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1296,7 +1296,7 @@
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>1537.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>48.45</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-25.69</t>
+          <t>24.37</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>9.00</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>37.72</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,12 +1444,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>1436</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1459,58 +1459,58 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>93.02</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>5.99</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.93</t>
+          <t>-2.95</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>45.04</t>
+          <t>45.71</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>43.61</v>
+        <v>43.81</v>
       </c>
       <c r="AN3" t="n">
-        <v>43.98</v>
+        <v>44.04</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>45.38</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>1334.55</t>
+          <t>336.50</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-99.17</t>
+          <t>-94.77</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>28227.69034090909</t>
+          <t>28335.18723404255</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>6884.0</t>
+          <t>73291.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>9869</v>
+        <v>21815.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>13280.9</t>
+          <t>17540.5</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>13072.58</v>
+        <v>14449.18</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-3411</t>
+          <t>4274</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-816.4971901541018</t>
+          <t>-215.247811154344</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-1765.508276203122</t>
+          <t>3091.623773344323</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>6884.0</t>
+          <t>73291.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-8.42</t>
+          <t>-2.91</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>45.09</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>45.05</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>48.45</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1743,127 +1743,127 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>0.88</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>151.0</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>45.7</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>5.38</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.18</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>-25.69</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-10-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-08-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-08-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>45.6</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>44.45</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>52.5</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>47.6</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>2.81</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>-4.20</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>3.71</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
           <t>1.44</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>318.0</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>45.3</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0.88</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3.38</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>-38.19</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2025-10-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2025-10-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-08-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-08-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>45.6</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>44.45</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>52.5</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>47.6</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>-4.20</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2025-12-01</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>7.80</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>-1.10</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,12 +1874,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>1436</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1889,58 +1889,58 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>85.14</t>
+          <t>93.02</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.90</t>
+          <t>-2.93</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>44.62</t>
+          <t>45.04</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>43.57</v>
+        <v>43.61</v>
       </c>
       <c r="AN4" t="n">
-        <v>43.95</v>
+        <v>43.98</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>45.26</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>507.74</t>
+          <t>1334.55</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-101.94</t>
+          <t>-99.17</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>28227.69034090909</t>
+          <t>28335.18723404255</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>14487.0</t>
+          <t>6884.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>9527.799999999999</v>
+        <v>9869</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>15415.0</t>
+          <t>13280.9</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>13104.9</v>
+        <v>13072.58</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-5887</t>
+          <t>-3411</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-643.9497199633709</t>
+          <t>-816.4971901541018</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-1526.178765692213</t>
+          <t>-1765.508276203122</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>14487.0</t>
+          <t>6884.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-9.22</t>
+          <t>-8.42</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,12 +2071,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>45.09</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>45.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>45.05</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>197.0</t>
+          <t>318.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>44.65</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>6.21</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-48.71</t>
+          <t>-38.19</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.83</t>
+          <t>7.80</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,17 +2304,17 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>1436</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>79.07</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -2324,53 +2324,53 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.98</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>-2.90</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>44.16</t>
+          <t>44.62</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>43.52</v>
+        <v>43.57</v>
       </c>
       <c r="AN5" t="n">
         <v>43.95</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>45.23</t>
+          <t>45.26</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>194.44</t>
+          <t>507.74</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-104.40</t>
+          <t>-101.94</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>28227.69034090909</t>
+          <t>28335.18723404255</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>8868.0</t>
+          <t>14487.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>7955.4</v>
+        <v>9527.799999999999</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>15511.6</t>
+          <t>15415.0</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>13262.22</v>
+        <v>13104.9</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-7556</t>
+          <t>-5887</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-483.5444389217631</t>
+          <t>-643.9497199633709</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-1944.380223330478</t>
+          <t>-1526.178765692213</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>8868.0</t>
+          <t>14487.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-10.52</t>
+          <t>-9.22</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2501,12 +2501,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>45.09</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,24 +2556,24 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
+          <t>46.0</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
+          <t>45.1</t>
+        </is>
+      </c>
+      <c r="CG5" t="inlineStr">
+        <is>
           <t>45.3</t>
         </is>
       </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>44.4</t>
-        </is>
-      </c>
-      <c r="CG5" t="inlineStr">
-        <is>
-          <t>44.65</t>
-        </is>
-      </c>
       <c r="CH5" t="inlineStr">
         <is>
           <t>18.72</t>
@@ -2586,7 +2586,7 @@
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>197.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,69 +2618,69 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>44.65</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>7.56</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.18</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>-48.71</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2025-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-10-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2025-08-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2025-08-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>45.6</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
           <t>44.45</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>2.74</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3.38</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>-48.61</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2025-10-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2025-10-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2025-08-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2025-08-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>45.6</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>44.45</t>
-        </is>
-      </c>
       <c r="S6" t="inlineStr">
         <is>
           <t>0</t>
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>4.83</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.81</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,37 +2734,37 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>1436</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>76.36</t>
+          <t>79.07</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>85.14</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -2774,33 +2774,33 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>43.82000000000001</t>
+          <t>44.16</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>43.49</v>
+        <v>43.52</v>
       </c>
       <c r="AN6" t="n">
-        <v>43.94</v>
+        <v>43.95</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>45.21</t>
+          <t>45.23</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>125.94</t>
+          <t>194.44</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-106.54</t>
+          <t>-104.40</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>28227.69034090909</t>
+          <t>28335.18723404255</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>5546.0</t>
+          <t>8868.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>8273.799999999999</v>
+        <v>7955.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>16100.5</t>
+          <t>15511.6</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>13310.48</v>
+        <v>13262.22</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-7826</t>
+          <t>-7556</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-217.9379326656332</t>
+          <t>-483.5444389217631</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-1870.333011980483</t>
+          <t>-1944.380223330478</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>5546.0</t>
+          <t>8868.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-10.92</t>
+          <t>-10.52</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>45.09</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>45.7</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>44.45</t>
+          <t>44.4</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>44.45</t>
+          <t>44.65</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="CJ6" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>-1.42</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>302.0</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>44.45</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>7.97</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-17.23</t>
+          <t>-48.61</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>-2.81</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>1436</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>76.36</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>72.02</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>2.69</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>43.92</t>
+          <t>43.82000000000001</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>43.47</v>
+        <v>43.49</v>
       </c>
       <c r="AN7" t="n">
         <v>43.94</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>45.23</t>
+          <t>45.21</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>91.47</t>
+          <t>125.94</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-108.60</t>
+          <t>-106.54</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>28227.69034090909</t>
+          <t>28335.18723404255</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>13560.0</t>
+          <t>5546.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>13265.8</v>
+        <v>8273.799999999999</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>16027.3</t>
+          <t>16100.5</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>13521.82</v>
+        <v>13310.48</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-2761</t>
+          <t>-7826</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>82.49753630070325</t>
+          <t>-217.9379326656332</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-1341.825102481189</t>
+          <t>-1870.333011980483</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>13560.0</t>
+          <t>5546.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-9.62</t>
+          <t>-10.92</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>45.09</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>45.7</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>44.45</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>44.45</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="CJ7" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>118.0</t>
+          <t>302.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>6.63</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>9.71</t>
+          <t>-17.23</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.87</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>1436</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>65.43</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>55.14</t>
+          <t>72.02</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>2.69</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-1.1</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-2.80</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>43.92</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>43.44</v>
+        <v>43.47</v>
       </c>
       <c r="AN8" t="n">
-        <v>43.92</v>
+        <v>43.94</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>45.19</t>
+          <t>45.23</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>41.21</t>
+          <t>91.47</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-110.57</t>
+          <t>-108.60</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>28227.69034090909</t>
+          <t>28335.18723404255</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>5178.0</t>
+          <t>13560.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>16692.8</v>
+        <v>13265.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>15215.7</t>
+          <t>16027.3</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>13519.76</v>
+        <v>13521.82</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>-2761</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>341.4652888065019</t>
+          <t>82.49753630070325</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-1397.534335250723</t>
+          <t>-1341.825102481189</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>5178.0</t>
+          <t>13560.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-12.63</t>
+          <t>-9.62</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,24 +3781,24 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
+          <t>2.41</t>
+        </is>
+      </c>
+      <c r="BT8" t="inlineStr">
+        <is>
           <t>2.33</t>
         </is>
       </c>
-      <c r="BT8" t="inlineStr">
-        <is>
-          <t>2.32</t>
-        </is>
-      </c>
       <c r="BU8" t="inlineStr">
         <is>
           <t>6.59</t>
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>45.09</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>43.45</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>45.3</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>43.45</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>43.6</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3876,7 +3876,7 @@
       </c>
       <c r="CJ8" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>118.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5.91</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>28.77</t>
+          <t>9.71</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.87</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>1436</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>50.62</t>
+          <t>65.43</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>66.26</t>
+          <t>55.14</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.92</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-2.80</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>43.84</t>
+          <t>43.9</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>43.45</v>
+        <v>43.44</v>
       </c>
       <c r="AN9" t="n">
-        <v>43.97</v>
+        <v>43.92</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>45.12</t>
+          <t>45.19</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>34.76</t>
+          <t>41.21</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-111.66</t>
+          <t>-110.57</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>28227.69034090909</t>
+          <t>28335.18723404255</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>6625.0</t>
+          <t>5178.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>21302.2</v>
+        <v>16692.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>16542.7</t>
+          <t>15215.7</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>13576.72</v>
+        <v>13519.76</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>4759</t>
+          <t>1477</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>657.6470386350882</t>
+          <t>341.4652888065019</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-529.1355843768179</t>
+          <t>-1397.534335250723</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>6625.0</t>
+          <t>5178.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-13.83</t>
+          <t>-12.63</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>45.09</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>43.1</t>
+          <t>43.45</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>44.1</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>42.8</t>
+          <t>43.45</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>43.0</t>
+          <t>43.6</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="CJ9" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-4.49</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>240.0</t>
+          <t>153.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>42.95</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>10.97</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>20.84</t>
+          <t>28.77</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>5.89</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-3.72</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>1436</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>49.38</t>
+          <t>50.62</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>82.72</t>
+          <t>66.26</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.74</t>
+          <t>-1.92</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-2.27</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>43.71</t>
+          <t>43.84</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>43.5</v>
+        <v>43.45</v>
       </c>
       <c r="AN10" t="n">
-        <v>44.03</v>
+        <v>43.97</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>45.06</t>
+          <t>45.12</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>44.24</t>
+          <t>34.76</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-112.67</t>
+          <t>-111.66</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>28227.69034090909</t>
+          <t>28335.18723404255</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>10460.0</t>
+          <t>6625.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>23067.8</v>
+        <v>21302.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>19089.8</t>
+          <t>16542.7</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>13602.9</v>
+        <v>13576.72</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>3978</t>
+          <t>4759</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>873.4256973645256</t>
+          <t>657.6470386350882</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>575.296044885079</t>
+          <t>-529.1355843768179</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>10460.0</t>
+          <t>6625.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-13.93</t>
+          <t>-13.83</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,22 +4641,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>45.09</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>44.5</t>
+          <t>43.1</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>44.9</t>
+          <t>44.1</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>42.6</t>
+          <t>42.8</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>42.95</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="CJ10" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-4.49</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>670.0</t>
+          <t>240.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>44.95</t>
+          <t>42.95</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>11.08</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>24.67</t>
+          <t>20.84</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16.44</t>
+          <t>5.89</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-3.72</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>1436</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>98.77</t>
+          <t>49.38</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>94.23</t>
+          <t>82.72</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>-1.74</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-2.27</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>43.31</t>
+          <t>43.71</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>43.58</v>
+        <v>43.5</v>
       </c>
       <c r="AN11" t="n">
-        <v>44.1</v>
+        <v>44.03</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>45.01</t>
+          <t>45.06</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>56.72</t>
+          <t>44.24</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.39</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-114.07</t>
+          <t>-112.67</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>28227.69034090909</t>
+          <t>28335.18723404255</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>30506.0</t>
+          <t>10460.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>23927.2</v>
+        <v>23067.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>19193.0</t>
+          <t>19089.8</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>13522.88</v>
+        <v>13602.9</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>4734</t>
+          <t>3978</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>927.631088724425</t>
+          <t>873.4256973645256</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>1721.616370799031</t>
+          <t>575.296044885079</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>30506.0</t>
+          <t>10460.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-9.92</t>
+          <t>-13.93</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>45.09</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>44.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>46.55</t>
+          <t>44.9</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>44.8</t>
+          <t>42.6</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>44.95</t>
+          <t>42.95</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="CJ11" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>685.0</t>
+          <t>670.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>44.95</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,102 +5208,102 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>6.94</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
+          <t>24.67</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2025-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-10-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2025-08-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2025-08-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>45.6</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>44.45</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>52.5</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>47.6</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>1.12</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
           <t>-4.20</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2025-10-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2025-10-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-08-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2025-08-29 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>45.6</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>44.45</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>52.5</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>47.6</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>1.24</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>-4.20</t>
-        </is>
-      </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16.81</t>
+          <t>16.44</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,276 +5314,276 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>1436</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>98.77</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>75.04</t>
+          <t>94.23</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>42.73999999999999</t>
+          <t>43.31</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>43.61</v>
+        <v>43.58</v>
       </c>
       <c r="AN12" t="n">
-        <v>44.12</v>
+        <v>44.1</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
+          <t>45.01</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>56.72</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>-0.17</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>-0.39</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>2.77</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>-114.07</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>2025/11/19</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>28335.18723404255</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>30506.0</t>
+        </is>
+      </c>
+      <c r="AX12" t="n">
+        <v>23927.2</v>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>19193.0</t>
+        </is>
+      </c>
+      <c r="AZ12" t="n">
+        <v>13522.88</v>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>4734</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>927.631088724425</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>1721.616370799031</t>
+        </is>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>30506.0</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>49.9</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>2025/08/12</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>-9.92</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>匯鑽科</t>
+        </is>
+      </c>
+      <c r="BJ12" t="inlineStr">
+        <is>
+          <t>匯鑽科</t>
+        </is>
+      </c>
+      <c r="BK12" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL12" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM12" t="inlineStr">
+        <is>
+          <t>0.79</t>
+        </is>
+      </c>
+      <c r="BN12" t="inlineStr">
+        <is>
+          <t>-10.56465687102404</t>
+        </is>
+      </c>
+      <c r="BO12" t="inlineStr">
+        <is>
+          <t>-13.69932964657055</t>
+        </is>
+      </c>
+      <c r="BP12" t="inlineStr">
+        <is>
+          <t>7.80229574004913</t>
+        </is>
+      </c>
+      <c r="BQ12" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS12" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="BT12" t="inlineStr">
+        <is>
+          <t>2.33</t>
+        </is>
+      </c>
+      <c r="BU12" t="inlineStr">
+        <is>
+          <t>6.59</t>
+        </is>
+      </c>
+      <c r="BV12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW12" t="inlineStr">
+        <is>
+          <t>8.25%</t>
+        </is>
+      </c>
+      <c r="BX12" t="inlineStr">
+        <is>
+          <t>-14.21%</t>
+        </is>
+      </c>
+      <c r="BY12" t="inlineStr">
+        <is>
+          <t>46.3</t>
+        </is>
+      </c>
+      <c r="BZ12" t="inlineStr">
+        <is>
+          <t>2356</t>
+        </is>
+      </c>
+      <c r="CA12" t="inlineStr">
+        <is>
+          <t>加工業務99.90%、勞務0.10% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>匯鑽科-其他電子業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC12" t="inlineStr">
+        <is>
+          <t>其他電子業右下上櫃</t>
+        </is>
+      </c>
+      <c r="CD12" t="inlineStr">
+        <is>
+          <t>45.5</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
+          <t>46.55</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
+          <t>44.8</t>
+        </is>
+      </c>
+      <c r="CG12" t="inlineStr">
+        <is>
           <t>44.95</t>
         </is>
       </c>
-      <c r="AP12" t="inlineStr">
-        <is>
-          <t>24.64</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>-0.34</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>-0.45</t>
-        </is>
-      </c>
-      <c r="AS12" t="inlineStr">
-        <is>
-          <t>2.77</t>
-        </is>
-      </c>
-      <c r="AT12" t="inlineStr">
-        <is>
-          <t>-116.07</t>
-        </is>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>2025/11/19</t>
-        </is>
-      </c>
-      <c r="AV12" t="inlineStr">
-        <is>
-          <t>28227.69034090909</t>
-        </is>
-      </c>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>30695.0</t>
-        </is>
-      </c>
-      <c r="AX12" t="n">
-        <v>18788.8</v>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>19613.1</t>
-        </is>
-      </c>
-      <c r="AZ12" t="n">
-        <v>13049.74</v>
-      </c>
-      <c r="BA12" t="inlineStr">
-        <is>
-          <t>-824</t>
-        </is>
-      </c>
-      <c r="BB12" t="inlineStr">
-        <is>
-          <t>783.2701283472239</t>
-        </is>
-      </c>
-      <c r="BC12" t="inlineStr">
-        <is>
-          <t>1149.944823147569</t>
-        </is>
-      </c>
-      <c r="BD12" t="inlineStr">
-        <is>
-          <t>30695.0</t>
-        </is>
-      </c>
-      <c r="BE12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF12" t="inlineStr">
-        <is>
-          <t>49.9</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr">
-        <is>
-          <t>2025/08/12</t>
-        </is>
-      </c>
-      <c r="BH12" t="inlineStr">
-        <is>
-          <t>-9.82</t>
-        </is>
-      </c>
-      <c r="BI12" t="inlineStr">
-        <is>
-          <t>匯鑽科</t>
-        </is>
-      </c>
-      <c r="BJ12" t="inlineStr">
-        <is>
-          <t>匯鑽科</t>
-        </is>
-      </c>
-      <c r="BK12" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BL12" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM12" t="inlineStr">
-        <is>
-          <t>0.79</t>
-        </is>
-      </c>
-      <c r="BN12" t="inlineStr">
-        <is>
-          <t>-10.56465687102404</t>
-        </is>
-      </c>
-      <c r="BO12" t="inlineStr">
-        <is>
-          <t>-13.69932964657055</t>
-        </is>
-      </c>
-      <c r="BP12" t="inlineStr">
-        <is>
-          <t>7.80229574004913</t>
-        </is>
-      </c>
-      <c r="BQ12" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
-        </is>
-      </c>
-      <c r="BR12" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS12" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
-      </c>
-      <c r="BT12" t="inlineStr">
-        <is>
-          <t>2.32</t>
-        </is>
-      </c>
-      <c r="BU12" t="inlineStr">
-        <is>
-          <t>6.59</t>
-        </is>
-      </c>
-      <c r="BV12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BW12" t="inlineStr">
-        <is>
-          <t>8.25%</t>
-        </is>
-      </c>
-      <c r="BX12" t="inlineStr">
-        <is>
-          <t>-14.21%</t>
-        </is>
-      </c>
-      <c r="BY12" t="inlineStr">
-        <is>
-          <t>45.09</t>
-        </is>
-      </c>
-      <c r="BZ12" t="inlineStr">
-        <is>
-          <t>2029</t>
-        </is>
-      </c>
-      <c r="CA12" t="inlineStr">
-        <is>
-          <t>加工業務99.90%、勞務0.10% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB12" t="inlineStr">
-        <is>
-          <t>匯鑽科-其他電子業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC12" t="inlineStr">
-        <is>
-          <t>其他電子業右下上櫃</t>
-        </is>
-      </c>
-      <c r="CD12" t="inlineStr">
-        <is>
-          <t>43.55</t>
-        </is>
-      </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>45.55</t>
-        </is>
-      </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>43.3</t>
-        </is>
-      </c>
-      <c r="CG12" t="inlineStr">
-        <is>
-          <t>45.0</t>
-        </is>
-      </c>
       <c r="CH12" t="inlineStr">
         <is>
           <t>18.72</t>
@@ -5596,7 +5596,7 @@
       </c>
       <c r="CJ12" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>678.728</t>
+          <t>801.854</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>86.9</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-5.49</t>
+          <t>-2.06</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-18.22</t>
+          <t>-18.79</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>3.88</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,73 +5744,73 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>802</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>67.28</t>
+          <t>62.35</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-2.41</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-7.49</t>
+          <t>-7.44</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>87.32000000000001</t>
+          <t>87.28</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>89.48</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="AN13" t="n">
-        <v>96.72</v>
+        <v>96.26000000000001</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>97.72</t>
+          <t>97.76</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>9.21</t>
+          <t>10.51</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-2.62</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-3.00</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-141.71</t>
+          <t>-140.65</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>352964405.0369318</t>
+          <t>352612641.6127659</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>59515377.0</t>
+          <t>69980794.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>61769492.8</v>
+        <v>64716425.2</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>65356195.9</t>
+          <t>66077711.5</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>234235775.26</v>
+        <v>222934351.1</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-3586703</t>
+          <t>-1361286</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-27073174.21872042</t>
+          <t>-25829835.19491547</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-21423089.14046149</t>
+          <t>-18991470.56398827</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>59515377.0</t>
+          <t>69980794.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>7.63</t>
+          <t>6.89</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>22.49</t>
+          <t>22.34</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>34.97</t>
+          <t>34.88</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>18453</t>
+          <t>18327</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
@@ -6006,12 +6006,12 @@
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>86.9</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>739.811</t>
+          <t>678.728</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-10.13</t>
+          <t>-5.49</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-18.60</t>
+          <t>-18.22</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,73 +6174,73 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>802</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>59.26</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>67.9</t>
+          <t>67.28</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-7.48</t>
+          <t>-7.49</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>87.32000000000001</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>89.87</v>
+        <v>89.48</v>
       </c>
       <c r="AN14" t="n">
-        <v>97.14</v>
+        <v>96.72</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>97.67</t>
+          <t>97.72</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>9.21</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-2.88</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-3.07</t>
+          <t>-3.00</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-142.67</t>
+          <t>-141.71</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>352964405.0369318</t>
+          <t>352612641.6127659</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>64813905.0</t>
+          <t>59515377.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>62364817.4</v>
+        <v>61769492.8</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>69391061.0</t>
+          <t>65356195.9</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>243715090.02</v>
+        <v>234235775.26</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-7026243</t>
+          <t>-3586703</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-28100462.4147675</t>
+          <t>-27073174.21872042</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-23010424.95897819</t>
+          <t>-21423089.14046149</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>64813905.0</t>
+          <t>59515377.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>7.13</t>
+          <t>7.63</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>22.49</t>
+          <t>22.34</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>34.97</t>
+          <t>34.88</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>18453</t>
+          <t>18327</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6431,17 +6431,17 @@
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>88.9</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1014.23</t>
+          <t>739.811</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-23.60</t>
+          <t>-10.13</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>4.90</t>
+          <t>3.58</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-1.84</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,12 +6604,12 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>802</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6619,58 +6619,58 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>61.16</t>
+          <t>67.9</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-7.36</t>
+          <t>-7.48</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>87.29999999999998</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>90.34</v>
+        <v>89.87</v>
       </c>
       <c r="AN15" t="n">
-        <v>97.52</v>
+        <v>97.14</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>97.62</t>
+          <t>97.67</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>6.07</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-3.00</t>
+          <t>-2.88</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-3.12</t>
+          <t>-3.07</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-143.32</t>
+          <t>-142.67</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>352964405.0369318</t>
+          <t>352612641.6127659</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>88951847.0</t>
+          <t>64813905.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>59081139.2</v>
+        <v>62364817.4</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>77327536.6</t>
+          <t>69391061.0</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>250820460.68</v>
+        <v>243715090.02</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-18246397</t>
+          <t>-7026243</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-29025923.77036555</t>
+          <t>-28100462.4147675</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-25023946.09403855</t>
+          <t>-23010424.95897819</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>88951847.0</t>
+          <t>64813905.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6806,7 +6806,7 @@
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>22.49</t>
+          <t>22.34</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>34.97</t>
+          <t>34.88</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>18453</t>
+          <t>18327</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6861,12 +6861,12 @@
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>88.9</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>461.141</t>
+          <t>1014.23</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>87.8</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-33.87</t>
+          <t>-23.60</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-17.94</t>
+          <t>-18.60</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>4.90</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,274 +7034,274 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>802</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>85.19</t>
+          <t>59.26</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>55.95</t>
+          <t>61.16</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-4.12</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-7.23</t>
+          <t>-7.36</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
+          <t>87.29999999999998</t>
+        </is>
+      </c>
+      <c r="AM16" t="n">
+        <v>90.34</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>97.52</v>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>97.62</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>3.61</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>-3.00</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>-3.12</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>7.19</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr">
+        <is>
+          <t>-143.32</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>2025/11/28</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>352612641.6127659</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>88951847.0</t>
+        </is>
+      </c>
+      <c r="AX16" t="n">
+        <v>59081139.2</v>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>77327536.6</t>
+        </is>
+      </c>
+      <c r="AZ16" t="n">
+        <v>250820460.68</v>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>-18246397</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>-29025923.77036555</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>-25023946.09403855</t>
+        </is>
+      </c>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>88951847.0</t>
+        </is>
+      </c>
+      <c r="BE16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF16" t="inlineStr">
+        <is>
+          <t>81.3</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>2025/07/28</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>7.13</t>
+        </is>
+      </c>
+      <c r="BI16" t="inlineStr">
+        <is>
+          <t>鉅祥</t>
+        </is>
+      </c>
+      <c r="BJ16" t="inlineStr">
+        <is>
+          <t>鉅祥</t>
+        </is>
+      </c>
+      <c r="BK16" t="inlineStr">
+        <is>
+          <t>電子零組件業</t>
+        </is>
+      </c>
+      <c r="BL16" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM16" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
+      <c r="BN16" t="inlineStr">
+        <is>
+          <t>-7.291353668658945</t>
+        </is>
+      </c>
+      <c r="BO16" t="inlineStr">
+        <is>
+          <t>11.64963320584363</t>
+        </is>
+      </c>
+      <c r="BP16" t="inlineStr">
+        <is>
+          <t>10.65346457950322</t>
+        </is>
+      </c>
+      <c r="BQ16" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR16" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS16" t="inlineStr">
+        <is>
+          <t>2.29</t>
+        </is>
+      </c>
+      <c r="BT16" t="inlineStr">
+        <is>
+          <t>4.02</t>
+        </is>
+      </c>
+      <c r="BU16" t="inlineStr">
+        <is>
+          <t>9.36</t>
+        </is>
+      </c>
+      <c r="BV16" t="inlineStr">
+        <is>
+          <t>22.34</t>
+        </is>
+      </c>
+      <c r="BW16" t="inlineStr">
+        <is>
+          <t>29.60%</t>
+        </is>
+      </c>
+      <c r="BX16" t="inlineStr">
+        <is>
+          <t>15.93%</t>
+        </is>
+      </c>
+      <c r="BY16" t="inlineStr">
+        <is>
+          <t>34.88</t>
+        </is>
+      </c>
+      <c r="BZ16" t="inlineStr">
+        <is>
+          <t>18327</t>
+        </is>
+      </c>
+      <c r="CA16" t="inlineStr">
+        <is>
+          <t>部品95.14%、模具3.09%、商品銷售1.03%、治具0.75% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB16" t="inlineStr">
+        <is>
+          <t>鉅祥-電子零組件業-上市</t>
+        </is>
+      </c>
+      <c r="CC16" t="inlineStr">
+        <is>
+          <t>電子零組件業右上上市</t>
+        </is>
+      </c>
+      <c r="CD16" t="inlineStr">
+        <is>
+          <t>87.5</t>
+        </is>
+      </c>
+      <c r="CE16" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="CF16" t="inlineStr">
+        <is>
+          <t>86.8</t>
+        </is>
+      </c>
+      <c r="CG16" t="inlineStr">
+        <is>
           <t>87.1</t>
-        </is>
-      </c>
-      <c r="AM16" t="n">
-        <v>90.84</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>97.92</v>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>97.54</t>
-        </is>
-      </c>
-      <c r="AP16" t="inlineStr">
-        <is>
-          <t>0.98</t>
-        </is>
-      </c>
-      <c r="AQ16" t="inlineStr">
-        <is>
-          <t>-3.11</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>-3.14</t>
-        </is>
-      </c>
-      <c r="AS16" t="inlineStr">
-        <is>
-          <t>7.19</t>
-        </is>
-      </c>
-      <c r="AT16" t="inlineStr">
-        <is>
-          <t>-143.71</t>
-        </is>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>2025/11/28</t>
-        </is>
-      </c>
-      <c r="AV16" t="inlineStr">
-        <is>
-          <t>352964405.0369318</t>
-        </is>
-      </c>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>40320203.0</t>
-        </is>
-      </c>
-      <c r="AX16" t="n">
-        <v>54978050.8</v>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>83135790.5</t>
-        </is>
-      </c>
-      <c r="AZ16" t="n">
-        <v>260959475.16</v>
-      </c>
-      <c r="BA16" t="inlineStr">
-        <is>
-          <t>-28157739</t>
-        </is>
-      </c>
-      <c r="BB16" t="inlineStr">
-        <is>
-          <t>-29753556.07515229</t>
-        </is>
-      </c>
-      <c r="BC16" t="inlineStr">
-        <is>
-          <t>-29592900.56933765</t>
-        </is>
-      </c>
-      <c r="BD16" t="inlineStr">
-        <is>
-          <t>40320203.0</t>
-        </is>
-      </c>
-      <c r="BE16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF16" t="inlineStr">
-        <is>
-          <t>81.3</t>
-        </is>
-      </c>
-      <c r="BG16" t="inlineStr">
-        <is>
-          <t>2025/07/28</t>
-        </is>
-      </c>
-      <c r="BH16" t="inlineStr">
-        <is>
-          <t>8.00</t>
-        </is>
-      </c>
-      <c r="BI16" t="inlineStr">
-        <is>
-          <t>鉅祥</t>
-        </is>
-      </c>
-      <c r="BJ16" t="inlineStr">
-        <is>
-          <t>鉅祥</t>
-        </is>
-      </c>
-      <c r="BK16" t="inlineStr">
-        <is>
-          <t>電子零組件業</t>
-        </is>
-      </c>
-      <c r="BL16" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM16" t="inlineStr">
-        <is>
-          <t>1.02</t>
-        </is>
-      </c>
-      <c r="BN16" t="inlineStr">
-        <is>
-          <t>-7.291353668658945</t>
-        </is>
-      </c>
-      <c r="BO16" t="inlineStr">
-        <is>
-          <t>11.64963320584363</t>
-        </is>
-      </c>
-      <c r="BP16" t="inlineStr">
-        <is>
-          <t>10.65346457950322</t>
-        </is>
-      </c>
-      <c r="BQ16" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR16" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS16" t="inlineStr">
-        <is>
-          <t>2.31</t>
-        </is>
-      </c>
-      <c r="BT16" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BU16" t="inlineStr">
-        <is>
-          <t>9.36</t>
-        </is>
-      </c>
-      <c r="BV16" t="inlineStr">
-        <is>
-          <t>22.49</t>
-        </is>
-      </c>
-      <c r="BW16" t="inlineStr">
-        <is>
-          <t>29.60%</t>
-        </is>
-      </c>
-      <c r="BX16" t="inlineStr">
-        <is>
-          <t>15.93%</t>
-        </is>
-      </c>
-      <c r="BY16" t="inlineStr">
-        <is>
-          <t>34.97</t>
-        </is>
-      </c>
-      <c r="BZ16" t="inlineStr">
-        <is>
-          <t>18453</t>
-        </is>
-      </c>
-      <c r="CA16" t="inlineStr">
-        <is>
-          <t>部品95.14%、模具3.09%、商品銷售1.03%、治具0.75% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB16" t="inlineStr">
-        <is>
-          <t>鉅祥-電子零組件業-上市</t>
-        </is>
-      </c>
-      <c r="CC16" t="inlineStr">
-        <is>
-          <t>電子零組件業右上上市</t>
-        </is>
-      </c>
-      <c r="CD16" t="inlineStr">
-        <is>
-          <t>87.9</t>
-        </is>
-      </c>
-      <c r="CE16" t="inlineStr">
-        <is>
-          <t>87.9</t>
-        </is>
-      </c>
-      <c r="CF16" t="inlineStr">
-        <is>
-          <t>86.9</t>
-        </is>
-      </c>
-      <c r="CG16" t="inlineStr">
-        <is>
-          <t>87.8</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7323,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>630.229</t>
+          <t>461.141</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-29.59</t>
+          <t>-33.87</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-18.60</t>
+          <t>-17.94</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>3.05</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,73 +7464,73 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>802</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>39.02</t>
+          <t>85.19</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>31.54</t>
+          <t>55.95</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-5.08</t>
+          <t>-4.12</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-7.16</t>
+          <t>-7.23</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>86.64</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>91.28</v>
+        <v>90.84</v>
       </c>
       <c r="AN17" t="n">
-        <v>98.31</v>
+        <v>97.92</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>97.43</t>
+          <t>97.54</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-4.05</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-3.11</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-3.15</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-143.82</t>
+          <t>-143.71</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>352964405.0369318</t>
+          <t>352612641.6127659</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>55246132.0</t>
+          <t>40320203.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>67438997.8</v>
+        <v>54978050.8</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>95782499.1</t>
+          <t>83135790.5</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>275665355.36</v>
+        <v>260959475.16</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-28343501</t>
+          <t>-28157739</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-29782766.16711858</t>
+          <t>-29753556.07515229</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-29852555.79943146</t>
+          <t>-29592900.56933765</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>55246132.0</t>
+          <t>40320203.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>7.13</t>
+          <t>8.00</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -7661,12 +7661,12 @@
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>22.49</t>
+          <t>22.34</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>34.97</t>
+          <t>34.88</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>18453</t>
+          <t>18327</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7721,17 +7721,17 @@
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.9</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>713.512</t>
+          <t>630.229</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-33.57</t>
+          <t>-29.59</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-17.85</t>
+          <t>-18.60</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,73 +7894,73 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>802</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>43.64</t>
+          <t>39.02</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>31.54</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-5.14</t>
+          <t>-5.08</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-7.33</t>
+          <t>-7.16</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>86.85999999999999</t>
+          <t>86.64</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>91.56999999999999</v>
+        <v>91.28</v>
       </c>
       <c r="AN18" t="n">
-        <v>98.81999999999999</v>
+        <v>98.31</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>97.34</t>
+          <t>97.43</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-8.10</t>
+          <t>-4.05</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-3.37</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-3.12</t>
+          <t>-3.15</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-143.38</t>
+          <t>-143.82</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>352964405.0369318</t>
+          <t>352612641.6127659</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>62492000.0</t>
+          <t>55246132.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>68942899</v>
+        <v>67438997.8</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>103776418.9</t>
+          <t>95782499.1</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>296624289.38</v>
+        <v>275665355.36</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-34833519</t>
+          <t>-28343501</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-29770077.14306169</t>
+          <t>-29782766.16711858</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-30756535.8138715</t>
+          <t>-29852555.79943146</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>62492000.0</t>
+          <t>55246132.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>7.13</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,22 +8081,22 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>22.49</t>
+          <t>22.34</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>34.97</t>
+          <t>34.88</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>18453</t>
+          <t>18327</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>557.755</t>
+          <t>713.512</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1.03</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-0.84</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-31.49</t>
+          <t>-33.57</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-19.07</t>
+          <t>-17.85</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,73 +8324,73 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>802</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>11.96</t>
+          <t>43.64</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>6.16</t>
+          <t>20.7</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-5.79</t>
+          <t>-5.14</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-7.52</t>
+          <t>-7.33</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>86.58</t>
+          <t>86.85999999999999</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>91.90000000000001</v>
+        <v>91.56999999999999</v>
       </c>
       <c r="AN19" t="n">
-        <v>99.37</v>
+        <v>98.81999999999999</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>97.25</t>
+          <t>97.34</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-15.28</t>
+          <t>-8.10</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-3.52</t>
+          <t>-3.37</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-3.12</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-142.50</t>
+          <t>-143.38</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>352964405.0369318</t>
+          <t>352612641.6127659</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>48395514.0</t>
+          <t>62492000.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>76417304.59999999</v>
+        <v>68942899</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>111545339.3</t>
+          <t>103776418.9</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>319430807.84</v>
+        <v>296624289.38</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-35128034</t>
+          <t>-34833519</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-29590721.02109627</t>
+          <t>-29770077.14306169</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-31725831.12686187</t>
+          <t>-30756535.8138715</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>48395514.0</t>
+          <t>62492000.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>8.12</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,22 +8511,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>22.49</t>
+          <t>22.34</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>34.97</t>
+          <t>34.88</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>18453</t>
+          <t>18327</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>85.9</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.57</t>
  